--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -1796,7 +1796,9 @@
  Cost considerations:
  • Dataset itself is open access (no cost).
  • Small-scale applications (e.g., testing models in Google Earth Engine or QGIS) incur negligible costs.
- • Larger-scale ML training and national-scale mapping may require cloud compute budgets</t>
+ • Larger-scale ML training and national-scale mapping may require cloud compute budgets
+• Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
+• Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1888,7 +1890,10 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>• Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.</t>
+          <t>Effective forest management and conservation require monitoring tree attributes such as height, crown diameter, and tree count to assess growth in reforested areas. These data enable the development of tools that can speed up the process to assess the success of reforestation efforts and other various ecological and forestry applications, including biomass estimation, forest health assessment, and carbon sequestration studies. Such tools could include the automated counting of trees, estimation of trees’ biophysical parameters from drone images such as tree crown diameter, and prediction of tree growth in relation to tree species and weather variables. In all these areas, AI can offer a cost-effective and scalable alternative to traditional methods of monitoring and counting.
+Concretely the following areas of restoration can be improved:
+1) Planning - create baseline assessment: By automatically detecting existing tree crowns, tools based on this dataset can create a baseline assessment of the current forest cover. This information is valuable for planning and prioritizing reforestation areas.
+2) Monitor Progress: Repeated application of the tree crown detection model can track the success of reforestation initiatives. The model can quantify the increase in tree cover over time, allowing for informed adjustments to reforestation strategies.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1975,7 +1980,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>• Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.</t>
+          <t xml:space="preserve">The land use/cover change datasets improve the understanding of the relationship between land cover/land use change and climate change. The can also be used to inform practice and policy on how best to manage various potential scenarios and combat deforestation.        </t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2211,7 +2216,14 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>This dataset contributes to improved understanding and mitigation of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management. 
+The project created open and accessible training and evaluation datasets for machine learning applications focused on forest cover and change in Indonesia. It contains collections of polygons of uniform land cover, with labels indicating land cover type and, possibly, information on land cover change over time. To label land cover patches, the team has reviewed high-resolution satellite imagery facilitated by Collect Earth Online (CEO) and augmented it with field visits to difficult-to-classify areas. It has prioritized areas with significant landcover diversity with a preference for areas with significant smallholder production of  oil palm, coconut, and other commodities - given the well-known difficulties of distinguishing oil palm 
+from coconut palm with lower resolution imagery.
+Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -2230,7 +2242,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>How to extend or improve:</t>
+          <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2288,11 +2300,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>• Add new field reference data from other cocoa-producing regions (e.g., Côte d’Ivoire, Nigeria) to increase transferability.</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
@@ -2352,11 +2360,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>• Integrate household-level socioeconomic data to study drivers of land use change and cocoa–forest dynamics.</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
@@ -2412,11 +2416,7 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>• Combine with climate and soil datasets to model sustainability scenarios.</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
@@ -2565,11 +2565,7 @@
           <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Limitations / ethical use:</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>CC-BY</t>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -570,7 +570,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Reduced inequality through access to info in local languages/NLP (SDG 10), Promote inclusive economic growth through financial inclusion (SDG 8)</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 8 (Promote inclusive economic growth through financial inclusion)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -667,7 +667,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climate Action, End hunger, achieve food security, sustainable agriculture (SDG 2)</t>
+          <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climate Action</t>
+          <t>SDG 13 (Climate Action)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climate Action, SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climate Action, SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
+          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climate action, clean energy SDG7</t>
+          <t>SDG 13 (Climate Action), SDG 7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Reduce inequality, SDG2</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1468,7 +1468,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climate action SDG 13, Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1962,7 +1962,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>SDG 15: Life on Land: sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>climate action (SDG 13), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
+          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2226,7 +2226,11 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -2344,7 +2348,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>End hunger, achieve food security, sustainable agriculture (SDG 2)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climate Action</t>
+          <t>SDG 13 (Climate Action)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -531,12 +531,12 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Funded by</t>
+          <t>GIZ Funded (Yes/No)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Info on fair sharing as as Digital Public Good</t>
+          <t xml:space="preserve">Info on fair sharing as as Digital Public Good </t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -553,89 +553,98 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Facilitating access to financial applications in informal settings in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Open Air Pollution Data for Patna and Gurugram</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Combatting Air Pollution and GHG Emissions in India through hyperlocal AI-powered mapping</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings. Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.</t>
+          <t>Under this initiative, a novel approach is employed by leveraging citizen scientists and IoT-based low-cost sensors to collect hyperlocal air quality data. This data is used to identify pollution sources and risk zones, facilitating targeted actions by regulatory authorities.To showcase data outreach, the project features the VAYU Android-based application and the VAYU citizen portal digital stack, which support targeted interventions and customized solutions backed by AI/ML algorithms. These tools potentially develop new approaches in air pollution management while reducing public investment costs.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>https://vayu.undp.org.in/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://github.com/undpindia/VAYU_OpenAir; https://github.com/EconAIorg/vayu-gnn/tree/main; https://github.com/Alphawarrior21/VayuAssist; https://github.com/akbp24/ClearSky; https://github.com/sherwaldeepesh/vayu_airnode</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 8 (Promote inclusive economic growth through financial inclusion)</t>
+          <t>SDG 13 (Climate Action)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dennis Asamoah Owusu (DOWUSU@ASHESI.EDU.GH)</t>
+          <t>UNDP India (https://www.undp.org/india)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The data is freely available for use based on the provided open source license and courtesy the funding from Lacuna Fund. We performed a stratified random sampling (5%) of the data for each language and reviewed it to get the following quality assessments.
- 0.1% of the Ga audios were of low quality
- 1.3% of the Fanti audios were of low qaulity.
- 1.6% of the Asanti Twi audios were of low quality.
- 2.8% of the Akuapem Twi audios were of low quality.
- Low quality means that what the user recorded did not match the given prompt either because there was a truncation or the recording was totally different from the prompt.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>The dataset might be used to devise more inclusive banking platforms that better understand users in in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The data for this project is collected by static and dynamic sensor. Static sensors are placed at known hotspots for air pollution while dynamic sensors are moved by citizen scientist continously. 
+•        2 Cities
+•        100+ Senors
+•        150+ Volunteers
+•        1000+ Records Collected
+•        ~10Million Data Points
+</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
+          <t>CC-BY</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Powered by: Ashesi University, Nokwary Technologies
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  UNDP India
+Catalyzed by: FAIR Forward - AI for All (https://www.bmz-digital.global/en/overview-of-initiatives/fair-forward/)
+Financed by: BMZ (https://www.bmz-digital.global/en/digital-transformation-and-development-cooperation/)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Elikplim Sabblah, Balthas Seibold</t>
+          <t>Jonas Nothnagel, Arun Kumar Yadav</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -649,45 +658,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enable Cashew, Cocoa and Coffee farmers to make good business decisions - Drone-based Agricultural Dataset for Crop Yield Estimation in Ghana and Uganda</t>
+          <t>Facilitating access to financial applications in informal settings in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa.
-  It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. Conventional methods of yield estimation are expensive, require a lot of labor and time, and are prone to error due to incomplete ground observations. This results in poor crop yield estimations and hinders farmers’ ability to appropriately plan and manage their fields and production pipelines. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions. Having key details about agricultural production readily accessible enables a timely harvest, helping farmers ensure healthy, fresh produce and, in addition, better sales.</t>
+          <t xml:space="preserve">This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings.  Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.  </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
+          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 8 (Promote inclusive economic growth through financial inclusion)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Darlington Akogo (darlington@gudra-studio.com), KaraAgro (https://www.karaagro.com/index.html)</t>
+          <t>Dennis Asamoah Owusu (DOWUSU@ASHESI.EDU.GH)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ghana,Uganda</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The data is freely available for use based on the provided open source license and courtesy the funding from Lacuna Fund. We performed a stratified random sampling (5%) of the data for each language and reviewed it to get the following quality assessments.
+0.1% of the Ga audios were of low quality
+1.3% of the Fanti audios were of low qaulity.
+1.6% of the Asanti Twi audios were of low quality.
+2.8% of the Akuapem Twi audios were of low quality.
+Low quality means that what the user recorded did not match the given prompt either because there was a truncation or the recording was totally different from the prompt.</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>The dataset might be used to devise more inclusive banking platforms that better understand users in  in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
@@ -695,14 +716,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Powered by: Karaagro AI - Ghana, Makerere AI Lab, Uganda Marconi Lab, National Coffee Research Institute, National Crops Resources Research Institute
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  Ashesi University, Nokwary Technologies
+Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Elikplim Sabblah</t>
+          <t xml:space="preserve">Elikplim Sabblah, Balthas Seibold </t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -712,14 +733,14 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Computer Vision / Drone Data</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -739,8 +760,8 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The dataset was created to enable translation from Kiswahili, which is the national language in Kenya, into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. All three languages are low resource, especially Kidaw'ida, which has only around 400,000 speakers and is at immediate risk of loss. By collecting the text and speech data, the project has taken a step towards preservation of these languages . The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On average, each corpus has thirty thousand sentence pairs. 
- In addition, the dataset has helped to preserve, revitalise and elevate the languages Kidaw'ida, Kalenjin, and Dholuo by making them work on Mozillas Common Voice Platform. The text and speech datasets are thereby supporting crowd-sourced voice recognition, promoting linguistic diversity and empoweromg local communities by enabling Natural Language Processing applications tailored to their needs. Namely, the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input). As of August 2025, 120 hours of speech data have been recorded on Common Voice in Dholuo (with 14692 sentences available), 92 hours have been recorded for Kalendjin (With 29900 sentences available) and 56 hours have been recorded for Kidaw'ida (with 11773 sentences available). To download the crowd-sourced speech datasets in Kidaw'ida, Kalenjin, and Dholuo, visit https://commonvoice.mozilla.org/en/datasets</t>
+          <t xml:space="preserve">The dataset was created to enable translation from Kiswahili, which is the national language in Kenya, into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. All three languages are low resource, especially Kidaw'ida, which has only around 400,000 speakers and is at immediate risk of loss. By collecting the text and speech data, the project has taken a step towards preservation of these languages . The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On average, each corpus has thirty thousand sentence pairs. 
+In addition, the dataset has helped to preserve, revitalise and elevate the languages Kidaw'ida, Kalenjin, and Dholuo by making them work on Mozillas Common Voice Platform. The text and speech datasets are thereby supporting crowd-sourced voice recognition, promoting linguistic diversity and empoweromg local communities by enabling Natural Language Processing applications tailored to their needs. Namely, the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input). As of August 2025, 120 hours of speech data have been recorded on Common Voice in Dholuo (with 14692 sentences available), 92 hours have been recorded for Kalendjin (With 29900 sentences available) and 56 hours have been recorded for Kidaw'ida (with 11773 sentences available). To download the crowd-sourced speech datasets in Kidaw'ida, Kalenjin, and Dholuo, visit https://commonvoice.mozilla.org/en/datasets </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -756,7 +777,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Voice, Text</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -777,9 +798,9 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>&gt; The datasets can help to build translation services from Kiswahili into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. 
- &gt; The datasets can help to preserve these three low resource languages, promote linguistic diversity and empower local communities by enabling Natural Language Processing applications tailored to their needs.
- &gt; the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input).</t>
+          <t xml:space="preserve">&gt; The datasets can help to build translation services from Kiswahili into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. 
+&gt; The datasets can help to preserve these three low resource languages, promote linguistic diversity and empower local communities by enabling Natural Language Processing applications tailored to their needs.
+&gt; the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input).  </t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -789,9 +810,9 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Powered by: USIU - Africa in cooperation with Kabarak University and Maseno University, Kenya
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:   USIU - Africa in cooperation with Kabarak University and Maseno University, Kenya
+Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -806,25 +827,25 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Natural Language Processing (NLP)</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2501.11003, https://github.com/waleghwa/low-resource-language-data, https://commonvoice.mozilla.org/en/datasets</t>
+          <t xml:space="preserve">https://arxiv.org/pdf/2501.11003, https://github.com/waleghwa/low-resource-language-data, https://commonvoice.mozilla.org/en/datasets </t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Comment Balthas: original title is "Building parallel corpora for Kenya’s Indigenous Languages and Swahili"
- DONE on 25.8., Balthas</t>
+DONE on 25.8., Balthas</t>
         </is>
       </c>
     </row>
@@ -843,7 +864,7 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>This dataset will help data scientists, government and users to measure solar energy adoption across Madagascar. It laid the groundwork needed to develop a solar panel detection algorithm working in Madagaskar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.
- The team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons.</t>
+The team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -874,9 +895,9 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Powered by: 
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  
+Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -890,7 +911,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -925,7 +946,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -945,13 +966,13 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The project developed and made the following resources available: 1. Manually Annotated Twitter Sentiment Dataset 2. Manually Annotated Sentiment Lexicon 3. Semi-automatically Translated emotion lexicon 4. Semi-automatically Translated sentiment lexicon 5. Large Scale Unlabeled Twitter Sentiment Corpus 6. Stop-words for Hausa, Igbo, Pidgin and Yoruba 7. text collection, filtering, processing and labeling methods to create datasets for these low-resource languages. 8. evaluation og a range of pre-trained models and transfer strategies on the dataset. 9. release of datasets, trained models, sentiment lexicons, and code to incentivize research on sentiment analysis in under-represented languages. Authors: Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
+          <t>The project developed and made the following resources available:   1. Manually Annotated Twitter Sentiment Dataset 2. Manually Annotated Sentiment Lexicon 3. Semi-automatically Translated emotion lexicon 4. Semi-automatically Translated sentiment lexicon 5. Large Scale Unlabeled Twitter Sentiment Corpus 6. Stop-words for Hausa, Igbo, Pidgin and Yoruba     7. text  collection,  filtering, processing  and  labeling  methods  to  create  datasets  for  these  low-resource  languages.   8. evaluation og a  range of  pre-trained  models  and  transfer  strategies  on  the  dataset. 9. release  of datasets,  trained  models,  sentiment  lexicons,  and  code  to  incentivize research on sentiment analysis in under-represented languages. Authors: Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284</t>
+          <t xml:space="preserve">NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284 </t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -961,9 +982,9 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Powered by: Bayero University, Kano, Nigeria, Ahmadu Bello University, Zaria, Nigeria, Masakhane NLP, HausaNLP, Kaduna state University 
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  Bayero University, Kano, Nigeria, Ahmadu Bello University, Zaria, Nigeria, Masakhane NLP, HausaNLP, Kaduna state University 
+Catalyzed by: Lacuna-Fund / Meridian &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -978,7 +999,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Natural language Processing” (NLP)</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -993,7 +1014,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1011,71 +1032,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Preserving privacy and avoiding gender bias of AI systems in Luganda, Lumasaba, Hausa, and Kanuri - The Lacuna personally identifiable information Text Dataset</t>
+          <t>Enable Cashew, Cocoa and Coffee farmers to make good business decisions - Drone-based Agricultural Dataset for Crop Yield Estimation in Ghana and Uganda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Lacuna PII Multilingual Text Dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
+          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa.
+ It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. Conventional methods of yield estimation are expensive, require a lot of labor and time, and are prone to error due to incomplete ground observations. This results in poor crop yield estimations and hinders farmers’ ability to appropriately plan and manage their fields and production pipelines. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions. Having key details about agricultural production readily accessible enables a timely harvest, helping farmers ensure healthy, fresh produce and, in addition, better sales.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/CGHWZE</t>
+          <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
+          <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Andrew Katumba - Makerere University (katumba@mak.ac.ug)</t>
+          <t>Darlington Akogo (darlington@gudra-studio.com), KaraAgro (https://www.karaagro.com/index.html)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Uganda,Kenya,Nigeria</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Text data:
- • Luganda: 4000 PII sentences with representation in entities of
- Person, Date, National identity, tribal identity, location, and organization.
- • Lumasaaba: 5000 PII sentences with representation in entities
- of Person, Date, National identity, tribal identity, location, and
- organization.
- • Hausa: 3000 PII sentences with representation in entities of Person, Date, National identity, tribal identity, location, and organization.
- • Kanuri: 3000 PII sentences with representation in entities of Person, Date, National identity, tribal identity, location, and organization
- For more, see data card here: https://dataverse.harvard.edu/file.xhtml?fileId=10577233&amp;version=2.0</t>
-        </is>
-      </c>
+          <t>Ghana,Uganda</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>This dataset of personally identifiable information (PII) can help any organization or initiative, that would like to comply with legal requirements while still being able to analyze and use and share data effectively in one of the languages in Luganda, Lumasaba, Hausa, and Kanuri. It can also be used to improve machine translation systems for these low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems.</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Powered by: Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global
- Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  Karaagro AI - Ghana, Makerere AI Lab, Uganda Marconi Lab, National Coffee Research Institute, National Crops Resources Research Institute
+Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t xml:space="preserve">Elikplim Sabblah </t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1085,26 +1095,18 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Natural language Processing” (NLP)</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://dataverse.harvard.edu/file.xhtml?fileId=10577234&amp;version=2.0</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>First editing DONE on 25.8., Balthas</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1114,47 +1116,71 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ecuadorian Dataset on Access, Demand, &amp; Availability of Electricity Supply</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ecuador Electricity Access &amp; Supply Data</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Preserving privacy and avoiding gender bias of AI systems in Luganda, Lumasaba, Hausa, and Kanuri - The Lacuna personally identifiable information Text Dataset</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The Lacuna PII Multilingual Text Dataset  contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages,  improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/CGHWZE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ESPOL University</t>
+          <t>Andrew Katumba - Makerere University (katumba@mak.ac.ug)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>Uganda,Kenya,Nigeria</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Text data:
+• Luganda: 4000 PII sentences with representation in entities of
+Person, Date, National identity, tribal identity, location, and organization.
+• Lumasaaba: 5000 PII sentences with representation in entities
+of Person, Date, National identity, tribal identity, location, and
+organization.
+• Hausa: 3000 PII sentences with representation in entities of Person, Date, National identity, tribal identity, location, and organization.
+• Kanuri: 3000 PII sentences with representation in entities of Person, Date, National identity, tribal identity, location, and organization
+For more, see data card here: https://dataverse.harvard.edu/file.xhtml?fileId=10577233&amp;version=2.0</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This dataset of personally identifiable information (PII) can help any organization or initiative, that would like to comply with legal requirements while still being able to analyze and use and share data effectively in one of the languages in Luganda, Lumasaba, Hausa, and Kanuri. It can also be used to improve machine translation systems for these low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. </t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Powered by: ESPOL University
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global
+Catalyzed by: Lacuna-Fund / Meridian &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>Balthas Seibold</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1162,18 +1188,26 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/file.xhtml?fileId=10577234&amp;version=2.0</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>First editing DONE on 28.8., Luisa - There´s no much information available</t>
+          <t>First editing DONE on 25.8., Balthas</t>
         </is>
       </c>
     </row>
@@ -1185,23 +1219,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Powering Rural Futures in West Africa: AI-Driven Demand Data for Smarter Electrification</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Ecuadorian Dataset on Access, Demand, &amp; Availability of Electricity Supply</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ecuador Electricity Access &amp; Supply Data</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Reiner Lemoine Institut gGmbH (RLI)</t>
+          <t>ESPOL University</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Benin,Ghana,Niger,Togo</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1210,23 +1252,35 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Powered by: Reiner Lemoine Institut gGmbH (RLI)
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>Powered by:  ESPOL University
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>First editing DONE on 28.8., Luisa - There´s no much information available</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1236,100 +1290,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Residential Energy and Weather Dataset (REWD) of Pakistan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Energy dataset of residential consumption from buildings across six 
- climatic zones in Pakistan.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The project produced an energy dataset of residential consumption data from buildings across six 
- climatic zones. This dataset represents a significant milestone in understanding energy consumption patterns in relation to weather conditions within developing nations. The energy dataset is recorded on a 1-minute granularity for entire household usage as well as for individual appliances. With over a year of detailed energy consumption data and 18 months of weather data collected from a diverse array of households across six distinct climatic zones, it is one of the most comprehensive datasets of its kind. This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Residential Energy and Weather Data (REWD) - Pakistan</t>
-        </is>
-      </c>
+          <t>Powering Rural Futures in West Africa: AI-Driven Demand Data for Smarter Electrification</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SDG 13 (Climate Action), SDG 7</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Tabular</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Lahore University of Management Sciences (LUMS)</t>
+          <t>Reiner Lemoine Institut gGmbH (RLI)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>This Dataset is available in the webpage of the Lahore University. The dataset consist oth three parallel corpora: 
- 1. Electricity consumption datacollected over year through advanced smart meters. The dataset consists of 60 households belonging to six major urban centers in varying climatic zones across the country. It is recorded on a 1-minute granularity for entire household usage as well as for individual appliances. 
- 2. Metadata encompassing building attributes and demographic information for each household. The households in the dataset represent a wide and mixed demographic, social structure, and financial background.
- 3. Meteorological dataset created with infromation of 18 months for six urban centers. It comprises of up to 10 essential variables: temperature, atmospheric pressure, humidity, dew, precipitation, wind direction, wind speed, solar radiation, solar energy and UV index</t>
-        </is>
-      </c>
+          <t>Benin,Ghana,Niger,Togo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>These valuable resources available can support academic research, policymaking, and energy sustainability initiatives. They can also be utilized by key stakeholders such as the Ministry of Climate Change, Ministry of Energy (Power Division), 
- Punjab Energy Efficiency &amp; Conservation Authority, and National Energy Efficiency &amp; 
- Conservation Authority (NEECA) Moreover, private sector companies can use the data for market assessment purposes and 
- strategic planning as new entrants in the restructured energy market.</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Powered by: [Lahore University(LUMS)]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Luisa Olaya</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+          <t>Powered by:  Reiner Lemoine Institut gGmbH (RLI)
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>First Editing done by Luisa 27.08.2025</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1339,69 +1341,62 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Datasets for transportation impact evaluation</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Urban roadspace classification data and model</t>
-        </is>
-      </c>
+          <t>Promoting energy conservation and market analysis in Pakistan through Residential Energy and Weather Data (REWD)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The team developed a labeled training dataset, derived from 50cm or better satellite imagery, based on a novel, pre-defined road space classification taxonomy appropriate for training and deployment of large-scale deep-learning models</t>
+          <t>This dataset helps to understand energy consumption patterns in relation to weather conditions in Pakistan. This can guide policymaking on energy and energy conservation, sustainabe energy initiatives and private sector use (market assessment and strategic planning as new entrants in the restructured energy market). 
+The project produced an energy dataset of residential consumption data from buildings across six climatic zones. The energy dataset is recorded on a 1-minute granularity for entire household usage as well as for individual appliances. With over a year of detailed energy consumption data and 18 months of weather data collected from a diverse array of households across six distinct climatic zones, it is one of the most comprehensive datasets of its kind. This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GitHub - yangshao2/UrbanInfraDL</t>
+          <t>Residential Energy and Weather Data (REWD) - Pakistan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>SDG 13 (Climate Action), SDG 7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fundación Despacio,World Resources Institute,Fundación Despacio</t>
+          <t>Lahore University of Management Sciences (LUMS)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dataset and model available in Github, however it doesn´t have a good exmplanation, which makes it hard to know what is it about.
- Dataset of roadspace from 15 areas of Bogota each 1Km. 
- Bogotá’s orthophoto and GIS layers. 
- Data Dictionary</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Model that was tested for the entire city of Bogotá to clasify urban roadspace..And it worked with 98% reliability. Unfortunately not more info available</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 license</t>
-        </is>
-      </c>
+          <t>This Dataset is available in the webpage of the Lahore University. The dataset consist oth three parallel corpora: 
+1. Electricity consumption datacollected over year through advanced smart meters. The dataset consists of 60 households belonging to six major urban centers in varying climatic zones across the country. It is recorded on a 1-minute granularity for entire household usage as well as for individual appliances.  
+2. Metadata encompassing building attributes and demographic information for each household. The households in the dataset represent a wide and mixed demographic, social structure, and financial background.
+3. Meteorological dataset created with infromation of 18 months for six urban centers. It comprises of up to 10 essential variables: temperature, atmospheric pressure, humidity, dew, precipitation, wind direction, wind speed, solar radiation, solar energy and UV index</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>The resources can support policymaking and inform energy sustainability initiatives. They can namely be  utilized by key stakeholders such as the Ministry of Climate Change, Ministry of Energy (Power Division),  Punjab Energy Efficiency &amp; Conservation Authority, and National Energy Efficiency &amp;  Conservation Authority (NEECA)  Moreover,  private sector companies can use the data for market assessment purposes and strategic planning as new entrants in the restructured energy market.  The resources can also support further academic research and innovation.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Powered by: [Fundación Despacio]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by: Lahore University (LUMS)
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1411,29 +1406,25 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Dataset &gt; Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Link to White paper</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>First Editing done by Luisa 28.08.2026</t>
+          <t>First Editing done by Luisa 27.08.2025, Title and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
         </is>
       </c>
     </row>
@@ -1445,60 +1436,58 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Machine learning training data for continental Ecuador and Galapagos</t>
+          <t>Datasets for transportation impact evaluation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Land cover/ use data for Ecuador and the Galapagos</t>
+          <t>Urban roadspace classification data and model</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The project created a 20.000 points land use/cover classification training dataset from existing data, 
- with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML) 
- models covering continental Ecuador and the Galapagos islands</t>
+          <t>The team developed a labeled training dataset, derived from 50cm or better satellite imagery, based on a novel, pre-defined road space classification taxonomy appropriate for training and deployment of large-scale deep-learning models</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LULC training data for Ecuador - ML</t>
+          <t>GitHub - yangshao2/UrbanInfraDL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fundacion Ecociencia</t>
+          <t>Fundación Despacio,World Resources Institute,Fundación Despacio</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Two datasets available: 
- - BaseDatosValidacionFinal30052: This is the raw dataset containing 20,000 georeferenced points along with their respective land cover classifications.
- - LULC Training Data for Ecuador ML: This dataset builds upon the first by incorporating additional information on the conservation status of each point. This includes whether the location falls within protected areas, indigenous territories, areas under government forest incentive programs, and other conservation-related designations.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Dataset and model available in Github. Dataset of  roadspace from 15 areas of Bogota each 1Km. 
+Bogotá’s orthophoto and GIS layers. 
+Data Dictionary </t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Model that was tested for the entire city of Bogotá to clasify urban roadspace..And it worked with 98% reliability. Unfortunately not more info available</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>CC-BY 4.0 license</t>
@@ -1506,9 +1495,9 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Powered by: [Ecociencia]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by: Fundación Despacio
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1518,7 +1507,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Dataset &gt; Model</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1529,19 +1518,18 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Quote: “Land cover/use temporal trends are essential to understand the status of the remaining natural cover and change trends. But understanding the drivers of land use/cover change with local precision has proved challenging when working with existing global-scale datasets. Lacuna Fund’s support will allow us to create a precise dataset that will elevate our ability to discriminate land use classes that are both temporally and spatially descriptive. This funding will also support an extra layer of data to support projects aimed at reducing the pressure on standing forests and help maintain the socio-natural systems that have successfully prevented conversion of forests for anthropogenic use.” 
- – Wagner Holguín, Coordinator of MapBiomas Ecuador, Fundación Ecociencia</t>
+          <t>Link to White paper</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>First Editing done by Luisa 28.08.2027</t>
+          <t>First Editing done by Luisa 28.08.2026 / Availability on Github: it doesn´t have a good exmplanation, which makes it hard to know what is it about.</t>
         </is>
       </c>
     </row>
@@ -1553,53 +1541,99 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Forest carbon sequestration in the Congo Basin: combining In Situ Data and Artificial Intelligence to unlock climate finance</t>
+          <t>Monitoring the impact of palm oil monoculture, shrimp aquaculture &amp; mining in continental Ecuador and the Galapagos using AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>The dataset can help to build systems, that can monitor the impact of palm oil monoculture, shrimp aquaculture, mining and other land transformations in continental Ecuador and Galapagos. The project created a 20.000 points land use/cover classification training dataset from existing data, with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML)  models covering continental Ecuador and the Galapagos islands.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LULC training data for Ecuador - ML</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>World Resources Institute</t>
+          <t>Fundacion Ecociencia</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Cameroon,DRC</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Two datasets available: 
+- BaseDatosValidacionFinal30052: This is the raw dataset containing 20,000 georeferenced points along with their respective land cover classifications.
+- LULC Training Data for Ecuador ML: This dataset builds upon the first by incorporating additional information on the conservation status of each point. This includes whether the location falls within protected areas, indigenous territories, areas under government forest incentive programs, and other conservation-related designations.</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation. </t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 license</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+          <t>Powered by:  Ecociencia
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Quote: "At a time when the Congo Basin has become the most important rainforest carbon sink, and one of the highest biodiversity hotspots in the world, understanding and tracking its dynamics is more urgent than ever if we want to achieve global 2030 climate and biodiversity goals. With support from Lacuna Fund, our project will help bring machine learning to scientists working on the ground to monitor this ecosystem. It will pilot innovative technologies to close knowledge gaps and help speed action towards better managing these rainforests, ensuring a better world for people, nature, and climate.” 
- — Teodyl Nkuintchua, Congo Basin Strategy and Engagement Leader and Country Manager for Republic of Congo, World Resources Institute Africa</t>
+          <t xml:space="preserve">Quote: “Land cover/use temporal trends are essential to understand the status of the remaining natural cover and change trends. But understanding the drivers of land use/cover change with local precision has proved challenging when working with existing global-scale datasets. Lacuna Fund’s support will allow us to create a precise dataset that will elevate our ability to discriminate land use classes that are both temporally and spatially descriptive. This funding will also support an extra layer of data to support projects aimed at reducing the pressure on standing forests and help maintain the socio-natural systems that have successfully prevented conversion of forests for anthropogenic use.” 
+– Wagner Holguín, Coordinator of MapBiomas Ecuador, Fundación Ecociencia </t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>First Editing done by Luisa 28.08.2027, titel and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1609,7 +1643,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuador with Biodiversity AI-Datasets</t>
+          <t xml:space="preserve">Forest carbon sequestration in the Congo Basin: combining In Situ Data and Artificial Intelligence to unlock climate finance </t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1620,27 +1654,23 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GEO Indigenous Alliance</t>
+          <t>World Resources Institute</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Ecuador,Kenya</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
-        </is>
-      </c>
+          <t>Cameroon,DRC</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1649,13 +1679,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Quote: “Through the integration of Indigenous knowledge and cutting-edge technology, the Ltome-Katip project not only addresses pressing environmental and technical machine learning challenges but empowers Indigenous communities to lead the way in conservation efforts. This initiative, in collaboration with the Rochester Institute and Space4Innovation, represents a true partnership between the Shuar tribe in the Ecuadorian Amazon and the Samburu tribe in northern Kenya, showcasing the power of collaboration and Indigenous knowledge in safeguarding our planet’s biodiversity.” 
- — Mario Vargas Shakaim (Shuar), Ltome-Katip Indigenous-Led Monitoring Project GEO Indigenous Alliance</t>
+          <t xml:space="preserve">Quote: "At a time when the Congo Basin has become the most important rainforest carbon sink, and one of the highest biodiversity hotspots in the world, understanding and tracking its dynamics is more urgent than ever if we want to achieve global 2030 climate and biodiversity goals. With support from Lacuna Fund, our project will help bring machine learning to scientists working on the ground to monitor this ecosystem. It will pilot innovative technologies to close knowledge gaps and help speed action towards better managing these rainforests, ensuring a better world for people, nature, and climate.”  
+— Teodyl Nkuintchua, Congo Basin Strategy and Engagement Leader and Country Manager for Republic of Congo, World Resources Institute Africa </t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -1669,7 +1699,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI for Mangrove Carbon Credits: Turning Forest Data into Climate Action in Côte d’Ivoire</t>
+          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuador with Biodiversity AI-Datasets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1680,23 +1710,27 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data354</t>
+          <t>GEO Indigenous Alliance</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>Ecuador,Kenya</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1705,13 +1739,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Quote: “As far as monitoring and calculating forest carbon stocks are concerned, there is still a major technological bottleneck blocking the large-scale development of forest carbon credits in Côte d’Ivoire, which needs to be overcome quickly. Remote sensing is a useful tool in the forest monitoring process; further studies should be carried out to enable it to meet the need for assessment on a smaller scale and to measure biomass directly. In this way, we can help decision-makers orient their conservation policies, but also support the process of rewarding small players, such as agricultural producers involved in agroforestry, private forestry, etc. Our aim, with the funds raised, is to provide practical field data to better train artificial intelligence algorithms for dynamic mapping of forest biomass and mangroves.” 
-  — Abraham Bio, Actum Dev General Manager</t>
+          <t xml:space="preserve">Quote: “Through the integration of Indigenous knowledge and cutting-edge technology, the Ltome-Katip project not only addresses pressing environmental and technical machine learning challenges but empowers Indigenous communities to lead the way in conservation efforts. This initiative, in collaboration with the Rochester Institute and Space4Innovation, represents a true partnership between the Shuar tribe in the Ecuadorian Amazon and the Samburu tribe in northern Kenya, showcasing the power of collaboration and Indigenous knowledge in safeguarding our planet’s biodiversity.” 
+— Mario Vargas Shakaim (Shuar), Ltome-Katip Indigenous-Led Monitoring Project GEO Indigenous Alliance </t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -1725,119 +1759,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mapping Cocoa Landscapes in Ghana: Reference Data for Tracking Land Use Change</t>
+          <t>AI for Mangrove Carbon Credits: Turning Forest Data into Climate Action in Côte d’Ivoire</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/15778396</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Center for Remote Sensing and Geographic Information Services</t>
+          <t>data354</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Content:
- • 21,031 geocoded cocoa farm polygons (including agroforestry and shadeless cocoa)
- • 14,192 homogeneous (shadeless) cocoa polygons digitized from farm plots
- • 20,035 additional points/polygons for other land uses (informal gold mining, degraded forest, oil palm, rubber)
- • 485 anonymised household clusters (from 4,444 individual surveys) providing socioeconomic context
- Collection methods:
- • OpenForis Ground (field-based polygon collection)
- • Collect Earth Online (land use mapping)
- • KoboToolbox (household survey data)
- Purpose: Reference dataset for remote sensing, land cover classification, and land use change mapping in cocoa production landscapes.
- Limitations:
- • Polygons represent portions of farms, not legal or property boundaries.
- • Farm sizes do not reflect entire holdings.
- • Not suitable for certification or compliance purposes.</t>
-        </is>
-      </c>
+          <t>Cote d'Ivoire</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>What can be done immediately:
- • Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
- • Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.
- • Support policy analysis on sustainable cocoa, land degradation, and restoration planning in Ghana.
- How to extend or improve:
- • Add new field reference data from other cocoa-producing regions (e.g., Côte d’Ivoire, Nigeria) to increase transferability.
- • Integrate household-level socioeconomic data to study drivers of land use change and cocoa–forest dynamics.
- • Combine with climate and soil datasets to model sustainability scenarios.
- Limitations / ethical use:
- • Must not be used for farm-level regulation or compliance; polygons are reference only.
- • Potential imbalances between cocoa vs. non-cocoa land use classes should be addressed in model training.
- • Users are encouraged to conduct an ethical AI assessment before deploying derived models.
- Cost considerations:
- • Dataset itself is open access (no cost).
- • Small-scale applications (e.g., testing models in Google Earth Engine or QGIS) incur negligible costs.
- • Larger-scale ML training and national-scale mapping may require cloud compute budgets
-• Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
-• Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Powered by: WRI, CERSGIS, NASA SERVIR, Earth System Science Center
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Jonas Nothnagel</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Computer Vision</t>
-        </is>
-      </c>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Quote: “We are extremely grateful to Lacuna Fund and are delighted that our reference data collection effort will contribute immensely to an evolving data ecosystem to set up scalable machine learning applications for monitoring land-use change in cocoa-forest mosaic landscapes. Led by the Centre for Remote Sensing and Geographic Services (CERSGIS) and supported by researchers from the Centre for Climate Change and Sustainability Studies University of Ghana, International Crops Research Institute for the Semi-Arid Tropics (ICRISAT), Boston University, and the University of Alabama in Huntsville through SERVIR West Africa and the SERVIR Global network, this work will leverage the local knowledge of youth and community members for science-based participatory data collection. This data will provide critical input for enabling the transformation of commodity-driven supply chain traceability and commercial opportunities for ecosystem sustainability. 
- — Foster Mensah Center for Remote Sensing and Geographic Information Services University of Ghana</t>
+          <t xml:space="preserve">Quote: “As far as monitoring and calculating forest carbon stocks are concerned, there is still a major technological bottleneck blocking the large-scale development of forest carbon credits in Côte d’Ivoire, which needs to be overcome quickly. Remote sensing is a useful tool in the forest monitoring process; further studies should be carried out to enable it to meet the need for assessment on a smaller scale and to measure biomass directly. In this way, we can help decision-makers orient their conservation policies, but also support the process of rewarding small players, such as agricultural producers involved in agroforestry, private forestry, etc. Our aim, with the funds raised, is to provide practical field data to better train artificial intelligence algorithms for dynamic mapping of forest biomass and mangroves.”   
+ — Abraham Bio, Actum Dev General Manager </t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -1851,18 +1815,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supporting reforestation in Kenya through AI-powered monitoring of trees</t>
+          <t>Mapping Cocoa Landscapes in Ghana: Reference Data for Tracking Land Use Change</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>This project developed a efficient AI-powered method and dataset for monitoring of trees in forests in Kenya. Accurate tree crown detection and other parameters will support reforestation efforts in several ways: The datasets enable the development of tools that can rapidly assess the success of reforestation efforts by enabling counting of trees, estimation of trees’ biophysical parameters from drone images, and prediction of tree growth in relation to tree species and weather variables. The data consists of a high-resolution dataset of drone imagery, ground truth tree parameter measurements, and aggregate weather data from a large, reforested area in Kenya.</t>
+          <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[not yet published]</t>
+          <t>https://zenodo.org/records/15778396</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1873,22 +1837,150 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Geospatial, Images</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Prof. Ciira Maina, Centre for Data Science and Artificial Intelligence, Dedan Kimathi University of Technology</t>
+          <t>Center for Remote Sensing and Geographic Information Services</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Content:
+• 21,031 geocoded cocoa farm polygons (including agroforestry and shadeless cocoa)
+• 14,192 homogeneous (shadeless) cocoa polygons digitized from farm plots
+• 20,035 additional points/polygons for other land uses (informal gold mining, degraded forest, oil palm, rubber)
+• 485 anonymised household clusters (from 4,444 individual surveys) providing socioeconomic context
+Collection methods:
+• OpenForis Ground (field-based polygon collection)
+• Collect Earth Online (land use mapping)
+• KoboToolbox (household survey data)
+Purpose: Reference dataset for remote sensing, land cover classification, and land use change mapping in cocoa production landscapes.
+Limitations:
+• Polygons represent portions of farms, not legal or property boundaries.
+• Farm sizes do not reflect entire holdings.
+• Not suitable for certification or compliance purposes.</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
+        <is>
+          <t>What can be done immediately:
+• Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
+• Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.
+• Support policy analysis on sustainable cocoa, land degradation, and restoration planning in Ghana.
+How to extend or improve:
+• Add new field reference data from other cocoa-producing regions (e.g., Côte d’Ivoire, Nigeria) to increase transferability.
+• Integrate household-level socioeconomic data to study drivers of land use change and cocoa–forest dynamics.
+• Combine with climate and soil datasets to model sustainability scenarios.
+Limitations / ethical use:
+• Must not be used for farm-level regulation or compliance; polygons are reference only.
+• Potential imbalances between cocoa vs. non-cocoa land use classes should be addressed in model training.
+• Users are encouraged to conduct an ethical AI assessment before deploying derived models.
+Cost considerations:
+• Dataset itself is open access (no cost).
+• Small-scale applications (e.g., testing models in Google Earth Engine or QGIS) incur negligible costs.
+• Larger-scale ML training and national-scale mapping may require cloud compute budgets
+• Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
+• Use as a benchmark dataset to evaluate remote sensing products in heterogeneous tropical landscapes.
+How to extend or improve: 
+• Add new field reference data from other cocoa-producing regions (e.g., Côte d’Ivoire, Nigeria) to increase transferability.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Powered by:  WRI, CERSGIS, NASA SERVIR, Earth System Science Center
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jonas Nothnagel</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote: “We are extremely grateful to Lacuna Fund and are delighted that our reference data collection effort will contribute immensely to an evolving data ecosystem to set up scalable machine learning applications for monitoring land-use change in cocoa-forest mosaic landscapes. Led by the Centre for Remote Sensing and Geographic Services (CERSGIS) and supported by researchers from the Centre for Climate Change and Sustainability Studies University of Ghana, International Crops Research Institute for the Semi-Arid Tropics (ICRISAT), Boston University, and the University of Alabama in Huntsville through SERVIR West Africa and the SERVIR Global network, this work will leverage the local knowledge of youth and community members for science-based participatory data collection. This data will provide critical input for enabling the transformation of commodity-driven supply chain traceability and commercial opportunities for ecosystem sustainability.  
+— Foster Mensah Center for Remote Sensing and Geographic Information Services University of Ghana </t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ui_17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supporting reforestation in Kenya through AI-powered monitoring of trees</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This project developed a efficient AI-powered method and dataset for monitoring of trees in forests in Kenya. Accurate tree crown detection and other parameters will support reforestation efforts in several ways: The datasets enable the development of tools that can rapidly assess the success of reforestation efforts by enabling counting of trees, estimation of trees’ biophysical parameters from drone images, and prediction of tree growth in relation to tree species and weather variables. The data consists of a high-resolution dataset of drone imagery, ground truth tree parameter measurements, and aggregate weather data from a large, reforested area in Kenya.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[not yet published]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing, Images</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Prof. Ciira Maina, Centre for Data Science and Artificial Intelligence, Dedan Kimathi University of Technology</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Effective forest management and conservation require monitoring tree attributes such as height, crown diameter, and tree count to assess growth in reforested areas. These data enable the development of tools that can speed up the process to assess the success of reforestation efforts and other various ecological and forestry applications, including biomass estimation, forest health assessment, and carbon sequestration studies. Such tools could include the automated counting of trees, estimation of trees’ biophysical parameters from drone images such as tree crown diameter, and prediction of tree growth in relation to tree species and weather variables. In all these areas, AI can offer a cost-effective and scalable alternative to traditional methods of monitoring and counting.
 Concretely the following areas of restoration can be improved:
@@ -1896,128 +1988,44 @@
 2) Monitor Progress: Repeated application of the tree crown detection model can track the success of reforestation initiatives. The model can quantify the increase in tree cover over time, allowing for informed adjustments to reforestation strategies.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Powered by: Dedan Kimathi University of Technology, Kenya
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Powered by:  Dedan Kimathi University of Technology, Kenya
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Balthas Seibold</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Dataset</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>https://www.dw.com/en/artificial-intelligence-boosts-kenyas-forestry-conservation/video-69618432, https://dekut-dsail.github.io/projects/treedetection.html, https://agu.confex.com/agu/agu24/meetingapp.cgi/Paper/1728502, https://ieeexplore.ieee.org/document/11060524</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>GIZ</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Original title: Remote sensing and weather dataset for improved reforestation monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ui_17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Combatting deforestation &amp; supporting natural resource management in Uganda through satellite imagery AI-datasets and National Forestry Inventory AI-datasets</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deforestation is a significant contributor to changes in land use/cover in Uganda. This challenge is intensified by agriculture’s extreme vulnerability to climate change. This project has generated datasets that can be utilized to predict land cover types or changes for informed decision-making in natural resource management. The data is accessible, quality satellite imagery datasets and National Forestry Inventory datasets. Specifically, Sentinel 2 and Hansen tree cover image datasets have been augmented with the inclusion of inventory datasets. A biomass mean stock per hectare dataset for each vegetation type has also been acquired. Annotation procedures of the different datasets allow for machine learning tasks.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[not yet published]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SDG 15: Life on Land: sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Makerere University</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The land use/cover change datasets improve the understanding of the relationship between land cover/land use change and climate change. The can also be used to inform practice and policy on how best to manage various potential scenarios and combat deforestation.        </t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Powered by: Makerere University in cooperation with the Uganda National Forestry Authority (NFA)
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Balthas Seibold</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Dataset &gt; Model</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Quote: “With funding from Lacuna Fund, satellite image and forest inventory datasets will help to develop machine learning models for prediction of land cover types or changes for informed decision-making in natural resource management. Under joint research from Makerere College of Agriculture and Environment Studies and Makerere AI Health Lab, and in partnership with the National Forestry Authority, Uganda, our land use/cover change datasets will improve our understanding of the relationship between land cover/land use change and climate change. It will also be useful in informing practice and policy on how best to manage various potential scenarios. 
- — Dr. Sarah Akello, College of Agriculture and Environmental Sciences, Makerere University</t>
+          <t>https://www.dw.com/en/artificial-intelligence-boosts-kenyas-forestry-conservation/video-69618432, https://dekut-dsail.github.io/projects/treedetection.html, https://agu.confex.com/agu/agu24/meetingapp.cgi/Paper/1728502, https://ieeexplore.ieee.org/document/11060524</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>original title: DATASETS FOR PREDICTION OF LAND USE/COVER CHANGES IN UGANDA</t>
+          <t>Original title: Remote sensing and weather dataset for improved reforestation monitoring</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2037,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>African Trees for Climate Resilience: A Comprehensive database</t>
-        </is>
-      </c>
+          <t>Combatting deforestation &amp; supporting natural resource management in Uganda through satellite imagery AI-datasets and National Forestry Inventory AI-datasets</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Extensive bioinformatics resource that leverages tree species’ medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.</t>
+          <t xml:space="preserve">Deforestation is a significant contributor to changes in land use/cover in Uganda. This challenge is intensified by agriculture’s extreme vulnerability to climate change. This project has generated datasets that can be utilized to predict land cover types or changes for informed decision-making in natural resource management. The data is accessible, quality satellite imagery datasets and National Forestry Inventory datasets.  Specifically, Sentinel 2 and Hansen tree cover image datasets have been augmented with the inclusion of inventory datasets. A biomass mean stock per hectare dataset for each vegetation type has also been acquired. Annotation procedures of the different datasets allow for machine learning tasks. </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2050,70 +2054,63 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Images, Tabular,</t>
-        </is>
-      </c>
+          <t>SDG 15: Life on Land: sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>University of Stellenbosch</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Angola,DRC,Germany,Kenya,Mozambique,Nigeria,South Africa,Tanzania,United Kingdom,Zambia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
+          <t xml:space="preserve">The land use/cover change datasets improve the understanding of the relationship between land cover/land use change and climate change. The can also be used to inform practice and policy on how best to manage various potential scenarios and combat deforestation.        </t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Powered by: [Stellenbosch University]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by: Makerere University in cooperation with the Uganda National Forestry Authority (NFA)
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>Balthas Seibold</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Computer Vision/Picture data</t>
-        </is>
-      </c>
+          <t>Dataset &gt; Model</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Quote: "We are excited that Lacuna Fund has provided Stellenbosch, and our team, with the opportunity to utilize these datasets to enable researchers to model the impacts of indigenous trees for adaptation and mitigation to climate change in southern Africa. This information is of the utmost importance in ensuring the continent can build resilience against the rapid unfolding of climate change which is affecting livelihoods and demanding that we find solutions.” 
- — Professor Guy Midgley, Acting Director at School for Climate Studies, Stellenbosch University</t>
+          <t xml:space="preserve">Quote: “With funding from Lacuna Fund, satellite image and forest inventory datasets will help to develop machine learning models for prediction of land cover types or changes for informed decision-making in natural resource management. Under joint research from Makerere College of Agriculture and Environment Studies and Makerere AI Health Lab, and in partnership with the National Forestry Authority, Uganda, our land use/cover change datasets will improve our understanding of the relationship between land cover/land use change and climate change. It will also be useful in informing practice and policy on how best to manage various potential scenarios. 
+— Dr. Sarah Akello, College of Agriculture and Environmental Sciences, Makerere University 
+</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>First Editing done by Luisa 28.08.2027</t>
+          <t>original title: DATASETS FOR PREDICTION OF LAND USE/COVER CHANGES IN UGANDA</t>
         </is>
       </c>
     </row>
@@ -2125,13 +2122,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
+          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin.</t>
+          <t>Extensive bioinformatics resource that leverages tree species’ medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2142,42 +2139,42 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
+          <t>Life on Land (SDG 15): sustainably manage forests</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Images, Tabular,</t>
+          <t>Images, Tabular</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Romain Lucas Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
+          <t>University of Stellenbosch</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>This datasets can be used to build systems for faster, more regular monitoring of mangrove conditions. This is essential to provide evidence that supports timely decisions for mangrove management and mitigate the outcomes of climate change.</t>
+          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Powered by: University of Abomey-Calavi, Republic of Benin 
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [Stellenbosch University]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>Luisa Olaya</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2187,20 +2184,25 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Computer Vision/Picture data</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Quote: "We are excited that Lacuna Fund has provided Stellenbosch, and our team, with the opportunity to utilize these datasets to enable researchers to model the impacts of indigenous trees for adaptation and mitigation to climate change in southern Africa. This information is of the utmost importance in ensuring the continent can build resilience against the rapid unfolding of climate change which is affecting livelihoods and demanding that we find solutions.” 
+— Professor Guy Midgley, Acting Director at School for Climate Studies, Stellenbosch University</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Original title: Datasets to understand mangroves health in relationship to climate change</t>
+          <t>First Editing done by Luisa 28.08.2027</t>
         </is>
       </c>
     </row>
@@ -2212,11 +2214,99 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Advancing oil palm mapping with social forestry and machine learning</t>
+          <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[not yet published]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Images, Tabular</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Romain Lucas        Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This datasets can be used to build systems for faster, more regular monitoring of mangrove conditions. This is essential to provide evidence that supports timely decisions for mangrove management and mitigate the outcomes of climate change.
+</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Powered by: University of Abomey-Calavi, Republic of Benin 
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Original title: Datasets to understand mangroves health in relationship to climate change</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ui_21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mitigating the impacts of oil palm cultivation on forests and climate change in Indonesia through AI and social forestry</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>This dataset contributes to improved understanding and mitigation of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management. 
 The project created open and accessible training and evaluation datasets for machine learning applications focused on forest cover and change in Indonesia. It contains collections of polygons of uniform land cover, with labels indicating land cover type and, possibly, information on land cover change over time. To label land cover patches, the team has reviewed high-resolution satellite imagery facilitated by Collect Earth Online (CEO) and augmented it with field visits to difficult-to-classify areas. It has prioritized areas with significant landcover diversity with a preference for areas with significant smallholder production of  oil palm, coconut, and other commodities - given the well-known difficulties of distinguishing oil palm 
@@ -2224,108 +2314,77 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[not yet published]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>RECOFTC</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Drone Imagery, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RECOFTC, Peter Cutter (peter.cutter@recoftc.org)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Quote: “Communities in the areas targeted by this project are challenged when it comes to mapping the rapidly changing forest landscapes on which they depend. The datasets this project generates will provide valuable insight into these dynamic patterns of change.” 
- — Gamma Galudra, Director, Indonesia Country Office, RECOFTC</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>GIZ</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ui_21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Inclusive MRV for India's Eastern Himalayas</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Balipara Foundation</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>India</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>Powered by:  RECOFTC
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>https://www.recoftc.org/sites/default/files/styles/image_scale_w1024/public/2025-03/dji_0037.jpg.webp?itok=l0ilgQi8</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Quote: “Lacuna Fund will be instrumental in supporting the development of an MRV system that will enable us to participatorily map the health of forests in the biodiverse Eastern Himalayan region with indigenous communities, facilitating targeted interventions for climate resilience through forest management – impacting the millions of people that depend on forests for their lives and livelihoods in the Eastern Himalayas.” 
- — Michael Dawson, Rural Futures – Anthropological Visioner, Balipara Foundation</t>
+          <t xml:space="preserve">https://www.recoftc.org/projects/advancing-oil-palm-mapping-social-forestry-and-machine-learning 
+Quote: “Communities in the areas targeted by this project are challenged when it comes to mapping the rapidly changing forest landscapes on which they depend. The datasets this project generates will provide valuable insight into these dynamic patterns of change.”  
+— Gamma Galudra, Director, Indonesia Country Office, RECOFTC </t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2339,27 +2398,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
+          <t>Inclusive MRV for India's Eastern Himalayas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
+          <t>Balipara Foundation</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>India</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2368,9 +2423,9 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2379,13 +2434,14 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Quote: “The Lacuna-funded Agro4Resilience Project offers Kenyan farmers and decision makers a pathway for informed decision-making that supports tree cover increase. It will also improve agricultural productivity and mitigate climate change effects through ecosystem services.” 
- — David Makori, International Centre of Insect Physiology and Ecology (ICIPE)</t>
+          <t xml:space="preserve">Quote: “Lacuna Fund will be instrumental in supporting the development of an MRV system that will enable us to participatorily map the health of forests in the biodiverse Eastern Himalayan region with indigenous communities, facilitating targeted interventions for climate resilience through forest management – impacting the millions of people that depend on forests for their lives and livelihoods in the Eastern Himalayas.”  
+— Michael Dawson, Rural Futures – Anthropological Visioner, Balipara Foundation 
+</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -2399,23 +2455,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QUANTIFYING COLOMBIAN MANGROVES ABOVEGROUND BIOMASS AND CARBON CONTENT</t>
+          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)</t>
+          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2424,9 +2484,9 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2435,13 +2495,13 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Quote: “The dataset compiled during the project will facilitate accurate AGB and AGC estimation in Colombian Caribbean mangroves, enabling better understanding of carbon storage and supporting conservation and management efforts. It will also provide a valuable resource for future research and monitoring activities related to these important coastal ecosystems. Furthermore, the methodology developed in this project might even be applied beyond the Colombian Caribbean to other mangrove ecosystems with similar structures.” 
- — María Cuevas-González, Geomatics Research Unit, Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)</t>
+          <t xml:space="preserve">Quote: “The Lacuna-funded Agro4Resilience Project offers Kenyan farmers and decision makers a pathway for informed decision-making that supports tree cover increase. It will also improve agricultural productivity and mitigate climate change effects through ecosystem services.” 
+— David Makori, International Centre of Insect Physiology and Ecology (ICIPE)  </t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -2455,7 +2515,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
+          <t>QUANTIFYING COLOMBIAN MANGROVES ABOVEGROUND BIOMASS AND CARBON CONTENT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2466,12 +2526,12 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>"Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana"</t>
+          <t>Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ghana,Netherlands</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2480,9 +2540,9 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Powered by: [ADD!!!]
- Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
- Financed by: BMZ</t>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2491,13 +2551,13 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
- — Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources</t>
+          <t xml:space="preserve">Quote: “The dataset compiled during the project will facilitate accurate AGB and AGC estimation in Colombian Caribbean mangroves, enabling better understanding of carbon storage and supporting conservation and management efforts. It will also provide a valuable resource for future research and monitoring activities related to these important coastal ecosystems. Furthermore, the methodology developed in this project might even be applied beyond the Colombian Caribbean to other mangrove ecosystems with similar structures.”  
+— María Cuevas-González, Geomatics Research Unit, Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)  </t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -2511,97 +2571,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open Air Pollution Data for Patna and Gurugram</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Combatting Air Pollution and GHG Emissions in India through hyperlocal AI-powered mapping</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Under this initiative, a novel approach is employed by leveraging citizen scientists and IoT-based low-cost sensors to collect hyperlocal air quality data. This data is used to identify pollution sources and risk zones, facilitating targeted actions by regulatory authorities.To showcase data outreach, the project features the VAYU Android-based application and the VAYU citizen portal digital stack, which support targeted interventions and customized solutions backed by AI/ML algorithms. These tools potentially develop new approaches in air pollution management while reducing public investment costs.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://vayu.undp.org.in/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://github.com/undpindia/VAYU_OpenAir; https://github.com/EconAIorg/vayu-gnn/tree/main; https://github.com/Alphawarrior21/VayuAssist; https://github.com/akbp24/ClearSky; https://github.com/sherwaldeepesh/vayu_airnode</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SDG 13 (Climate Action)</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+          <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>UNDP India (https://www.undp.org/india)</t>
+          <t>"Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana"</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>The data for this project is collected by static and dynamic sensor. Static sensors are placed at known hotspots for air pollution while dynamic sensors are moved by citizen scientist continously. 
- • 2 Cities
- • 100+ Senors
- • 150+ Volunteers
- • 1000+ Records Collected
- • ~10Million Data Points</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
-        </is>
-      </c>
+          <t>Ghana,Netherlands</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>CC-BY</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Powered by: UNDP India
- Catalyzed by: FAIR Forward - AI for All (https://www.bmz-digital.global/en/overview-of-initiatives/fair-forward/)
- Financed by: BMZ (https://www.bmz-digital.global/en/digital-transformation-and-development-cooperation/)</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Jonas Nothnagel, Arun Kumar Yadav</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Dataset &gt; Model &gt; Pilot &gt; Use-Case</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Computer Vision</t>
-        </is>
-      </c>
+          <t>Powered by:  [ADD!!!]
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
+— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>GIZ</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>SDG 13</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 8 (Promote inclusive economic growth through financial inclusion)</t>
+          <t>SDG 10, SDG 8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -772,7 +772,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Reduced inequality through access to info in local languages/NLP (SDG 10), Achieve Gender Equality (SGD 5), achieve food security, sustainable agriculture (SDG 2)</t>
+          <t>SDG 10, SDG 5, SDG 2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -875,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>SDG 13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,11 +1228,7 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -1353,7 +1349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Residential Energy and Weather Data (REWD) - Pakistan</t>
+          <t>https://lei.lums.edu.pk/datasets/residential-energy-and-weather-data-pakistan.html</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1451,7 +1447,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GitHub - yangshao2/UrbanInfraDL</t>
+          <t>https://github.com/yangshao2/UrbanInfraDL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1487,7 +1483,11 @@
           <t>Model that was tested for the entire city of Bogotá to clasify urban roadspace..And it worked with 98% reliability. Unfortunately not more info available</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>The resources allow local governments, urban and infraestructure planning offices to evaluate how much area of the city is destined toe ach mode of transportation. It will be possible to include percentaje of area distribuited per mode as public and transportation allocation policies, to evaluate equity and accessibility.</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>CC-BY 4.0 license</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LULC training data for Ecuador - ML</t>
+          <t>https://www.kaggle.com/datasets/mapbiomasecuador/lulc-training-data-for-ecuador-ml/data</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1699,18 +1699,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuador with Biodiversity AI-Datasets</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuadorian Amazon with Biodiversity AI-Datasets</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ltome-Katip: Pioneering Indigenous-Led Biodiversity Datasets for Ethical AI in Kenya and the Ecuadorian Amazon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>The Ltome-Katip datasets are the first Indigenous-labelled bioacoustic datasets designed specifically to support the development of ethical AI for biodiversity monitoring. Co-created by Indigenous data stewards from the Samburu tribe in northern Kenya and the Shuar Nation in the Ecuadorian Amazon, the recordings focus on two sentinel species: Ltome (elephant) and Katip (rodent), both of which signal ecological shifts under climate stress. All data were collected, annotated, and governed by the Indigenous communities, following locally defined protocols rooted in Indigenous data sovereignty. These datasets are not only scientifically valuable — they establish a precedent for how Indigenous communities can lead in setting standards for responsible, consent-based AI development.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://arbimon.org/p/namunyak-conservancy-reteti-elephant-sanctuary; https://arbimon.org/p/shakiam-ecuadorian-amazon/insights</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SGD 1, 2, 3, 4, 5, 8,10, 13, 15 </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Drone Imagery, Text, Voice, Geospatial/Remote Sensing, Images, Meterological, Tabular, Other</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GEO Indigenous Alliance</t>
+          <t>Space4Innovation, Diana Mastracci diana@space4innovation.com</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1720,27 +1740,59 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t xml:space="preserve">Ltome-Katip Indigenous Bioacoustic Dataset
+Regions: Samburu (Kenya) · Shuar (Ecuadorian Amazon)
+Custodians: Chief Titus Letaapo (Samburu tribe) (Namunyak Conservancy), Chief Mario Vargas Shakaim (Shuar Nation) (MUSAP Biological Station), and Space4Innovation
+This dataset contains Indigenous-labelled bioacoustic recordings from two ecosystems—semi-arid savannah and tropical rainforest—collected through AudioMoth bioacustic sensors. Data include species-specific sounds (e.g., elephants, rodents), environmental background, and associated metadata following the CARE Principles for Indigenous Data Governance.
+Use cases: biodiversity monitoring, species classification, human–wildlife conflict alerts, and AI model training for conservation.
+Limitations: class imbalance (key species overrepresented), environmental noise, and spatial clustering; users should apply noise filtering and ethical review before reuse. These audio data are collected 24/7 when deployed in time periods ranging from hours to several weeks. The data are acquired from multiple microphones spread across the study site. Each microphone has a unique serial number and the geographic locations are provided using GPS. The data are time stamped, however there are data gaps in time and space due to logistics, equipment failure, or power loss. The original data are stored as 16-bit WAV files and are available. To make the data more widely available, they have been uploaded to the Arbimon.org platform. The Arbimon cloud platform is built for bioacoustics analysis using various ML . 
+License: CC BY-NC-SA 4.0 — reuse and adaptation allowed for non-commercial purposes, with attribution and benefit sharing to Indigenous custodians.
+</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>The Ltome-Katip system uses Indigenous-labelled bioacoustic data to train AI models that detect and classify species like elephants in Samburu (Kenya) and rodents in the Ecuadorian Amazon. These models are already being used to monitor biodiversity, understand ecological stress, and support early warning systems rooted in Indigenous governance. What sets Ltome-Katip apart is that both the dataset and its governance model were co-designed by Indigenous communities. All development follows the CARE Principles for Indigenous Data Sovereignty, and any replication must go through an Ethical AI Assessment to ensure consent, transparency, and benefit-sharing. This project sets a new global benchmark for community-led, responsible AI in biodiversity and conservation.
+The data is processed using the Arbimon platform, where recordings are visualized as spectrograms and labelled through bounding boxes by trained Indigenous data stewards. The outputs — including geospatial and temporal metadata — can be downloaded as CSV files and used for further machine learning or integration with other ecological datasets. These tools are already generating insights into ecosystem change and human–wildlife conflict. The core team is now actively designing Ltome-Katip 2, a next-phase expansion that will deepen Indigenous-led data infrastructure, extend sensor coverage, and explore AI integration with the Namunyak app. While plans are in development, we are currently seeking aligned funding to support this work, which will remain entirely Indigenous-led and ethically governed at every stage.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>The Ltome-Katip datasets can already be used to detect and classify species such as elephants and rodents, enabling real-time biodiversity monitoring and alerts for human–wildlife conflict. They also support ecosystem health assessments by capturing patterns in species richness, activity cycles, and climate-driven changes. Indigenous-led early warning systems are already being built using these datasets and dashboards, allowing communities to visualize and act on local ecological shifts. Researchers can extend this work by adding new species, integrating satellite data, applying transfer learning, or developing explainable AI tools to improve accuracy and cross-ecosystem usability. All reuse must respect Indigenous data sovereignty, undergo an ethical AI review, and credit the original communities. The Ltome-Katip core team is actively seeking funding for the next phase — Ltome-Katip 2 — which will expand the sensor network, strengthen community data infrastructure, and integrate AI capabilities into the Namunyak Indigenous app.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>License: CC BY-NC-SA 4.0 — reuse and adaptation allowed for non-commercial purposes, with attribution and benefit sharing to Indigenous custodians.</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  Space4Innovation, Namunyak Conservancy, GEO Indigenous Alliance, MUSAP &amp; Rochester Institute for Technology
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Diana Mastracci, Space4Innovation, GEO Indigenous Alliance</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Earth Observation &amp; other</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Through the integration of Indigenous knowledge and cutting-edge technology, the Ltome-Katip project not only addresses pressing environmental and technical machine learning challenges but empowers Indigenous communities to lead the way in conservation efforts. This initiative, in collaboration with the Rochester Institute and Space4Innovation, represents a true partnership between the Shuar tribe in the Ecuadorian Amazon and the Samburu tribe in northern Kenya, showcasing the power of collaboration and Indigenous knowledge in safeguarding our planet’s biodiversity.” 
-— Mario Vargas Shakaim (Shuar), Ltome-Katip Indigenous-Led Monitoring Project GEO Indigenous Alliance </t>
+— Mario Vargas Shakaim (Shuar), Ltome-Katip Indigenous-Led Monitoring Project GEO Indigenous Alliance https://www.linkedin.com/pulse/when-future-already-here-now-its-being-filmed-diana-mastracci-sanchez-y5rue.     https://www.linkedin.com/pulse/embracing-uncertainty-hidden-strength-science-diana-mastracci-sanchez-qdj5e.   https://www.linkedin.com/pulse/bridging-worlds-indigenous-led-innovation-remote-mastracci-sanchez-yjqfe.    https://www.rit.edu/dirs/research/ltome-katip-indigenous-led-labelling-inclusive-ai-addressing-human-wildlife-conflict-and.    https://www.rit.edu/news/professor-helps-bring-machine-learning-indigenous-communities </t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1749,7 +1801,11 @@
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>trello board with key messages: https://trello.com/invite/b/669bafb78c890345b83127a3/ATTIcf32f650c44aa08c718541da28f2559e8E474BA5/ltome-katip-comms-plan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1762,12 +1818,24 @@
           <t>AI for Mangrove Carbon Credits: Turning Forest Data into Climate Action in Côte d’Ivoire</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WatchMyTree</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://figshare.com/articles/dataset/The_First_Open_Dataset_of_Mangrove_Above-_and_Belowground_Biomass_and_Soil_Carbon_Stocks_in_C_te_d_Ivoire_Insights_from_Fresco_and_Sassandra_/30258772</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>data354</t>
@@ -1790,7 +1858,11 @@
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
@@ -1952,11 +2024,7 @@
           <t>This project developed a efficient AI-powered method and dataset for monitoring of trees in forests in Kenya. Accurate tree crown detection and other parameters will support reforestation efforts in several ways: The datasets enable the development of tools that can rapidly assess the success of reforestation efforts by enabling counting of trees, estimation of trees’ biophysical parameters from drone images, and prediction of tree growth in relation to tree species and weather variables. The data consists of a high-resolution dataset of drone imagery, ground truth tree parameter measurements, and aggregate weather data from a large, reforested area in Kenya.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[not yet published]</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
@@ -2046,11 +2114,7 @@
           <t xml:space="preserve">Deforestation is a significant contributor to changes in land use/cover in Uganda. This challenge is intensified by agriculture’s extreme vulnerability to climate change. This project has generated datasets that can be utilized to predict land cover types or changes for informed decision-making in natural resource management. The data is accessible, quality satellite imagery datasets and National Forestry Inventory datasets.  Specifically, Sentinel 2 and Hansen tree cover image datasets have been augmented with the inclusion of inventory datasets. A biomass mean stock per hectare dataset for each vegetation type has also been acquired. Annotation procedures of the different datasets allow for machine learning tasks. </t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[not yet published]</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
@@ -2125,15 +2189,19 @@
           <t>African Trees for Climate Resilience: A Comprehensive Database</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SAT-CARe</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Extensive bioinformatics resource that leverages tree species’ medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
+          <t>Extensive bioinformatics resource that leverages tree species’ distribution, medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[not yet published]</t>
+          <t>https://www.gbif.org/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2144,12 +2212,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Images, Tabular</t>
+          <t>Images, Tabular, Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>University of Stellenbosch</t>
+          <t>Professor Guy F Midgley gfmidgley@sun.ac.za University of Stellenbosch</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2157,14 +2225,26 @@
           <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>An extensive relational floristic and plant functional database which, together with matching biogeoclimatic data sets and implementation of the distribution model, may describe the biogeoclimatic relationships and projects the growth and ecological success of all sufficiently recorded Southern African trees under current and future climatic conditions</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Automation of a species distribution model that leverages a novel mechanistically based algorithm for 1) quantification of currently suitable planting-range conditions and 2) projection of climate risk for future planting-range suitability. This primary screening effort can be cross-referenced for adaptation and mitigation use-value sources to aid in tree species selection.</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>open source</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Powered by:  [Stellenbosch University]
@@ -2179,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Dataset &gt; Model &gt; Pilot</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2187,7 +2267,11 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Possible to draw maps of species distribution for present and futrue climates, as one initial output, but also to run hundreds of species filtered by key trait characteristics that indicate suitability for climate mitigation and adaptation</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>Quote: "We are excited that Lacuna Fund has provided Stellenbosch, and our team, with the opportunity to utilize these datasets to enable researchers to model the impacts of indigenous trees for adaptation and mitigation to climate change in southern Africa. This information is of the utmost importance in ensuring the continent can build resilience against the rapid unfolding of climate change which is affecting livelihoods and demanding that we find solutions.” 
@@ -2223,11 +2307,7 @@
           <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[not yet published]</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
@@ -2314,15 +2394,12 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>[not yet published]</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>SDG 13 (Climate Action), 
+SDG 15 (Life on Land)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2402,14 +2479,36 @@
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>An AI-Driven Dataset for Nature-Positive Livelihoods and Forest Restoration in Eastern Himalayas.This open-access dataset and digital MRV (Monitoring, Reporting, and Verification) toolkit was  developed to help communities, NGOs and policymakers in the Eastern Himalayas measure and manage the links between forests, livelihoods and climate resilience. The project was created in response to a persistent data gap in the Himalayan region where limited open data and difficult terrain have hindered effective monitoring of forest degradation and the impact of restoration programs. Using locally calibrated AI models trained on Indian biomass data, the system combines satellite observations with ground level socio-economic surveys to measure forest dependency, identify degradation hotspots and track restoration outcomes. All datasets ranging from community level livelihood surveys in Sikkim and Mizoram to forest biomass and land use layers in Assam are openly available. Together they form a replicable, open-source “digital public good” that can be used to train local AI models for forest monitoring, biodiversity accounting or impact assessment. By providing a scalable, context-aware dataset, this initiative enables indigenous start-ups, environmental NGOs and impact investors to quantify nature positive outcomes, align with IRIS+ indicators, and guide conservation investments.
+The goal is to make environmental monitoring inclusive and data driven, empowering local actors to track changes in forest carbon, identify erosion risks and measure the socio-economic benefits of restoration. Ultimately, this approach helps governments, researchers and entrepreneurs build locally adapted AI systems that support both ecosystem regeneration and sustainable livelihoods in fragile mountain regions.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://github.com/vertify-earth/biomass-prediction-NorthEastIndia; https://zenodo.org/records/16536024</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1WaunaB-HU-j9UDs-X5Fn1vJ15H4ENMe-lcEgWM9l3Eg/edit?usp=sharing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Balipara Foundation</t>
+          <t>Vertify.earth, Michael Anthony michael@vertify.earth ,
+Alsisar Impact, Saurabh Singhavi saurabh@alsisarimpact.com</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2417,21 +2516,59 @@
           <t>India</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>This dataset integrates geospatial and socio-economic information to monitor forest restoration and livelihoods in the Eastern Himalayas. It combines satellite data from Sentinel-1, Sentinel-2, Landsat-8, and PALSAR with 500+ ground truth points and nearly 300 household surveys collected in Assam, Sikkim, and Mizoram. The data support AI applications for biomass estimation, deforestation detection and nature positive impact assessment.
+A locally trained biomass model improves accuracy for South Asian forest types, addressing calibration bias in global datasets. All personal identifiers have been removed, and sensitive coordinates anonymized to protect community privacy. The dataset is published under a CC-BY 4.0 license and maintained by Vertify.earth GmbH and Earth Analytics India Pvt Ltd, ensuring its ongoing usability as an open and replicable foundation for environmental AI and digital MRV systems.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The AI model estimates forest biomass and vegetation health in the Eastern Himalayas using multi-source satellite data combined with local ground measurements. It outputs Above-Ground Biomass (AGB) maps, enabling accurate tracking of forest carbon, degradation, and restoration progress.
+The model accepts pre-processed satellite imagery as input and produces spatial biomass layers compatible with MRV dashboards. It runs on standard Python environments and can be adapted for other tropical regions with local calibration.
+Calibrated for South Asian forests; retraining is needed for other regions. Seasonal cloud cover can affect results. All training data are anonymized, and community consent was obtained. Users should validate outputs locally before application. Released under CC-BY 4.0 for open reuse and replication. Please credit Vertify.earth and Earth Analytics India and share improvements through the Vertify.earth GitHub
+</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>This dataset and AI model can be used immediately for forest monitoring, restoration planning and impact measurement in mountain and forested regions. Users can map biomass, detect forest loss or assess community-level livelihood impacts by combining the open dataset with freely available satellite imagery. NGOs, research institutions, investors can directly apply the dataset to design or evaluate nature positive projects, while developers can integrate the AI model into their own MRV dashboards. Researchers and AI developers can extend this work by retraining the biomass model with local field data from other regions or adding new layers such as soil moisture or biodiversity indicators. Ethical replication should include community consent and data validation steps to ensure fair and context aware use.
+Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
+Model use: Free, standard cloud or local compute</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  Vertify.earth GmbH, Earth Analytics India Pvt Ltd, Balipara Foundation, Alsisar Impact
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Arundhati Deshmukh</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case &gt;  Use-Case with Business Model</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Earth Observation / Satellite &amp; Drone Data</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>https://felt.com/embed/map/Nature-Audit-on-Agapi-Sourcing-Sites-JBeP3LpnTCmabCOFb9AVrAC?loc=27.317897%2C88.595673%2C15.25z</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Lacuna Fund will be instrumental in supporting the development of an MRV system that will enable us to participatorily map the health of forests in the biodiverse Eastern Himalayan region with indigenous communities, facilitating targeted interventions for climate resilience through forest management – impacting the millions of people that depend on forests for their lives and livelihoods in the Eastern Himalayas.”  
@@ -2458,16 +2595,32 @@
           <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Climate resilience through agroforestry</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The Agrof4Resilience geospatial datasets are open-access utilized by artificial intelligence (AI) and machine learning (ML) algorithms that are aimed at creating more robust, productive, resilient and diverse agro-ecological systems to achieve productive agro-ecosystems that have potential to improve resilience over time. This is crucial especially in dryland which are plagued with land degredation and other effects of climate change. The data demonstrates that agroforestry in Kenya is fairly low while models developed from the data indicate high agroforestry potential in Kenya. This is affected by socioeconomic factors such as education levels, occupation, age, landsize, income, gender, marital status, cultural beliefs, and family size. These datasets could be utilized to demostrate regions and practices that are environementally and socio-economically sound. This could provide insights on practices that could enhance livelihoods and promote environmental resilience in target communities across Kenya. The data was collected from 35 out of 47 counties in Kenya, spread across four predetermined transects that cover four main agro-ecological zones, and stored in a freely accessible database within icipe’s servers.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://dmmg.icipe.org/dataportal/dataset/data-enabled-climate-shock-absorbance-and-ecosystem-resilience</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
@@ -2478,9 +2631,17 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This geospatial datasets comprises both land use/landcover (LULC) data, plot sampling and socio-economic data from 35 out of 47 counties in Kenya spread across four main agroclimatic zones in Kenya. It contains machine learning-ready data of 2,391 LULC points and polygones of the collected LULC classes, that show the different land uses across Kenya. It also contains a total of a total of 8,194 plant location (gps) points of individual tagged plants collected from a total of 224 1-ha plots from 35 counties in Kenya. Information on the species identification, diameter at breast height (DBH), height, and canopy size is provided. In addition, socio-economic data from 46 focused group discussions with over 44% women and 18% youth conducted within the 35 counties is provided and clearly labeled, detailing agroforestry systems (AFSs) preferences, gender roles, and youth participation in agroforestry systems (AFSs). </t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The database provides information on tree/plant-level, plot-level and landscape scale across Kenya. Measurements such as DBH, tree height, canopy size and tree identification have been provided. In addition, socio-economic data such as agroforestry systems (AFSs) preferences, gender roles, and youth participation in AFSs are also provided. The datasets are readily and freely available to users who can integrate it to AI and ML algorithms and models as ground-truth data to train and/or validate the models associated and/or related to agroforestry and carbon sequestration across Kenya. The models developed using the Agrof4Resilience data could utilize and take advantage of satellite data from various sources that are both freely available or with commercial licences. </t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
@@ -2490,7 +2651,11 @@
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
@@ -2515,18 +2680,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QUANTIFYING COLOMBIAN MANGROVES ABOVEGROUND BIOMASS AND CARBON CONTENT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>Quantifying Colombian mangroves aboveground biomass and carbon content</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mapping Blue Carbon: Quantifying Mangrove Carbon Stocks for Climate Action and Conservation in the Colombian Caribbean</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This open-access dataset supports machine learning (ML) applications for mangrove forest monitoring, addressing the need for more openly available and well-annotated datasets to calibrate and validate ML models. It focuses on improving the estimation of above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian Caribbean mangroves. The pilot area, Via Parque Isla de Salamanca National Natural Park (VIPIS) in the Magdalena department, is a Ramsar and UNESCO Biosphere Reserve. Existing global AGB and AGC models often lack the precision and cost-effectiveness needed for regional monitoring.
+The dataset includes both plot-level and tree-level field measurements from 20 newly surveyed plots, providing detailed attributes such as DBH, height, species, AGB (from allometric equations), and AGC. Using these field data, high-resolution satellite imagery, and machine learning models, satellite-based AGB and AGC maps covering ~6,000 ha of mangroves at 10 m spatial resolution have also been generated. </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://acceso-datos-ambientales-invemar.hub.arcgis.com/maps/a0cab53befd44804923800a194c703d6/about</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SDG 15 (Life of Land)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)</t>
+          <t>María Cuevas (mcuevas@cttc.es / Centre Tecnològic de Telecomunicacions de Catalunya, CTTC, Spain),  Cristian Montes (cristian.montes@invemar.org.co / Instituto de Investigaciones Marinas y Costeras José Benito Vives de Andreis, INVEMAR, Colombia)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2534,20 +2720,54 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This geodatabase contains geospatial information collected and processed under the LACUNA project, aimed at quantifying above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian mangroves, specifically in the VIPIS area (Vía Parque Isla de Salamanca). The data are organized into two main datasets: Ground_truth and Satellite AGB/AGC.
+Ground_truth Dataset – Field and reference data:
+•  MangroveTrees (point layer): Structural details of individual trees, including DBH, height, species, AGB, and AGC, for trees in 20 sampled plots.
+•  MangrovePlot (point layer): Centroids of the 20 plots, with aggregated AGB and AGC per plot.
+•  TreesCanopy (polygon layer): Tree canopy projections with attributes linked to MangroveTrees.
+•  MangrovePlots (polygon layer): Plot boundaries (10 × 10 m) with estimated AGB and AGC values.
+Satellite AGB/AGC Dataset – Remote-sensing derived data:
+•  Provides 10 m resolution maps of AGB and AGC for 2025, generated using Sentinel-1 and Sentinel-2 data combined with in-situ measurements and a Random Forest machine learning model.
+</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The geodatabase provides detailed plot-level and tree-level field data from Colombian Caribbean mangroves, including measurements such as DBH, height, species, above-ground biomass (AGB), and above-ground carbon (AGC). Users can directly integrate the Ground_truth dataset with other similar field datasets to train and validate machine learning models for accurate estimation of mangrove biomass and carbon stocks.
+The satellite dataset supports spatially explicit analysis of forest structure, carbon dynamics, and environmental factors influencing mangrove ecosystems. Combined with additional datasets, it can help improve model robustness, enable cross-site comparisons, and enhance predictive accuracy.
+Beyond modeling, the dataset facilitates carbon stock quantification, conservation planning, forest management, and climate policy development. </t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  CTTC &amp; INVEMAR
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>María Cuevas</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
@@ -2574,41 +2794,97 @@
           <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Forecasting availaibiltiy of tropical forest resources (leaves, flowers, fruits and seeds) for local communities, forest resource managers, conservationists and restoration managers.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>The health of tropical forest ecosystems faces pressures from climate change, threatening the sustainable supply of leaves, flowers and fruits which provide important resources for wildlife, domestic animals and human settlements. Monitoring the timing of plant life cycle events (phenology) is one effective way to track the availability of plant resources and the impact of climate change and weather variability on their sustainable supply. This dataset is on 48 weeks of liana and tree phenology from ground observations, traditonal ecological knowedge and camera traps in the canopy in two tropical forest ecosystems (a moist semi-deciduous and a dry semi-deciduous forest). The dataset also includes land surface phenology from satellite images and in situ weather data. Phenology data from multiple sources and climate data could be combined via a machine learning model that can be used to predict phenology at community and landscape scales. This data will enhance the representation of tropical African forests in phenology research and contribute meaningful data from tropical African forests for machine learning applications in climate, forests and biodiversity conservation. The images and phenology labels could also be used to train an automation of identifying phenology events in forest canopy images.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://doi.org/10.5281/zenodo.15704554; https://doi.org/10.4121/d97e338b-dc94-4e3d-a473-6dd3d4b48898.v1; https://doi.org/10.4121/9e6b4bca-f3d3-40f3-a8f5-4f71f7790c2f.v1; https://doi.org/10.4121/7e6d7ca3-060d-4ca5-bd83-d779b598c11d.v1 </t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SDG 15 (Life of Land)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tabular, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>"Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana"</t>
+          <t>Bismark Ofosu-Bamfo (bismark.ofosu-bamfo@uenr.edu.gh; bofosubamfo@gmail.com) and Daniel Yawson (daniel.yawson@uenr.edu.gh) Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana/Raul Zurita-Milla (r.zurita-milla@utwente.nl) and Rosa Aguilar (r.aguilar@utwente.nl) Department of Geo-Information Processing, Faculty ITC, University of Twente, The Netherlands. Primary contact/Maintainance of datasets: Bismark Ofosu-Bamfo</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ghana,Netherlands</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Description of clean folder (raw folder also available)
+The folder contains files of clean datasets employed for various datasets. 
+ i. climate_dataset.csv
+ii. daily_climate_gr_data.csv
+iii. ground_phenology_dataset.csv
+iv. pheno_pulse_dataset.csv
+v. rbg_chromatic_coordinates.csv
+vi. tek_phenology_dataset.csv
+vii. Satellite images derived phenology (provided at https://data.4tu.nl)
+License
+Creative Commons Attribution 4.0 International</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  University of Energy and Natural Resources and University of Twente
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bismark Ofosu-Bamfo</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Climate and Forests</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>GhanaPhenoPulse — Zooniverse</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
-— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources</t>
+          <t xml:space="preserve">Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
+— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
+Ghana News Agency: https://gna.org.gh/2025/07/realistic-phenology-data-key-to-predicting-crop-cycles-dr-ofosu-bamfo-2/
+Joy News (video): https://g.co/kgs/5byh6f7 </t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2616,8 +2892,787 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> This is a global digital public good under open-source licenses as named under CC-BY 4.0 license.</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ui_26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Corpus sobre cultura Qom</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>This project creates two open-access speech corpora for the Qom language, an indigenous language of the Gran Chaco region, to combat its digital marginalization. It was created to provide the foundational data needed to build language technologies like machine translators and voice assistants, which are crucial for its preservation and modern use. The dataset includes a high-quality, professionally recorded corpus and a larger, community-collected corpus capturing diverse dialects, genders, and ages. Linguistically annotated and openly available, this resource directly empowers the Qom community by involving them in its creation and enables developers and researchers to build educational and cultural applications. This initiative supports the linguistic sovereignty of indigenous peoples and aligns with the goals of the International Decade of Indigenous Languages.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Instituto de Lingüística, Facultad de Filosofia y Letras, Universidad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A known limitation is the potential demographic imbalance between the two corpora. The High-Quality Corpus is small (5 hours) and aims for gender parity, but the larger Community Corpus (10+ hours) has a primary focus on geographic and age distribution, with gender balance being a secondary concern. This could introduce a bias where the "high-quality" benchmark is not fully representative of the entire community's speech. Steps for ethical use include a participatory methodology where the community defines culturally relevant topics for recordings, obtaining informed consent that details data usage, and anonymizing speaker identities in the published data. The plan to measure inter-annotator agreement ensures the linguistic annotations are reliable and valid.
+Maintenance &amp; Point of Contact: Maintenance responsibility lies with the leading researchers from the University of Buenos Aires (UBA) and CONICET. The project is designed to build capacity within the Qom community, suggesting a long-term goal of empowering local members to contribute to and maintain the resource.
+Data License &amp; Rights: The data is intended for open access, though a specific license is not named in the text. The explicit goal of promoting use and diffusion via open access suggests a permissive license like Creative Commons (e.g., CC BY or CC BY-SA). Users would likely have the right to reuse and build upon the data for research, education, and application development, with the restriction that attribution must be given to the creators and the Qom community, aligning with the project's ethos of empowering and recognizing the community.M</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>With this corpus, researchers and developers can immediately build foundational language technologies for Qom. Specific use cases include training automated speech recognition (ASR) systems to transcribe Qom speech, developing text-to-speech synthesizers for educational content, and creating basic machine translation tools between Qom and Spanish. The community-collected corpus is particularly valuable for building applications that understand diverse dialects and real-world speech patterns. Developers can extend this work by using the data to train more sophisticated natural language processing (NLP) models for sentiment analysis, grammar checking, or conversational AI assistants tailored to the community's needs. A critical limitation to consider is the demographic imbalance between the two corpora; the high-quality corpus is small and aims for gender balance, while the larger community corpus prioritizes age and geography, which could introduce bias. Replicators must engage in an ethical AI assessment, ensuring any application involves the Qom community in a participatory manner to avoid exploitation and ensure cultural appropriateness. Building a basic application would have low compute costs (est. $100-500 for training on cloud GPUs) if using the existing data for fine-tuning, but significant investment is required for ethical community engagement and continuous improvement.
+Sustainability and Future Plans: Long-term maintenance relies on the lead researchers at UBA/CONICET and the empowerment of trained Qom community members. The plan for sustainability includes using the corpus to build useful community tools that encourage ongoing use and contribution. Readers can partner with the research institutions for linguistic expertise and with the Qom communities directly for data expansion and validation, ensuring the resource evolves with the language.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ui_27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Crafting a Bilingual Dataset for Biomedical Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>This project addresses a critical gap in healthcare technology by creating a high-quality, bilingual English-Luganda dataset for medical applications. It was developed because the lack of such data prevents the creation of effective digital health tools for millions of Luganda speakers in Uganda, hindering access to accurate medical information. The dataset is built through interviews with healthcare workers, collection of naturalistic clinic speech, translation of medical guidelines, and aggregation of existing resources. Openly available, this dataset can be used by NGOs, health agencies, and local developers to build life-saving applications like diagnostic assistants, automated translation of health materials, and voice-based medical record systems, directly contributing to improved health outcomes and equitable access to care.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SDG 3 (Good Health and Well-being); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The Infectious Diseases Institute Limited</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A key limitation is the reliance on professional translators and healthcare workers for data creation, which may not fully capture the language used by patients from diverse educational backgrounds, potentially introducing a bias towards more formal or clinical Luganda. The use of existing materials like clinical guidelines also risks propagating any biases present in those original documents. Ethical steps are robust: all data from health sessions is collected with consent, translations are reviewed by both professional linguists and healthcare professionals for medical accuracy, and the focus on community involvement through interviews aims to ground the dataset in authentic, culturally appropriate communication.
+Maintenance &amp; Point of Contact: The maintenance responsibility likely falls to the project team and their host institutions. The mention of approaching the Infectious Diseases Institute (IDI) IRB indicates an ongoing relationship with a major local health institution, which could be a key partner for long-term updates and curation.
+Data License &amp; Rights: The text does not specify a license, but the nature of the project (aiming to improve public health) strongly implies an intention for open access. A license like CC BY or CC BY-NC would be appropriate, allowing researchers and developers to use and build upon the data for non-commercial health applications, requiring attribution to the creators. Restrictions would include the ethical imperative to use the data responsibly in medical contexts and to give back to the Luganda-speaking communities by improving health outcomes.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>This dataset enables the immediate development of critical healthcare NLP applications for Luganda speakers. Developers can build automated translation tools for patient information leaflets, symptom checkers, and public health advisories, or create voice-based interfaces for mobile health apps that allow users to interact in Luganda. Researchers can use it to train and benchmark models for cross-lingual information retrieval, allowing healthcare workers to access English-language medical databases using Luganda queries. This work can be extended by expanding the dataset to include more specialized medical domains (e.g., mental health, nutrition) or by developing speech-based datasets for voice-enabled clinic tools. A key limitation is the potential bias towards formal, clinical language from professionals, which may not reflect patient vocabulary. Any replication must undergo a rigorous ethical assessment focused on medical accuracy and patient safety; outputs must be reviewed by healthcare professionals. The cost to build a application is moderate (est. $1k-5k for compute) due to the complexity of medical language, but the primary cost is in ongoing expert validation to ensure safety.
+Sustainability and Future Plans: Sustainability is tied to partnerships with health institutions like the Infectious Diseases Institute (IDI). The dataset can be kept up-to-date by continuously incorporating new translated guidelines and anonymized, consented health communication data. Readers from the global health and AI communities can collaborate by contributing new parallel health texts or helping to fine-tune models for specific medical tasks.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ui_28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Project Empowering Indigenous Communities:  AI-Driven Data Corpus for the Revitalization of Indigenous Languages Spoken in Chile"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>This initiative builds multimodal text and speech corpora for the Rapa Nui and Mapudungun languages (including its Pehuenche, Guluche, Lafkenche, and Huilliche variants) to reverse their exclusion from the digital world. Created in direct response to community needs, it expands on a previous machine translation prototype to include diverse dialects and crucial speech data for the many speakers who are not literate in their native tongue. The open-source corpora will allow local and international developers to create more robust and inclusive language technologies, such as accurate speech-to-text systems. This empowers indigenous communities in Chile to use their languages in daily digital life, safeguarding ancestral knowledge and fostering cultural preservation through technology.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pontifical Catholic University of Chile</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A significant acknowledged limitation is the inability to guarantee equal gender and age distribution in the Open Dialogue Speech corpus due to access challenges, which could create imbalances. The Annotated Speech corpus, being read from pre-selected texts, lacks the spontaneity of natural conversation. Ethically, this project is exemplary. It directly responds to community-identified needs, includes an intercultural validation process with published reports, and conducts specific research into community perspectives on Generative AI to guide future ethical development. This ensures the project is community-driven and culturally respectful.
+Maintenance &amp; Point of Contact: The project team, which has pioneered previous work with these communities, is responsible. The deep partnership with Indigenous institutions and the focus on capacity-building suggest a shared, long-term responsibility for maintaining and updating the datasets.
+Data License &amp; Rights: Data will be published alongside detailed documentation and reports. The use of standard formats (MP3, JSONL) ensures interoperability. A permissive license is expected to foster reuse. The commitment to open dialogue and community guidance implies that while the data is for replication and innovation, any future commercial or sensitive use would require further community consultation and benefit-sharing, potentially formalized through a license like CC BY-SA or a community-specific protocol.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>This multi-modal corpus allows for the immediate creation of robust machine translation systems between Spanish and Rapa Nui/Mapudungun variants, directly addressing a community-identified need. Developers can build web browser plugins or mobile apps for real-time translation of text. The speech data enables the development of speech-to-text tools for transcribing elder storytelling and creating subtitled media, as well as text-to-speech systems for hearing written content. Researchers can extend this work by using the collected prompt-response pairs and community feedback reports as a foundation for developing culturally-aligned generative AI models in the future. The critical limitation is the acknowledged imbalance in the open dialogue speech corpus regarding gender and age distribution. Future work must strictly follow the project's ethical framework, using their published reports on community perspectives to guide development and always partnering with indigenous institutions for intercultural validation. Building a translation app would have moderate compute costs (est. $2k-10k), but the non-negotiable cost is the time and resource investment required for deep, respectful community collaboration.
+Sustainability and Future Plans: The long-term plan is for the partnered Indigenous institutions to become stewards of the data and resulting technologies. The project's methodology of community engagement is a replicable model for sustainability. Readers can engage by adopting this participatory methodology in their own work, by contributing to the expansion of the text corpus with new themes, or by helping to transcribe the open dialogue speech data.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model &gt; Pilot</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ui_29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Development of a modern Paraguayan Guarani dataset for core NLP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>This project develops a large, modern corpus of Paraguayan Guarani to overcome its status as a low-resource language despite having millions of speakers. It addresses the lack of data for building essential Natural Language Processing (NLP) tools. The key innovation is its focus on two distinct varieties: half the corpus is in "pure" Guarani and the other half in "Jopara," the common code-switched mix of Guarani and Spanish. This openly licensed dataset, annotated to international standards, is a foundational resource for researchers and developers to create part-of-speech taggers, parsers, and educational tools. It will directly enhance platforms like Maitei for learning Guarani, empowering educators and students and ensuring the language thrives in the digital age.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Text, Tabular</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Itapua</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Paraguay, Spain, Uruguay</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A known challenge is categorizing texts on a spectrum from "pure" Guarani to "Jopara," a process that requires nuanced linguistic judgment and could introduce subjectivity. The translation hackathon, while innovative, might produce translations that vary in quality and naturalness. The project plans to mitigate these issues through rigorous annotation guidelines, expert linguist oversight, and measures to identify biases related to gender or ethnicity. The very structure of including both varieties is an ethical step to avoid privileging one form of the language over another.
+Maintenance &amp; Point of Contact: The project team is responsible for the initial release. The plan to release the dataset on the Universal Dependencies repository and Hugging Face places it within ecosystems that have built-in mechanisms for community maintenance, versioning, and updates by the global NLP community.
+Data License &amp; Rights: The data will be published under an explicit Creative Commons Attribution 4.0 (CC BY 4.0) license. This is a clear, permissive license that allows anyone to reuse, share, and adapt the data for any purpose, even commercially, as long as they give appropriate credit to the creators. This maximizes the potential for innovation while ensuring recognition.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>This meticulously annotated corpus is a ready-to-use resource for training core NLP tools. Developers can immediately train part-of-speech taggers, dependency parsers, and named entity recognizers for both "academic" Guarani and "Jopara." These tools can be integrated into platforms like Maitei and CINACINA to create intelligent grammar exercises, reading comprehension helpers, and writing assistants. Researchers can extend this work by using the UD-formatted data to include Guarani in massive multilingual NLP models, ensuring the language is represented in future technologies. A key challenge for replication is the subjective spectrum between pure Guarani and Jopara, which requires nuanced linguistic expertise to handle correctly. Future projects must account for this dialect continuum and avoid biasing systems towards one variety. The cost to build upon this work is relatively low (est. $500-2k for compute) as the expensive data creation and annotation is complete; costs are primarily for model training and application development.
+Sustainability and Future Plans: The release of the dataset into the Universal Dependencies repository embeds it within a global ecosystem with built-in version control and community maintenance. The long-term plan is for the NLP community to maintain and extend the resource. Readers can contribute by submitting improvements to the UD annotations, using the data to build new applications that demonstrate value, or organizing new hackathons to expand the corpus.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ui_30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AfriFact &amp; AfriGuard: Dataset for Fact-Checking, Robust Refusal</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>This project creates datasets for fact-checking and harmful prompt refusal in 10 major African languages (Afrikaans, Amharic, Ewe, Hausa, Igbo, Oromo, Shona, Swahili, Yoruba, Zulu). It was created to ensure the safety and reliability of large language models (LLMs) for African users, preventing the spread of misinformation and malicious use. The datasets are manually curated by experts, translating and adapting existing English benchmarks to include locally relevant knowledge from African sources. Openly available, these resources empower local fact-checking organizations, AI developers, and social media platforms to build and audit AI systems that refuse harmful requests and provide accurate, verified information in local languages, fostering a safer digital ecosystem.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Masakhane Institute</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Benin, Chad, Democratic Republic of the Congo, Ethiopia, Gambia, Kenya, Lesotho, Mauritania, Mozambique, Niger, Nigeria, Senegal, South Africa, eSwatini, Togo, Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A major limitation is the project's foundation on translating existing English prompts from datasets like MALICIOUSINSTRUCT. This carries the risk of importing cultural contexts and harmful concepts that are not relevant or are differently perceived in African societies, creating a cultural bias. Steps to ensure ethical use include careful curation and filtering of English prompts to select those most relevant to the African context, extensive training for translators, and a multi-layered quality assurance process (AfriCOMET, back-translation, coordinator review) to ensure accuracy and cultural appropriateness.
+Maintenance &amp; Point of Contact: Maintenance is a community effort coordinated through Masakhane members for each language. This distributed model leverages local expertise but requires strong coordination to ensure consistent updates and quality control across all ten languages.
+Data License &amp; Rights: The datasets are derived from existing resources, so their licenses will need to be compatible. The project will likely adopt a permissive license similar to its sources (e.g., MIT, Apache 2.0, or CC BY) to encourage reuse in AI safety research. Users can replicate the methods and use the data to build safer AI systems, with the restriction that they must acknowledge the source and the contribution of the African NLP community.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>This dataset allows for the immediate development of crucial AI safety features for the 10 African languages. Developers can build content moderation filters for social media platforms, "refusal" mechanisms for chatbots to reject harmful requests in local languages, and fact-checking browser extensions that flag misinformation. Researchers can use the dataset to benchmark the safety and truthfulness of existing LLMs for these languages, holding model developers accountable. This work can be extended by adding more languages, generating more nuanced and culturally-specific harmful prompts, and developing automated evaluation metrics tailored to African linguistic structures. The critical limitation is the risk of cultural bias, as the project translates English prompts, potentially importing concepts irrelevant to African contexts. Replication must include the project's rigorous multi-step validation process (AfriCOMET, back-translation, native speaker review) to ensure cultural relevance and accuracy. The cost to implement a safety layer is low to moderate (est. $1k-5k) as it often involves fine-tuning or designing prompts for an existing model rather than training from scratch.
+Sustainability and Future Plans: Sustainability is managed through the Masakhane network's distributed model, where language leads maintain their respective components. The project aligns with global AI safety initiatives. Readers can contribute by becoming language coordinators within Masakhane, helping to translate more prompts, or developing better automated evaluation tools for their language.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ui_31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Empowering Ethnic Voices in Tanzania</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>This project creates a comprehensive speech and text dataset for six endangered Ethnic Community Languages (ECLs) in Tanzania to prevent their extinction and promote digital inclusion. It addresses the dominance of Swahili and English which excludes these communities from technological advancements. The dataset comprises over 450 hours of transcribed and translated audio from interviews and storytelling, capturing rich cultural narratives. This open resource enables the development of automatic speech recognition (ASR) systems, bilingual educational tools, and accessible healthcare communication apps. NGOs, government agencies, and local tech developers can use this to build services that empower marginalized communities, preserve cultural heritage, and ensure everyone can access information in their first language.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sokoine University of Agriculture</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>United Republic of Tanzania</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A potential limitation is the sourcing of written text from religious and academic centers (e.g., Bible translations, theses), which may over-represent certain genres, dialects, or ideological viewpoints, creating a lexical and thematic bias. Ethical steps are comprehensive: data collection is based on informed consent, speaker demographics are recorded to ensure diversity, rigorous quality assurance involves native speakers, and the data will be uploaded to Mozilla Common Voice for community-driven validation and expansion, ensuring ongoing community oversight.
+Maintenance &amp; Point of Contact: The project team is initially responsible. The strategy of uploading to Mozilla Common Voice is a masterstroke for maintenance, as it explicitly transfers long-term curation, validation, and expansion to the global and local community, ensuring the dataset remains a living resource.
+Data License &amp; Rights: The data will be hosted on Zenodo with a DOI under a CC BY 4.0 license. This is a gold standard for open scientific data, allowing full reuse and replication for any purpose with attribution. The explicit goal is to enhance reusability for NLP research and applications, empowering a wide range of users from developers to government agencies.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>This large-scale speech and text corpus enables the immediate development of automatic speech recognition (ASR) systems for the six ECLs. This can power voice-activated applications for education (e.g., literacy tools), information access (e.g., voice search), and cultural preservation (e.g., transcribing oral histories). The bilingual text supports the development of translated educational materials. Researchers can extend this work by using the data to build speech synthesis systems that give a voice to digital assistants in these languages. A major limitation is the sourcing of written text from religious/academic centers, which may bias the data towards a specific register. Future users must supplement this data with more contemporary, colloquial text sources. The cost to build a functional ASR model is high (est. $10k-50k+ for compute) due to the volume of audio data required for training, but leveraging pre-trained models can reduce this cost.
+Sustainability and Future Plans: The most robust sustainability plan is the intention to upload data to Mozilla Common Voice, a platform designed for community-driven, continuous data collection and validation. This ensures long-term maintenance by the speakers themselves. Readers can contribute instantly by validating existing clips on Common Voice or recording new sentences in the target languages, directly helping to improve the dataset.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ui_32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MOZNLP-UP: Scaling Up Mozambican Language Coverage towards NLP inclusion</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>This project expands NLP resources for four key Mozambican languages—Emakhuwa, Xichangana, Nyanja, and Sena—spoken by nearly 25 million people. It was created to provide essential language technology tools for critical domains like news broadcasting and bilingual education, where local language variants are crucial. The project produces a multi-way translation dataset and open translation models, focusing specifically on capturing unique Mozambican dialects and loanword adaptations. The resulting open-language technology platform, featuring dictionary lookup and computer-assisted translation (CAT) tools, can be used by journalists, teachers, and government agencies to create content and services. This fosters digital inclusion and empowers communities by breaking down language barriers in access to information.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 9 (Industry, Innovation and Infrastructure); SDG 4 (Quality Education) </t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SCHOOL OF COMMUNICATION AND ARTS (ECA) - University Eduardo Mondlane</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A key focus is on capturing unique Mozambican variants, but a limitation is the risk of these nuances being flattened by using general-purpose pre-trained models (like mT5 or NLLB) for fine-tuning. The project addresses this by developing loanword annotations and creating in-domain evaluation sets to better measure model performance on local usage. Ethical steps include collaboration with linguistic professionals and using workshops to develop localized translation guidelines, ensuring the data reflects authentic language use.
+Maintenance &amp; Point of Contact: The project team will maintain the models and benchmarks on Hugging Face. The rollout of the MUZALING platform (with CAT tools and a dictionary) suggests the team or a partnered Mozambican institution will be responsible for maintaining this applied tool for end-users.
+Data License &amp; Rights: The models and benchmarks will be made available on Hugging Face, which typically uses open licenses like MIT or Apache 2.0 for models and CC BY for data. This allows full public use for replication and innovation. The tools are intended for public use to facilitate language access, meaning developers, businesses, and government agencies can integrate them into their services to promote digital inclusion.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>This project provides the resources to immediately deploy practical machine translation (MT) tools. Developers can integrate the trained models into the MUZALING platform to offer computer-assisted translation (CAT) tools for journalists, dictionary lookup for students, and real-time translation features for news websites or government portals. Researchers can extend the work by using the loanword annotations to study language evolution or by adapting the models for other domains like legal or educational text. A limitation is the risk that the models might not perfectly capture local variants, especially for informal text. Replication should use the provided in-domain evaluation sets, not just general ones like FLORES+, to accurately gauge performance on local usage. The cost to run an existing model is low (est. cents per user), but the cost to train new models from scratch or for new languages is high (est. $10k+).
+Sustainability and Future Plans: The project aims for sustainability through the public release of models on Hugging Face and the operationalization of the MUZALING platform. Long-term maintenance will likely fall to a Mozambican institution. Readers can collaborate by using and improving the open-source models, contributing new parallel text data, or helping to localize other software and content using these tools.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model &gt; Pilot</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ui_33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Constructing a Multilingual Parallel Corpus Dataset of Nahuatl and Totonaco</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>This project builds a parallel corpus for Nahuatl and Totonaco variants from Puebla, Mexico, with translations into Spanish and English. It addresses the gap between legal mandates for indigenous language rights and the practical lack of human and technological resources to implement them. The corpus is constructed through fieldwork and community engagement to ensure authenticity and quality. This open dataset is a foundational tool for developers and government agencies to build accurate machine translation systems, automated public service information platforms, and educational materials. It empowers indigenous communities by ensuring their right to access information and services in their native language, fostering greater inclusion and cultural preservation.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Benemérita Universidad Autónoma de Puebla</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Brazil, Ireland, Mexico, United Kingdom</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>This parallel corpus enables the immediate development of Spanish-Nahuatl and Spanish-Totonaco machine translation systems. These can be used to translate public service information, legal documents, and educational materials, directly supporting the implementation of linguistic rights laws in Mexico. Developers can build simple web and mobile apps for phrase translation to aid communication in healthcare or municipal settings. The work can be extended by focusing on speech data collection to create speech-to-speech translation tools, which are often more needed for oral languages. A significant challenge is the complexity of the languages and the variations between communities, which requires careful dialectal management. Any replication must be done in close partnership with anthropologists and linguists who understand the socio-linguistic context. The cost is primarily in development and community engagement (est. $5k-15k+), as the data structure itself is not overly complex for modern MT systems.
+Sustainability and Future Plans: The interdisciplinary team, including anthropologists and community specialists, is key to sustainability. Their deep ties to the communities in Puebla ensure that the project is grounded in real needs. Readers can engage by collaborating with this team to expand the corpus to other variants or by developing specific applications for the state government to use in serving its citizens.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ui_34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>African Tone Project</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>This project creates a time-aligned, annotated audio-visual dataset specifically focused on the tonal features of African languages. It addresses a critical gap in NLP, as tone—a fundamental linguistic feature—is often omitted from datasets, severely hampering the development of accurate speech and language technologies for these languages. The dataset includes both elicited words and natural conversations across different language varieties. Openly available, this resource is invaluable for linguists, speech technology researchers, and language revitalization teams. It enables the development of tone-aware speech recognition and synthesis systems, which are essential for creating truly effective and natural digital tools for the hundreds of millions of speakers of tonal languages in Africa.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Voice, Images</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>African Languages Technologies Initiative</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Canada, Ghana, Nigeria</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Critical Limitations &amp; Ethical Use: A significant challenge is the technical complexity of consistently annotating tone across multiple languages and speakers, which requires highly skilled annotators and can lead to inconsistency. The focus on lab-quality recording with headset microphones, while excellent for clarity, may not fully capture the acoustic properties of speech in naturalistic environments. Ethically, the project is strong: it involves native-speaker linguists in transcription assessment, strives for demographic diversity in speakers, and collaborates with communities to create tone-marking conventions where they don't exist, empowering them linguistically.
+Maintenance &amp; Point of Contact: The Principal Investigators (PIs) and language leads, who are native-speaker linguists, are responsible for the core data assessment and correction. The project is positioned as a resource for the broader research and community communities, suggesting long-term maintenance by the host academic institutions.
+Data License &amp; Rights: The use of archival-standard formats (.wav, .mov) and detailed annotations makes it a high-value resource. While a license is not specified, its creation for the broader research community suggests an open license (likely CC BY) would be used. This would allow linguists and NLP researchers to use it for replication and groundbreaking work on tonal languages. The rights would include use for analysis and model training, with the restriction that users must acknowledge the source and the contributing communities.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>This dataset is a foundational resource for groundbreaking research and development on tonal languages. Immediately, linguists can use it for phonetic and phonological analysis of tone. NLP researchers can use it to train and benchmark tone-aware speech recognition and synthesis models, which are essential for building effective voice AI for these languages. Developers can extend this work by exploring how tone information improves the performance of everything from keyword spotting to speaker identification systems. The primary limitation is the extreme technical complexity of consistently annotating tone across speakers and contexts. Replicating this work requires specialized linguistic expertise in phonetics and the specific languages. The cost to collect and annotate a similar dataset for a new language is very high (est. $50k-100k+) due to the need for expert linguists, high-quality equipment, and extensive manual labor.
+Sustainability and Future Plans: The project is sustained by its academic value to the fields of linguistics and NLP. The PIs and language leads are responsible for maintenance. The high-quality, archival-standard data ensures its long-term usability. Readers can contribute by using the data for their research, publishing findings that highlight its value, and advocating for more resources to be dedicated to the study of tonal phenomena in AI.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3646,25 +3646,97 @@
       <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ui_35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Eyes on the Ground Image Data</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Smallholder Farmer Field Monitoring with Machine Learning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>This machine learning dataset of smallholder farmer's fields includes georeferenced crop images along with labels on input use, crop management, phenology, crop damage, and yields, collected across 8 counties in Kenya. This dataset enables the development of AI systems to monitor crop conditions, predict yields, and support agricultural decision-making for smallholder farmers.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://radiantearth.github.io/stac-browser/#/external/raw.githubusercontent.com/khufkens/EotG_data/main/release_v1/EotG_images/catalog.json</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Images, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Georeferenced crop images with labels on input use, crop management, phenology, crop damage, and yields from 8 counties in Kenya. Machine learning ready dataset for smallholder agriculture monitoring.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Enables crop monitoring, yield prediction, and agricultural decision support systems for smallholder farmers.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop AI applications for crop monitoring, yield estimation, damage assessment, and agricultural advisory services. It supports the development of precision agriculture tools specifically designed for smallholder farming systems.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Authors: Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Computer Vision, Remote Sensing</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
@@ -3673,6 +3745,826 @@
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ui_36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Corrected Geolocations for Eastern Africa Crop Cut Yield Estimation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>This dataset includes corrected geolocations of fields, improving the usability of the most expansive Eastern Africa crop cut yield estimation. Collected by the non-profit One Acre Fund from 2015 – 2019, this dataset covers major crop producing regions in Kenya, Rwanda, and Tanzania. It enables accurate yield mapping and agricultural monitoring across East Africa.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/140eLeY3Z_JALFa0B77ZTP9gFt-mSPWXl</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tabular, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>One Acre Fund</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Kenya, Rwanda, Tanzania</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Corrected geolocations of maize fields with yield data from 2015-2019 covering major crop producing regions in Kenya, Rwanda, and Tanzania. Most expansive Eastern Africa crop cut yield estimation dataset.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Enables accurate yield mapping, crop monitoring, and agricultural planning across East Africa using corrected geolocation data.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>This dataset can be used for yield prediction modeling, agricultural policy planning, food security assessments, and developing precision agriculture applications for East African smallholder farmers.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>One Acre Fund</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>One Acre Fund</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Agricultural Informatics, Geospatial Analysis</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ui_37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IoT Water Quality Management for Aquaponics Systems</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>This project built a remotely monitored and controlled Internet of Things (IoT) fish pond water quality management system for the generation of labeled datasets both for conventional ponds and the aquaponic pond systems. It enables monitoring and optimization of water quality parameters for sustainable aquaculture.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/ogbuokiriblessing/sensor-based-aquaponics-fish-pond-datasets</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tabular, IoT Sensor Data</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>IoT sensor data from fish pond water quality monitoring systems including conventional ponds and aquaponic systems. Labeled datasets for water quality parameters monitoring.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Enables automated water quality monitoring, predictive maintenance for aquaculture systems, and optimization of aquaponics operations.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop IoT-based monitoring systems for aquaculture, predictive models for water quality management, and automated control systems for sustainable fish farming operations.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Authors: Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>IoT, Aquaculture Technology</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ui_38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AI-Powered Crop Disease Detection for Food Security Crops</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>This dataset contains a repository of image and spectrometry datasets for five main food security crops in Sub-Saharan Africa: cassava, maize, beans, bananas, and cocoa. Collected and curated in collaboration with the in-country agricultural experts, the datasets deliver a wide range of machine learning applications, including classification, object detection, early crop disease detection, and spatial analysis. The team collected and annotated 127,046 images and 39,300 spectral data points.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/dataverse/airlabug/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Images, Spectrometry Data</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Uganda, Tanzania, Ghana</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>127,046 images and 39,300 spectral data points for cassava, maize, beans, bananas, and cocoa. Annotated datasets for classification, object detection, early crop disease detection, and spatial analysis.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Enables crop disease classification, early detection systems, pest identification, and spatial analysis for food security crops in Sub-Saharan Africa.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop mobile applications for crop disease diagnosis, early warning systems for pest outbreaks, and precision agriculture tools for smallholder farmers growing food security crops.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Authors: Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Computer Vision, Agricultural Technology</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ui_39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pastoral Community Land Use and Livestock Movement Patterns</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>This dataset focuses on locations with predominantly pastoral communities in northern Tanzania to identify fine and broad-scale movements of livestock and land use patterns and to understand how these relate to communal conflicts. It is a high-quality, accurate and labeled dataset containing detailed information on ~ 2000 communal resources (e.g., rangelands, water points, and dips) and their use patterns for over 220 villages across four large districts in northern Tanzania, representative of pastoral systems of livestock production in East Africa.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>http://dtlp.nottech.co.tz/index.html</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing, Tabular</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Gladness Mwanga (gladnessg@nm-aist.ac.tz), Divine Ekwem (divine.ekwem@glasgow.ac.uk)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Detailed information on ~2000 communal resources and use patterns for over 220 villages across four districts in northern Tanzania. Covers rangelands, water points, dips and livestock movement patterns.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Enables land use planning, conflict prediction, livestock migration route identification, and infrastructure placement for pastoral communities.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop tools for community land use planning, conflict early warning systems, infrastructure development planning for pastoral areas, and sustainable rangeland management systems.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Authors: Dr. Divine Ekwem (University of Glasgow), Gladness Mwanga (Nelson Mandela African Institution of Science and Technology), Professor Gabriel Shirima (Nelson Mandela African Institution of Science and Technology), Professor Mizech Chagunda (University of Hohenheim)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dr. Divine Ekwem, Gladness Mwanga, Professor Gabriel Shirima, Professor Mizech Chagunda</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Geospatial Analysis, Land Use Planning</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ui_40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yield Prediction and Crop Insurance for Smallholder Farmers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The project created labeled yield estimates from 3000 farmers, and was used to train prediction models for yield prediction across the country, consequently using the dataset to generate high resolution crop mask layers for the different value chains. The yield prediction models were enhanced by other biophysical datasets ranging from soil properties and climate related indicators. The datasets proved a concept of scalable machine learning models training, which may be able to respond more appropriately and cost-effectively to agricultural stressors.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/10060610</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Tabular, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Seth Odhiambo (sodhiambo@pula.io)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Labeled yield estimates from 3000 farmers with biophysical datasets including soil properties and climate indicators. High resolution crop mask layers for different value chains.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Enables yield prediction models, crop insurance products, and agricultural risk assessment for smallholder farmers accessing financial services.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop crop insurance products, yield prediction systems, agricultural lending platforms, and risk assessment tools for financial institutions serving smallholder farmers.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Pula Advisors</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Seth Odhiambo, Pula Advisors</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Agricultural Technology, Financial Technology</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ui_41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Continental Crop Field Boundary Detection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>This dataset provides continent-wide crop field labels for Africa, improving the availability and use of crop field boundary (parcel) maps. It contains 42,403 annotated geospatial polygons indicating the boundaries of individual crop fields spanning the years 2017-2023. This enables the development of automated field boundary detection systems for agricultural monitoring across Africa.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/11060871</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://github.com/agroimpacts/lacunalabels</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mary Dziedzorm Afenyo (mary@farmerline.co), Lyndon Estes (lestes@clarku.edu), Primož Kovačič (primoz@spatialcollective.com)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Multi-country Africa</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>42,403 annotated geospatial polygons of crop field boundaries spanning 2017-2023 across Africa. Continent-wide dataset for field boundary detection.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Enables automated crop field boundary detection, agricultural area estimation, and crop monitoring systems across Africa.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop automated field boundary detection systems, agricultural statistics generation, crop area estimation tools, and satellite-based monitoring systems for African agriculture.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Farmerline, Clark University, Spatial Collective</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Wussah, A., Afenyo, M., Osei, A.K., Gathigi, M., Kovačič, P., Muhando, J., Addai, F., Akakpo, E.S., Allotey, M., Amkoya, P., Amponsem, E., Dadon, K.D., Gyan, V., Harrison X.G., Heltzel, E., Juma, C., Mdawida, R., Miroyo, A., Mucha, J., Mugami, J., Mwawaza, F., Nyarko, D., Oduor, P., Ohemeng, K., Segbefia, S.I.D., Tumbula, T., Wambua, F., Yeboah, F., Estes, L.D.</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Computer Vision, Remote Sensing</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>GitHub: https://github.com/agroimpacts/lacunalabels, AWS Open Data Registry: https://registry.opendata.aws/africa-field-boundary-labels/</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ui_42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Crop Type Classification for Agricultural Decision Making</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CropHarvest increases the understanding of the main types of food production in Sub-Saharan Africa and can help inform decision-making around agricultural development, early warning systems, and regional trade. It is a global, open-source remote sensing dataset for crop-type classification in Sub-Saharan Africa – specifically in Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, and Nigeria. The team expanded on an existing dataset to include new labeled data points, ground data for crop type mapping, street-level images, crowdsourced labeled images, and price data.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://github.com/nasaharvest/cropharvest</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing, Images</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Catherine Nakalembe (cnakalem@umd.edu)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, Nigeria</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Remote sensing dataset for crop-type classification across 12 Sub-Saharan African countries. Includes labeled data points, ground data, street-level images, and price data.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Enables crop type classification, agricultural development planning, early warning systems, and regional trade analysis for Sub-Saharan Africa.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop crop monitoring systems, early warning systems for food security, agricultural trade analysis tools, and policy support systems for agricultural development.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NASA Harvest, University of Maryland</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tseng, G., Zvonkov, I., Nakalembe, C.L., Kerner, H.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Remote Sensing, Agricultural Informatics</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/record/7257688#.ZFATwuzMI0Q</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ui_43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Drone-Based Crop Yield Estimation for Tree Crops</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa. It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Images, Drone Imagery</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Darlington Akogo (darlington@gudra-studio.com)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ghana, Uganda</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees. Supports yield estimation, crop type detection, fruit detection and counting, and maturity stage detection.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Enables automated yield estimation, harvest planning, fruit quality assessment, and business decision support for tree crop farmers.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>This dataset can be used to develop mobile applications for yield estimation, harvest timing optimization tools, fruit quality assessment systems, and agricultural business planning platforms for tree crop farmers.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>KaraAgro AI, Makerere AI Lab</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Darlington Akogo, Cyril Akafia, Harriet Fiagbor, Stephen Torkpo, Christian Kusi, Joyce Nakatumba-Nabende</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Computer Vision, Drone Technology</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>agriculture-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4566,6 +4566,612 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ui_44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Rabies diagnosis, outbreak prediction, resource allocation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>This dataset will help in the real-time and remote diagnosis of rabies disease for humans and animals in low-resource settings. A time series approach can be applied to the outbreak dataset to predict the number of rabies cases likely to occur within an area after a given time interval. This approach can help with resource mobilization, too, such as identifying the number of vaccines required in a specific area at a given time. The number of observations from the two datasets is 12,684. There are three datasets for rabies diagnosis for animals and humans, with 7,081 and 4,585 observations, respectively. In the outbreak prediction dataset, 1,018 observations were accounted for.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/10068758</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Machine Learning Dataset</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Asa Emmanuel: asakalonga@gmail.com, Kennedy Lushasi: klushasi@ihi.or.tz</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>12,684 observations</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Three datasets: animal diagnosis (7,081 observations), human diagnosis (4,585 observations), outbreak prediction (1,018 observations)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Disease diagnosis and prediction</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Asa Emmanuel, Rebecca Chaula, Deogratias Mzurikwao, Joel Changalucha, Kennedy Lushasi</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ui_45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Childhood Malnutrition in Chile</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Child malnutrition analysis, health cost estimation, biopsychosocial determinant identification</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>This data repository will evaluate factors that contribute to child malnutrition in Chile and children's nutritional status, as well as the associated costs. The focus at this stage is on estimating health costs associated with child malnutrition and identifying biopsychosocial determinants that lead to it.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://goblab.uai.cl/proyecto-reduccion-de-la-malnutricion-infantil-en-chile/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Health Policy Dataset</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Maria Paz Hermosilla: paz.hermosilla@uai.cl</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Sensitive data with controlled access for relevant research projects</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Child health and nutrition policy</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Controlled Access</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Ministry of Health, Chile; GobLab, School of Government, Adolfo IbaÃ±ez University, Chile; FONASA; Health Superintendency, JUNAEB</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ministry of Health Chile, GobLab, FONASA, Health Superintendency, JUNAEB</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Statistical Analysis</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Controlled Access</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ui_46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lacuna Malaria Datasets</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Malaria diagnosis, object detection research, medical imaging</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>This dataset will aid in the diagnosis of malaria. The dataset contains annotated images of blood samples collected in Uganda and Ghana with objects of interest, including parasites and white blood cells. It significantly increases the number of available microscopy images â€“ including metadata â€“ by 6,000 thick blood slides and 2,000 thin blood slides for use in object detection research and other areas of inquiry.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/VEADSE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Medical Imaging Dataset</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Rose Nakasi: g.nakasi.rose@gmail.com or rose.nakasi@mak.ac.ug</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Uganda, Ghana</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>8,000 blood slides (6,000 thick + 2,000 thin)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Annotated microscopy images with parasites and white blood cells, thick and thin blood slides</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Malaria diagnosis and medical imaging</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Makerere Artificial Intelligence Lab; minoHealth</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Makerere Artificial Intelligence Lab, minoHealth</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Object Detection</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ui_47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mortality risk prediction, postoperative recovery prediction, anesthesia practice analysis</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>This dataset can be used to identify patterns of intraoperative anesthesia practice and predict postoperative length of stay and risk of mortality based on intraoperative variables. It includes 2,066 intraoperative anesthesia records from two academic centers in sub-Saharan Africa. The team photographed completed intraoperative anesthesia records using a smartphone, de-identified the images, and securely uploaded them to a HIPAA-compliant server. Using a combination of computer vision AI and manual extraction techniques, the team collected comprehensive intraoperative data: demographic data, medication data, hemodynamic data, physiological data, anesthesia type, surgery type, postoperative length of stay, and 30-day postoperative mortality.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://portal.ithriv.org/#/public_commons/project/d9fc062c-64c9-4481-80e7-3db4aba17e00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Clinical Dataset</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Bhiken Naik: bin4n@uvahealth.org</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2,066 intraoperative anesthesia records</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Comprehensive intraoperative data including demographics, medications, hemodynamics, physiology, anesthesia/surgery types, outcomes</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Anesthesia and surgical outcomes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>University of Virginia; School of Medicine and Pharmacy, University of Rwanda and King Faisal Hospital, African Health Sciences University; Safe Surgery South Africa</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bhiken Naik, Paulin Banguti, Hyla Kluyts, Ryan Folks</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Predictive Modeling</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ui_48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Brain tumor segmentation, machine learning model development, neurological disease management</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The BraTS-Africa dataset is an aggregation of magnetic resonance imaging (MRI) scans from six centers in Nigeria aimed at providing a public dataset for the development of machine-learning solutions for the management of brain tumors in African patients. This dataset serves as a starting framework for future expansion in other regions of Africa. The team processed and annotated a total of 584 images from 146 patient scans. Ninety-five of these scans are presumed to have diffuse glioma, and 51 of them have other types of central nervous system (CNS) neoplasms. Expert radiologists annotated three distinct tumor sub-regions to delineate the enhancing tumor (ET), the necrotic tumor core (NCR), and the peritumoral oedematous/infiltrated tissue (ED) sub-regions.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.cancerimagingarchive.net</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Medical Imaging Dataset</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Udunna Anazodo: udunna.anazodo@mcgill.ca</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>584 images from 146 patient scans</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MRI scans with expert annotations for three tumor sub-regions: enhancing tumor (ET), necrotic tumor core (NCR), peritumoral oedematous tissue (ED)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Neuroimaging and brain tumor analysis</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Medical Artificial Intelligence (MAI) Lab (Lagos, Nigeria); The National Hospital (Abuja, Nigeria); Lagos University Teaching Hospital; Lagos State University Teaching Hospital; NSIA-Kano Diagnostic Center; Federal Medical Centre (Umuahia, Nigeria); Lily Hospital (Benin, Nigeria); University of Pennsylvania (Philadelphia, USA); Indiana University (Indianapolis, USA); Scripps Clinic Medical Group (San Diego, USA); McGill University (Montreal, Canada)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Maruf Adewole, Abiodun Fatade, Oluyemisi Toyobo, Farouk Dako, Udunna Anazodo, et al.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Image Segmentation</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ui_49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Parasite detection, diarrhea diagnosis, smartphone microscopy, rural healthcare</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>This dataset helps to detect diarrhea-causing parasites in resource-limited rural areas, particularly across the Global South, where access to expensive diagnostic tools is limited. It contains approximately 400,000 microscopic slide images from water, vegetable, and stool samples from four different provinces across Nepal, making it one of the largest datasets of its kind. The team collected water samples from different sources (i.e., tap water, bottled water, lake, river, pond, stream, spring water, wetland, well, and borewell) and used seven different types of vegetables. Using the dataset and annotations available, this team trained different deep-learning models to automatically detect parasites, specifically Giardia and Cryptosporidium cysts.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/13913469</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Medical Imaging Dataset</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bishesh Khanal: bishesh.khanal@naamii.org.np</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Approximately 400,000 microscopic slide images</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Images from water, vegetable, and stool samples captured using smartphone and brightfield microscopes, focused on Giardia and Cryptosporidium detection</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Parasitology and rural diagnostics</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Nepal Applied Mathematics and Informatics Institute for Research (NAAMII); Kathmandu Institute of Applied Science (KIAS); Nyaya Health Nepal, Bayalpata; Provincial Public Health Laboratory (PPHL)-Janakpur; Kathmandu Institute of Child Health (KIOCH)-Damak</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bishesh Khanal, Udit Chandra Aryal, Safal Thapaliya, et al.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Object Detection</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>CC-BY 4.0 International</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,11 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Info on fair sharing as as Digital Public Good</t>
         </is>
       </c>
     </row>
@@ -649,6 +654,7 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,6 +751,7 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,6 +855,7 @@
 DONE on 25.8., Balthas</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,6 +924,7 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1023,6 +1032,7 @@
           <t>DONE on 25.8., Balthas</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1107,6 +1117,7 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1210,6 +1221,7 @@
           <t>First editing DONE on 25.8., Balthas</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1277,6 +1289,7 @@
           <t>First editing DONE on 28.8., Luisa - There´s no much information available</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1328,6 +1341,7 @@
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1423,6 +1437,7 @@
           <t>First Editing done by Luisa 27.08.2025, Title and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1532,6 +1547,7 @@
           <t>First Editing done by Luisa 28.08.2026 / Availability on Github: it doesn´t have a good exmplanation, which makes it hard to know what is it about.</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1634,6 +1650,7 @@
           <t>First Editing done by Luisa 28.08.2027, titel and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1690,6 +1707,7 @@
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1806,6 +1824,7 @@
           <t>trello board with key messages: https://trello.com/invite/b/669bafb78c890345b83127a3/ATTIcf32f650c44aa08c718541da28f2559e8E474BA5/ltome-katip-comms-plan</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1878,6 +1897,7 @@
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2006,6 +2026,7 @@
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2096,6 +2117,7 @@
           <t>Original title: Remote sensing and weather dataset for improved reforestation monitoring</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2177,6 +2199,7 @@
           <t>original title: DATASETS FOR PREDICTION OF LAND USE/COVER CHANGES IN UGANDA</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2289,6 +2312,7 @@
           <t>First Editing done by Luisa 28.08.2027</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2373,6 +2397,7 @@
           <t>Original title: Datasets to understand mangroves health in relationship to climate change</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2466,6 +2491,7 @@
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2583,6 +2609,7 @@
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2671,6 +2698,7 @@
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2782,6 +2810,7 @@
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2898,6 +2927,7 @@
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2978,6 +3008,7 @@
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3062,6 +3093,7 @@
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3146,6 +3178,7 @@
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3230,6 +3263,7 @@
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3314,6 +3348,7 @@
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3398,6 +3433,7 @@
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3482,6 +3518,7 @@
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3560,6 +3597,7 @@
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3644,6 +3682,7 @@
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3745,6 +3784,7 @@
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3846,6 +3886,7 @@
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3947,6 +3988,7 @@
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4048,6 +4090,7 @@
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4149,6 +4192,7 @@
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4250,6 +4294,7 @@
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4359,6 +4404,7 @@
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4464,6 +4510,7 @@
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4565,6 +4612,7 @@
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4666,6 +4714,7 @@
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4767,6 +4816,7 @@
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4868,6 +4918,7 @@
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4969,6 +5020,7 @@
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5070,6 +5122,7 @@
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5171,6 +5224,447 @@
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ui_50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://thinkingmachines.github.io/project-cchain/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Climate Data</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Thinking Machines Data Science | data-for-development@thinkingmachin.es</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Powered by: Thinking Machines Data Science, Inc., Epimetrics, Inc., Manila Observatory, Philippine Action for Community-led Shelter Initiatives, Inc.
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Patricia Anne Faustino, JC Albert Peralta, Veronica Marie Araneta, Dafrose Camille Bajaro, Abigail Moreno (Thinking Machines Data Science, Inc.), John Q. Wong, Anne Kathlyn Baladad, Luis Antonio Desquitado, Matthew Limlengco, Carlos Miguel Resurreccion (Epimetrics, Inc.), Faye Abigail Cruz, Dr. Julie Mae Dado, Leia Pauline Tonga (Manila Observatory), Ericka Lynne Nava (Philippine Action for Community-led Shelter Initiatives, Inc.)</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Climate Science</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>climate-banner</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Added via climate dataset integration - extracted from climate.html</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ui_51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/collinsudanor/abattoir-air-quality-dataset/data</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Climate Data</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Emmanuel Chukwuma | emmanuel.chukwuma@apse-ngo.org</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Powered by: Alliance for Progressive and Sustainable Environment
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Emmanuel Chukwuma, Uche Okonkwo, Chukwuemeka Umeobi, Jervis Okafor, Sixtus Ezenwankwo, Shadrach Ugwu, Awonge Precious, Cynthia Egdede, Esther Eyo (Alliance for Progressive and Sustainable Environment)</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Climate Science</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>climate-banner</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Added via climate dataset integration - extracted from climate.html</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ui_52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.scidb.cn/en/detail?dataSetId=2b499b91a4464fffa9f60fc8b51da03e&amp;version=V2</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Climate Data</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Mauritius, Rodrigues, and Agalega Islands</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Powered by: University of Mauritius
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Yogesh Beeharry, Ravish Gokool, Yatindra Kumar Ramgolam, Aatish Chiniah (University of Mauritius)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Climate Science</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>climate-banner</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Added via climate dataset integration - extracted from climate.html</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ui_53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Climate Data</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Fabienne Rafidiharinirina | f.rafidiharinirina@association-maidi.mg or assomaidi@gmail.com</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Powered by: Madagascar Initiatives for Digital Innovation
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fabienne Rafidiharinirina (Madagascar Initiatives for Digital Innovation)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Climate Science</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>climate-banner</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Added via climate dataset integration - extracted from climate.html</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ui_54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/14195731</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Climate Data</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Dr. Zeeshan Shafiq | zeeshanshafiq@uetpeshawar.edu.pk</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Powered by: CISNR UET Peshawar
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Zeeshan Shafiq, Prof. Dr. Gul Muhammad Khan, Engr. Sarmad Rafique, Engr. Muhammad Bilal Khan, Engr. Umer Khan, Engr. Mansoor Khan, Engr. Niaz Khan, Engr. Musa Khan, Engr. Abdul Moiz (CISNR UET Peshawar)</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Climate Science</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>climate-banner</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Added via climate dataset integration - extracted from climate.html</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5666,6 +5666,1502 @@
       </c>
       <c r="X55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ui_55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://github.com/hausanlp/NaijaSenti</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Powered by: Multiple authors collaboration
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, Pavel Brazdil (Multiple authors collaboration)</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ui_56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://github.com/asmelashteka/HornMT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Horn of Africa (Ethiopia, Eritrea)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Powered by: Horn of Africa research collaboration
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi (Horn of Africa research collaboration)</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ui_57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/6N5V1K</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Owen McOnyango (Maseno University), Florence Indede (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Owen McOnyango, Florence Indede, Lilian D.A. Wanzare (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ui_58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/KLCKL5</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Florence Indede, Owen McOnyango, Lilian D.A. Wanzare (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ui_59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KenSpeech: Swahili Speech Transcriptions</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/YHXJSU</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Dorcas Awino (University of Nairobi), Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (Maseno University), Owen McOnyango (Maseno University), Florence Indede (Maseno University)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Dorcas Awino, Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare, Barack Wanjawa, Owen McOnyango, Florence Indede (Maseno University), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ui_60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/NOAT0W</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Lilian D.A Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (University of Nairobi), Lawrence Muchemi (University of Nairobi)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lilian D.A Wanzare, Florence Indede, Owen McOnyango (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ui_61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/OTL0LM</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Barack Wanjawa (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare, Florence Indede, Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University)</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ui_62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Africa (Multi-country)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Powered by: Multiple collaborating institutions
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ui_63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/lafand-mt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Africa (Multi-country)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Powered by: Multiple collaborating institutions
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ui_64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/masakhane-pos</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Africa (Multi-country)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Powered by: Multiple collaborating institutions
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ui_65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Dennis Asamoah Owusu, DOWUSU@ASHESI.EDU.GH</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Powered by: Ashesi University and collaborating institutions
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dennis Asamoah Owusu, Multiple collaborators (Ashesi University and collaborating institutions)</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ui_66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Gerald Nweya (GERALDNWEYA@GMAIL.COM) and Emeka Onwuegbuzia (EONWUEGBUZIA@GMAIL.COM)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Powered by: Igbo NLP research collaboration
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gerald Nweya, Emeka Onwuegbuzia (Igbo NLP research collaboration)</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ui_67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://robotsmali-ai.github.io/datasets/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Christopher Homan, christopher.m.homan.phd@gmail.com</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Mali/France</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Powered by: Multi-institutional collaboration
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Allahsera Auguste Tapo, Michael Leventhal, Valentin Vydrin, Sebastian Diarra, Marcos Zampieri, Emily Prud'Hommeaux, Jean Jacque Méric, Christopher Homan (Multi-institutional collaboration)</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ui_68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Makerere University NLP Datasets</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/dataverse/makerereuniversitylacuna</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Andrew Katumba | andrew.katumba@mak.ac.ug</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Uganda, Tanzania, Kenya</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Powered by: Makerere University, Maseno University, TYD Innovation Incubator
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Katumba Andrew, Nakatumba-Nabende Joyce, Babirye Claire, Mukiibi Jonathan, Tusubira Jeremy, Bateesa Tobias, Wairagala Eric Peter, Fridah Katushemererwe, Mutebi Chodrine, Nabende Peter, Sentanda Medadi, Ssenkungu Ivan (Makerere University), Wanzare Lilian (Maseno University), Davis David (TYD Innovation Incubator)</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ui_69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://github.com/csikasote/bigc</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Claytone Sikasote | claytonsikasote@gmail.com</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Powered by: University of Zambia, George Mason University
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Claytone Sikasote, Eunice Mukonde – Mulenga (University of Zambia), Md Mahfuz Ibn Alam, Antonios Anastasopoulos (George Mason University)</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ui_70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KALLAAMA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://github.com/gauthelo/kallaama-speech-dataset</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Aminata Ndiaye | amina.ndiaye@jokalante.com and Elodie Gauthier | elodie.gauthier@orange.com</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Powered by: Jokalante, Dakar, Senegal, Orange Innovation, Lannion, France, Ecole Polytechnique de Thiès, Senegal
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Aminata Ndiaye Diallo (Jokalante, Dakar, Senegal), Elodie Gauthier (Orange Innovation, Lannion, France), Abdoulaye Guissé (Ecole Polytechnique de Thiès, Senegal)</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ui_71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NaijaVoices: Our Language is Our Strength</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Language Technology</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Language Data</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>info@naijavoices.com</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Powered by: NaijaVoices project
+Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Multiple contributors (NaijaVoices project)</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>language-banner</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Added via language dataset integration - extracted from language.html</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,6 @@
           <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>CC-BY</t>
@@ -645,16 +644,11 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -667,7 +661,6 @@
           <t>Facilitating access to financial applications in informal settings in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings.  Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.  </t>
@@ -678,7 +671,6 @@
           <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>SDG 10, SDG 8</t>
@@ -709,7 +701,6 @@
 Low quality means that what the user recorded did not match the given prompt either because there was a truncation or the recording was totally different from the prompt.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>The dataset might be used to devise more inclusive banking platforms that better understand users in  in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
@@ -742,16 +733,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -764,7 +750,6 @@
           <t>Enabling machine translation from Kiswahili into the indigenous Kenyan languages Kidaw'ida, Kalenjin, and Dholuo, preserving these languages &amp; supporting crowd-sourced voice recognition via Mozilla Common Voice for these languages</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">The dataset was created to enable translation from Kiswahili, which is the national language in Kenya, into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. All three languages are low resource, especially Kidaw'ida, which has only around 400,000 speakers and is at immediate risk of loss. By collecting the text and speech data, the project has taken a step towards preservation of these languages . The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On average, each corpus has thirty thousand sentence pairs. 
@@ -776,7 +761,6 @@
           <t>https://zenodo.org/records/13355021</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>SDG 10, SDG 5, SDG 2</t>
@@ -802,7 +786,6 @@
           <t>The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On averate, each corpus has thirty thousand sentence pairs. This dataset is available on Zenodo and on GitHub where it will continue to be grown and its quality improved. The project had a total of 105 speakers who came from different parts of each region where the three languages are spoken. Thus, different regional accents were included in the speech data, making the dataset more representative. Furthermore, both male and female speakers were contributing to the voice data.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">&gt; The datasets can help to build translation services from Kiswahili into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. 
@@ -837,7 +820,6 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t xml:space="preserve">https://arxiv.org/pdf/2501.11003, https://github.com/waleghwa/low-resource-language-data, https://commonvoice.mozilla.org/en/datasets </t>
@@ -848,14 +830,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Comment Balthas: original title is "Building parallel corpora for Kenya’s Indigenous Languages and Swahili"
 DONE on 25.8., Balthas</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -868,7 +848,6 @@
           <t>Helping to measure solar energy adoption across Madagascar via AI - Labelled Open solar panel data for Madagascar</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>This dataset will help data scientists, government and users to measure solar energy adoption across Madagascar. It laid the groundwork needed to develop a solar panel detection algorithm working in Madagaskar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.
@@ -880,13 +859,11 @@
           <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>SDG 13</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Fabienne Rafidiharinirina (f.rafidiharinirina@association-maidi.mg), Association Maidi (assomaidi@gmail.com)</t>
@@ -897,10 +874,6 @@
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Powered by:  
@@ -908,23 +881,16 @@
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -937,7 +903,6 @@
           <t>Detecting sentiments and combatting hate speech in Hausa, Igbo, Nigerian-Pidgin and Yorùbá - NaijaSenti: a Nigerian Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>The NaijaSenti dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria. It consists of around 30,000 annotated tweets per language (except for Nigerian-Pidgin), including a significant fraction of code-mixed tweets. These datasets are useful not only for sentiment analysis but also for hate speech detection. The open-source package consists of datasets, trained models, sentiment lexicons, and code. With more than 200 million people and 522 native languages, Nigeria is the most populous and linguistically diverse country in Africa, as well as the third most multilingual country in the world. The majority of the population speaks either Hausa, Igbo, Yorùbá, or Nigerian-Pidgin.</t>
@@ -978,7 +943,6 @@
           <t>The project developed and made the following resources available:   1. Manually Annotated Twitter Sentiment Dataset 2. Manually Annotated Sentiment Lexicon 3. Semi-automatically Translated emotion lexicon 4. Semi-automatically Translated sentiment lexicon 5. Large Scale Unlabeled Twitter Sentiment Corpus 6. Stop-words for Hausa, Igbo, Pidgin and Yoruba     7. text  collection,  filtering, processing  and  labeling  methods  to  create  datasets  for  these  low-resource  languages.   8. evaluation og a  range of  pre-trained  models  and  transfer  strategies  on  the  dataset. 9. release  of datasets,  trained  models,  sentiment  lexicons,  and  code  to  incentivize research on sentiment analysis in under-represented languages. Authors: Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284 </t>
@@ -1026,13 +990,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>DONE on 25.8., Balthas</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,7 +1007,6 @@
           <t>Enable Cashew, Cocoa and Coffee farmers to make good business decisions - Drone-based Agricultural Dataset for Crop Yield Estimation in Ghana and Uganda</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa.
@@ -1057,7 +1018,6 @@
           <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -1078,9 +1038,6 @@
           <t>Ghana,Uganda</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
@@ -1108,16 +1065,11 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1130,7 +1082,6 @@
           <t>Preserving privacy and avoiding gender bias of AI systems in Luganda, Lumasaba, Hausa, and Kanuri - The Lacuna personally identifiable information Text Dataset</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>The Lacuna PII Multilingual Text Dataset  contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages,  improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
@@ -1141,7 +1092,6 @@
           <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/CGHWZE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
@@ -1175,13 +1125,11 @@
 For more, see data card here: https://dataverse.harvard.edu/file.xhtml?fileId=10577233&amp;version=2.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset of personally identifiable information (PII) can help any organization or initiative, that would like to comply with legal requirements while still being able to analyze and use and share data effectively in one of the languages in Luganda, Lumasaba, Hausa, and Kanuri. It can also be used to improve machine translation systems for these low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. </t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Powered by:  Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global
@@ -1204,7 +1152,6 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>https://dataverse.harvard.edu/file.xhtml?fileId=10577234&amp;version=2.0</t>
@@ -1215,13 +1162,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>First editing DONE on 25.8., Balthas</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1239,11 +1184,6 @@
           <t>Ecuador Electricity Access &amp; Supply Data</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>ESPOL University</t>
@@ -1254,10 +1194,6 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Powered by:  ESPOL University
@@ -1275,21 +1211,16 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>First editing DONE on 28.8., Luisa - There´s no much information available</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1302,12 +1233,6 @@
           <t>Powering Rural Futures in West Africa: AI-Driven Demand Data for Smarter Electrification</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Reiner Lemoine Institut gGmbH (RLI)</t>
@@ -1318,10 +1243,6 @@
           <t>Benin,Ghana,Niger,Togo</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>Powered by:  Reiner Lemoine Institut gGmbH (RLI)
@@ -1329,19 +1250,11 @@
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1354,7 +1267,6 @@
           <t>Promoting energy conservation and market analysis in Pakistan through Residential Energy and Weather Data (REWD)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>This dataset helps to understand energy consumption patterns in relation to weather conditions in Pakistan. This can guide policymaking on energy and energy conservation, sustainabe energy initiatives and private sector use (market assessment and strategic planning as new entrants in the restructured energy market). 
@@ -1366,7 +1278,6 @@
           <t>https://lei.lums.edu.pk/datasets/residential-energy-and-weather-data-pakistan.html</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 7</t>
@@ -1395,13 +1306,11 @@
 3. Meteorological dataset created with infromation of 18 months for six urban centers. It comprises of up to 10 essential variables: temperature, atmospheric pressure, humidity, dew, precipitation, wind direction, wind speed, solar radiation, solar energy and UV index</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>The resources can support policymaking and inform energy sustainability initiatives. They can namely be  utilized by key stakeholders such as the Ministry of Climate Change, Ministry of Energy (Power Division),  Punjab Energy Efficiency &amp; Conservation Authority, and National Energy Efficiency &amp;  Conservation Authority (NEECA)  Moreover,  private sector companies can use the data for market assessment purposes and strategic planning as new entrants in the restructured energy market.  The resources can also support further academic research and innovation.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Powered by: Lahore University (LUMS)
@@ -1424,20 +1333,16 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 27.08.2025, Title and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1465,7 +1370,6 @@
           <t>https://github.com/yangshao2/UrbanInfraDL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -1530,7 +1434,6 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>Link to White paper</t>
@@ -1541,13 +1444,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 28.08.2026 / Availability on Github: it doesn´t have a good exmplanation, which makes it hard to know what is it about.</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1560,7 +1461,6 @@
           <t>Monitoring the impact of palm oil monoculture, shrimp aquaculture &amp; mining in continental Ecuador and the Galapagos using AI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>The dataset can help to build systems, that can monitor the impact of palm oil monoculture, shrimp aquaculture, mining and other land transformations in continental Ecuador and Galapagos. The project created a 20.000 points land use/cover classification training dataset from existing data, with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML)  models covering continental Ecuador and the Galapagos islands.</t>
@@ -1571,7 +1471,6 @@
           <t>https://www.kaggle.com/datasets/mapbiomasecuador/lulc-training-data-for-ecuador-ml/data</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -1599,7 +1498,6 @@
 - LULC Training Data for Ecuador ML: This dataset builds upon the first by incorporating additional information on the conservation status of each point. This includes whether the location falls within protected areas, indigenous territories, areas under government forest incentive programs, and other conservation-related designations.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation. </t>
@@ -1632,7 +1530,6 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Land cover/use temporal trends are essential to understand the status of the remaining natural cover and change trends. But understanding the drivers of land use/cover change with local precision has proved challenging when working with existing global-scale datasets. Lacuna Fund’s support will allow us to create a precise dataset that will elevate our ability to discriminate land use classes that are both temporally and spatially descriptive. This funding will also support an extra layer of data to support projects aimed at reducing the pressure on standing forests and help maintain the socio-natural systems that have successfully prevented conversion of forests for anthropogenic use.” 
@@ -1644,13 +1541,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 28.08.2027, titel and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1663,12 +1558,6 @@
           <t xml:space="preserve">Forest carbon sequestration in the Congo Basin: combining In Situ Data and Artificial Intelligence to unlock climate finance </t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>World Resources Institute</t>
@@ -1679,10 +1568,6 @@
           <t>Cameroon,DRC</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Powered by:  [ADD!!!]
@@ -1690,10 +1575,6 @@
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: "At a time when the Congo Basin has become the most important rainforest carbon sink, and one of the highest biodiversity hotspots in the world, understanding and tracking its dynamics is more urgent than ever if we want to achieve global 2030 climate and biodiversity goals. With support from Lacuna Fund, our project will help bring machine learning to scientists working on the ground to monitor this ecosystem. It will pilot innovative technologies to close knowledge gaps and help speed action towards better managing these rainforests, ensuring a better world for people, nature, and climate.”  
@@ -1705,9 +1586,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1735,7 +1613,6 @@
           <t>https://arbimon.org/p/namunyak-conservancy-reteti-elephant-sanctuary; https://arbimon.org/p/shakiam-ecuadorian-amazon/insights</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">SGD 1, 2, 3, 4, 5, 8,10, 13, 15 </t>
@@ -1806,7 +1683,6 @@
           <t>Earth Observation &amp; other</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Through the integration of Indigenous knowledge and cutting-edge technology, the Ltome-Katip project not only addresses pressing environmental and technical machine learning challenges but empowers Indigenous communities to lead the way in conservation efforts. This initiative, in collaboration with the Rochester Institute and Space4Innovation, represents a true partnership between the Shuar tribe in the Ecuadorian Amazon and the Samburu tribe in northern Kenya, showcasing the power of collaboration and Indigenous knowledge in safeguarding our planet’s biodiversity.” 
@@ -1818,13 +1694,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>trello board with key messages: https://trello.com/invite/b/669bafb78c890345b83127a3/ATTIcf32f650c44aa08c718541da28f2559e8E474BA5/ltome-katip-comms-plan</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1842,14 +1716,11 @@
           <t>WatchMyTree</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>https://figshare.com/articles/dataset/The_First_Open_Dataset_of_Mangrove_Above-_and_Belowground_Biomass_and_Soil_Carbon_Stocks_in_C_te_d_Ivoire_Insights_from_Fresco_and_Sassandra_/30258772</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Tabular</t>
@@ -1865,10 +1736,6 @@
           <t>Cote d'Ivoire</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Powered by:  [ADD!!!]
@@ -1876,14 +1743,11 @@
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “As far as monitoring and calculating forest carbon stocks are concerned, there is still a major technological bottleneck blocking the large-scale development of forest carbon credits in Côte d’Ivoire, which needs to be overcome quickly. Remote sensing is a useful tool in the forest monitoring process; further studies should be carried out to enable it to meet the need for assessment on a smaller scale and to measure biomass directly. In this way, we can help decision-makers orient their conservation policies, but also support the process of rewarding small players, such as agricultural producers involved in agroforestry, private forestry, etc. Our aim, with the funds raised, is to provide practical field data to better train artificial intelligence algorithms for dynamic mapping of forest biomass and mangroves.”   
@@ -1895,9 +1759,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1910,7 +1771,6 @@
           <t>Mapping Cocoa Landscapes in Ghana: Reference Data for Tracking Land Use Change</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
@@ -1921,7 +1781,6 @@
           <t>https://zenodo.org/records/15778396</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -1960,7 +1819,6 @@
 • Not suitable for certification or compliance purposes.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>What can be done immediately:
@@ -2012,7 +1870,6 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “We are extremely grateful to Lacuna Fund and are delighted that our reference data collection effort will contribute immensely to an evolving data ecosystem to set up scalable machine learning applications for monitoring land-use change in cocoa-forest mosaic landscapes. Led by the Centre for Remote Sensing and Geographic Services (CERSGIS) and supported by researchers from the Centre for Climate Change and Sustainability Studies University of Ghana, International Crops Research Institute for the Semi-Arid Tropics (ICRISAT), Boston University, and the University of Alabama in Huntsville through SERVIR West Africa and the SERVIR Global network, this work will leverage the local knowledge of youth and community members for science-based participatory data collection. This data will provide critical input for enabling the transformation of commodity-driven supply chain traceability and commercial opportunities for ecosystem sustainability.  
@@ -2024,9 +1881,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2039,14 +1893,11 @@
           <t>Supporting reforestation in Kenya through AI-powered monitoring of trees</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>This project developed a efficient AI-powered method and dataset for monitoring of trees in forests in Kenya. Accurate tree crown detection and other parameters will support reforestation efforts in several ways: The datasets enable the development of tools that can rapidly assess the success of reforestation efforts by enabling counting of trees, estimation of trees’ biophysical parameters from drone images, and prediction of tree growth in relation to tree species and weather variables. The data consists of a high-resolution dataset of drone imagery, ground truth tree parameter measurements, and aggregate weather data from a large, reforested area in Kenya.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -2067,8 +1918,6 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Effective forest management and conservation require monitoring tree attributes such as height, crown diameter, and tree count to assess growth in reforested areas. These data enable the development of tools that can speed up the process to assess the success of reforestation efforts and other various ecological and forestry applications, including biomass estimation, forest health assessment, and carbon sequestration studies. Such tools could include the automated counting of trees, estimation of trees’ biophysical parameters from drone images such as tree crown diameter, and prediction of tree growth in relation to tree species and weather variables. In all these areas, AI can offer a cost-effective and scalable alternative to traditional methods of monitoring and counting.
@@ -2099,8 +1948,6 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>https://www.dw.com/en/artificial-intelligence-boosts-kenyas-forestry-conservation/video-69618432, https://dekut-dsail.github.io/projects/treedetection.html, https://agu.confex.com/agu/agu24/meetingapp.cgi/Paper/1728502, https://ieeexplore.ieee.org/document/11060524</t>
@@ -2111,13 +1958,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Original title: Remote sensing and weather dataset for improved reforestation monitoring</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2130,20 +1975,16 @@
           <t>Combatting deforestation &amp; supporting natural resource management in Uganda through satellite imagery AI-datasets and National Forestry Inventory AI-datasets</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">Deforestation is a significant contributor to changes in land use/cover in Uganda. This challenge is intensified by agriculture’s extreme vulnerability to climate change. This project has generated datasets that can be utilized to predict land cover types or changes for informed decision-making in natural resource management. The data is accessible, quality satellite imagery datasets and National Forestry Inventory datasets.  Specifically, Sentinel 2 and Hansen tree cover image datasets have been augmented with the inclusion of inventory datasets. A biomass mean stock per hectare dataset for each vegetation type has also been acquired. Annotation procedures of the different datasets allow for machine learning tasks. </t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>SDG 15: Life on Land: sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Makerere University</t>
@@ -2154,14 +1995,11 @@
           <t>Uganda</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">The land use/cover change datasets improve the understanding of the relationship between land cover/land use change and climate change. The can also be used to inform practice and policy on how best to manage various potential scenarios and combat deforestation.        </t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Powered by: Makerere University in cooperation with the Uganda National Forestry Authority (NFA)
@@ -2179,8 +2017,6 @@
           <t>Dataset &gt; Model</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “With funding from Lacuna Fund, satellite image and forest inventory datasets will help to develop machine learning models for prediction of land cover types or changes for informed decision-making in natural resource management. Under joint research from Makerere College of Agriculture and Environment Studies and Makerere AI Health Lab, and in partnership with the National Forestry Authority, Uganda, our land use/cover change datasets will improve our understanding of the relationship between land cover/land use change and climate change. It will also be useful in informing practice and policy on how best to manage various potential scenarios. 
@@ -2193,13 +2029,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>original title: DATASETS FOR PREDICTION OF LAND USE/COVER CHANGES IN UGANDA</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2227,7 +2061,6 @@
           <t>https://www.gbif.org/</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Life on Land (SDG 15): sustainably manage forests</t>
@@ -2306,13 +2139,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 28.08.2027</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2325,14 +2156,11 @@
           <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
@@ -2353,15 +2181,12 @@
           <t>Benin</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">This datasets can be used to build systems for faster, more regular monitoring of mangrove conditions. This is essential to provide evidence that supports timely decisions for mangrove management and mitigate the outcomes of climate change.
 </t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Powered by: University of Abomey-Calavi, Republic of Benin 
@@ -2384,20 +2209,16 @@
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Original title: Datasets to understand mangroves health in relationship to climate change</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2410,7 +2231,6 @@
           <t>Mitigating the impacts of oil palm cultivation on forests and climate change in Indonesia through AI and social forestry</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>This dataset contributes to improved understanding and mitigation of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management. 
@@ -2419,8 +2239,6 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), 
@@ -2442,14 +2260,11 @@
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Powered by:  RECOFTC
@@ -2489,9 +2304,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2504,7 +2316,6 @@
           <t>Inclusive MRV for India's Eastern Himalayas</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>An AI-Driven Dataset for Nature-Positive Livelihoods and Forest Restoration in Eastern Himalayas.This open-access dataset and digital MRV (Monitoring, Reporting, and Verification) toolkit was  developed to help communities, NGOs and policymakers in the Eastern Himalayas measure and manage the links between forests, livelihoods and climate resilience. The project was created in response to a persistent data gap in the Himalayan region where limited open data and difficult terrain have hindered effective monitoring of forest degradation and the impact of restoration programs. Using locally calibrated AI models trained on Indian biomass data, the system combines satellite observations with ground level socio-economic surveys to measure forest dependency, identify degradation hotspots and track restoration outcomes. All datasets ranging from community level livelihood surveys in Sikkim and Mizoram to forest biomass and land use layers in Assam are openly available. Together they form a replicable, open-source “digital public good” that can be used to train local AI models for forest monitoring, biodiversity accounting or impact assessment. By providing a scalable, context-aware dataset, this initiative enables indigenous start-ups, environmental NGOs and impact investors to quantify nature positive outcomes, align with IRIS+ indicators, and guide conservation investments.
@@ -2607,9 +2418,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2637,7 +2445,6 @@
           <t>https://dmmg.icipe.org/dataportal/dataset/data-enabled-climate-shock-absorbance-and-ecosystem-resilience</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -2663,13 +2470,11 @@
           <t xml:space="preserve">This geospatial datasets comprises both land use/landcover (LULC) data, plot sampling and socio-economic data from 35 out of 47 counties in Kenya spread across four main agroclimatic zones in Kenya. It contains machine learning-ready data of 2,391 LULC points and polygones of the collected LULC classes, that show the different land uses across Kenya. It also contains a total of a total of 8,194 plant location (gps) points of individual tagged plants collected from a total of 224 1-ha plots from 35 counties in Kenya. Information on the species identification, diameter at breast height (DBH), height, and canopy size is provided. In addition, socio-economic data from 46 focused group discussions with over 44% women and 18% youth conducted within the 35 counties is provided and clearly labeled, detailing agroforestry systems (AFSs) preferences, gender roles, and youth participation in agroforestry systems (AFSs). </t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">The database provides information on tree/plant-level, plot-level and landscape scale across Kenya. Measurements such as DBH, tree height, canopy size and tree identification have been provided. In addition, socio-economic data such as agroforestry systems (AFSs) preferences, gender roles, and youth participation in AFSs are also provided. The datasets are readily and freely available to users who can integrate it to AI and ML algorithms and models as ground-truth data to train and/or validate the models associated and/or related to agroforestry and carbon sequestration across Kenya. The models developed using the Agrof4Resilience data could utilize and take advantage of satellite data from various sources that are both freely available or with commercial licences. </t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Powered by:  [ADD!!!]
@@ -2677,14 +2482,11 @@
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The Lacuna-funded Agro4Resilience Project offers Kenyan farmers and decision makers a pathway for informed decision-making that supports tree cover increase. It will also improve agricultural productivity and mitigate climate change effects through ecosystem services.” 
@@ -2696,9 +2498,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2727,7 +2526,6 @@
           <t>https://acceso-datos-ambientales-invemar.hub.arcgis.com/maps/a0cab53befd44804923800a194c703d6/about</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>SDG 15 (Life of Land)</t>
@@ -2761,7 +2559,6 @@
 </t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">The geodatabase provides detailed plot-level and tree-level field data from Colombian Caribbean mangroves, including measurements such as DBH, height, species, above-ground biomass (AGB), and above-ground carbon (AGC). Users can directly integrate the Ground_truth dataset with other similar field datasets to train and validate machine learning models for accurate estimation of mangrove biomass and carbon stocks.
@@ -2796,7 +2593,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The dataset compiled during the project will facilitate accurate AGB and AGC estimation in Colombian Caribbean mangroves, enabling better understanding of carbon storage and supporting conservation and management efforts. It will also provide a valuable resource for future research and monitoring activities related to these important coastal ecosystems. Furthermore, the methodology developed in this project might even be applied beyond the Colombian Caribbean to other mangrove ecosystems with similar structures.”  
@@ -2808,9 +2604,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2838,7 +2631,6 @@
           <t xml:space="preserve">https://doi.org/10.5281/zenodo.15704554; https://doi.org/10.4121/d97e338b-dc94-4e3d-a473-6dd3d4b48898.v1; https://doi.org/10.4121/9e6b4bca-f3d3-40f3-a8f5-4f71f7790c2f.v1; https://doi.org/10.4121/7e6d7ca3-060d-4ca5-bd83-d779b598c11d.v1 </t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>SDG 15 (Life of Land)</t>
@@ -2874,8 +2666,6 @@
 Creative Commons Attribution 4.0 International</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
@@ -2926,8 +2716,6 @@
           <t xml:space="preserve"> This is a global digital public good under open-source licenses as named under CC-BY 4.0 license.</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2940,14 +2728,11 @@
           <t>Corpus sobre cultura Qom</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>This project creates two open-access speech corpora for the Qom language, an indigenous language of the Gran Chaco region, to combat its digital marginalization. It was created to provide the foundational data needed to build language technologies like machine translators and voice assistants, which are crucial for its preservation and modern use. The dataset includes a high-quality, professionally recorded corpus and a larger, community-collected corpus capturing diverse dialects, genders, and ages. Linguistically annotated and openly available, this resource directly empowers the Qom community by involving them in its creation and enables developers and researchers to build educational and cultural applications. This initiative supports the linguistic sovereignty of indigenous peoples and aligns with the goals of the International Decade of Indigenous Languages.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
@@ -2981,13 +2766,11 @@
 Sustainability and Future Plans: Long-term maintenance relies on the lead researchers at UBA/CONICET and the empowerment of trained Qom community members. The plan for sustainability includes using the corpus to build useful community tools that encourage ongoing use and contribution. Readers can partner with the research institutions for linguistic expertise and with the Qom communities directly for data expansion and validation, ensuring the resource evolves with the language.</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -2998,17 +2781,11 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3021,14 +2798,11 @@
           <t>Crafting a Bilingual Dataset for Biomedical Natural Language Processing</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>This project addresses a critical gap in healthcare technology by creating a high-quality, bilingual English-Luganda dataset for medical applications. It was developed because the lack of such data prevents the creation of effective digital health tools for millions of Luganda speakers in Uganda, hindering access to accurate medical information. The dataset is built through interviews with healthcare workers, collection of naturalistic clinic speech, translation of medical guidelines, and aggregation of existing resources. Openly available, this dataset can be used by NGOs, health agencies, and local developers to build life-saving applications like diagnostic assistants, automated translation of health materials, and voice-based medical record systems, directly contributing to improved health outcomes and equitable access to care.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>SDG 3 (Good Health and Well-being); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
@@ -3062,13 +2836,11 @@
 Sustainability and Future Plans: Sustainability is tied to partnerships with health institutions like the Infectious Diseases Institute (IDI). The dataset can be kept up-to-date by continuously incorporating new translated guidelines and anonymized, consented health communication data. Readers from the global health and AI communities can collaborate by contributing new parallel health texts or helping to fine-tune models for specific medical tasks.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3084,16 +2856,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3106,14 +2873,11 @@
           <t>Project Empowering Indigenous Communities:  AI-Driven Data Corpus for the Revitalization of Indigenous Languages Spoken in Chile"</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>This initiative builds multimodal text and speech corpora for the Rapa Nui and Mapudungun languages (including its Pehuenche, Guluche, Lafkenche, and Huilliche variants) to reverse their exclusion from the digital world. Created in direct response to community needs, it expands on a previous machine translation prototype to include diverse dialects and crucial speech data for the many speakers who are not literate in their native tongue. The open-source corpora will allow local and international developers to create more robust and inclusive language technologies, such as accurate speech-to-text systems. This empowers indigenous communities in Chile to use their languages in daily digital life, safeguarding ancestral knowledge and fostering cultural preservation through technology.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
@@ -3147,13 +2911,11 @@
 Sustainability and Future Plans: The long-term plan is for the partnered Indigenous institutions to become stewards of the data and resulting technologies. The project's methodology of community engagement is a replicable model for sustainability. Readers can engage by adopting this participatory methodology in their own work, by contributing to the expansion of the text corpus with new themes, or by helping to transcribe the open dialogue speech data.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3169,16 +2931,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3191,14 +2948,11 @@
           <t>Development of a modern Paraguayan Guarani dataset for core NLP</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>This project develops a large, modern corpus of Paraguayan Guarani to overcome its status as a low-resource language despite having millions of speakers. It addresses the lack of data for building essential Natural Language Processing (NLP) tools. The key innovation is its focus on two distinct varieties: half the corpus is in "pure" Guarani and the other half in "Jopara," the common code-switched mix of Guarani and Spanish. This openly licensed dataset, annotated to international standards, is a foundational resource for researchers and developers to create part-of-speech taggers, parsers, and educational tools. It will directly enhance platforms like Maitei for learning Guarani, empowering educators and students and ensuring the language thrives in the digital age.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
@@ -3232,13 +2986,11 @@
 Sustainability and Future Plans: The release of the dataset into the Universal Dependencies repository embeds it within a global ecosystem with built-in version control and community maintenance. The long-term plan is for the NLP community to maintain and extend the resource. Readers can contribute by submitting improvements to the UD annotations, using the data to build new applications that demonstrate value, or organizing new hackathons to expand the corpus.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3254,16 +3006,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3276,14 +3023,11 @@
           <t>AfriFact &amp; AfriGuard: Dataset for Fact-Checking, Robust Refusal</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>This project creates datasets for fact-checking and harmful prompt refusal in 10 major African languages (Afrikaans, Amharic, Ewe, Hausa, Igbo, Oromo, Shona, Swahili, Yoruba, Zulu). It was created to ensure the safety and reliability of large language models (LLMs) for African users, preventing the spread of misinformation and malicious use. The datasets are manually curated by experts, translating and adapting existing English benchmarks to include locally relevant knowledge from African sources. Openly available, these resources empower local fact-checking organizations, AI developers, and social media platforms to build and audit AI systems that refuse harmful requests and provide accurate, verified information in local languages, fostering a safer digital ecosystem.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
@@ -3317,13 +3061,11 @@
 Sustainability and Future Plans: Sustainability is managed through the Masakhane network's distributed model, where language leads maintain their respective components. The project aligns with global AI safety initiatives. Readers can contribute by becoming language coordinators within Masakhane, helping to translate more prompts, or developing better automated evaluation tools for their language.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3339,16 +3081,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3361,14 +3098,11 @@
           <t>Empowering Ethnic Voices in Tanzania</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>This project creates a comprehensive speech and text dataset for six endangered Ethnic Community Languages (ECLs) in Tanzania to prevent their extinction and promote digital inclusion. It addresses the dominance of Swahili and English which excludes these communities from technological advancements. The dataset comprises over 450 hours of transcribed and translated audio from interviews and storytelling, capturing rich cultural narratives. This open resource enables the development of automatic speech recognition (ASR) systems, bilingual educational tools, and accessible healthcare communication apps. NGOs, government agencies, and local tech developers can use this to build services that empower marginalized communities, preserve cultural heritage, and ensure everyone can access information in their first language.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
@@ -3402,13 +3136,11 @@
 Sustainability and Future Plans: The most robust sustainability plan is the intention to upload data to Mozilla Common Voice, a platform designed for community-driven, continuous data collection and validation. This ensures long-term maintenance by the speakers themselves. Readers can contribute instantly by validating existing clips on Common Voice or recording new sentences in the target languages, directly helping to improve the dataset.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3424,16 +3156,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3446,14 +3173,11 @@
           <t>MOZNLP-UP: Scaling Up Mozambican Language Coverage towards NLP inclusion</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>This project expands NLP resources for four key Mozambican languages—Emakhuwa, Xichangana, Nyanja, and Sena—spoken by nearly 25 million people. It was created to provide essential language technology tools for critical domains like news broadcasting and bilingual education, where local language variants are crucial. The project produces a multi-way translation dataset and open translation models, focusing specifically on capturing unique Mozambican dialects and loanword adaptations. The resulting open-language technology platform, featuring dictionary lookup and computer-assisted translation (CAT) tools, can be used by journalists, teachers, and government agencies to create content and services. This fosters digital inclusion and empowers communities by breaking down language barriers in access to information.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 9 (Industry, Innovation and Infrastructure); SDG 4 (Quality Education) </t>
@@ -3487,13 +3211,11 @@
 Sustainability and Future Plans: The project aims for sustainability through the public release of models on Hugging Face and the operationalization of the MUZALING platform. Long-term maintenance will likely fall to a Mozambican institution. Readers can collaborate by using and improving the open-source models, contributing new parallel text data, or helping to localize other software and content using these tools.</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3509,16 +3231,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3531,14 +3248,11 @@
           <t>Constructing a Multilingual Parallel Corpus Dataset of Nahuatl and Totonaco</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>This project builds a parallel corpus for Nahuatl and Totonaco variants from Puebla, Mexico, with translations into Spanish and English. It addresses the gap between legal mandates for indigenous language rights and the practical lack of human and technological resources to implement them. The corpus is constructed through fieldwork and community engagement to ensure authenticity and quality. This open dataset is a foundational tool for developers and government agencies to build accurate machine translation systems, automated public service information platforms, and educational materials. It empowers indigenous communities by ensuring their right to access information and services in their native language, fostering greater inclusion and cultural preservation.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
@@ -3559,20 +3273,17 @@
           <t>Brazil, Ireland, Mexico, United Kingdom</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>This parallel corpus enables the immediate development of Spanish-Nahuatl and Spanish-Totonaco machine translation systems. These can be used to translate public service information, legal documents, and educational materials, directly supporting the implementation of linguistic rights laws in Mexico. Developers can build simple web and mobile apps for phrase translation to aid communication in healthcare or municipal settings. The work can be extended by focusing on speech data collection to create speech-to-speech translation tools, which are often more needed for oral languages. A significant challenge is the complexity of the languages and the variations between communities, which requires careful dialectal management. Any replication must be done in close partnership with anthropologists and linguists who understand the socio-linguistic context. The cost is primarily in development and community engagement (est. $5k-15k+), as the data structure itself is not overly complex for modern MT systems.
 Sustainability and Future Plans: The interdisciplinary team, including anthropologists and community specialists, is key to sustainability. Their deep ties to the communities in Puebla ensure that the project is grounded in real needs. Readers can engage by collaborating with this team to expand the corpus to other variants or by developing specific applications for the state government to use in serving its citizens.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3588,16 +3299,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3610,14 +3316,11 @@
           <t>African Tone Project</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>This project creates a time-aligned, annotated audio-visual dataset specifically focused on the tonal features of African languages. It addresses a critical gap in NLP, as tone—a fundamental linguistic feature—is often omitted from datasets, severely hampering the development of accurate speech and language technologies for these languages. The dataset includes both elicited words and natural conversations across different language varieties. Openly available, this resource is invaluable for linguists, speech technology researchers, and language revitalization teams. It enables the development of tone-aware speech recognition and synthesis systems, which are essential for creating truly effective and natural digital tools for the hundreds of millions of speakers of tonal languages in Africa.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
@@ -3651,13 +3354,11 @@
 Sustainability and Future Plans: The project is sustained by its academic value to the fields of linguistics and NLP. The PIs and language leads are responsible for maintenance. The high-quality, archival-standard data ensures its long-term usability. Readers can contribute by using the data for their research, publishing findings that highlight its value, and advocating for more resources to be dedicated to the study of tonal phenomena in AI.</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3673,16 +3374,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3710,7 +3406,6 @@
           <t>https://radiantearth.github.io/stac-browser/#/external/raw.githubusercontent.com/khufkens/EotG_data/main/release_v1/EotG_images/catalog.json</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -3776,15 +3471,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3812,7 +3503,6 @@
           <t>https://drive.google.com/drive/folders/140eLeY3Z_JALFa0B77ZTP9gFt-mSPWXl</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -3878,15 +3568,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3914,7 +3600,6 @@
           <t>https://www.kaggle.com/ogbuokiriblessing/sensor-based-aquaponics-fish-pond-datasets</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
@@ -3980,15 +3665,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4016,7 +3697,6 @@
           <t>https://dataverse.harvard.edu/dataverse/airlabug/</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -4082,15 +3762,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4118,7 +3794,6 @@
           <t>http://dtlp.nottech.co.tz/index.html</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
@@ -4184,15 +3859,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4220,7 +3891,6 @@
           <t>https://zenodo.org/records/10060610</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
@@ -4286,15 +3956,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4402,9 +4068,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4432,7 +4095,6 @@
           <t>https://github.com/nasaharvest/cropharvest</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -4508,9 +4170,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4538,7 +4197,6 @@
           <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
@@ -4604,15 +4262,11 @@
           <t>agriculture-banner.jpg</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4640,7 +4294,6 @@
           <t>https://zenodo.org/records/10068758</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4701,8 +4354,6 @@
           <t>Diagnostic</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4713,8 +4364,6 @@
           <t>CC-BY 4.0 International</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4742,7 +4391,6 @@
           <t>https://goblab.uai.cl/proyecto-reduccion-de-la-malnutricion-infantil-en-chile/</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4803,8 +4451,6 @@
           <t>Statistical Analysis</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4815,8 +4461,6 @@
           <t>Controlled Access</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4844,7 +4488,6 @@
           <t>https://doi.org/10.7910/DVN/VEADSE</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4905,8 +4548,6 @@
           <t>Object Detection</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4917,8 +4558,6 @@
           <t>CC-BY 4.0 International</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4946,7 +4585,6 @@
           <t>https://portal.ithriv.org/#/public_commons/project/d9fc062c-64c9-4481-80e7-3db4aba17e00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Health</t>
@@ -5007,8 +4645,6 @@
           <t>Predictive Modeling</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5019,8 +4655,6 @@
           <t>CC-BY 4.0 International</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5048,7 +4682,6 @@
           <t>https://www.cancerimagingarchive.net</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Health</t>
@@ -5109,8 +4742,6 @@
           <t>Image Segmentation</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5121,8 +4752,6 @@
           <t>CC-BY 4.0 International</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5150,7 +4779,6 @@
           <t>https://zenodo.org/records/13913469</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Health</t>
@@ -5211,8 +4839,6 @@
           <t>Object Detection</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5223,8 +4849,6 @@
           <t>CC-BY 4.0 International</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5237,7 +4861,6 @@
           <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
@@ -5248,7 +4871,6 @@
           <t>https://thinkingmachines.github.io/project-cchain/</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5269,10 +4891,6 @@
           <t>Philippines</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>Powered by: Thinking Machines Data Science, Inc., Epimetrics, Inc., Manila Observatory, Philippine Action for Community-led Shelter Initiatives, Inc.
@@ -5300,19 +4918,16 @@
           <t>climate-banner</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Added via climate dataset integration - extracted from climate.html</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5325,7 +4940,6 @@
           <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
@@ -5336,7 +4950,6 @@
           <t>https://www.kaggle.com/datasets/collinsudanor/abattoir-air-quality-dataset/data</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5357,10 +4970,6 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Powered by: Alliance for Progressive and Sustainable Environment
@@ -5388,19 +4997,16 @@
           <t>climate-banner</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Added via climate dataset integration - extracted from climate.html</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5413,7 +5019,6 @@
           <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
@@ -5424,7 +5029,6 @@
           <t>https://www.scidb.cn/en/detail?dataSetId=2b499b91a4464fffa9f60fc8b51da03e&amp;version=V2</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5445,10 +5049,6 @@
           <t>Mauritius, Rodrigues, and Agalega Islands</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Powered by: University of Mauritius
@@ -5476,19 +5076,16 @@
           <t>climate-banner</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Added via climate dataset integration - extracted from climate.html</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5501,7 +5098,6 @@
           <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
@@ -5512,7 +5108,6 @@
           <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5533,10 +5128,6 @@
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Powered by: Madagascar Initiatives for Digital Innovation
@@ -5564,19 +5155,16 @@
           <t>climate-banner</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Added via climate dataset integration - extracted from climate.html</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5589,7 +5177,6 @@
           <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
@@ -5600,7 +5187,6 @@
           <t>https://zenodo.org/records/14195731</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5621,10 +5207,6 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Powered by: CISNR UET Peshawar
@@ -5652,19 +5234,16 @@
           <t>climate-banner</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Added via climate dataset integration - extracted from climate.html</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5677,7 +5256,6 @@
           <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
@@ -5688,15 +5266,14 @@
           <t>https://github.com/hausanlp/NaijaSenti</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5709,10 +5286,11 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://github.com/hausanlp/NaijaSenti</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Powered by: Multiple authors collaboration
@@ -5740,19 +5318,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5765,7 +5340,6 @@
           <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
@@ -5776,15 +5350,14 @@
           <t>https://github.com/asmelashteka/HornMT</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5797,10 +5370,11 @@
           <t>Horn of Africa (Ethiopia, Eritrea)</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://github.com/asmelashteka/HornMT</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Powered by: Horn of Africa research collaboration
@@ -5828,19 +5402,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5853,7 +5424,6 @@
           <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
@@ -5864,15 +5434,14 @@
           <t>https://doi.org/10.7910/DVN/6N5V1K</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5885,10 +5454,11 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Languages covered: Kiswahili, Dholuo, Luhya-Lubukusu, Luhya-Logooli, Luhya-Lumarachi</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
@@ -5916,19 +5486,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5941,7 +5508,6 @@
           <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
@@ -5952,15 +5518,14 @@
           <t>https://doi.org/10.7910/DVN/KLCKL5</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5973,10 +5538,11 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Languages covered: Dholuo, Luhya-Lumarachi, Luhya-Lulogooli, Luhya-Lubukusu</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
@@ -6004,19 +5570,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6029,7 +5592,6 @@
           <t>KenSpeech: Swahili Speech Transcriptions</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
@@ -6040,15 +5602,14 @@
           <t>https://doi.org/10.7910/DVN/YHXJSU</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6061,10 +5622,11 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Languages covered: Swahili</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
@@ -6092,19 +5654,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6117,7 +5676,6 @@
           <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
@@ -6128,15 +5686,14 @@
           <t>https://doi.org/10.7910/DVN/NOAT0W</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6149,10 +5706,11 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Languages covered: Dholuo, Luhya-Lumarachi, Luhya-Lubukusu, Luhya-Lulogooli</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
@@ -6180,19 +5738,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6205,7 +5760,6 @@
           <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
@@ -6216,15 +5770,14 @@
           <t>https://doi.org/10.7910/DVN/OTL0LM</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6237,10 +5790,11 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Languages covered: Swahili</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
@@ -6268,19 +5822,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6293,7 +5844,6 @@
           <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
@@ -6304,15 +5854,14 @@
           <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6325,10 +5874,11 @@
           <t>Africa (Multi-country)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Powered by: Multiple collaborating institutions
@@ -6356,19 +5906,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6381,7 +5928,6 @@
           <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
@@ -6392,15 +5938,14 @@
           <t>https://github.com/masakhane-io/lafand-mt</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6413,10 +5958,11 @@
           <t>Africa (Multi-country)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/lafand-mt</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Powered by: Multiple collaborating institutions
@@ -6444,19 +5990,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6469,7 +6012,6 @@
           <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
@@ -6480,15 +6022,14 @@
           <t>https://github.com/masakhane-io/masakhane-pos</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6501,10 +6042,11 @@
           <t>Africa (Multi-country)</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/masakhane-pos</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Powered by: Multiple collaborating institutions
@@ -6532,19 +6074,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6557,7 +6096,6 @@
           <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
@@ -6568,15 +6106,14 @@
           <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6589,10 +6126,11 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>Powered by: Ashesi University and collaborating institutions
@@ -6620,19 +6158,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6645,7 +6180,6 @@
           <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
@@ -6656,15 +6190,14 @@
           <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6677,10 +6210,11 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>Powered by: Igbo NLP research collaboration
@@ -6708,19 +6242,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6733,7 +6264,6 @@
           <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
@@ -6744,15 +6274,14 @@
           <t>https://robotsmali-ai.github.io/datasets/</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6765,10 +6294,11 @@
           <t>Mali/France</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Languages covered: Bambara, French</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>Powered by: Multi-institutional collaboration
@@ -6796,19 +6326,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6821,7 +6348,6 @@
           <t>Makerere University NLP Datasets</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
@@ -6832,15 +6358,14 @@
           <t>https://dataverse.harvard.edu/dataverse/makerereuniversitylacuna</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6853,10 +6378,6 @@
           <t>Uganda, Tanzania, Kenya</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>Powered by: Makerere University, Maseno University, TYD Innovation Incubator
@@ -6884,19 +6405,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6909,7 +6427,6 @@
           <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
@@ -6920,15 +6437,14 @@
           <t>https://github.com/csikasote/bigc</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6941,10 +6457,11 @@
           <t>Zambia</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://github.com/csikasote/bigc</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>Powered by: University of Zambia, George Mason University
@@ -6972,19 +6489,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6997,7 +6511,6 @@
           <t>KALLAAMA</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
@@ -7008,15 +6521,14 @@
           <t>https://github.com/gauthelo/kallaama-speech-dataset</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7029,10 +6541,6 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>Powered by: Jokalante, Dakar, Senegal, Orange Innovation, Lannion, France, Ecole Polytechnique de Thiès, Senegal
@@ -7060,19 +6568,16 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7085,7 +6590,6 @@
           <t>NaijaVoices: Our Language is Our Strength</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
@@ -7096,15 +6600,14 @@
           <t>Not specified in source</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Language Technology</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Language Data</t>
+          <t>Text/Language</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7117,10 +6620,11 @@
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Languages covered: Hausa, Igbo, and Yoruba</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>Powered by: NaijaVoices project
@@ -7148,19 +6652,795 @@
           <t>language-banner</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Added via language dataset integration - extracted from language.html</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ui_72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AFRIDOC-MT is a document-level and multi-way translation dataset from English into five African languages — Amharic, Hausa, Swahili, Yorùbá, and Zulu. The dataset comprises 334 health and 271 information technology news documents, all of which were human-translated from English to these languages. Each domain has at least 10,000 parallel sentences per language pair and supports multiway translation, allowing translation not only between English and the African languages but also among the African languages themselves. This dataset can be used to evaluate the ability of existing neural machine translation (NMT) models and large language models (LLMs) to translate at the document level.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/afridoc-mt</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Jesujoba O. Alabi | jalabi@lsv.uni-saarland.de</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Languages covered: Amharic, Hausa, Swahili, Yorùbá, and Zulu</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Jesujoba O. Alabi (Saarland University), Israel Abebe, Miaoran Zhang, Dawei Zhu, Dietrich Klakow, Cristina España-Bonet (DFKI), Rachel Bawden (INRIA), David Adelani (McGill University), Clement Oyeleke Odoje, Idris Akinade (University of Ibadan), and others</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ui_73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>This team has developed five conversational AI and benchmark datasets for 16 languages across the African continent: AfriXNLI (natural language inference), AfriMMLU (knowledge-based multi-choice questions), AfriMGSM (grade school mathematics), AfriIntent (intent classification), and AfriSlot (slot classification). These datasets cover languages including Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu. These text-only datasets are useful for conversational chatbots in real-life applications such as banking, restaurants, travel agencies, and more.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://github.com/masakhane-io/masakhane-nlu</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>David Adelani | david.adelani@mila.quebec</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Languages covered: Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>David Ifeoluwa Adelani (McGill University &amp; Mila), Hao Yu, Andiswa Bukula, Mmasibidi Setaka, Rooweither Mabuya (SADiLaR), and Masakhane Research Foundation</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ui_74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lacuna PII Multilingual Dataset</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>This dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The team collected 3,000 sentences for both Kanuri and Hausa, 5,000 for Lumasaba, and 4,000 for Luganda. Potential use cases include named entity recognition (NER), text classification, privacy-preserving data analysis and research, language modeling, machine translation, and linguistic research. The team aimed to curate a dataset that is gender inclusive, and their work highlighted the need for standardized guidelines for annotating low-resourced languages.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/CGHWZE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Andrew Katumba | katumba@mak.ac.ug, Milena Haykowska | milena.haykowska@clearglobal.org, Peter Nabende | nabende@gmail.com</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Languages covered: Luganda, Lumasaba, Hausa, and Kanuri</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Andrew Katumba (Makerere University), Jenifer Winfred Namuyanja, Nakakande Bridget Cecile (Marconi Research Lab), Joyce Nakatumba-Nabende, Ann Lisa Nabiryo, Peter Nabende, Eric Peter Wairagala (Makerere AI Lab), Milena Haykowska, Andrew Bredenkamp, Mariam Mohanna, Alp Öktem, Etienne de Crecy (Clear Global)</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ui_75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AfriHate is a hate and offensive speech corpus for 15 African languages: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya. The dataset annotates tweets using "offensive," "hateful," and "normal" classes, with target classes such as politics, ethnicity, gender, religion, and disability. The team also created AfriEmotion for emotion detection. Overall, they collected and annotated 10,000 instances each for hate speech and emotion detection per language, making 150,000 annotated observations. This is the first publicly available dataset for hate and offensive speech detection in these target languages.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Abinew Ali Ayele | abinewaliayele@gmail.com, Seid Muhie Yiman | muhie.yimam@uni-hamburg.de, Shamsuddeen Hassan Muhammad | muhammad@imperial.ac.uk</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Languages covered: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Abinew Ali Ayele, Esubalew Alemneh Jalew (Bahir Dar University), Shamsuddeen Hassan Muhammad (Bayero University Kano, Imperial College London), Ibrahim Said Ahmad, Idris Abdulmumin (Ahmadu Bello University), Seid Muhie Yimam (University of Hamburg)</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ui_76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ethio Speech Corpora</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ethio Speech Corpora comprises over 391 hours of recorded audio in six Ethiopian languages: Amharic (68 hours), Tigrigna (62 hours), Oromo (70 hours), Somali (56 hours), Afar (68 hours), and Sidama (68 hours). This project is a valuable resource for developing well-performing automatic speech recognition (ASR) systems for these languages in monolingual, multilingual, and cross-lingual setups. Use cases include dictation systems, transcription systems, assistive technologies, spoken dialogue systems, speech translation, and other speech technologies. The dataset maintains gender and age balance of readers across six working languages used across regional states of Ethiopia.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Solomon Teferra Abate | solomon.teferra@aau.edu.et</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Languages covered: Amharic, Tigrigna, Oromo, Somali, Afar, Sidama</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Solomon Teferra Abate (PhD), Martha Yifiru Tachbelie (PhD), Michael Melese Woldeyohannes (PhD), Hafte Abera, Bantegize Addis Alemayehu, Wondwossen Mulugeta (PhD) (Addis Ababa University, School of Information Science)</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Website: https://ethiospeech.com/</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ui_77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>This dataset was created to enable translation from Kiswahili, Kenya's national language, into three indigenous languages: Kidaw'ida, Kalenjin, and Dholuo. All three are low-resource languages, with Kidaw'ida having only around 400,000 speakers and being at immediate risk of loss. The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili, Kalenjin-Kiswahili, and Dholuo-Kiswahili, with each corpus averaging thirty thousand sentence pairs. The project has also contributed to Mozilla Common Voice Platform with 120 hours in Dholuo, 92 hours in Kalenjin, and 56 hours in Kidaw'ida for crowd-sourced voice recognition.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://commonvoice.mozilla.org/en/datasets</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Audrey Mbogho | ambogho@usiu.ac.ke</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Languages covered: Kidaw'ida, Kalenjin, Dholuo, Kiswahili</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Audrey Mbogho, United States International University Africa, and collaborating institutions</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ui_78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Expanding a parallel corpus of Portuguese and the Bantu language Emakhuwa</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Language Technology Development</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>This dataset includes the translation of 1,897 news articles comprising 660,242 words from Portuguese to Emakhuwa, an indigenous language of Mozambique. Each article includes news headline, content, and topic classification labels. Articles are divided into training (1,337), development (185), and testing (375) sets, categorized by topics: politics, economy, culture, sports, health, society, and world news. Use cases include topic classification, translation, and loanword recognition. The dataset has shown promising outcomes when fine-tuning multilingual models like ByT5, M2M100, and NLLB200, with improvements in translation quality using loanword information.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/collections/LIACC/makhuwa-nlp-66a93ea22df7f4b31e96a5ab</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Text/Language</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Felermino D. M. A. Ali | felermino.ali@unilurio.ac.mz or felerminoali@gmail.com</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Languages covered: Emakhuwa, Portuguese</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NLP Models, Language Processing Applications</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Various Open Licenses</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Felermino Dário Mário António Ali (Lurio University, LIACC, CLUP University of Porto), Henrique Lopes Cardoso (FEUP, LIACC), Rui Sousa Silva (Faculty of Arts and Humanities, CLUP University of Porto)</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>language-banner.jpg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Open Access</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Available as Digital Public Good</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -6597,7 +6597,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Not specified in source</t>
+          <t>https://naijavoices.com/membership#membership_tiers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Comments</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Info on fair sharing as as Digital Public Good</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -556,11 +551,7 @@
           <t>ui_1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Open Air Pollution Data for Patna and Gurugram</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Combatting Air Pollution and GHG Emissions in India through hyperlocal AI-powered mapping</t>
@@ -617,9 +608,10 @@
           <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CC-BY</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -644,11 +636,15 @@
           <t>Computer Vision</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,6 +657,7 @@
           <t>Facilitating access to financial applications in informal settings in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga.</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings.  Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.  </t>
@@ -671,6 +668,7 @@
           <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>SDG 10, SDG 8</t>
@@ -701,6 +699,7 @@
 Low quality means that what the user recorded did not match the given prompt either because there was a truncation or the recording was totally different from the prompt.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>The dataset might be used to devise more inclusive banking platforms that better understand users in  in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
@@ -733,11 +732,15 @@
           <t>NLP</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -750,10 +753,11 @@
           <t>Enabling machine translation from Kiswahili into the indigenous Kenyan languages Kidaw'ida, Kalenjin, and Dholuo, preserving these languages &amp; supporting crowd-sourced voice recognition via Mozilla Common Voice for these languages</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">The dataset was created to enable translation from Kiswahili, which is the national language in Kenya, into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. All three languages are low resource, especially Kidaw'ida, which has only around 400,000 speakers and is at immediate risk of loss. By collecting the text and speech data, the project has taken a step towards preservation of these languages . The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On average, each corpus has thirty thousand sentence pairs. 
-In addition, the dataset has helped to preserve, revitalise and elevate the languages Kidaw'ida, Kalenjin, and Dholuo by making them work on Mozillas Common Voice Platform. The text and speech datasets are thereby supporting crowd-sourced voice recognition, promoting linguistic diversity and empoweromg local communities by enabling Natural Language Processing applications tailored to their needs. Namely, the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input). As of August 2025, 120 hours of speech data have been recorded on Common Voice in Dholuo (with 14692 sentences available), 92 hours have been recorded for Kalendjin (With 29900 sentences available) and 56 hours have been recorded for Kidaw'ida (with 11773 sentences available). To download the crowd-sourced speech datasets in Kidaw'ida, Kalenjin, and Dholuo, visit https://commonvoice.mozilla.org/en/datasets </t>
+In addition, the dataset has helped to preserve, revitalise and elevate the languages Kidaw'ida, Kalenjin, and Dholuo by making them work on Mozillas Common Voice Platform. The text and speech datasets are thereby supporting crowd-sourced voice recognition, promoting linguistic diversity and empoweromg local communities by enabling Natural Language Processing applications tailored to their needs. Namely, the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input). As of August 2025, 120 hours of speech data have been recorded on Common Voice in Dholuo (with 14692 sentences available), 92 hours have been recorded for Kalendjin (With 29900 sentences available) and 56 hours have been recorded for Kidaw'ida (with 11773 sentences available). To download the crowd-sourced speech datasets in Kidaw'ida, Kalenjin, and Dholuo, visit https://datacollective.mozillafoundation.org/datasets?q=common+voice </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -761,6 +765,7 @@
           <t>https://zenodo.org/records/13355021</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>SDG 10, SDG 5, SDG 2</t>
@@ -786,6 +791,7 @@
           <t>The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On averate, each corpus has thirty thousand sentence pairs. This dataset is available on Zenodo and on GitHub where it will continue to be grown and its quality improved. The project had a total of 105 speakers who came from different parts of each region where the three languages are spoken. Thus, different regional accents were included in the speech data, making the dataset more representative. Furthermore, both male and female speakers were contributing to the voice data.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">&gt; The datasets can help to build translation services from Kiswahili into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. 
@@ -820,9 +826,10 @@
           <t>NLP</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://arxiv.org/pdf/2501.11003, https://github.com/waleghwa/low-resource-language-data, https://commonvoice.mozilla.org/en/datasets </t>
+          <t xml:space="preserve">https://arxiv.org/pdf/2501.11003 , https://github.com/waleghwa/low-resource-language-data, https://datacollective.mozillafoundation.org/datasets?q=common+voice  </t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -830,6 +837,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Comment Balthas: original title is "Building parallel corpora for Kenya’s Indigenous Languages and Swahili"
@@ -848,6 +856,7 @@
           <t>Helping to measure solar energy adoption across Madagascar via AI - Labelled Open solar panel data for Madagascar</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>This dataset will help data scientists, government and users to measure solar energy adoption across Madagascar. It laid the groundwork needed to develop a solar panel detection algorithm working in Madagaskar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.
@@ -859,11 +868,13 @@
           <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>SDG 13</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Fabienne Rafidiharinirina (f.rafidiharinirina@association-maidi.mg), Association Maidi (assomaidi@gmail.com)</t>
@@ -874,6 +885,10 @@
           <t>Madagascar</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Powered by:  
@@ -881,16 +896,22 @@
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -903,6 +924,7 @@
           <t>Detecting sentiments and combatting hate speech in Hausa, Igbo, Nigerian-Pidgin and Yorùbá - NaijaSenti: a Nigerian Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>The NaijaSenti dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria. It consists of around 30,000 annotated tweets per language (except for Nigerian-Pidgin), including a significant fraction of code-mixed tweets. These datasets are useful not only for sentiment analysis but also for hate speech detection. The open-source package consists of datasets, trained models, sentiment lexicons, and code. With more than 200 million people and 522 native languages, Nigeria is the most populous and linguistically diverse country in Africa, as well as the third most multilingual country in the world. The majority of the population speaks either Hausa, Igbo, Yorùbá, or Nigerian-Pidgin.</t>
@@ -943,6 +965,7 @@
           <t>The project developed and made the following resources available:   1. Manually Annotated Twitter Sentiment Dataset 2. Manually Annotated Sentiment Lexicon 3. Semi-automatically Translated emotion lexicon 4. Semi-automatically Translated sentiment lexicon 5. Large Scale Unlabeled Twitter Sentiment Corpus 6. Stop-words for Hausa, Igbo, Pidgin and Yoruba     7. text  collection,  filtering, processing  and  labeling  methods  to  create  datasets  for  these  low-resource  languages.   8. evaluation og a  range of  pre-trained  models  and  transfer  strategies  on  the  dataset. 9. release  of datasets,  trained  models,  sentiment  lexicons,  and  code  to  incentivize research on sentiment analysis in under-represented languages. Authors: Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284 </t>
@@ -950,7 +973,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -990,6 +1013,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>DONE on 25.8., Balthas</t>
@@ -1007,6 +1031,7 @@
           <t>Enable Cashew, Cocoa and Coffee farmers to make good business decisions - Drone-based Agricultural Dataset for Crop Yield Estimation in Ghana and Uganda</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa.
@@ -1018,6 +1043,7 @@
           <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -1038,6 +1064,9 @@
           <t>Ghana,Uganda</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
@@ -1065,11 +1094,15 @@
           <t>Computer Vision</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1082,6 +1115,7 @@
           <t>Preserving privacy and avoiding gender bias of AI systems in Luganda, Lumasaba, Hausa, and Kanuri - The Lacuna personally identifiable information Text Dataset</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>The Lacuna PII Multilingual Text Dataset  contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages,  improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
@@ -1092,6 +1126,7 @@
           <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/CGHWZE</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
@@ -1125,11 +1160,13 @@
 For more, see data card here: https://dataverse.harvard.edu/file.xhtml?fileId=10577233&amp;version=2.0</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset of personally identifiable information (PII) can help any organization or initiative, that would like to comply with legal requirements while still being able to analyze and use and share data effectively in one of the languages in Luganda, Lumasaba, Hausa, and Kanuri. It can also be used to improve machine translation systems for these low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. </t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Powered by:  Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global
@@ -1152,6 +1189,7 @@
           <t>NLP</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>https://dataverse.harvard.edu/file.xhtml?fileId=10577234&amp;version=2.0</t>
@@ -1162,6 +1200,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>First editing DONE on 25.8., Balthas</t>
@@ -1184,6 +1223,11 @@
           <t>Ecuador Electricity Access &amp; Supply Data</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>ESPOL University</t>
@@ -1194,6 +1238,10 @@
           <t>Ecuador</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Powered by:  ESPOL University
@@ -1211,11 +1259,15 @@
           <t>Dataset</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>First editing DONE on 28.8., Luisa - There´s no much information available</t>
@@ -1233,6 +1285,24 @@
           <t>Powering Rural Futures in West Africa: AI-Driven Demand Data for Smarter Electrification</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The project provides two openly accessible datasets that were developed through a complete, reproducible data pipeline combining machine learning with stochastic energy-system simulation. The first dataset contains predicted appliance ownership and household counts for all 1,209 administrative level 2 regions (adm2) across Nigeria, Ghana, Togo, Benin, and Niger, derived from satellite-based features and socio-economic indicators using models trained on more than 3,500 household surveys. The second dataset consists of high-resolution synthetic electricity demand profiles generated with the RAMP tool, offering minute-by-minute load curves for an entire year for each adm2 region. Together, these datasets provide a unique, representative, and scalable foundation for understanding residential electricity demand in regions where measured data is scarce or entirely unavailable.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/3S7KPQ; https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/9WT7FJ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDG7 (Universal Energy Access) </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Reiner Lemoine Institut gGmbH (RLI)</t>
@@ -1240,9 +1310,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Benin,Ghana,Niger,Togo</t>
-        </is>
-      </c>
+          <t>Benin,Ghana,Niger,Togo, Nigeria</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+The two datasets provide complementary, high-resolution information on household electricity demand across 1,209 administrative level 2 regions in West Africa. The ML dataset contains per-region estimates of household numbers, appliance ownership across 17 categories, and cluster identifiers reflecting typical appliance-use behaviour. The demand dataset includes both full-year, minute-resolution load profiles (527,040 time steps per region) and aggregated daily curves, along with summary statistics such as minimum, maximum, mean, and total annual demand. Files are structured as standardized CSVs, organized by country, and kept in manageable sizes. Users can easily import the data into analytical workflows for energy planning, electrification modelling, scenario design, or spatial analysis. Because the pipeline is fully open source, users may also retrain models, adjust appliance usage parameters, or generate new simulations tailored to local contexts. Together, the datasets offer granular, scalable, and customizable inputs for researchers, utilities, developers, and policymakers working on electricity access and energy-system planning.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>The datasets can be used directly for energy planning, electrification modelling, mini-grid prefeasibility assessments, academic research, or scenario analysis. Users may download the ML dataset to analyse expected appliance adoption patterns or to integrate the predicted household numbers into broader socio-economic models. The synthetic demand profiles can be imported into any energy modelling environment (e.g., Python, R, Excel, PowerFactory, PyPSA, OSeMOSYS) to simulate grid expansion, evaluate supply adequacy, or study temporal consumption behaviour. Because the full codebase is open source, users can also adapt individual steps of the pipeline—such as updating input features, retraining the ML model with local survey data, or running customized RAMP simulations—to generate new or localized demand profiles. Access to both datasets is free under a CC-BY 4.0 license, and additional resources such as documentation, example scripts, and workshop materials are available via GitHub and Harvard Dataverse. This ensures that researchers, planners, and practitioners can build on the existing workflow at no cost and with minimal technical barriers.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>Powered by:  Reiner Lemoine Institut gGmbH (RLI)
@@ -1250,11 +1333,22 @@
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Clara Neyrand</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1267,6 +1361,7 @@
           <t>Promoting energy conservation and market analysis in Pakistan through Residential Energy and Weather Data (REWD)</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>This dataset helps to understand energy consumption patterns in relation to weather conditions in Pakistan. This can guide policymaking on energy and energy conservation, sustainabe energy initiatives and private sector use (market assessment and strategic planning as new entrants in the restructured energy market). 
@@ -1278,6 +1373,7 @@
           <t>https://lei.lums.edu.pk/datasets/residential-energy-and-weather-data-pakistan.html</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), SDG 7</t>
@@ -1306,11 +1402,13 @@
 3. Meteorological dataset created with infromation of 18 months for six urban centers. It comprises of up to 10 essential variables: temperature, atmospheric pressure, humidity, dew, precipitation, wind direction, wind speed, solar radiation, solar energy and UV index</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>The resources can support policymaking and inform energy sustainability initiatives. They can namely be  utilized by key stakeholders such as the Ministry of Climate Change, Ministry of Energy (Power Division),  Punjab Energy Efficiency &amp; Conservation Authority, and National Energy Efficiency &amp;  Conservation Authority (NEECA)  Moreover,  private sector companies can use the data for market assessment purposes and strategic planning as new entrants in the restructured energy market.  The resources can also support further academic research and innovation.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Powered by: Lahore University (LUMS)
@@ -1333,11 +1431,14 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 27.08.2025, Title and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
@@ -1370,6 +1471,7 @@
           <t>https://github.com/yangshao2/UrbanInfraDL</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -1409,7 +1511,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CC-BY 4.0 license</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1434,6 +1536,7 @@
           <t>Computer Vision</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>Link to White paper</t>
@@ -1444,6 +1547,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 28.08.2026 / Availability on Github: it doesn´t have a good exmplanation, which makes it hard to know what is it about.</t>
@@ -1461,6 +1565,7 @@
           <t>Monitoring the impact of palm oil monoculture, shrimp aquaculture &amp; mining in continental Ecuador and the Galapagos using AI</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>The dataset can help to build systems, that can monitor the impact of palm oil monoculture, shrimp aquaculture, mining and other land transformations in continental Ecuador and Galapagos. The project created a 20.000 points land use/cover classification training dataset from existing data, with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML)  models covering continental Ecuador and the Galapagos islands.</t>
@@ -1471,6 +1576,7 @@
           <t>https://www.kaggle.com/datasets/mapbiomasecuador/lulc-training-data-for-ecuador-ml/data</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -1498,6 +1604,7 @@
 - LULC Training Data for Ecuador ML: This dataset builds upon the first by incorporating additional information on the conservation status of each point. This includes whether the location falls within protected areas, indigenous territories, areas under government forest incentive programs, and other conservation-related designations.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation. </t>
@@ -1505,7 +1612,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CC-BY 4.0 license</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1530,6 +1637,7 @@
           <t>Computer Vision</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Land cover/use temporal trends are essential to understand the status of the remaining natural cover and change trends. But understanding the drivers of land use/cover change with local precision has proved challenging when working with existing global-scale datasets. Lacuna Fund’s support will allow us to create a precise dataset that will elevate our ability to discriminate land use classes that are both temporally and spatially descriptive. This funding will also support an extra layer of data to support projects aimed at reducing the pressure on standing forests and help maintain the socio-natural systems that have successfully prevented conversion of forests for anthropogenic use.” 
@@ -1541,6 +1649,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>First Editing done by Luisa 28.08.2027, titel and description revised by Balthas on 2.9. to strenghten the "What can I do with this dataset" dimension - catchy title.</t>
@@ -1558,6 +1667,12 @@
           <t xml:space="preserve">Forest carbon sequestration in the Congo Basin: combining In Situ Data and Artificial Intelligence to unlock climate finance </t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>World Resources Institute</t>
@@ -1568,13 +1683,21 @@
           <t>Cameroon,DRC</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  World Resource Institution 
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: "At a time when the Congo Basin has become the most important rainforest carbon sink, and one of the highest biodiversity hotspots in the world, understanding and tracking its dynamics is more urgent than ever if we want to achieve global 2030 climate and biodiversity goals. With support from Lacuna Fund, our project will help bring machine learning to scientists working on the ground to monitor this ecosystem. It will pilot innovative technologies to close knowledge gaps and help speed action towards better managing these rainforests, ensuring a better world for people, nature, and climate.”  
@@ -1586,6 +1709,8 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1613,6 +1738,7 @@
           <t>https://arbimon.org/p/namunyak-conservancy-reteti-elephant-sanctuary; https://arbimon.org/p/shakiam-ecuadorian-amazon/insights</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">SGD 1, 2, 3, 4, 5, 8,10, 13, 15 </t>
@@ -1658,7 +1784,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>License: CC BY-NC-SA 4.0 — reuse and adaptation allowed for non-commercial purposes, with attribution and benefit sharing to Indigenous custodians.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1683,6 +1809,7 @@
           <t>Earth Observation &amp; other</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Through the integration of Indigenous knowledge and cutting-edge technology, the Ltome-Katip project not only addresses pressing environmental and technical machine learning challenges but empowers Indigenous communities to lead the way in conservation efforts. This initiative, in collaboration with the Rochester Institute and Space4Innovation, represents a true partnership between the Shuar tribe in the Ecuadorian Amazon and the Samburu tribe in northern Kenya, showcasing the power of collaboration and Indigenous knowledge in safeguarding our planet’s biodiversity.” 
@@ -1694,6 +1821,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>trello board with key messages: https://trello.com/invite/b/669bafb78c890345b83127a3/ATTIcf32f650c44aa08c718541da28f2559e8E474BA5/ltome-katip-comms-plan</t>
@@ -1716,11 +1844,14 @@
           <t>WatchMyTree</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>https://figshare.com/articles/dataset/The_First_Open_Dataset_of_Mangrove_Above-_and_Belowground_Biomass_and_Soil_Carbon_Stocks_in_C_te_d_Ivoire_Insights_from_Fresco_and_Sassandra_/30258772</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Tabular</t>
@@ -1736,18 +1867,25 @@
           <t>Cote d'Ivoire</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Powered by:  [ADD!!!]
+          <t>Powered by:  Data354
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “As far as monitoring and calculating forest carbon stocks are concerned, there is still a major technological bottleneck blocking the large-scale development of forest carbon credits in Côte d’Ivoire, which needs to be overcome quickly. Remote sensing is a useful tool in the forest monitoring process; further studies should be carried out to enable it to meet the need for assessment on a smaller scale and to measure biomass directly. In this way, we can help decision-makers orient their conservation policies, but also support the process of rewarding small players, such as agricultural producers involved in agroforestry, private forestry, etc. Our aim, with the funds raised, is to provide practical field data to better train artificial intelligence algorithms for dynamic mapping of forest biomass and mangroves.”   
@@ -1759,6 +1897,8 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1771,6 +1911,7 @@
           <t>Mapping Cocoa Landscapes in Ghana: Reference Data for Tracking Land Use Change</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
@@ -1781,6 +1922,7 @@
           <t>https://zenodo.org/records/15778396</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -1819,6 +1961,7 @@
 • Not suitable for certification or compliance purposes.</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>What can be done immediately:
@@ -1845,7 +1988,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1870,6 +2013,7 @@
           <t>Computer Vision</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “We are extremely grateful to Lacuna Fund and are delighted that our reference data collection effort will contribute immensely to an evolving data ecosystem to set up scalable machine learning applications for monitoring land-use change in cocoa-forest mosaic landscapes. Led by the Centre for Remote Sensing and Geographic Services (CERSGIS) and supported by researchers from the Centre for Climate Change and Sustainability Studies University of Ghana, International Crops Research Institute for the Semi-Arid Tropics (ICRISAT), Boston University, and the University of Alabama in Huntsville through SERVIR West Africa and the SERVIR Global network, this work will leverage the local knowledge of youth and community members for science-based participatory data collection. This data will provide critical input for enabling the transformation of commodity-driven supply chain traceability and commercial opportunities for ecosystem sustainability.  
@@ -1881,6 +2025,8 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1890,14 +2036,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supporting reforestation in Kenya through AI-powered monitoring of trees</t>
+          <t>Miti360: A Comprehensive Dataset for AI-Powered Forest Monitoring</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Miti360: A Machine Learning Ready Dataset for Automated and Scalable Forest Monitoring</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>This project developed a efficient AI-powered method and dataset for monitoring of trees in forests in Kenya. Accurate tree crown detection and other parameters will support reforestation efforts in several ways: The datasets enable the development of tools that can rapidly assess the success of reforestation efforts by enabling counting of trees, estimation of trees’ biophysical parameters from drone images, and prediction of tree growth in relation to tree species and weather variables. The data consists of a high-resolution dataset of drone imagery, ground truth tree parameter measurements, and aggregate weather data from a large, reforested area in Kenya.</t>
-        </is>
-      </c>
+          <t>Miti360 is an integrated, machine-learning ready dataset for individual-tree and stand-level reforestation monitoring that fuses high-resolution drone orthophotos, terrestrial stereo and single images, precise ground measurements (tree height, crown diameter, basal diameter and GPS locations), species labels, and multi-year weather time series for nearby stations. The collection is designed to support detection, segmentation, species classification, and biophysical parameter estimation (e.g., crown diameter, height, biomass proxies), and to enable linking short-term growth dynamics to weather. Data are provided in standard GIS and ML formats (GeoTIFF, JPEG, JSON, SHP, time-series API) for immediate integration into research and operational pipelines.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://github.com/DeKUT-DSAIL/miti360</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
@@ -1918,12 +2075,34 @@
           <t>Kenya</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miti360 contains the following core components and formats (quantities as provided):
+- Orthophotos (GeoTIFF): high-resolution stitched orthomosaics (2 GeoTIFFs) and 844 orthophoto tiles exported for annotation. 
+- Tree crown annotations (orthophoto): ~24,000 annotated crowns (bounding boxes) exported in JSON; 1,208 crowns have species labels and are also provided as a 1208-feature shapefile (SHP). 
+- Ground measurements (numeric): 1,208 measurement records (600 individual trees sampled twice across two campaigns) in JSON — fields include tree height, crown diameter, basal diameter, and GPS coordinates. 
+- Terrestrial single images: 1,208 JPEG images paired with semantic segmentation masks (mask files exported alongside images). 
+- Terrestrial stereo images: 2,416 JPEG stereoscopic image pairs (left/right) with corresponding masks for 3D/photogrammetric workflows. 
+- Weather time series: daily data spanning 8 years from 40 stations, accessible via an API endpoint for linking meteorological drivers to growth. 
+All annotations and metadata use common interchange formats (JSON, SHP, GeoTIFF, JPEG) to enable GIS analyses and ML training without format conversion
+</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Effective forest management and conservation require monitoring tree attributes such as height, crown diameter, and tree count to assess growth in reforested areas. These data enable the development of tools that can speed up the process to assess the success of reforestation efforts and other various ecological and forestry applications, including biomass estimation, forest health assessment, and carbon sequestration studies. Such tools could include the automated counting of trees, estimation of trees’ biophysical parameters from drone images such as tree crown diameter, and prediction of tree growth in relation to tree species and weather variables. In all these areas, AI can offer a cost-effective and scalable alternative to traditional methods of monitoring and counting.
-Concretely the following areas of restoration can be improved:
-1) Planning - create baseline assessment: By automatically detecting existing tree crowns, tools based on this dataset can create a baseline assessment of the current forest cover. This information is valuable for planning and prioritizing reforestation areas.
-2) Monitor Progress: Repeated application of the tree crown detection model can track the success of reforestation initiatives. The model can quantify the increase in tree cover over time, allowing for informed adjustments to reforestation strategies.</t>
+          <t xml:space="preserve">The Miti360 dataset is intended for training and assessing machine learning models in various forestry applications.
+- Use the orthophoto tiles and bounding box annotations to train models for individual tree detection, counting, and classification from aerial imagery.
+- Use the terrestrial stereoscopic images to develop and benchmark 3D computer vision models for automating forest inventory, such as estimating biophysical parameters.
+- Combine the ground-truth measurements (TH, CD, BD) and weather data to train models that determine quantitative relationships between tree growth and local weather conditions.
+- Leverage the multi-year data (2024-2025) to analyse changes in biophysical parameters and determine which tree species are growing well in the reforested area.
+The dataset is designed to be integrated. By augmenting this dataset with others, one can
+- Combine Miti360 with other global forestry datasets mentioned in the report (like NEON Crowns or Auto Arborist) to train models with greater geographic diversity, addressing a key gap this dataset was built to fill.
+- Augment the dataset with socio-economic data on local farming to explore and validate the contribution of farmers to reforestation, an application suggested in the report.
+Cost &amp; resources one can use:
+- Cost: Only associated compute costs
+- Resources: The source code used for data analysis as well as preliminary models trained on the dataset will be made available.
+</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1948,6 +2127,8 @@
           <t>Dataset</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>https://www.dw.com/en/artificial-intelligence-boosts-kenyas-forestry-conservation/video-69618432, https://dekut-dsail.github.io/projects/treedetection.html, https://agu.confex.com/agu/agu24/meetingapp.cgi/Paper/1728502, https://ieeexplore.ieee.org/document/11060524</t>
@@ -1958,6 +2139,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Original title: Remote sensing and weather dataset for improved reforestation monitoring</t>
@@ -1967,61 +2149,101 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ui_18</t>
+          <t>ui_19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combatting deforestation &amp; supporting natural resource management in Uganda through satellite imagery AI-datasets and National Forestry Inventory AI-datasets</t>
+          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAT-CARe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deforestation is a significant contributor to changes in land use/cover in Uganda. This challenge is intensified by agriculture’s extreme vulnerability to climate change. This project has generated datasets that can be utilized to predict land cover types or changes for informed decision-making in natural resource management. The data is accessible, quality satellite imagery datasets and National Forestry Inventory datasets.  Specifically, Sentinel 2 and Hansen tree cover image datasets have been augmented with the inclusion of inventory datasets. A biomass mean stock per hectare dataset for each vegetation type has also been acquired. Annotation procedures of the different datasets allow for machine learning tasks. </t>
-        </is>
-      </c>
+          <t>Extensive bioinformatics resource that leverages tree species’ distribution, medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.gbif.org/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SDG 15: Life on Land: sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>Life on Land (SDG 15): sustainably manage forests</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Images, Tabular, Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Makerere University</t>
+          <t>Professor Guy F Midgley gfmidgley@sun.ac.za University of Stellenbosch</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>An extensive relational floristic and plant functional database which, together with matching biogeoclimatic data sets and implementation of the distribution model, may describe the biogeoclimatic relationships and projects the growth and ecological success of all sufficiently recorded Southern African trees under current and future climatic conditions</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Automation of a species distribution model that leverages a novel mechanistically based algorithm for 1) quantification of currently suitable planting-range conditions and 2) projection of climate risk for future planting-range suitability. This primary screening effort can be cross-referenced for adaptation and mitigation use-value sources to aid in tree species selection.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">The land use/cover change datasets improve the understanding of the relationship between land cover/land use change and climate change. The can also be used to inform practice and policy on how best to manage various potential scenarios and combat deforestation.        </t>
+          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Powered by: Makerere University in cooperation with the Uganda National Forestry Authority (NFA)
+          <t>Powered by:  Stellenbosch University
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>Luisa Olaya</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Dataset &gt; Model</t>
+          <t>Dataset &gt; Model &gt; Pilot</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Possible to draw maps of species distribution for present and futrue climates, as one initial output, but also to run hundreds of species filtered by key trait characteristics that indicate suitability for climate mitigation and adaptation</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote: “With funding from Lacuna Fund, satellite image and forest inventory datasets will help to develop machine learning models for prediction of land cover types or changes for informed decision-making in natural resource management. Under joint research from Makerere College of Agriculture and Environment Studies and Makerere AI Health Lab, and in partnership with the National Forestry Authority, Uganda, our land use/cover change datasets will improve our understanding of the relationship between land cover/land use change and climate change. It will also be useful in informing practice and policy on how best to manage various potential scenarios. 
-— Dr. Sarah Akello, College of Agriculture and Environmental Sciences, Makerere University 
-</t>
+          <t>Quote: "We are excited that Lacuna Fund has provided Stellenbosch, and our team, with the opportunity to utilize these datasets to enable researchers to model the impacts of indigenous trees for adaptation and mitigation to climate change in southern Africa. This information is of the utmost importance in ensuring the continent can build resilience against the rapid unfolding of climate change which is affecting livelihoods and demanding that we find solutions.” 
+— Professor Guy Midgley, Acting Director at School for Climate Studies, Stellenbosch University</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2029,209 +2251,110 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>original title: DATASETS FOR PREDICTION OF LAND USE/COVER CHANGES IN UGANDA</t>
+          <t>First Editing done by Luisa 28.08.2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ui_19</t>
+          <t>ui_20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SAT-CARe</t>
-        </is>
-      </c>
+          <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Extensive bioinformatics resource that leverages tree species’ distribution, medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://www.gbif.org/</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests</t>
+          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Images, Tabular, Geospatial/Remote Sensing</t>
+          <t>Images, Tabular</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Professor Guy F Midgley gfmidgley@sun.ac.za University of Stellenbosch</t>
+          <t>Romain Lucas        Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>An extensive relational floristic and plant functional database which, together with matching biogeoclimatic data sets and implementation of the distribution model, may describe the biogeoclimatic relationships and projects the growth and ecological success of all sufficiently recorded Southern African trees under current and future climatic conditions</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Automation of a species distribution model that leverages a novel mechanistically based algorithm for 1) quantification of currently suitable planting-range conditions and 2) projection of climate risk for future planting-range suitability. This primary screening effort can be cross-referenced for adaptation and mitigation use-value sources to aid in tree species selection.</t>
-        </is>
-      </c>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>open source</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Powered by:  [Stellenbosch University]
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Luisa Olaya</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Dataset &gt; Model &gt; Pilot</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Computer Vision</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Possible to draw maps of species distribution for present and futrue climates, as one initial output, but also to run hundreds of species filtered by key trait characteristics that indicate suitability for climate mitigation and adaptation</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Quote: "We are excited that Lacuna Fund has provided Stellenbosch, and our team, with the opportunity to utilize these datasets to enable researchers to model the impacts of indigenous trees for adaptation and mitigation to climate change in southern Africa. This information is of the utmost importance in ensuring the continent can build resilience against the rapid unfolding of climate change which is affecting livelihoods and demanding that we find solutions.” 
-— Professor Guy Midgley, Acting Director at School for Climate Studies, Stellenbosch University</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>First Editing done by Luisa 28.08.2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ui_20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Images, Tabular</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Romain Lucas        Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Benin</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">This datasets can be used to build systems for faster, more regular monitoring of mangrove conditions. This is essential to provide evidence that supports timely decisions for mangrove management and mitigate the outcomes of climate change.
 </t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Powered by: University of Abomey-Calavi, Republic of Benin 
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Balthas Seibold</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Original title: Datasets to understand mangroves health in relationship to climate change</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>ui_21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Mitigating the impacts of oil palm cultivation on forests and climate change in Indonesia through AI and social forestry</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>This dataset contributes to improved understanding and mitigation of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management. 
 The project created open and accessible training and evaluation datasets for machine learning applications focused on forest cover and change in Indonesia. It contains collections of polygons of uniform land cover, with labels indicating land cover type and, possibly, information on land cover change over time. To label land cover patches, the team has reviewed high-resolution satellite imagery facilitated by Collect Earth Online (CEO) and augmented it with field visits to difficult-to-classify areas. It has prioritized areas with significant landcover diversity with a preference for areas with significant smallholder production of  oil palm, coconut, and other commodities - given the well-known difficulties of distinguishing oil palm 
@@ -2239,127 +2362,135 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), 
 SDG 15 (Life on Land)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Drone Imagery, Geospatial/Remote Sensing</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>RECOFTC, Peter Cutter (peter.cutter@recoftc.org)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Powered by:  RECOFTC
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Balthas Seibold</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://www.recoftc.org/sites/default/files/styles/image_scale_w1024/public/2025-03/dji_0037.jpg.webp?itok=l0ilgQi8</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.recoftc.org/projects/advancing-oil-palm-mapping-social-forestry-and-machine-learning 
 Quote: “Communities in the areas targeted by this project are challenged when it comes to mapping the rapidly changing forest landscapes on which they depend. The datasets this project generates will provide valuable insight into these dynamic patterns of change.”  
 — Gamma Galudra, Director, Indonesia Country Office, RECOFTC </t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>ui_22</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Inclusive MRV for India's Eastern Himalayas</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>An AI-Driven Dataset for Nature-Positive Livelihoods and Forest Restoration in Eastern Himalayas.This open-access dataset and digital MRV (Monitoring, Reporting, and Verification) toolkit was  developed to help communities, NGOs and policymakers in the Eastern Himalayas measure and manage the links between forests, livelihoods and climate resilience. The project was created in response to a persistent data gap in the Himalayan region where limited open data and difficult terrain have hindered effective monitoring of forest degradation and the impact of restoration programs. Using locally calibrated AI models trained on Indian biomass data, the system combines satellite observations with ground level socio-economic surveys to measure forest dependency, identify degradation hotspots and track restoration outcomes. All datasets ranging from community level livelihood surveys in Sikkim and Mizoram to forest biomass and land use layers in Assam are openly available. Together they form a replicable, open-source “digital public good” that can be used to train local AI models for forest monitoring, biodiversity accounting or impact assessment. By providing a scalable, context-aware dataset, this initiative enables indigenous start-ups, environmental NGOs and impact investors to quantify nature positive outcomes, align with IRIS+ indicators, and guide conservation investments.
 The goal is to make environmental monitoring inclusive and data driven, empowering local actors to track changes in forest carbon, identify erosion risks and measure the socio-economic benefits of restoration. Ultimately, this approach helps governments, researchers and entrepreneurs build locally adapted AI systems that support both ecosystem regeneration and sustainable livelihoods in fragile mountain regions.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://github.com/vertify-earth/biomass-prediction-NorthEastIndia; https://zenodo.org/records/16536024</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/1WaunaB-HU-j9UDs-X5Fn1vJ15H4ENMe-lcEgWM9l3Eg/edit?usp=sharing</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Vertify.earth, Michael Anthony michael@vertify.earth ,
 Alsisar Impact, Saurabh Singhavi saurabh@alsisarimpact.com</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>This dataset integrates geospatial and socio-economic information to monitor forest restoration and livelihoods in the Eastern Himalayas. It combines satellite data from Sentinel-1, Sentinel-2, Landsat-8, and PALSAR with 500+ ground truth points and nearly 300 household surveys collected in Assam, Sikkim, and Mizoram. The data support AI applications for biomass estimation, deforestation detection and nature positive impact assessment.
 A locally trained biomass model improves accuracy for South Asian forest types, addressing calibration bias in global datasets. All personal identifiers have been removed, and sensitive coordinates anonymized to protect community privacy. The dataset is published under a CC-BY 4.0 license and maintained by Vertify.earth GmbH and Earth Analytics India Pvt Ltd, ensuring its ongoing usability as an open and replicable foundation for environmental AI and digital MRV systems.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">The AI model estimates forest biomass and vegetation health in the Eastern Himalayas using multi-source satellite data combined with local ground measurements. It outputs Above-Ground Biomass (AGB) maps, enabling accurate tracking of forest carbon, degradation, and restoration progress.
 The model accepts pre-processed satellite imagery as input and produces spatial biomass layers compatible with MRV dashboards. It runs on standard Python environments and can be adapted for other tropical regions with local calibration.
@@ -2367,186 +2498,197 @@
 </t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>This dataset and AI model can be used immediately for forest monitoring, restoration planning and impact measurement in mountain and forested regions. Users can map biomass, detect forest loss or assess community-level livelihood impacts by combining the open dataset with freely available satellite imagery. NGOs, research institutions, investors can directly apply the dataset to design or evaluate nature positive projects, while developers can integrate the AI model into their own MRV dashboards. Researchers and AI developers can extend this work by retraining the biomass model with local field data from other regions or adding new layers such as soil moisture or biodiversity indicators. Ethical replication should include community consent and data validation steps to ensure fair and context aware use.
 Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
 Model use: Free, standard cloud or local compute</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Powered by:  Vertify.earth GmbH, Earth Analytics India Pvt Ltd, Balipara Foundation, Alsisar Impact
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Arundhati Deshmukh</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case &gt;  Use-Case with Business Model</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Earth Observation / Satellite &amp; Drone Data</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://felt.com/embed/map/Nature-Audit-on-Agapi-Sourcing-Sites-JBeP3LpnTCmabCOFb9AVrAC?loc=27.317897%2C88.595673%2C15.25z</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “Lacuna Fund will be instrumental in supporting the development of an MRV system that will enable us to participatorily map the health of forests in the biodiverse Eastern Himalayan region with indigenous communities, facilitating targeted interventions for climate resilience through forest management – impacting the millions of people that depend on forests for their lives and livelihoods in the Eastern Himalayas.”  
 — Michael Dawson, Rural Futures – Anthropological Visioner, Balipara Foundation 
 </t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ui_23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Climate resilience through agroforestry</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The Agrof4Resilience geospatial datasets are open-access utilized by artificial intelligence (AI) and machine learning (ML) algorithms that are aimed at creating more robust, productive, resilient and diverse agro-ecological systems to achieve productive agro-ecosystems that have potential to improve resilience over time. This is crucial especially in dryland which are plagued with land degredation and other effects of climate change. The data demonstrates that agroforestry in Kenya is fairly low while models developed from the data indicate high agroforestry potential in Kenya. This is affected by socioeconomic factors such as education levels, occupation, age, landsize, income, gender, marital status, cultural beliefs, and family size. These datasets could be utilized to demostrate regions and practices that are environementally and socio-economically sound. This could provide insights on practices that could enhance livelihoods and promote environmental resilience in target communities across Kenya. The data was collected from 35 out of 47 counties in Kenya, spread across four predetermined transects that cover four main agro-ecological zones, and stored in a freely accessible database within icipe’s servers.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://dmmg.icipe.org/dataportal/dataset/data-enabled-climate-shock-absorbance-and-ecosystem-resilience</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This geospatial datasets comprises both land use/landcover (LULC) data, plot sampling and socio-economic data from 35 out of 47 counties in Kenya spread across four main agroclimatic zones in Kenya. It contains machine learning-ready data of 2,391 LULC points and polygones of the collected LULC classes, that show the different land uses across Kenya. It also contains a total of a total of 8,194 plant location (gps) points of individual tagged plants collected from a total of 224 1-ha plots from 35 counties in Kenya. Information on the species identification, diameter at breast height (DBH), height, and canopy size is provided. In addition, socio-economic data from 46 focused group discussions with over 44% women and 18% youth conducted within the 35 counties is provided and clearly labeled, detailing agroforestry systems (AFSs) preferences, gender roles, and youth participation in agroforestry systems (AFSs). </t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The database provides information on tree/plant-level, plot-level and landscape scale across Kenya. Measurements such as DBH, tree height, canopy size and tree identification have been provided. In addition, socio-economic data such as agroforestry systems (AFSs) preferences, gender roles, and youth participation in AFSs are also provided. The datasets are readily and freely available to users who can integrate it to AI and ML algorithms and models as ground-truth data to train and/or validate the models associated and/or related to agroforestry and carbon sequestration across Kenya. The models developed using the Agrof4Resilience data could utilize and take advantage of satellite data from various sources that are both freely available or with commercial licences. </t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Powered by:  ICIPE
+Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
+Financed by: BMZ</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote: “The Lacuna-funded Agro4Resilience Project offers Kenyan farmers and decision makers a pathway for informed decision-making that supports tree cover increase. It will also improve agricultural productivity and mitigate climate change effects through ecosystem services.” 
+— David Makori, International Centre of Insect Physiology and Ecology (ICIPE)  </t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ui_23</t>
+          <t>ui_24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
+          <t>Quantifying Colombian mangroves aboveground biomass and carbon content</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Climate resilience through agroforestry</t>
+          <t>Mapping Blue Carbon: Quantifying Mangrove Carbon Stocks for Climate Action and Conservation in the Colombian Caribbean</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>The Agrof4Resilience geospatial datasets are open-access utilized by artificial intelligence (AI) and machine learning (ML) algorithms that are aimed at creating more robust, productive, resilient and diverse agro-ecological systems to achieve productive agro-ecosystems that have potential to improve resilience over time. This is crucial especially in dryland which are plagued with land degredation and other effects of climate change. The data demonstrates that agroforestry in Kenya is fairly low while models developed from the data indicate high agroforestry potential in Kenya. This is affected by socioeconomic factors such as education levels, occupation, age, landsize, income, gender, marital status, cultural beliefs, and family size. These datasets could be utilized to demostrate regions and practices that are environementally and socio-economically sound. This could provide insights on practices that could enhance livelihoods and promote environmental resilience in target communities across Kenya. The data was collected from 35 out of 47 counties in Kenya, spread across four predetermined transects that cover four main agro-ecological zones, and stored in a freely accessible database within icipe’s servers.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://dmmg.icipe.org/dataportal/dataset/data-enabled-climate-shock-absorbance-and-ecosystem-resilience</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Geospatial/Remote Sensing</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This geospatial datasets comprises both land use/landcover (LULC) data, plot sampling and socio-economic data from 35 out of 47 counties in Kenya spread across four main agroclimatic zones in Kenya. It contains machine learning-ready data of 2,391 LULC points and polygones of the collected LULC classes, that show the different land uses across Kenya. It also contains a total of a total of 8,194 plant location (gps) points of individual tagged plants collected from a total of 224 1-ha plots from 35 counties in Kenya. Information on the species identification, diameter at breast height (DBH), height, and canopy size is provided. In addition, socio-economic data from 46 focused group discussions with over 44% women and 18% youth conducted within the 35 counties is provided and clearly labeled, detailing agroforestry systems (AFSs) preferences, gender roles, and youth participation in agroforestry systems (AFSs). </t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The database provides information on tree/plant-level, plot-level and landscape scale across Kenya. Measurements such as DBH, tree height, canopy size and tree identification have been provided. In addition, socio-economic data such as agroforestry systems (AFSs) preferences, gender roles, and youth participation in AFSs are also provided. The datasets are readily and freely available to users who can integrate it to AI and ML algorithms and models as ground-truth data to train and/or validate the models associated and/or related to agroforestry and carbon sequestration across Kenya. The models developed using the Agrof4Resilience data could utilize and take advantage of satellite data from various sources that are both freely available or with commercial licences. </t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Powered by:  [ADD!!!]
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quote: “The Lacuna-funded Agro4Resilience Project offers Kenyan farmers and decision makers a pathway for informed decision-making that supports tree cover increase. It will also improve agricultural productivity and mitigate climate change effects through ecosystem services.” 
-— David Makori, International Centre of Insect Physiology and Ecology (ICIPE)  </t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ui_24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Quantifying Colombian mangroves aboveground biomass and carbon content</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mapping Blue Carbon: Quantifying Mangrove Carbon Stocks for Climate Action and Conservation in the Colombian Caribbean</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">This open-access dataset supports machine learning (ML) applications for mangrove forest monitoring, addressing the need for more openly available and well-annotated datasets to calibrate and validate ML models. It focuses on improving the estimation of above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian Caribbean mangroves. The pilot area, Via Parque Isla de Salamanca National Natural Park (VIPIS) in the Magdalena department, is a Ramsar and UNESCO Biosphere Reserve. Existing global AGB and AGC models often lack the precision and cost-effectiveness needed for regional monitoring.
 The dataset includes both plot-level and tree-level field measurements from 20 newly surveyed plots, providing detailed attributes such as DBH, height, species, AGB (from allometric equations), and AGC. Using these field data, high-resolution satellite imagery, and machine learning models, satellite-based AGB and AGC maps covering ~6,000 ha of mangroves at 10 m spatial resolution have also been generated. </t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://acceso-datos-ambientales-invemar.hub.arcgis.com/maps/a0cab53befd44804923800a194c703d6/about</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>SDG 15 (Life of Land)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>María Cuevas (mcuevas@cttc.es / Centre Tecnològic de Telecomunicacions de Catalunya, CTTC, Spain),  Cristian Montes (cristian.montes@invemar.org.co / Instituto de Investigaciones Marinas y Costeras José Benito Vives de Andreis, INVEMAR, Colombia)</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">This geodatabase contains geospatial information collected and processed under the LACUNA project, aimed at quantifying above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian mangroves, specifically in the VIPIS area (Vía Parque Isla de Salamanca). The data are organized into two main datasets: Ground_truth and Satellite AGB/AGC.
 Ground_truth Dataset – Field and reference data:
@@ -2559,99 +2701,104 @@
 </t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">The geodatabase provides detailed plot-level and tree-level field data from Colombian Caribbean mangroves, including measurements such as DBH, height, species, above-ground biomass (AGB), and above-ground carbon (AGC). Users can directly integrate the Ground_truth dataset with other similar field datasets to train and validate machine learning models for accurate estimation of mangrove biomass and carbon stocks.
 The satellite dataset supports spatially explicit analysis of forest structure, carbon dynamics, and environmental factors influencing mangrove ecosystems. Combined with additional datasets, it can help improve model robustness, enable cross-site comparisons, and enhance predictive accuracy.
 Beyond modeling, the dataset facilitates carbon stock quantification, conservation planning, forest management, and climate policy development. </t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Powered by:  CTTC &amp; INVEMAR
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>María Cuevas</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The dataset compiled during the project will facilitate accurate AGB and AGC estimation in Colombian Caribbean mangroves, enabling better understanding of carbon storage and supporting conservation and management efforts. It will also provide a valuable resource for future research and monitoring activities related to these important coastal ecosystems. Furthermore, the methodology developed in this project might even be applied beyond the Colombian Caribbean to other mangrove ecosystems with similar structures.”  
 — María Cuevas-González, Geomatics Research Unit, Centre Tecnològic de Telecomunicacions de Catalunya (CTTC)  </t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>ui_25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Forecasting availaibiltiy of tropical forest resources (leaves, flowers, fruits and seeds) for local communities, forest resource managers, conservationists and restoration managers.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>The health of tropical forest ecosystems faces pressures from climate change, threatening the sustainable supply of leaves, flowers and fruits which provide important resources for wildlife, domestic animals and human settlements. Monitoring the timing of plant life cycle events (phenology) is one effective way to track the availability of plant resources and the impact of climate change and weather variability on their sustainable supply. This dataset is on 48 weeks of liana and tree phenology from ground observations, traditonal ecological knowedge and camera traps in the canopy in two tropical forest ecosystems (a moist semi-deciduous and a dry semi-deciduous forest). The dataset also includes land surface phenology from satellite images and in situ weather data. Phenology data from multiple sources and climate data could be combined via a machine learning model that can be used to predict phenology at community and landscape scales. This data will enhance the representation of tropical African forests in phenology research and contribute meaningful data from tropical African forests for machine learning applications in climate, forests and biodiversity conservation. The images and phenology labels could also be used to train an automation of identifying phenology events in forest canopy images.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">https://doi.org/10.5281/zenodo.15704554; https://doi.org/10.4121/d97e338b-dc94-4e3d-a473-6dd3d4b48898.v1; https://doi.org/10.4121/9e6b4bca-f3d3-40f3-a8f5-4f71f7790c2f.v1; https://doi.org/10.4121/7e6d7ca3-060d-4ca5-bd83-d779b598c11d.v1 </t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>SDG 15 (Life of Land)</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Tabular, Geospatial/Remote Sensing</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Bismark Ofosu-Bamfo (bismark.ofosu-bamfo@uenr.edu.gh; bofosubamfo@gmail.com) and Daniel Yawson (daniel.yawson@uenr.edu.gh) Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana/Raul Zurita-Milla (r.zurita-milla@utwente.nl) and Rosa Aguilar (r.aguilar@utwente.nl) Department of Geo-Information Processing, Faculty ITC, University of Twente, The Netherlands. Primary contact/Maintainance of datasets: Bismark Ofosu-Bamfo</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Description of clean folder (raw folder also available)
 The folder contains files of clean datasets employed for various datasets. 
@@ -2666,39 +2813,41 @@
 Creative Commons Attribution 4.0 International</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Powered by:  University of Energy and Natural Resources and University of Twente
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Bismark Ofosu-Bamfo</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Climate and Forests</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>GhanaPhenoPulse — Zooniverse</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
 — Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
@@ -2706,516 +2855,655 @@
 Joy News (video): https://g.co/kgs/5byh6f7 </t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t xml:space="preserve"> This is a global digital public good under open-source licenses as named under CC-BY 4.0 license.</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>ui_26</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Corpus sobre cultura Qom</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>This project creates two open-access speech corpora for the Qom language, an indigenous language of the Gran Chaco region, to combat its digital marginalization. It was created to provide the foundational data needed to build language technologies like machine translators and voice assistants, which are crucial for its preservation and modern use. The dataset includes a high-quality, professionally recorded corpus and a larger, community-collected corpus capturing diverse dialects, genders, and ages. Linguistically annotated and openly available, this resource directly empowers the Qom community by involving them in its creation and enables developers and researchers to build educational and cultural applications. This initiative supports the linguistic sovereignty of indigenous peoples and aligns with the goals of the International Decade of Indigenous Languages.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Text, Voice</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Instituto de Lingüística, Facultad de Filosofia y Letras, Universidad de Buenos Aires</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A known limitation is the potential demographic imbalance between the two corpora. The High-Quality Corpus is small (5 hours) and aims for gender parity, but the larger Community Corpus (10+ hours) has a primary focus on geographic and age distribution, with gender balance being a secondary concern. This could introduce a bias where the "high-quality" benchmark is not fully representative of the entire community's speech. Steps for ethical use include a participatory methodology where the community defines culturally relevant topics for recordings, obtaining informed consent that details data usage, and anonymizing speaker identities in the published data. The plan to measure inter-annotator agreement ensures the linguistic annotations are reliable and valid.
 Maintenance &amp; Point of Contact: Maintenance responsibility lies with the leading researchers from the University of Buenos Aires (UBA) and CONICET. The project is designed to build capacity within the Qom community, suggesting a long-term goal of empowering local members to contribute to and maintain the resource.
 Data License &amp; Rights: The data is intended for open access, though a specific license is not named in the text. The explicit goal of promoting use and diffusion via open access suggests a permissive license like Creative Commons (e.g., CC BY or CC BY-SA). Users would likely have the right to reuse and build upon the data for research, education, and application development, with the restriction that attribution must be given to the creators and the Qom community, aligning with the project's ethos of empowering and recognizing the community.M</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>With this corpus, researchers and developers can immediately build foundational language technologies for Qom. Specific use cases include training automated speech recognition (ASR) systems to transcribe Qom speech, developing text-to-speech synthesizers for educational content, and creating basic machine translation tools between Qom and Spanish. The community-collected corpus is particularly valuable for building applications that understand diverse dialects and real-world speech patterns. Developers can extend this work by using the data to train more sophisticated natural language processing (NLP) models for sentiment analysis, grammar checking, or conversational AI assistants tailored to the community's needs. A critical limitation to consider is the demographic imbalance between the two corpora; the high-quality corpus is small and aims for gender balance, while the larger community corpus prioritizes age and geography, which could introduce bias. Replicators must engage in an ethical AI assessment, ensuring any application involves the Qom community in a participatory manner to avoid exploitation and ensure cultural appropriateness. Building a basic application would have low compute costs (est. $100-500 for training on cloud GPUs) if using the existing data for fine-tuning, but significant investment is required for ethical community engagement and continuous improvement.
 Sustainability and Future Plans: Long-term maintenance relies on the lead researchers at UBA/CONICET and the empowerment of trained Qom community members. The plan for sustainability includes using the corpus to build useful community tools that encourage ongoing use and contribution. Readers can partner with the research institutions for linguistic expertise and with the Qom communities directly for data expansion and validation, ensuring the resource evolves with the language.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ui_27</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Crafting a Bilingual Dataset for Biomedical Natural Language Processing</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>This project addresses a critical gap in healthcare technology by creating a high-quality, bilingual English-Luganda dataset for medical applications. It was developed because the lack of such data prevents the creation of effective digital health tools for millions of Luganda speakers in Uganda, hindering access to accurate medical information. The dataset is built through interviews with healthcare workers, collection of naturalistic clinic speech, translation of medical guidelines, and aggregation of existing resources. Openly available, this dataset can be used by NGOs, health agencies, and local developers to build life-saving applications like diagnostic assistants, automated translation of health materials, and voice-based medical record systems, directly contributing to improved health outcomes and equitable access to care.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>SDG 3 (Good Health and Well-being); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Text, Voice</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>The Infectious Diseases Institute Limited</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A key limitation is the reliance on professional translators and healthcare workers for data creation, which may not fully capture the language used by patients from diverse educational backgrounds, potentially introducing a bias towards more formal or clinical Luganda. The use of existing materials like clinical guidelines also risks propagating any biases present in those original documents. Ethical steps are robust: all data from health sessions is collected with consent, translations are reviewed by both professional linguists and healthcare professionals for medical accuracy, and the focus on community involvement through interviews aims to ground the dataset in authentic, culturally appropriate communication.
 Maintenance &amp; Point of Contact: The maintenance responsibility likely falls to the project team and their host institutions. The mention of approaching the Infectious Diseases Institute (IDI) IRB indicates an ongoing relationship with a major local health institution, which could be a key partner for long-term updates and curation.
 Data License &amp; Rights: The text does not specify a license, but the nature of the project (aiming to improve public health) strongly implies an intention for open access. A license like CC BY or CC BY-NC would be appropriate, allowing researchers and developers to use and build upon the data for non-commercial health applications, requiring attribution to the creators. Restrictions would include the ethical imperative to use the data responsibly in medical contexts and to give back to the Luganda-speaking communities by improving health outcomes.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>This dataset enables the immediate development of critical healthcare NLP applications for Luganda speakers. Developers can build automated translation tools for patient information leaflets, symptom checkers, and public health advisories, or create voice-based interfaces for mobile health apps that allow users to interact in Luganda. Researchers can use it to train and benchmark models for cross-lingual information retrieval, allowing healthcare workers to access English-language medical databases using Luganda queries. This work can be extended by expanding the dataset to include more specialized medical domains (e.g., mental health, nutrition) or by developing speech-based datasets for voice-enabled clinic tools. A key limitation is the potential bias towards formal, clinical language from professionals, which may not reflect patient vocabulary. Any replication must undergo a rigorous ethical assessment focused on medical accuracy and patient safety; outputs must be reviewed by healthcare professionals. The cost to build a application is moderate (est. $1k-5k for compute) due to the complexity of medical language, but the primary cost is in ongoing expert validation to ensure safety.
 Sustainability and Future Plans: Sustainability is tied to partnerships with health institutions like the Infectious Diseases Institute (IDI). The dataset can be kept up-to-date by continuously incorporating new translated guidelines and anonymized, consented health communication data. Readers from the global health and AI communities can collaborate by contributing new parallel health texts or helping to fine-tune models for specific medical tasks.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>ui_28</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Project Empowering Indigenous Communities:  AI-Driven Data Corpus for the Revitalization of Indigenous Languages Spoken in Chile"</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>This initiative builds multimodal text and speech corpora for the Rapa Nui and Mapudungun languages (including its Pehuenche, Guluche, Lafkenche, and Huilliche variants) to reverse their exclusion from the digital world. Created in direct response to community needs, it expands on a previous machine translation prototype to include diverse dialects and crucial speech data for the many speakers who are not literate in their native tongue. The open-source corpora will allow local and international developers to create more robust and inclusive language technologies, such as accurate speech-to-text systems. This empowers indigenous communities in Chile to use their languages in daily digital life, safeguarding ancestral knowledge and fostering cultural preservation through technology.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Text, Voice</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Pontifical Catholic University of Chile</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A significant acknowledged limitation is the inability to guarantee equal gender and age distribution in the Open Dialogue Speech corpus due to access challenges, which could create imbalances. The Annotated Speech corpus, being read from pre-selected texts, lacks the spontaneity of natural conversation. Ethically, this project is exemplary. It directly responds to community-identified needs, includes an intercultural validation process with published reports, and conducts specific research into community perspectives on Generative AI to guide future ethical development. This ensures the project is community-driven and culturally respectful.
 Maintenance &amp; Point of Contact: The project team, which has pioneered previous work with these communities, is responsible. The deep partnership with Indigenous institutions and the focus on capacity-building suggest a shared, long-term responsibility for maintaining and updating the datasets.
 Data License &amp; Rights: Data will be published alongside detailed documentation and reports. The use of standard formats (MP3, JSONL) ensures interoperability. A permissive license is expected to foster reuse. The commitment to open dialogue and community guidance implies that while the data is for replication and innovation, any future commercial or sensitive use would require further community consultation and benefit-sharing, potentially formalized through a license like CC BY-SA or a community-specific protocol.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>This multi-modal corpus allows for the immediate creation of robust machine translation systems between Spanish and Rapa Nui/Mapudungun variants, directly addressing a community-identified need. Developers can build web browser plugins or mobile apps for real-time translation of text. The speech data enables the development of speech-to-text tools for transcribing elder storytelling and creating subtitled media, as well as text-to-speech systems for hearing written content. Researchers can extend this work by using the collected prompt-response pairs and community feedback reports as a foundation for developing culturally-aligned generative AI models in the future. The critical limitation is the acknowledged imbalance in the open dialogue speech corpus regarding gender and age distribution. Future work must strictly follow the project's ethical framework, using their published reports on community perspectives to guide development and always partnering with indigenous institutions for intercultural validation. Building a translation app would have moderate compute costs (est. $2k-10k), but the non-negotiable cost is the time and resource investment required for deep, respectful community collaboration.
 Sustainability and Future Plans: The long-term plan is for the partnered Indigenous institutions to become stewards of the data and resulting technologies. The project's methodology of community engagement is a replicable model for sustainability. Readers can engage by adopting this participatory methodology in their own work, by contributing to the expansion of the text corpus with new themes, or by helping to transcribe the open dialogue speech data.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Dataset &gt; Model &gt; Pilot</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>ui_29</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Development of a modern Paraguayan Guarani dataset for core NLP</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>This project develops a large, modern corpus of Paraguayan Guarani to overcome its status as a low-resource language despite having millions of speakers. It addresses the lack of data for building essential Natural Language Processing (NLP) tools. The key innovation is its focus on two distinct varieties: half the corpus is in "pure" Guarani and the other half in "Jopara," the common code-switched mix of Guarani and Spanish. This openly licensed dataset, annotated to international standards, is a foundational resource for researchers and developers to create part-of-speech taggers, parsers, and educational tools. It will directly enhance platforms like Maitei for learning Guarani, empowering educators and students and ensuring the language thrives in the digital age.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Text, Tabular</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Universidad Nacional de Itapua</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Paraguay, Spain, Uruguay</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A known challenge is categorizing texts on a spectrum from "pure" Guarani to "Jopara," a process that requires nuanced linguistic judgment and could introduce subjectivity. The translation hackathon, while innovative, might produce translations that vary in quality and naturalness. The project plans to mitigate these issues through rigorous annotation guidelines, expert linguist oversight, and measures to identify biases related to gender or ethnicity. The very structure of including both varieties is an ethical step to avoid privileging one form of the language over another.
 Maintenance &amp; Point of Contact: The project team is responsible for the initial release. The plan to release the dataset on the Universal Dependencies repository and Hugging Face places it within ecosystems that have built-in mechanisms for community maintenance, versioning, and updates by the global NLP community.
 Data License &amp; Rights: The data will be published under an explicit Creative Commons Attribution 4.0 (CC BY 4.0) license. This is a clear, permissive license that allows anyone to reuse, share, and adapt the data for any purpose, even commercially, as long as they give appropriate credit to the creators. This maximizes the potential for innovation while ensuring recognition.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>This meticulously annotated corpus is a ready-to-use resource for training core NLP tools. Developers can immediately train part-of-speech taggers, dependency parsers, and named entity recognizers for both "academic" Guarani and "Jopara." These tools can be integrated into platforms like Maitei and CINACINA to create intelligent grammar exercises, reading comprehension helpers, and writing assistants. Researchers can extend this work by using the UD-formatted data to include Guarani in massive multilingual NLP models, ensuring the language is represented in future technologies. A key challenge for replication is the subjective spectrum between pure Guarani and Jopara, which requires nuanced linguistic expertise to handle correctly. Future projects must account for this dialect continuum and avoid biasing systems towards one variety. The cost to build upon this work is relatively low (est. $500-2k for compute) as the expensive data creation and annotation is complete; costs are primarily for model training and application development.
 Sustainability and Future Plans: The release of the dataset into the Universal Dependencies repository embeds it within a global ecosystem with built-in version control and community maintenance. The long-term plan is for the NLP community to maintain and extend the resource. Readers can contribute by submitting improvements to the UD annotations, using the data to build new applications that demonstrate value, or organizing new hackathons to expand the corpus.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Dataset &gt; Model</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ui_30</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>AfriFact &amp; AfriGuard: Dataset for Fact-Checking, Robust Refusal</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>This project creates datasets for fact-checking and harmful prompt refusal in 10 major African languages (Afrikaans, Amharic, Ewe, Hausa, Igbo, Oromo, Shona, Swahili, Yoruba, Zulu). It was created to ensure the safety and reliability of large language models (LLMs) for African users, preventing the spread of misinformation and malicious use. The datasets are manually curated by experts, translating and adapting existing English benchmarks to include locally relevant knowledge from African sources. Openly available, these resources empower local fact-checking organizations, AI developers, and social media platforms to build and audit AI systems that refuse harmful requests and provide accurate, verified information in local languages, fostering a safer digital ecosystem.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Masakhane Institute</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Benin, Chad, Democratic Republic of the Congo, Ethiopia, Gambia, Kenya, Lesotho, Mauritania, Mozambique, Niger, Nigeria, Senegal, South Africa, eSwatini, Togo, Zimbabwe</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A major limitation is the project's foundation on translating existing English prompts from datasets like MALICIOUSINSTRUCT. This carries the risk of importing cultural contexts and harmful concepts that are not relevant or are differently perceived in African societies, creating a cultural bias. Steps to ensure ethical use include careful curation and filtering of English prompts to select those most relevant to the African context, extensive training for translators, and a multi-layered quality assurance process (AfriCOMET, back-translation, coordinator review) to ensure accuracy and cultural appropriateness.
 Maintenance &amp; Point of Contact: Maintenance is a community effort coordinated through Masakhane members for each language. This distributed model leverages local expertise but requires strong coordination to ensure consistent updates and quality control across all ten languages.
 Data License &amp; Rights: The datasets are derived from existing resources, so their licenses will need to be compatible. The project will likely adopt a permissive license similar to its sources (e.g., MIT, Apache 2.0, or CC BY) to encourage reuse in AI safety research. Users can replicate the methods and use the data to build safer AI systems, with the restriction that they must acknowledge the source and the contribution of the African NLP community.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>This dataset allows for the immediate development of crucial AI safety features for the 10 African languages. Developers can build content moderation filters for social media platforms, "refusal" mechanisms for chatbots to reject harmful requests in local languages, and fact-checking browser extensions that flag misinformation. Researchers can use the dataset to benchmark the safety and truthfulness of existing LLMs for these languages, holding model developers accountable. This work can be extended by adding more languages, generating more nuanced and culturally-specific harmful prompts, and developing automated evaluation metrics tailored to African linguistic structures. The critical limitation is the risk of cultural bias, as the project translates English prompts, potentially importing concepts irrelevant to African contexts. Replication must include the project's rigorous multi-step validation process (AfriCOMET, back-translation, native speaker review) to ensure cultural relevance and accuracy. The cost to implement a safety layer is low to moderate (est. $1k-5k) as it often involves fine-tuning or designing prompts for an existing model rather than training from scratch.
 Sustainability and Future Plans: Sustainability is managed through the Masakhane network's distributed model, where language leads maintain their respective components. The project aligns with global AI safety initiatives. Readers can contribute by becoming language coordinators within Masakhane, helping to translate more prompts, or developing better automated evaluation tools for their language.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ui_31</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Empowering Ethnic Voices in Tanzania</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>This project creates a comprehensive speech and text dataset for six endangered Ethnic Community Languages (ECLs) in Tanzania to prevent their extinction and promote digital inclusion. It addresses the dominance of Swahili and English which excludes these communities from technological advancements. The dataset comprises over 450 hours of transcribed and translated audio from interviews and storytelling, capturing rich cultural narratives. This open resource enables the development of automatic speech recognition (ASR) systems, bilingual educational tools, and accessible healthcare communication apps. NGOs, government agencies, and local tech developers can use this to build services that empower marginalized communities, preserve cultural heritage, and ensure everyone can access information in their first language.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Text, Voice</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Sokoine University of Agriculture</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>United Republic of Tanzania</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A potential limitation is the sourcing of written text from religious and academic centers (e.g., Bible translations, theses), which may over-represent certain genres, dialects, or ideological viewpoints, creating a lexical and thematic bias. Ethical steps are comprehensive: data collection is based on informed consent, speaker demographics are recorded to ensure diversity, rigorous quality assurance involves native speakers, and the data will be uploaded to Mozilla Common Voice for community-driven validation and expansion, ensuring ongoing community oversight.
 Maintenance &amp; Point of Contact: The project team is initially responsible. The strategy of uploading to Mozilla Common Voice is a masterstroke for maintenance, as it explicitly transfers long-term curation, validation, and expansion to the global and local community, ensuring the dataset remains a living resource.
 Data License &amp; Rights: The data will be hosted on Zenodo with a DOI under a CC BY 4.0 license. This is a gold standard for open scientific data, allowing full reuse and replication for any purpose with attribution. The explicit goal is to enhance reusability for NLP research and applications, empowering a wide range of users from developers to government agencies.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>This large-scale speech and text corpus enables the immediate development of automatic speech recognition (ASR) systems for the six ECLs. This can power voice-activated applications for education (e.g., literacy tools), information access (e.g., voice search), and cultural preservation (e.g., transcribing oral histories). The bilingual text supports the development of translated educational materials. Researchers can extend this work by using the data to build speech synthesis systems that give a voice to digital assistants in these languages. A major limitation is the sourcing of written text from religious/academic centers, which may bias the data towards a specific register. Future users must supplement this data with more contemporary, colloquial text sources. The cost to build a functional ASR model is high (est. $10k-50k+ for compute) due to the volume of audio data required for training, but leveraging pre-trained models can reduce this cost.
 Sustainability and Future Plans: The most robust sustainability plan is the intention to upload data to Mozilla Common Voice, a platform designed for community-driven, continuous data collection and validation. This ensures long-term maintenance by the speakers themselves. Readers can contribute instantly by validating existing clips on Common Voice or recording new sentences in the target languages, directly helping to improve the dataset.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ui_32</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>MOZNLP-UP: Scaling Up Mozambican Language Coverage towards NLP inclusion</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>This project expands NLP resources for four key Mozambican languages—Emakhuwa, Xichangana, Nyanja, and Sena—spoken by nearly 25 million people. It was created to provide essential language technology tools for critical domains like news broadcasting and bilingual education, where local language variants are crucial. The project produces a multi-way translation dataset and open translation models, focusing specifically on capturing unique Mozambican dialects and loanword adaptations. The resulting open-language technology platform, featuring dictionary lookup and computer-assisted translation (CAT) tools, can be used by journalists, teachers, and government agencies to create content and services. This fosters digital inclusion and empowers communities by breaking down language barriers in access to information.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 9 (Industry, Innovation and Infrastructure); SDG 4 (Quality Education) </t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>SCHOOL OF COMMUNICATION AND ARTS (ECA) - University Eduardo Mondlane</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Mozambique</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A key focus is on capturing unique Mozambican variants, but a limitation is the risk of these nuances being flattened by using general-purpose pre-trained models (like mT5 or NLLB) for fine-tuning. The project addresses this by developing loanword annotations and creating in-domain evaluation sets to better measure model performance on local usage. Ethical steps include collaboration with linguistic professionals and using workshops to develop localized translation guidelines, ensuring the data reflects authentic language use.
 Maintenance &amp; Point of Contact: The project team will maintain the models and benchmarks on Hugging Face. The rollout of the MUZALING platform (with CAT tools and a dictionary) suggests the team or a partnered Mozambican institution will be responsible for maintaining this applied tool for end-users.
 Data License &amp; Rights: The models and benchmarks will be made available on Hugging Face, which typically uses open licenses like MIT or Apache 2.0 for models and CC BY for data. This allows full public use for replication and innovation. The tools are intended for public use to facilitate language access, meaning developers, businesses, and government agencies can integrate them into their services to promote digital inclusion.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>This project provides the resources to immediately deploy practical machine translation (MT) tools. Developers can integrate the trained models into the MUZALING platform to offer computer-assisted translation (CAT) tools for journalists, dictionary lookup for students, and real-time translation features for news websites or government portals. Researchers can extend the work by using the loanword annotations to study language evolution or by adapting the models for other domains like legal or educational text. A limitation is the risk that the models might not perfectly capture local variants, especially for informal text. Replication should use the provided in-domain evaluation sets, not just general ones like FLORES+, to accurately gauge performance on local usage. The cost to run an existing model is low (est. cents per user), but the cost to train new models from scratch or for new languages is high (est. $10k+).
 Sustainability and Future Plans: The project aims for sustainability through the public release of models on Hugging Face and the operationalization of the MUZALING platform. Long-term maintenance will likely fall to a Mozambican institution. Readers can collaborate by using and improving the open-source models, contributing new parallel text data, or helping to localize other software and content using these tools.</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Dataset &gt; Model &gt; Pilot</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ui_33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Constructing a Multilingual Parallel Corpus Dataset of Nahuatl and Totonaco</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>This project builds a parallel corpus for Nahuatl and Totonaco variants from Puebla, Mexico, with translations into Spanish and English. It addresses the gap between legal mandates for indigenous language rights and the practical lack of human and technological resources to implement them. The corpus is constructed through fieldwork and community engagement to ensure authenticity and quality. This open dataset is a foundational tool for developers and government agencies to build accurate machine translation systems, automated public service information platforms, and educational materials. It empowers indigenous communities by ensuring their right to access information and services in their native language, fostering greater inclusion and cultural preservation.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Text, Voice</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Benemérita Universidad Autónoma de Puebla</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Brazil, Ireland, Mexico, United Kingdom</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>This parallel corpus enables the immediate development of Spanish-Nahuatl and Spanish-Totonaco machine translation systems. These can be used to translate public service information, legal documents, and educational materials, directly supporting the implementation of linguistic rights laws in Mexico. Developers can build simple web and mobile apps for phrase translation to aid communication in healthcare or municipal settings. The work can be extended by focusing on speech data collection to create speech-to-speech translation tools, which are often more needed for oral languages. A significant challenge is the complexity of the languages and the variations between communities, which requires careful dialectal management. Any replication must be done in close partnership with anthropologists and linguists who understand the socio-linguistic context. The cost is primarily in development and community engagement (est. $5k-15k+), as the data structure itself is not overly complex for modern MT systems.
+Sustainability and Future Plans: The interdisciplinary team, including anthropologists and community specialists, is key to sustainability. Their deep ties to the communities in Puebla ensure that the project is grounded in real needs. Readers can engage by collaborating with this team to expand the corpus to other variants or by developing specific applications for the state government to use in serving its citizens.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Alondra Arellano</t>
@@ -3223,7 +3511,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Dataset &gt; Model &gt; Pilot</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3231,132 +3519,173 @@
           <t>NLP</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ui_33</t>
+          <t>ui_34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Constructing a Multilingual Parallel Corpus Dataset of Nahuatl and Totonaco</t>
-        </is>
-      </c>
+          <t>African Tone Project</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>This project builds a parallel corpus for Nahuatl and Totonaco variants from Puebla, Mexico, with translations into Spanish and English. It addresses the gap between legal mandates for indigenous language rights and the practical lack of human and technological resources to implement them. The corpus is constructed through fieldwork and community engagement to ensure authenticity and quality. This open dataset is a foundational tool for developers and government agencies to build accurate machine translation systems, automated public service information platforms, and educational materials. It empowers indigenous communities by ensuring their right to access information and services in their native language, fostering greater inclusion and cultural preservation.</t>
-        </is>
-      </c>
+          <t>This project creates a time-aligned, annotated audio-visual dataset specifically focused on the tonal features of African languages. It addresses a critical gap in NLP, as tone—a fundamental linguistic feature—is often omitted from datasets, severely hampering the development of accurate speech and language technologies for these languages. The dataset includes both elicited words and natural conversations across different language varieties. Openly available, this resource is invaluable for linguists, speech technology researchers, and language revitalization teams. It enables the development of tone-aware speech recognition and synthesis systems, which are essential for creating truly effective and natural digital tools for the hundreds of millions of speakers of tonal languages in Africa.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Voice, Images</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Benemérita Universidad Autónoma de Puebla</t>
+          <t>African Languages Technologies Initiative</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Brazil, Ireland, Mexico, United Kingdom</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>This parallel corpus enables the immediate development of Spanish-Nahuatl and Spanish-Totonaco machine translation systems. These can be used to translate public service information, legal documents, and educational materials, directly supporting the implementation of linguistic rights laws in Mexico. Developers can build simple web and mobile apps for phrase translation to aid communication in healthcare or municipal settings. The work can be extended by focusing on speech data collection to create speech-to-speech translation tools, which are often more needed for oral languages. A significant challenge is the complexity of the languages and the variations between communities, which requires careful dialectal management. Any replication must be done in close partnership with anthropologists and linguists who understand the socio-linguistic context. The cost is primarily in development and community engagement (est. $5k-15k+), as the data structure itself is not overly complex for modern MT systems.
-Sustainability and Future Plans: The interdisciplinary team, including anthropologists and community specialists, is key to sustainability. Their deep ties to the communities in Puebla ensure that the project is grounded in real needs. Readers can engage by collaborating with this team to expand the corpus to other variants or by developing specific applications for the state government to use in serving its citizens.</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Alondra Arellano</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>NLP</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ui_34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>African Tone Project</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>This project creates a time-aligned, annotated audio-visual dataset specifically focused on the tonal features of African languages. It addresses a critical gap in NLP, as tone—a fundamental linguistic feature—is often omitted from datasets, severely hampering the development of accurate speech and language technologies for these languages. The dataset includes both elicited words and natural conversations across different language varieties. Openly available, this resource is invaluable for linguists, speech technology researchers, and language revitalization teams. It enables the development of tone-aware speech recognition and synthesis systems, which are essential for creating truly effective and natural digital tools for the hundreds of millions of speakers of tonal languages in Africa.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Voice, Images</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>African Languages Technologies Initiative</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
           <t>Canada, Ghana, Nigeria</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A significant challenge is the technical complexity of consistently annotating tone across multiple languages and speakers, which requires highly skilled annotators and can lead to inconsistency. The focus on lab-quality recording with headset microphones, while excellent for clarity, may not fully capture the acoustic properties of speech in naturalistic environments. Ethically, the project is strong: it involves native-speaker linguists in transcription assessment, strives for demographic diversity in speakers, and collaborates with communities to create tone-marking conventions where they don't exist, empowering them linguistically.
 Maintenance &amp; Point of Contact: The Principal Investigators (PIs) and language leads, who are native-speaker linguists, are responsible for the core data assessment and correction. The project is positioned as a resource for the broader research and community communities, suggesting long-term maintenance by the host academic institutions.
 Data License &amp; Rights: The use of archival-standard formats (.wav, .mov) and detailed annotations makes it a high-value resource. While a license is not specified, its creation for the broader research community suggests an open license (likely CC BY) would be used. This would allow linguists and NLP researchers to use it for replication and groundbreaking work on tonal languages. The rights would include use for analysis and model training, with the restriction that users must acknowledge the source and the contributing communities.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>This dataset is a foundational resource for groundbreaking research and development on tonal languages. Immediately, linguists can use it for phonetic and phonological analysis of tone. NLP researchers can use it to train and benchmark tone-aware speech recognition and synthesis models, which are essential for building effective voice AI for these languages. Developers can extend this work by exploring how tone information improves the performance of everything from keyword spotting to speaker identification systems. The primary limitation is the extreme technical complexity of consistently annotating tone across speakers and contexts. Replicating this work requires specialized linguistic expertise in phonetics and the specific languages. The cost to collect and annotate a similar dataset for a new language is very high (est. $50k-100k+) due to the need for expert linguists, high-quality equipment, and extensive manual labor.
 Sustainability and Future Plans: The project is sustained by its academic value to the fields of linguistics and NLP. The PIs and language leads are responsible for maintenance. The high-quality, archival-standard data ensures its long-term usability. Readers can contribute by using the data for their research, publishing findings that highlight its value, and advocating for more resources to be dedicated to the study of tonal phenomena in AI.</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ui_35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dataset for Prediction of Landuse and Landcover changes in Uganda</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Acquisition and Analysis of groundtruth data and Remote Sensing Imagery to develop and Artificial Intelligence solution for Prediction Landuse and Landcover changes in Uganda</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>This project provides Uganda’s first openly accessible AI-ready satellite imagery dataset designed to predict land-use and land-cover change. It was created to address persistent deforestation and the lack of reliable, context-specific data needed to detect, forecast, and manage ecosystem degradation. Through an open-source replication kit including annotated Sentinel-2 and Hansen datasets, protocols, and inventory data, this products enables local innovators, forest agencies, and policymakers to build AI tools for monitoring forests, planning restoration, and supporting NDC and SDG15 actions. Its goal is to improve early detection of land-cover change, strengthen climate-smart decision-making, and empower local institutions with high-quality geospatial data.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1. Landus Landcover Datasets (2015 -2023), 2. ArcGIS Pro Project, ArcGIS DEEPLearning Model for Tree Species. https://1drv.ms/f/c/BFFEF9896BFF8791/Es68F3WluONJjORAR_WvTloBdtisO9TGsGyWR8Se5xNYDA?e=q0Afso</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SDG 13: Climate Action
+By detecting deforestation, modelling future LULC trends, and supporting climate-smart planning, the project strengthens adaptation and mitigation strategies in Uganda.
+SDG 15: Life on Land
+Central to the project, as it supports forest conservation, ecosystem restoration, biodiversity protection, and reduction of land degradation.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing, Images</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Makerere University, Makerere AI Lab: https://mak.ac.ug, https://air.ug/    2. National Forestry Authority (NFA): https://nfa.go.ug/  </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>The dataset provides georeferenced, annotated Sentinel-2 and Hansen imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. Users can train AI models for landuse and landcover classification, detect deforestation, validate predictions, and support restoration planning. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>The AI application analyzes historical satellite imagery gereated landuse and landcover maps (2015-2024) and predicts future landuse and land-cover change, offering simple inputs including Sentinel-2 and Hansen datasets of tree cover and outputs such as classified maps and simulations for 2025 and 2030. It identifies deforestation, farmland expansion, and urban growth patterns, supporting evidence-based land management. While highly accurate (ANN: 85.2% OA), limitations include data inconsistencies, sampling bias, and reliance on remote-sensing quality. Ethical use requires adherence to responsible-AI assessment, transparency, and proper citation. The model runs on standard GIS/AI software (QGIS, google colab, Jupyter-notebook) with no special hardware. All derived datasets and protocols are open for reuse under an open license; users must credit the original project to strengthen community knowledge and track downstream impact.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>One can immediately use this AI system to classify landuse and landcover types, detect deforestation, and generate LULC predictions for 2025–2030. Users can replicate the full workflow from preprocessing imagery, training ANN models, and simulating future change scenarios to support forest monitoring, restoration planning, district land-use decision-making, or environmental reporting. Researchers can extend the work by integrating socio-economic variables, testing hybrid models, adding additional years of imagery, or adapting the model to new districts. Replication requires awareness of limitations such as sampling imbalance, image quality differences, and potential classification bias; an ethical-AI review is recommended for all downstream use. Costs remain low because the tools (QGIS, GEE, SEPAL) and datasets are free; only compute for model training (standard PCs) and technical time are required. All datasets, protocols, and documentation form an open public-good resource, with opportunities for collaboration through Makerere AI Lab and NFA.</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Makerere University, College of Agriculture, College of computing and Information science and the National Forestry Authority</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3366,7 +3695,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Dataset &gt; Model &gt; Pilot</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3374,86 +3703,107 @@
           <t>NLP</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manuscript under review  on AI SPATIO-TEMPORAL ANALYSIS AND PREDICTION OF LAND USE AND LAND COVER CHANGES IN SELECTED DISTRICTS IN UGANDA </t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ui_35</t>
+          <t>ui_36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eyes on the Ground Image Data</t>
+          <t>Residential Electricity Consumption Dataset for Sri Lanka</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Smallholder Farmer Field Monitoring with Machine Learning</t>
+          <t>Towards Reliable Detection of Inefficient Residential Electricity Usage for Policy Intervention</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>This machine learning dataset of smallholder farmer's fields includes georeferenced crop images along with labels on input use, crop management, phenology, crop damage, and yields, collected across 8 counties in Kenya. This dataset enables the development of AI systems to monitor crop conditions, predict yields, and support agricultural decision-making for smallholder farmers.</t>
+          <t>This project aims to develop a longitudinal household-level electricity dataset by integrating repeated survey data with high-frequency smart meter &amp; non-smart meter data. The survey component captures detailed information about household demographics, dwelling characteristics, appliance ownership, and energy-related behaviors, enabling these attributes to be linked to observed electricity consumption patterns.
+The resulting dataset is meant to facilitate analysis around experimentation with behavioral nudges, tariff reforms, and other demand-side management solutions relevant to energy affordability, efficiency, and policy in Sri Lanka.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://radiantearth.github.io/stac-browser/#/external/raw.githubusercontent.com/khufkens/EotG_data/main/release_v1/EotG_images/catalog.json</t>
+          <t>https://ieee-dataport.org/open-access/residential-electricity-consumption-dataset-sri-lanka-recon-sl</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://github.com/LIRNEasia/SL_electricity_consumption</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>SGD 7: Affordable and Clean Energy</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Images, Geospatial/Remote Sensing</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+          <t xml:space="preserve">Merl Chandana - Team Lead, Data Algorithms &amp; Policy (merl@lirneasia.net)
+Nilusha Kapugama - COO, LIRNEasia (nilusha@lirneasia.net) </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Georeferenced crop images with labels on input use, crop management, phenology, crop damage, and yields from 8 counties in Kenya. Machine learning ready dataset for smallholder agriculture monitoring.</t>
+          <t>Limitations include limited representativeness due to smart meter coverage spanning only about 10% of LECO customers, residual missingness and contiguous gaps in smart meter time-series data that reduce suitability for fine-grained analysis, and potential recall or estimation bias in selected self-reported survey variables.
+To support responsible and ethical use, the dataset is released with explicit documentation of these limitations, clearly defined suitable and unsuitable use cases, and strong guidance against national-level inference, income estimation, appliance-level disaggregation, or real-time operational forecasting. All data are de-identified, aggregated at the household meter level, and intended strictly for research, re-use, and replication</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Enables crop monitoring, yield prediction, and agricultural decision support systems for smallholder farmers.</t>
+          <t>The AI application analyzes historical smart meter electricity consumption data and household survey information to identify anomalous energy-use patterns associated with potentially inefficient appliance usage. It operates on six-hour interval load profiles collected over approximately one year from 1,438 households and produces outputs such as household-level anomaly scores, ranked lists of high-risk households, and comparative anomaly detection results across multiple modeling strategies. The system detects unusual consumption behavior using LSTM-based autoencoders, including a global model, cluster-based models derived from appliance usage patterns, and group-specific models based on socio-economic class. In the absence of labeled ground truth, model performance is evaluated using proxy indicators such as appliance age, household built year, power factor, and nighttime load ratio, both individually and in combination.  Limitations include the lack of true anomaly labels and potential bias introduced by proxy-based validation. The model is implemented using standard AI and data analysis tools (Python, TensorFlow/PyTorch) and can be run on consumer-grade hardware without specialized infrastructure. The framework is scalable, reproducible, and suitable for integration into utility analytics workflows to support evidence-based energy efficiency interventions.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>This dataset can be used to develop AI applications for crop monitoring, yield estimation, damage assessment, and agricultural advisory services. It supports the development of precision agriculture tools specifically designed for smallholder farming systems.</t>
+          <t xml:space="preserve">This dataset and AI system can be used immediately by energy utilities, researchers, and policymakers to analyze smart meter data and identify households with potentially inefficient electricity usage, enabling targeted energy audits, awareness programs, or appliance replacement initiatives without requiring appliance-level sub-metering. However, given the contextual nature of the dataset (data from one provider within Sri Lanka), real-life applications are best developed in parternships with Lanka Electricity Company (LECO). Lanka Electricity Company has also shared interest in using this in demand forecasting and planning.
+</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
+          <t>The dataset is publicly available under the Creative Commons Attribution 4.0 International (CC BY 4.0) license</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Authors: Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+          <t xml:space="preserve">Lanka Electricity Company https://www.leco.lk/index_e.php </t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
+          <t>Merl Chandana</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3463,46 +3813,62 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Computer Vision, Remote Sensing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>agriculture-banner.jpg</t>
+          <t>https://drive.google.com/file/d/1zom3RRACTZrXGBB1bDRfz0nw2ZoRCgtZ/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Manuscript under review Descriptor: Residential Electricity Consumption Dataset for Sri Lanka (RECON-SL) submitted to IEEE Data Descriptions</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>The dataset is publicly available under the Creative Commons Attribution 4.0 International (CC BY 4.0) license. This means that third parties are free to access, use, share, and modify the dataset, provided they give appropriate credit.</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ui_36</t>
+          <t>ui_37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
+          <t>Eyes on the Ground Image Data</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Corrected Geolocations for Eastern Africa Crop Cut Yield Estimation</t>
+          <t>Eyes on the Ground Image Data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>This dataset includes corrected geolocations of fields, improving the usability of the most expansive Eastern Africa crop cut yield estimation. Collected by the non-profit One Acre Fund from 2015 – 2019, this dataset covers major crop producing regions in Kenya, Rwanda, and Tanzania. It enables accurate yield mapping and agricultural monitoring across East Africa.</t>
+          <t>This machine learning dataset of smallholder farmer's fields includes georeferenced crop images along with labels on input use, crop management, phenology, crop damage, and yields, collected across 8 counties in Kenya. This dataset enables the development of AI systems to monitor crop conditions, predict yields, and support agricultural decision-making for smallholder farmers.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/140eLeY3Z_JALFa0B77ZTP9gFt-mSPWXl</t>
-        </is>
-      </c>
+          <t>https://radiantearth.github.io/stac-browser/#/external/raw.githubusercontent.com/khufkens/EotG_data/main/release_v1/EotG_images/catalog.json</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -3510,49 +3876,25 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tabular, Geospatial/Remote Sensing</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>One Acre Fund</t>
+          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Kenya, Rwanda, Tanzania</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Corrected geolocations of maize fields with yield data from 2015-2019 covering major crop producing regions in Kenya, Rwanda, and Tanzania. Most expansive Eastern Africa crop cut yield estimation dataset.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Enables accurate yield mapping, crop monitoring, and agricultural planning across East Africa using corrected geolocation data.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>This dataset can be used for yield prediction modeling, agricultural policy planning, food security assessments, and developing precision agriculture applications for East African smallholder farmers.</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>One Acre Fund</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>One Acre Fund</t>
-        </is>
-      </c>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3560,96 +3902,76 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Agricultural Informatics, Geospatial Analysis</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ui_37</t>
+          <t>ui_38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
+          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IoT Water Quality Management for Aquaponics Systems</t>
+          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>This project built a remotely monitored and controlled Internet of Things (IoT) fish pond water quality management system for the generation of labeled datasets both for conventional ponds and the aquaponic pond systems. It enables monitoring and optimization of water quality parameters for sustainable aquaculture.</t>
+          <t>This dataset includes corrected geolocations of fields, improving the usability of the most expansive Eastern Africa crop cut yield estimation. Collected by the non-profit One Acre Fund from 2015 – 2019, this dataset covers major crop producing regions in Kenya, Rwanda, and Tanzania. It enables accurate yield mapping and agricultural monitoring across East Africa.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/ogbuokiriblessing/sensor-based-aquaponics-fish-pond-datasets</t>
-        </is>
-      </c>
+          <t>https://drive.google.com/drive/folders/140eLeY3Z_JALFa0B77ZTP9gFt-mSPWXl</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tabular, IoT Sensor Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
+          <t>One Acre Fund</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>IoT sensor data from fish pond water quality monitoring systems including conventional ponds and aquaponic systems. Labeled datasets for water quality parameters monitoring.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Enables automated water quality monitoring, predictive maintenance for aquaculture systems, and optimization of aquaponics operations.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop IoT-based monitoring systems for aquaculture, predictive models for water quality management, and automated control systems for sustainable fish farming operations.</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Authors: Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
-        </is>
-      </c>
+          <t>Kenya, Rwanda, Tanzania</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3657,96 +3979,76 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>IoT, Aquaculture Technology</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ui_38</t>
+          <t>ui_39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
+          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI-Powered Crop Disease Detection for Food Security Crops</t>
+          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>This dataset contains a repository of image and spectrometry datasets for five main food security crops in Sub-Saharan Africa: cassava, maize, beans, bananas, and cocoa. Collected and curated in collaboration with the in-country agricultural experts, the datasets deliver a wide range of machine learning applications, including classification, object detection, early crop disease detection, and spatial analysis. The team collected and annotated 127,046 images and 39,300 spectral data points.</t>
+          <t>This project built a remotely monitored and controlled Internet of Things (IoT) fish pond water quality management system for the generation of labeled datasets both for conventional ponds and the aquaponic pond systems. It enables monitoring and optimization of water quality parameters for sustainable aquaculture.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://dataverse.harvard.edu/dataverse/airlabug/</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/ogbuokiriblessing/sensor-based-aquaponics-fish-pond-datasets</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Images, Spectrometry Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
+          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Uganda, Tanzania, Ghana</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>127,046 images and 39,300 spectral data points for cassava, maize, beans, bananas, and cocoa. Annotated datasets for classification, object detection, early crop disease detection, and spatial analysis.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Enables crop disease classification, early detection systems, pest identification, and spatial analysis for food security crops in Sub-Saharan Africa.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop mobile applications for crop disease diagnosis, early warning systems for pest outbreaks, and precision agriculture tools for smallholder farmers growing food security crops.</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Authors: Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3754,96 +4056,76 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Computer Vision, Agricultural Technology</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ui_39</t>
+          <t>ui_40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
+          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pastoral Community Land Use and Livestock Movement Patterns</t>
+          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>This dataset focuses on locations with predominantly pastoral communities in northern Tanzania to identify fine and broad-scale movements of livestock and land use patterns and to understand how these relate to communal conflicts. It is a high-quality, accurate and labeled dataset containing detailed information on ~ 2000 communal resources (e.g., rangelands, water points, and dips) and their use patterns for over 220 villages across four large districts in northern Tanzania, representative of pastoral systems of livestock production in East Africa.</t>
+          <t>This dataset contains a repository of image and spectrometry datasets for five main food security crops in Sub-Saharan Africa: cassava, maize, beans, bananas, and cocoa. Collected and curated in collaboration with the in-country agricultural experts, the datasets deliver a wide range of machine learning applications, including classification, object detection, early crop disease detection, and spatial analysis. The team collected and annotated 127,046 images and 39,300 spectral data points.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>http://dtlp.nottech.co.tz/index.html</t>
-        </is>
-      </c>
+          <t>https://dataverse.harvard.edu/dataverse/airlabug/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing, Tabular</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Gladness Mwanga (gladnessg@nm-aist.ac.tz), Divine Ekwem (divine.ekwem@glasgow.ac.uk)</t>
+          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Detailed information on ~2000 communal resources and use patterns for over 220 villages across four districts in northern Tanzania. Covers rangelands, water points, dips and livestock movement patterns.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Enables land use planning, conflict prediction, livestock migration route identification, and infrastructure placement for pastoral communities.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop tools for community land use planning, conflict early warning systems, infrastructure development planning for pastoral areas, and sustainable rangeland management systems.</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Authors: Dr. Divine Ekwem (University of Glasgow), Gladness Mwanga (Nelson Mandela African Institution of Science and Technology), Professor Gabriel Shirima (Nelson Mandela African Institution of Science and Technology), Professor Mizech Chagunda (University of Hohenheim)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Dr. Divine Ekwem, Gladness Mwanga, Professor Gabriel Shirima, Professor Mizech Chagunda</t>
-        </is>
-      </c>
+          <t>Uganda, Tanzania, Ghana</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3851,198 +4133,153 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Geospatial Analysis, Land Use Planning</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ui_40</t>
+          <t>ui_41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
+          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yield Prediction and Crop Insurance for Smallholder Farmers</t>
+          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>The project created labeled yield estimates from 3000 farmers, and was used to train prediction models for yield prediction across the country, consequently using the dataset to generate high resolution crop mask layers for the different value chains. The yield prediction models were enhanced by other biophysical datasets ranging from soil properties and climate related indicators. The datasets proved a concept of scalable machine learning models training, which may be able to respond more appropriately and cost-effectively to agricultural stressors.</t>
+          <t>This dataset focuses on locations with predominantly pastoral communities in northern Tanzania to identify fine and broad-scale movements of livestock and land use patterns and to understand how these relate to communal conflicts. It is a high-quality, accurate and labeled dataset containing detailed information on ~ 2000 communal resources (e.g., rangelands, water points, and dips) and their use patterns for over 220 villages across four large districts in northern Tanzania, representative of pastoral systems of livestock production in East Africa.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://zenodo.org/records/10060610</t>
-        </is>
-      </c>
+          <t>http://dtlp.nottech.co.tz/index.html</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tabular, Geospatial/Remote Sensing</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Seth Odhiambo (sodhiambo@pula.io)</t>
+          <t>Gladness Mwanga (gladnessg@nm-aist.ac.tz), Divine Ekwem (divine.ekwem@glasgow.ac.uk)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Labeled yield estimates from 3000 farmers with biophysical datasets including soil properties and climate indicators. High resolution crop mask layers for different value chains.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Enables yield prediction models, crop insurance products, and agricultural risk assessment for smallholder farmers accessing financial services.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop crop insurance products, yield prediction systems, agricultural lending platforms, and risk assessment tools for financial institutions serving smallholder farmers.</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Pula Advisors</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Seth Odhiambo, Pula Advisors</t>
-        </is>
-      </c>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Dataset &gt; Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Agricultural Technology, Financial Technology</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ui_41</t>
+          <t>ui_42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
+          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Continental Crop Field Boundary Detection</t>
+          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>This dataset provides continent-wide crop field labels for Africa, improving the availability and use of crop field boundary (parcel) maps. It contains 42,403 annotated geospatial polygons indicating the boundaries of individual crop fields spanning the years 2017-2023. This enables the development of automated field boundary detection systems for agricultural monitoring across Africa.</t>
+          <t>The project created labeled yield estimates from 3000 farmers, and was used to train prediction models for yield prediction across the country, consequently using the dataset to generate high resolution crop mask layers for the different value chains. The yield prediction models were enhanced by other biophysical datasets ranging from soil properties and climate related indicators. The datasets proved a concept of scalable machine learning models training, which may be able to respond more appropriately and cost-effectively to agricultural stressors.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://zenodo.org/records/11060871</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://github.com/agroimpacts/lacunalabels</t>
-        </is>
-      </c>
+          <t>https://zenodo.org/records/10060610</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mary Dziedzorm Afenyo (mary@farmerline.co), Lyndon Estes (lestes@clarku.edu), Primož Kovačič (primoz@spatialcollective.com)</t>
+          <t>Seth Odhiambo (sodhiambo@pula.io)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Multi-country Africa</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>42,403 annotated geospatial polygons of crop field boundaries spanning 2017-2023 across Africa. Continent-wide dataset for field boundary detection.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Enables automated crop field boundary detection, agricultural area estimation, and crop monitoring systems across Africa.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop automated field boundary detection systems, agricultural statistics generation, crop area estimation tools, and satellite-based monitoring systems for African agriculture.</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Farmerline, Clark University, Spatial Collective</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Wussah, A., Afenyo, M., Osei, A.K., Gathigi, M., Kovačič, P., Muhando, J., Addai, F., Akakpo, E.S., Allotey, M., Amkoya, P., Amponsem, E., Dadon, K.D., Gyan, V., Harrison X.G., Heltzel, E., Juma, C., Mdawida, R., Miroyo, A., Mucha, J., Mugami, J., Mwawaza, F., Nyarko, D., Oduor, P., Ohemeng, K., Segbefia, S.I.D., Tumbula, T., Wambua, F., Yeboah, F., Estes, L.D.</t>
-        </is>
-      </c>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4050,51 +4287,50 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Computer Vision, Remote Sensing</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>GitHub: https://github.com/agroimpacts/lacunalabels, AWS Open Data Registry: https://registry.opendata.aws/africa-field-boundary-labels/</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ui_42</t>
+          <t>ui_43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
+          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Crop Type Classification for Agricultural Decision Making</t>
+          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CropHarvest increases the understanding of the main types of food production in Sub-Saharan Africa and can help inform decision-making around agricultural development, early warning systems, and regional trade. It is a global, open-source remote sensing dataset for crop-type classification in Sub-Saharan Africa – specifically in Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, and Nigeria. The team expanded on an existing dataset to include new labeled data points, ground data for crop type mapping, street-level images, crowdsourced labeled images, and price data.</t>
+          <t>This dataset provides continent-wide crop field labels for Africa, improving the availability and use of crop field boundary (parcel) maps. It contains 42,403 annotated geospatial polygons indicating the boundaries of individual crop fields spanning the years 2017-2023. This enables the development of automated field boundary detection systems for agricultural monitoring across Africa.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://github.com/nasaharvest/cropharvest</t>
-        </is>
-      </c>
+          <t>https://zenodo.org/records/11060871</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
@@ -4102,151 +4338,102 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing, Images</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Catherine Nakalembe (cnakalem@umd.edu)</t>
+          <t>Mary Dziedzorm Afenyo (mary@farmerline.co), Lyndon Estes (lestes@clarku.edu), Primož Kovačič (primoz@spatialcollective.com)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, Nigeria</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Remote sensing dataset for crop-type classification across 12 Sub-Saharan African countries. Includes labeled data points, ground data, street-level images, and price data.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Enables crop type classification, agricultural development planning, early warning systems, and regional trade analysis for Sub-Saharan Africa.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop crop monitoring systems, early warning systems for food security, agricultural trade analysis tools, and policy support systems for agricultural development.</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>NASA Harvest, University of Maryland</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Tseng, G., Zvonkov, I., Nakalembe, C.L., Kerner, H.</t>
-        </is>
-      </c>
+          <t>Multi-country Africa</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Dataset &gt; Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Remote Sensing, Agricultural Informatics</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/record/7257688#.ZFATwuzMI0Q</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ui_43</t>
+          <t>ui_44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
+          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Drone-Based Crop Yield Estimation for Tree Crops</t>
+          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa. It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions.</t>
+          <t>CropHarvest increases the understanding of the main types of food production in Sub-Saharan Africa and can help inform decision-making around agricultural development, early warning systems, and regional trade. It is a global, open-source remote sensing dataset for crop-type classification in Sub-Saharan Africa – specifically in Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, and Nigeria. The team expanded on an existing dataset to include new labeled data points, ground data for crop type mapping, street-level images, crowdsourced labeled images, and price data.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
-        </is>
-      </c>
+          <t>https://github.com/nasaharvest/cropharvest</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Images, Drone Imagery</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Darlington Akogo (darlington@gudra-studio.com)</t>
+          <t>Catherine Nakalembe (cnakalem@umd.edu)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ghana, Uganda</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees. Supports yield estimation, crop type detection, fruit detection and counting, and maturity stage detection.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Enables automated yield estimation, harvest planning, fruit quality assessment, and business decision support for tree crop farmers.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>This dataset can be used to develop mobile applications for yield estimation, harvest timing optimization tools, fruit quality assessment systems, and agricultural business planning platforms for tree crop farmers.</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>KaraAgro AI, Makerere AI Lab</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Darlington Akogo, Cyril Akafia, Harriet Fiagbor, Stephen Torkpo, Christian Kusi, Joyce Nakatumba-Nabende</t>
-        </is>
-      </c>
+          <t>Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, Nigeria</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4254,96 +4441,76 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Computer Vision, Drone Technology</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>agriculture-banner.jpg</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ui_44</t>
+          <t>ui_45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
+          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rabies diagnosis, outbreak prediction, resource allocation</t>
+          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>This dataset will help in the real-time and remote diagnosis of rabies disease for humans and animals in low-resource settings. A time series approach can be applied to the outbreak dataset to predict the number of rabies cases likely to occur within an area after a given time interval. This approach can help with resource mobilization, too, such as identifying the number of vaccines required in a specific area at a given time. The number of observations from the two datasets is 12,684. There are three datasets for rabies diagnosis for animals and humans, with 7,081 and 4,585 observations, respectively. In the outbreak prediction dataset, 1,018 observations were accounted for.</t>
+          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa. It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://zenodo.org/records/10068758</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Machine Learning Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Asa Emmanuel: asakalonga@gmail.com, Kennedy Lushasi: klushasi@ihi.or.tz</t>
+          <t>Darlington Akogo (darlington@gudra-studio.com)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>12,684 observations</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Three datasets: animal diagnosis (7,081 observations), human diagnosis (4,585 observations), outbreak prediction (1,018 observations)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Disease diagnosis and prediction</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Asa Emmanuel, Rebecca Chaula, Deogratias Mzurikwao, Joel Changalucha, Kennedy Lushasi</t>
-        </is>
-      </c>
+          <t>Ghana, Uganda</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4351,46 +4518,50 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ui_45</t>
+          <t>ui_46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Childhood Malnutrition in Chile</t>
+          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Child malnutrition analysis, health cost estimation, biopsychosocial determinant identification</t>
+          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>This data repository will evaluate factors that contribute to child malnutrition in Chile and children's nutritional status, as well as the associated costs. The focus at this stage is on estimating health costs associated with child malnutrition and identifying biopsychosocial determinants that lead to it.</t>
+          <t>This dataset will help in the real-time and remote diagnosis of rabies disease for humans and animals in low-resource settings. A time series approach can be applied to the outbreak dataset to predict the number of rabies cases likely to occur within an area after a given time interval. This approach can help with resource mobilization, too, such as identifying the number of vaccines required in a specific area at a given time. The number of observations from the two datasets is 12,684. There are three datasets for rabies diagnosis for animals and humans, with 7,081 and 4,585 observations, respectively. In the outbreak prediction dataset, 1,018 observations were accounted for.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://goblab.uai.cl/proyecto-reduccion-de-la-malnutricion-infantil-en-chile/</t>
-        </is>
-      </c>
+          <t>https://zenodo.org/records/10068758</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4398,49 +4569,25 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Health Policy Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Maria Paz Hermosilla: paz.hermosilla@uai.cl</t>
+          <t>Asa Emmanuel: asakalonga@gmail.com, Kennedy Lushasi: klushasi@ihi.or.tz</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Sensitive data with controlled access for relevant research projects</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Child health and nutrition policy</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Controlled Access</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Ministry of Health, Chile; GobLab, School of Government, Adolfo IbaÃ±ez University, Chile; FONASA; Health Superintendency, JUNAEB</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Ministry of Health Chile, GobLab, FONASA, Health Superintendency, JUNAEB</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4448,46 +4595,50 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Statistical Analysis</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Controlled Access</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ui_46</t>
+          <t>ui_47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lacuna Malaria Datasets</t>
+          <t>Childhood Malnutrition in Chile</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Malaria diagnosis, object detection research, medical imaging</t>
+          <t>Childhood Malnutrition in Chile</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>This dataset will aid in the diagnosis of malaria. The dataset contains annotated images of blood samples collected in Uganda and Ghana with objects of interest, including parasites and white blood cells. It significantly increases the number of available microscopy images â€“ including metadata â€“ by 6,000 thick blood slides and 2,000 thin blood slides for use in object detection research and other areas of inquiry.</t>
+          <t>This data repository will evaluate factors that contribute to child malnutrition in Chile and children's nutritional status, as well as the associated costs. The focus at this stage is on estimating health costs associated with child malnutrition and identifying biopsychosocial determinants that lead to it.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/VEADSE</t>
-        </is>
-      </c>
+          <t>https://goblab.uai.cl/proyecto-reduccion-de-la-malnutricion-infantil-en-chile/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4495,49 +4646,25 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Medical Imaging Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Rose Nakasi: g.nakasi.rose@gmail.com or rose.nakasi@mak.ac.ug</t>
+          <t>Maria Paz Hermosilla: paz.hermosilla@uai.cl</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Uganda, Ghana</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>8,000 blood slides (6,000 thick + 2,000 thin)</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Annotated microscopy images with parasites and white blood cells, thick and thin blood slides</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Malaria diagnosis and medical imaging</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Makerere Artificial Intelligence Lab; minoHealth</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Makerere Artificial Intelligence Lab, minoHealth</t>
-        </is>
-      </c>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4545,46 +4672,50 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Object Detection</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ui_47</t>
+          <t>ui_48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
+          <t>Lacuna Malaria Datasets</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mortality risk prediction, postoperative recovery prediction, anesthesia practice analysis</t>
+          <t>Lacuna Malaria Datasets</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>This dataset can be used to identify patterns of intraoperative anesthesia practice and predict postoperative length of stay and risk of mortality based on intraoperative variables. It includes 2,066 intraoperative anesthesia records from two academic centers in sub-Saharan Africa. The team photographed completed intraoperative anesthesia records using a smartphone, de-identified the images, and securely uploaded them to a HIPAA-compliant server. Using a combination of computer vision AI and manual extraction techniques, the team collected comprehensive intraoperative data: demographic data, medication data, hemodynamic data, physiological data, anesthesia type, surgery type, postoperative length of stay, and 30-day postoperative mortality.</t>
+          <t>This dataset will aid in the diagnosis of malaria. The dataset contains annotated images of blood samples collected in Uganda and Ghana with objects of interest, including parasites and white blood cells. It significantly increases the number of available microscopy images â€“ including metadata â€“ by 6,000 thick blood slides and 2,000 thin blood slides for use in object detection research and other areas of inquiry.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://portal.ithriv.org/#/public_commons/project/d9fc062c-64c9-4481-80e7-3db4aba17e00</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/VEADSE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4592,49 +4723,25 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Clinical Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Bhiken Naik: bin4n@uvahealth.org</t>
+          <t>Rose Nakasi: g.nakasi.rose@gmail.com or rose.nakasi@mak.ac.ug</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2,066 intraoperative anesthesia records</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Comprehensive intraoperative data including demographics, medications, hemodynamics, physiology, anesthesia/surgery types, outcomes</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Anesthesia and surgical outcomes</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>University of Virginia; School of Medicine and Pharmacy, University of Rwanda and King Faisal Hospital, African Health Sciences University; Safe Surgery South Africa</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Bhiken Naik, Paulin Banguti, Hyla Kluyts, Ryan Folks</t>
-        </is>
-      </c>
+          <t>Uganda, Ghana</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4642,46 +4749,50 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Predictive Modeling</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ui_48</t>
+          <t>ui_49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
+          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brain tumor segmentation, machine learning model development, neurological disease management</t>
+          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>The BraTS-Africa dataset is an aggregation of magnetic resonance imaging (MRI) scans from six centers in Nigeria aimed at providing a public dataset for the development of machine-learning solutions for the management of brain tumors in African patients. This dataset serves as a starting framework for future expansion in other regions of Africa. The team processed and annotated a total of 584 images from 146 patient scans. Ninety-five of these scans are presumed to have diffuse glioma, and 51 of them have other types of central nervous system (CNS) neoplasms. Expert radiologists annotated three distinct tumor sub-regions to delineate the enhancing tumor (ET), the necrotic tumor core (NCR), and the peritumoral oedematous/infiltrated tissue (ED) sub-regions.</t>
+          <t>This dataset can be used to identify patterns of intraoperative anesthesia practice and predict postoperative length of stay and risk of mortality based on intraoperative variables. It includes 2,066 intraoperative anesthesia records from two academic centers in sub-Saharan Africa. The team photographed completed intraoperative anesthesia records using a smartphone, de-identified the images, and securely uploaded them to a HIPAA-compliant server. Using a combination of computer vision AI and manual extraction techniques, the team collected comprehensive intraoperative data: demographic data, medication data, hemodynamic data, physiological data, anesthesia type, surgery type, postoperative length of stay, and 30-day postoperative mortality.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.cancerimagingarchive.net</t>
-        </is>
-      </c>
+          <t>https://portal.ithriv.org/#/public_commons/project/d9fc062c-64c9-4481-80e7-3db4aba17e00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4689,49 +4800,25 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Medical Imaging Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Udunna Anazodo: udunna.anazodo@mcgill.ca</t>
+          <t>Bhiken Naik: bin4n@uvahealth.org</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>584 images from 146 patient scans</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>MRI scans with expert annotations for three tumor sub-regions: enhancing tumor (ET), necrotic tumor core (NCR), peritumoral oedematous tissue (ED)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Neuroimaging and brain tumor analysis</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Medical Artificial Intelligence (MAI) Lab (Lagos, Nigeria); The National Hospital (Abuja, Nigeria); Lagos University Teaching Hospital; Lagos State University Teaching Hospital; NSIA-Kano Diagnostic Center; Federal Medical Centre (Umuahia, Nigeria); Lily Hospital (Benin, Nigeria); University of Pennsylvania (Philadelphia, USA); Indiana University (Indianapolis, USA); Scripps Clinic Medical Group (San Diego, USA); McGill University (Montreal, Canada)</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Maruf Adewole, Abiodun Fatade, Oluyemisi Toyobo, Farouk Dako, Udunna Anazodo, et al.</t>
-        </is>
-      </c>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4739,46 +4826,50 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Image Segmentation</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ui_49</t>
+          <t>ui_50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
+          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Parasite detection, diarrhea diagnosis, smartphone microscopy, rural healthcare</t>
+          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>This dataset helps to detect diarrhea-causing parasites in resource-limited rural areas, particularly across the Global South, where access to expensive diagnostic tools is limited. It contains approximately 400,000 microscopic slide images from water, vegetable, and stool samples from four different provinces across Nepal, making it one of the largest datasets of its kind. The team collected water samples from different sources (i.e., tap water, bottled water, lake, river, pond, stream, spring water, wetland, well, and borewell) and used seven different types of vegetables. Using the dataset and annotations available, this team trained different deep-learning models to automatically detect parasites, specifically Giardia and Cryptosporidium cysts.</t>
+          <t>The BraTS-Africa dataset is an aggregation of magnetic resonance imaging (MRI) scans from six centers in Nigeria aimed at providing a public dataset for the development of machine-learning solutions for the management of brain tumors in African patients. This dataset serves as a starting framework for future expansion in other regions of Africa. The team processed and annotated a total of 584 images from 146 patient scans. Ninety-five of these scans are presumed to have diffuse glioma, and 51 of them have other types of central nervous system (CNS) neoplasms. Expert radiologists annotated three distinct tumor sub-regions to delineate the enhancing tumor (ET), the necrotic tumor core (NCR), and the peritumoral oedematous/infiltrated tissue (ED) sub-regions.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://zenodo.org/records/13913469</t>
-        </is>
-      </c>
+          <t>https://www.cancerimagingarchive.net</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Health</t>
@@ -4786,49 +4877,25 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Medical Imaging Dataset</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Bishesh Khanal: bishesh.khanal@naamii.org.np</t>
+          <t>Udunna Anazodo: udunna.anazodo@mcgill.ca</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Approximately 400,000 microscopic slide images</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Images from water, vegetable, and stool samples captured using smartphone and brightfield microscopes, focused on Giardia and Cryptosporidium detection</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Parasitology and rural diagnostics</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Nepal Applied Mathematics and Informatics Institute for Research (NAAMII); Kathmandu Institute of Applied Science (KIAS); Nyaya Health Nepal, Bayalpata; Provincial Public Health Laboratory (PPHL)-Janakpur; Kathmandu Institute of Child Health (KIOCH)-Damak</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Bishesh Khanal, Udit Chandra Aryal, Safal Thapaliya, et al.</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4836,73 +4903,76 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Object Detection</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 International</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ui_50</t>
+          <t>ui_51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
+          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
+          <t>This dataset helps to detect diarrhea-causing parasites in resource-limited rural areas, particularly across the Global South, where access to expensive diagnostic tools is limited. It contains approximately 400,000 microscopic slide images from water, vegetable, and stool samples from four different provinces across Nepal, making it one of the largest datasets of its kind. The team collected water samples from different sources (i.e., tap water, bottled water, lake, river, pond, stream, spring water, wetland, well, and borewell) and used seven different types of vegetables. Using the dataset and annotations available, this team trained different deep-learning models to automatically detect parasites, specifically Giardia and Cryptosporidium cysts.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://thinkingmachines.github.io/project-cchain/</t>
-        </is>
-      </c>
+          <t>https://zenodo.org/records/13913469</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Climate Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Thinking Machines Data Science | data-for-development@thinkingmachin.es</t>
+          <t>Bishesh Khanal: bishesh.khanal@naamii.org.np</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Powered by: Thinking Machines Data Science, Inc., Epimetrics, Inc., Manila Observatory, Philippine Action for Community-led Shelter Initiatives, Inc.
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Patricia Anne Faustino, JC Albert Peralta, Veronica Marie Araneta, Dafrose Camille Bajaro, Abigail Moreno (Thinking Machines Data Science, Inc.), John Q. Wong, Anne Kathlyn Baladad, Luis Antonio Desquitado, Matthew Limlengco, Carlos Miguel Resurreccion (Epimetrics, Inc.), Faye Abigail Cruz, Dr. Julie Mae Dado, Leia Pauline Tonga (Manila Observatory), Ericka Lynne Nava (Philippine Action for Community-led Shelter Initiatives, Inc.)</t>
-        </is>
-      </c>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4910,46 +4980,50 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Climate Science</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>climate-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Added via climate dataset integration - extracted from climate.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ui_51</t>
+          <t>ui_52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
+          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
+          <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/collinsudanor/abattoir-air-quality-dataset/data</t>
-        </is>
-      </c>
+          <t>https://thinkingmachines.github.io/project-cchain/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -4957,31 +5031,25 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Climate Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Emmanuel Chukwuma | emmanuel.chukwuma@apse-ngo.org</t>
+          <t>Thinking Machines Data Science | data-for-development@thinkingmachin.es</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Powered by: Alliance for Progressive and Sustainable Environment
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Emmanuel Chukwuma, Uche Okonkwo, Chukwuemeka Umeobi, Jervis Okafor, Sixtus Ezenwankwo, Shadrach Ugwu, Awonge Precious, Cynthia Egdede, Esther Eyo (Alliance for Progressive and Sustainable Environment)</t>
-        </is>
-      </c>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4989,46 +5057,50 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Climate Science</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>climate-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Added via climate dataset integration - extracted from climate.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ui_52</t>
+          <t>ui_53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
+          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
+          <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.scidb.cn/en/detail?dataSetId=2b499b91a4464fffa9f60fc8b51da03e&amp;version=V2</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/datasets/collinsudanor/abattoir-air-quality-dataset/data</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5036,31 +5108,25 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Climate Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Emmanuel Chukwuma | emmanuel.chukwuma@apse-ngo.org</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Mauritius, Rodrigues, and Agalega Islands</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Powered by: University of Mauritius
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Yogesh Beeharry, Ravish Gokool, Yatindra Kumar Ramgolam, Aatish Chiniah (University of Mauritius)</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5068,46 +5134,50 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Climate Science</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>climate-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Added via climate dataset integration - extracted from climate.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ui_53</t>
+          <t>ui_54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
+          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
+          <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
-        </is>
-      </c>
+          <t>https://www.scidb.cn/en/detail?dataSetId=2b499b91a4464fffa9f60fc8b51da03e&amp;version=V2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5115,31 +5185,25 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Climate Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Fabienne Rafidiharinirina | f.rafidiharinirina@association-maidi.mg or assomaidi@gmail.com</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Madagascar</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Powered by: Madagascar Initiatives for Digital Innovation
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Fabienne Rafidiharinirina (Madagascar Initiatives for Digital Innovation)</t>
-        </is>
-      </c>
+          <t>Mauritius, Rodrigues, and Agalega Islands</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5147,46 +5211,50 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Climate Science</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>climate-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Added via climate dataset integration - extracted from climate.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ui_54</t>
+          <t>ui_55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
+          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
+          <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://zenodo.org/records/14195731</t>
-        </is>
-      </c>
+          <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action)</t>
@@ -5194,31 +5262,25 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Climate Data</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Dr. Zeeshan Shafiq | zeeshanshafiq@uetpeshawar.edu.pk</t>
+          <t>Fabienne Rafidiharinirina | f.rafidiharinirina@association-maidi.mg or assomaidi@gmail.com</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Powered by: CISNR UET Peshawar
-Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Zeeshan Shafiq, Prof. Dr. Gul Muhammad Khan, Engr. Sarmad Rafique, Engr. Muhammad Bilal Khan, Engr. Umer Khan, Engr. Mansoor Khan, Engr. Niaz Khan, Engr. Musa Khan, Engr. Abdul Moiz (CISNR UET Peshawar)</t>
-        </is>
-      </c>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5226,83 +5288,76 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Climate Science</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>climate-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Added via climate dataset integration - extracted from climate.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ui_55</t>
+          <t>ui_56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
+          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
+          <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://github.com/hausanlp/NaijaSenti</t>
-        </is>
-      </c>
+          <t>https://zenodo.org/records/14195731</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>SDG 13 (Climate Action)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
+          <t>Dr. Zeeshan Shafiq | zeeshanshafiq@uetpeshawar.edu.pk</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://github.com/hausanlp/NaijaSenti</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Powered by: Multiple authors collaboration
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, Pavel Brazdil (Multiple authors collaboration)</t>
-        </is>
-      </c>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5310,46 +5365,50 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ui_56</t>
+          <t>ui_57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
+          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
+          <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://github.com/asmelashteka/HornMT</t>
-        </is>
-      </c>
+          <t>https://github.com/hausanlp/NaijaSenti</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5357,36 +5416,25 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi</t>
+          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Horn of Africa (Ethiopia, Eritrea)</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://github.com/asmelashteka/HornMT</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Powered by: Horn of Africa research collaboration
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi (Horn of Africa research collaboration)</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5394,46 +5442,50 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ui_57</t>
+          <t>ui_58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
+          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
+          <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/6N5V1K</t>
-        </is>
-      </c>
+          <t>https://github.com/asmelashteka/HornMT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5441,36 +5493,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Owen McOnyango (Maseno University), Florence Indede (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
+          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Languages covered: Kiswahili, Dholuo, Luhya-Lubukusu, Luhya-Logooli, Luhya-Lumarachi</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Owen McOnyango, Florence Indede, Lilian D.A. Wanzare (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
+          <t>Horn of Africa (Ethiopia, Eritrea)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5478,46 +5519,50 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ui_58</t>
+          <t>ui_59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
+          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
+          <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/KLCKL5</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/6N5V1K</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5525,12 +5570,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
+          <t>Owen McOnyango (Maseno University), Florence Indede (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5538,23 +5583,12 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Languages covered: Dholuo, Luhya-Lumarachi, Luhya-Lulogooli, Luhya-Lubukusu</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Florence Indede, Owen McOnyango, Lilian D.A. Wanzare (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5562,46 +5596,50 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ui_59</t>
+          <t>ui_60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KenSpeech: Swahili Speech Transcriptions</t>
+          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
+          <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/YHXJSU</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/KLCKL5</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5609,12 +5647,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Dorcas Awino (University of Nairobi), Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (Maseno University), Owen McOnyango (Maseno University), Florence Indede (Maseno University)</t>
+          <t>Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5622,23 +5660,12 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Languages covered: Swahili</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Dorcas Awino, Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare, Barack Wanjawa, Owen McOnyango, Florence Indede (Maseno University), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5646,46 +5673,50 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ui_60</t>
+          <t>ui_61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
+          <t>KenSpeech: Swahili Speech Transcriptions</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KenSpeech: Swahili Speech Transcriptions</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
+          <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/NOAT0W</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/YHXJSU</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5693,12 +5724,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Lilian D.A Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (University of Nairobi), Lawrence Muchemi (University of Nairobi)</t>
+          <t>Dorcas Awino (University of Nairobi), Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (Maseno University), Owen McOnyango (Maseno University), Florence Indede (Maseno University)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5706,23 +5737,12 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Languages covered: Dholuo, Luhya-Lumarachi, Luhya-Lubukusu, Luhya-Lulogooli</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Powered by: Maseno University, University of Nairobi, Africa Nazarene University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lilian D.A Wanzare, Florence Indede, Owen McOnyango (Maseno University), Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5730,46 +5750,50 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ui_61</t>
+          <t>ui_62</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
+          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
+          <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/OTL0LM</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/NOAT0W</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5777,12 +5801,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Barack Wanjawa (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
+          <t>Lilian D.A Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (University of Nairobi), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5790,23 +5814,12 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Languages covered: Swahili</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Powered by: University of Nairobi, Maseno University, Africa Nazarene University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Barack Wanjawa, Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare, Florence Indede, Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5814,46 +5827,50 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ui_62</t>
+          <t>ui_63</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
+          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
+          <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
-        </is>
-      </c>
+          <t>https://doi.org/10.7910/DVN/OTL0LM</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5861,36 +5878,25 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
+          <t>Barack Wanjawa (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Africa (Multi-country)</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Powered by: Multiple collaborating institutions
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
-        </is>
-      </c>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5898,46 +5904,50 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ui_63</t>
+          <t>ui_64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
+          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
+          <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://github.com/masakhane-io/lafand-mt</t>
-        </is>
-      </c>
+          <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -5945,7 +5955,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5958,70 +5968,59 @@
           <t>Africa (Multi-country)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://github.com/masakhane-io/lafand-mt</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Powered by: Multiple collaborating institutions
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ui_64</t>
+          <t>ui_65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
+          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
+          <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://github.com/masakhane-io/masakhane-pos</t>
-        </is>
-      </c>
+          <t>https://github.com/masakhane-io/lafand-mt</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6029,7 +6028,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6042,70 +6041,59 @@
           <t>Africa (Multi-country)</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://github.com/masakhane-io/masakhane-pos</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Powered by: Multiple collaborating institutions
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>David Ifeoluwa Adelani, Multiple collaborators (Multiple collaborating institutions)</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ui_65</t>
+          <t>ui_66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
+          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
+          <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
-        </is>
-      </c>
+          <t>https://github.com/masakhane-io/masakhane-pos</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6113,83 +6101,72 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Dennis Asamoah Owusu, DOWUSU@ASHESI.EDU.GH</t>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Powered by: Ashesi University and collaborating institutions
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Dennis Asamoah Owusu, Multiple collaborators (Ashesi University and collaborating institutions)</t>
-        </is>
-      </c>
+          <t>Africa (Multi-country)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ui_66</t>
+          <t>ui_67</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
+          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
+          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
-        </is>
-      </c>
+          <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6197,83 +6174,72 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Gerald Nweya (GERALDNWEYA@GMAIL.COM) and Emeka Onwuegbuzia (EONWUEGBUZIA@GMAIL.COM)</t>
+          <t>Dennis Asamoah Owusu, DOWUSU@ASHESI.EDU.GH</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Powered by: Igbo NLP research collaboration
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Gerald Nweya, Emeka Onwuegbuzia (Igbo NLP research collaboration)</t>
-        </is>
-      </c>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ui_67</t>
+          <t>ui_68</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
+          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
+          <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://robotsmali-ai.github.io/datasets/</t>
-        </is>
-      </c>
+          <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6281,83 +6247,72 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Christopher Homan, christopher.m.homan.phd@gmail.com</t>
+          <t>Gerald Nweya (GERALDNWEYA@GMAIL.COM) and Emeka Onwuegbuzia (EONWUEGBUZIA@GMAIL.COM)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Mali/France</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Languages covered: Bambara, French</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Powered by: Multi-institutional collaboration
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Allahsera Auguste Tapo, Michael Leventhal, Valentin Vydrin, Sebastian Diarra, Marcos Zampieri, Emily Prud'Hommeaux, Jean Jacque Méric, Christopher Homan (Multi-institutional collaboration)</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ui_68</t>
+          <t>ui_69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Makerere University NLP Datasets</t>
+          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
+          <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://dataverse.harvard.edu/dataverse/makerereuniversitylacuna</t>
-        </is>
-      </c>
+          <t>https://robotsmali-ai.github.io/datasets/</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6365,78 +6320,72 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Andrew Katumba | andrew.katumba@mak.ac.ug</t>
+          <t>Christopher Homan, christopher.m.homan.phd@gmail.com</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Uganda, Tanzania, Kenya</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Powered by: Makerere University, Maseno University, TYD Innovation Incubator
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Katumba Andrew, Nakatumba-Nabende Joyce, Babirye Claire, Mukiibi Jonathan, Tusubira Jeremy, Bateesa Tobias, Wairagala Eric Peter, Fridah Katushemererwe, Mutebi Chodrine, Nabende Peter, Sentanda Medadi, Ssenkungu Ivan (Makerere University), Wanzare Lilian (Maseno University), Davis David (TYD Innovation Incubator)</t>
-        </is>
-      </c>
+          <t>Mali/France</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ui_69</t>
+          <t>ui_70</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
+          <t>Makerere University NLP Datasets</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Makerere University NLP Datasets</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
+          <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://github.com/csikasote/bigc</t>
-        </is>
-      </c>
+          <t>https://dataverse.harvard.edu/dataverse/makerereuniversitylacuna</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6444,83 +6393,72 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Claytone Sikasote | claytonsikasote@gmail.com</t>
+          <t>Andrew Katumba | andrew.katumba@mak.ac.ug</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>https://github.com/csikasote/bigc</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Powered by: University of Zambia, George Mason University
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Claytone Sikasote, Eunice Mukonde – Mulenga (University of Zambia), Md Mahfuz Ibn Alam, Antonios Anastasopoulos (George Mason University)</t>
-        </is>
-      </c>
+          <t>Uganda, Tanzania, Kenya</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ui_70</t>
+          <t>ui_71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KALLAAMA</t>
+          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
+          <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://github.com/gauthelo/kallaama-speech-dataset</t>
-        </is>
-      </c>
+          <t>https://github.com/csikasote/bigc</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6528,78 +6466,72 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Aminata Ndiaye | amina.ndiaye@jokalante.com and Elodie Gauthier | elodie.gauthier@orange.com</t>
+          <t>Claytone Sikasote | claytonsikasote@gmail.com</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Powered by: Jokalante, Dakar, Senegal, Orange Innovation, Lannion, France, Ecole Polytechnique de Thiès, Senegal
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Aminata Ndiaye Diallo (Jokalante, Dakar, Senegal), Elodie Gauthier (Orange Innovation, Lannion, France), Abdoulaye Guissé (Ecole Polytechnique de Thiès, Senegal)</t>
-        </is>
-      </c>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ui_71</t>
+          <t>ui_72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NaijaVoices: Our Language is Our Strength</t>
+          <t>KALLAAMA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>KALLAAMA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
+          <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://naijavoices.com/membership#membership_tiers</t>
-        </is>
-      </c>
+          <t>https://github.com/gauthelo/kallaama-speech-dataset</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6607,88 +6539,72 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>info@naijavoices.com</t>
+          <t>Aminata Ndiaye | amina.ndiaye@jokalante.com and Elodie Gauthier | elodie.gauthier@orange.com</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Languages covered: Hausa, Igbo, and Yoruba</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Powered by: NaijaVoices project
-Catalyzed by: Lacuna-Fund / Meridian (Language-call) &amp; FAIR Forward - AI for All
-Financed by: BMZ</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Multiple contributors (NaijaVoices project)</t>
-        </is>
-      </c>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>language-banner</t>
-        </is>
-      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Added via language dataset integration - extracted from language.html</t>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ui_72</t>
+          <t>ui_73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
+          <t>NaijaVoices: Our Language is Our Strength</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>NaijaVoices: Our Language is Our Strength</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AFRIDOC-MT is a document-level and multi-way translation dataset from English into five African languages — Amharic, Hausa, Swahili, Yorùbá, and Zulu. The dataset comprises 334 health and 271 information technology news documents, all of which were human-translated from English to these languages. Each domain has at least 10,000 parallel sentences per language pair and supports multiway translation, allowing translation not only between English and the African languages but also among the African languages themselves. This dataset can be used to evaluate the ability of existing neural machine translation (NMT) models and large language models (LLMs) to translate at the document level.</t>
+          <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://github.com/masakhane-io/afridoc-mt</t>
-        </is>
-      </c>
+          <t>https://naijavoices.com/membership#membership_tiers</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6696,111 +6612,72 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Jesujoba O. Alabi | jalabi@lsv.uni-saarland.de</t>
+          <t>info@naijavoices.com</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Multiple African Countries</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Languages covered: Amharic, Hausa, Swahili, Yorùbá, and Zulu</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Jesujoba O. Alabi (Saarland University), Israel Abebe, Miaoran Zhang, Dawei Zhu, Dietrich Klakow, Cristina España-Bonet (DFKI), Rachel Bawden (INRIA), David Adelani (McGill University), Clement Oyeleke Odoje, Idris Akinade (University of Ibadan), and others</t>
-        </is>
-      </c>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ui_73</t>
+          <t>ui_74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
+          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>This team has developed five conversational AI and benchmark datasets for 16 languages across the African continent: AfriXNLI (natural language inference), AfriMMLU (knowledge-based multi-choice questions), AfriMGSM (grade school mathematics), AfriIntent (intent classification), and AfriSlot (slot classification). These datasets cover languages including Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu. These text-only datasets are useful for conversational chatbots in real-life applications such as banking, restaurants, travel agencies, and more.</t>
+          <t>AFRIDOC-MT is a document-level and multi-way translation dataset from English into five African languages — Amharic, Hausa, Swahili, Yorùbá, and Zulu. The dataset comprises 334 health and 271 information technology news documents, all of which were human-translated from English to these languages. Each domain has at least 10,000 parallel sentences per language pair and supports multiway translation, allowing translation not only between English and the African languages but also among the African languages themselves. This dataset can be used to evaluate the ability of existing neural machine translation (NMT) models and large language models (LLMs) to translate at the document level.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://github.com/masakhane-io/masakhane-nlu</t>
-        </is>
-      </c>
+          <t>https://github.com/masakhane-io/afridoc-mt</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6808,12 +6685,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>David Adelani | david.adelani@mila.quebec</t>
+          <t>Jesujoba O. Alabi | jalabi@lsv.uni-saarland.de</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6821,98 +6698,59 @@
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Languages covered: Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>David Ifeoluwa Adelani (McGill University &amp; Mila), Hao Yu, Andiswa Bukula, Mmasibidi Setaka, Rooweither Mabuya (SADiLaR), and Masakhane Research Foundation</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ui_74</t>
+          <t>ui_75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lacuna PII Multilingual Dataset</t>
+          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>This dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The team collected 3,000 sentences for both Kanuri and Hausa, 5,000 for Lumasaba, and 4,000 for Luganda. Potential use cases include named entity recognition (NER), text classification, privacy-preserving data analysis and research, language modeling, machine translation, and linguistic research. The team aimed to curate a dataset that is gender inclusive, and their work highlighted the need for standardized guidelines for annotating low-resourced languages.</t>
+          <t>This team has developed five conversational AI and benchmark datasets for 16 languages across the African continent: AfriXNLI (natural language inference), AfriMMLU (knowledge-based multi-choice questions), AfriMGSM (grade school mathematics), AfriIntent (intent classification), and AfriSlot (slot classification). These datasets cover languages including Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu. These text-only datasets are useful for conversational chatbots in real-life applications such as banking, restaurants, travel agencies, and more.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7910/DVN/CGHWZE</t>
-        </is>
-      </c>
+          <t>https://github.com/masakhane-io/masakhane-nlu</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -6920,12 +6758,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Andrew Katumba | katumba@mak.ac.ug, Milena Haykowska | milena.haykowska@clearglobal.org, Peter Nabende | nabende@gmail.com</t>
+          <t>David Adelani | david.adelani@mila.quebec</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6933,93 +6771,59 @@
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Languages covered: Luganda, Lumasaba, Hausa, and Kanuri</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Andrew Katumba (Makerere University), Jenifer Winfred Namuyanja, Nakakande Bridget Cecile (Marconi Research Lab), Joyce Nakatumba-Nabende, Ann Lisa Nabiryo, Peter Nabende, Eric Peter Wairagala (Makerere AI Lab), Milena Haykowska, Andrew Bredenkamp, Mariam Mohanna, Alp Öktem, Etienne de Crecy (Clear Global)</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ui_75</t>
+          <t>ui_76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
+          <t>Lacuna PII Multilingual Dataset</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>Lacuna PII Multilingual Dataset</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AfriHate is a hate and offensive speech corpus for 15 African languages: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya. The dataset annotates tweets using "offensive," "hateful," and "normal" classes, with target classes such as politics, ethnicity, gender, religion, and disability. The team also created AfriEmotion for emotion detection. Overall, they collected and annotated 10,000 instances each for hate speech and emotion detection per language, making 150,000 annotated observations. This is the first publicly available dataset for hate and offensive speech detection in these target languages.</t>
-        </is>
-      </c>
+          <t>This dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The team collected 3,000 sentences for both Kanuri and Hausa, 5,000 for Lumasaba, and 4,000 for Luganda. Potential use cases include named entity recognition (NER), text classification, privacy-preserving data analysis and research, language modeling, machine translation, and linguistic research. The team aimed to curate a dataset that is gender inclusive, and their work highlighted the need for standardized guidelines for annotating low-resourced languages.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/CGHWZE</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -7027,12 +6831,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Abinew Ali Ayele | abinewaliayele@gmail.com, Seid Muhie Yiman | muhie.yimam@uni-hamburg.de, Shamsuddeen Hassan Muhammad | muhammad@imperial.ac.uk</t>
+          <t>Andrew Katumba | katumba@mak.ac.ug, Milena Haykowska | milena.haykowska@clearglobal.org, Peter Nabende | nabende@gmail.com</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7040,93 +6844,55 @@
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Languages covered: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Abinew Ali Ayele, Esubalew Alemneh Jalew (Bahir Dar University), Shamsuddeen Hassan Muhammad (Bayero University Kano, Imperial College London), Ibrahim Said Ahmad, Idris Abdulmumin (Ahmadu Bello University), Seid Muhie Yimam (University of Hamburg)</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ui_76</t>
+          <t>ui_77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ethio Speech Corpora</t>
+          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ethio Speech Corpora comprises over 391 hours of recorded audio in six Ethiopian languages: Amharic (68 hours), Tigrigna (62 hours), Oromo (70 hours), Somali (56 hours), Afar (68 hours), and Sidama (68 hours). This project is a valuable resource for developing well-performing automatic speech recognition (ASR) systems for these languages in monolingual, multilingual, and cross-lingual setups. Use cases include dictation systems, transcription systems, assistive technologies, spoken dialogue systems, speech translation, and other speech technologies. The dataset maintains gender and age balance of readers across six working languages used across regional states of Ethiopia.</t>
-        </is>
-      </c>
+          <t>AfriHate is a hate and offensive speech corpus for 15 African languages: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya. The dataset annotates tweets using "offensive," "hateful," and "normal" classes, with target classes such as politics, ethnicity, gender, religion, and disability. The team also created AfriEmotion for emotion detection. Overall, they collected and annotated 10,000 instances each for hate speech and emotion detection per language, making 150,000 annotated observations. This is the first publicly available dataset for hate and offensive speech detection in these target languages.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -7134,12 +6900,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Solomon Teferra Abate | solomon.teferra@aau.edu.et</t>
+          <t>Abinew Ali Ayele | abinewaliayele@gmail.com, Seid Muhie Yiman | muhie.yimam@uni-hamburg.de, Shamsuddeen Hassan Muhammad | muhammad@imperial.ac.uk</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7147,103 +6913,55 @@
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Languages covered: Amharic, Tigrigna, Oromo, Somali, Afar, Sidama</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Solomon Teferra Abate (PhD), Martha Yifiru Tachbelie (PhD), Michael Melese Woldeyohannes (PhD), Hafte Abera, Bantegize Addis Alemayehu, Wondwossen Mulugeta (PhD) (Addis Ababa University, School of Information Science)</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Website: https://ethiospeech.com/</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ui_77</t>
+          <t>ui_78</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
+          <t>Ethio Speech Corpora</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Language Technology Development</t>
+          <t>Ethio Speech Corpora</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>This dataset was created to enable translation from Kiswahili, Kenya's national language, into three indigenous languages: Kidaw'ida, Kalenjin, and Dholuo. All three are low-resource languages, with Kidaw'ida having only around 400,000 speakers and being at immediate risk of loss. The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili, Kalenjin-Kiswahili, and Dholuo-Kiswahili, with each corpus averaging thirty thousand sentence pairs. The project has also contributed to Mozilla Common Voice Platform with 120 hours in Dholuo, 92 hours in Kalenjin, and 56 hours in Kidaw'ida for crowd-sourced voice recognition.</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://commonvoice.mozilla.org/en/datasets</t>
-        </is>
-      </c>
+          <t>Ethio Speech Corpora comprises over 391 hours of recorded audio in six Ethiopian languages: Amharic (68 hours), Tigrigna (62 hours), Oromo (70 hours), Somali (56 hours), Afar (68 hours), and Sidama (68 hours). This project is a valuable resource for developing well-performing automatic speech recognition (ASR) systems for these languages in monolingual, multilingual, and cross-lingual setups. Use cases include dictation systems, transcription systems, assistive technologies, spoken dialogue systems, speech translation, and other speech technologies. The dataset maintains gender and age balance of readers across six working languages used across regional states of Ethiopia.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>SDG 4</t>
@@ -7251,12 +6969,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Text/Language</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Audrey Mbogho | ambogho@usiu.ac.ke</t>
+          <t>Solomon Teferra Abate | solomon.teferra@aau.edu.et</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7264,181 +6982,208 @@
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Languages covered: Kidaw'ida, Kalenjin, Dholuo, Kiswahili</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Audrey Mbogho, United States International University Africa, and collaborating institutions</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ui_78</t>
+          <t>ui_79</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>This dataset was created to enable translation from Kiswahili, Kenya's national language, into three indigenous languages: Kidaw'ida, Kalenjin, and Dholuo. All three are low-resource languages, with Kidaw'ida having only around 400,000 speakers and being at immediate risk of loss. The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili, Kalenjin-Kiswahili, and Dholuo-Kiswahili, with each corpus averaging thirty thousand sentence pairs. The project has also contributed to Mozilla Common Voice Platform with 120 hours in Dholuo, 92 hours in Kalenjin, and 56 hours in Kidaw'ida for crowd-sourced voice recognition.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://commonvoice.mozilla.org/en/datasets</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Audrey Mbogho | ambogho@usiu.ac.ke</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Multiple African Countries</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ui_80</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>Expanding a parallel corpus of Portuguese and the Bantu language Emakhuwa</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Language Technology Development</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Expanding a parallel corpus of Portuguese and the Bantu language Emakhuwa</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>This dataset includes the translation of 1,897 news articles comprising 660,242 words from Portuguese to Emakhuwa, an indigenous language of Mozambique. Each article includes news headline, content, and topic classification labels. Articles are divided into training (1,337), development (185), and testing (375) sets, categorized by topics: politics, economy, culture, sports, health, society, and world news. Use cases include topic classification, translation, and loanword recognition. The dataset has shown promising outcomes when fine-tuning multilingual models like ByT5, M2M100, and NLLB200, with improvements in translation quality using loanword information.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>https://huggingface.co/collections/LIACC/makhuwa-nlp-66a93ea22df7f4b31e96a5ab</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>SDG 4</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Text/Language</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Felermino D. M. A. Ali | felermino.ali@unilurio.ac.mz or felerminoali@gmail.com</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Languages covered: Emakhuwa, Portuguese</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>NLP Models, Language Processing Applications</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>This dataset enables development of natural language processing applications, machine translation systems, speech recognition, and other language technology tools.</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Various Open Licenses</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Felermino Dário Mário António Ali (Lurio University, LIACC, CLUP University of Porto), Henrique Lopes Cardoso (FEUP, LIACC), Rui Sousa Silva (Faculty of Arts and Humanities, CLUP University of Porto)</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Natural Language Processing</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>language-banner.jpg</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Open Access</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
         <is>
           <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Available as Digital Public Good</t>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lacuna Fund Language Dataset</t>
         </is>
       </c>
     </row>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,84 +431,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Dataset Speaking Titles</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Use Case Speaking Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description - What can be done with this? What is this about?</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset Link</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Model/Use-Case Links</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Domain/SDG</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Point of Contact/Communities</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Country Team</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Data - Key Characteristics</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Model/Use-Case - Key Characteristics</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Deep Dive - How can you concretely work with this and build on this?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Organizations Involved</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Project ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Dataset Speaking Titles</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Use Case Speaking Title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description - What can be done with this? What is this about?</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dataset Link</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Model/Use-Case Links</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Domain/SDG</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Point of Contact/Communities</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Country Team</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Data - Key Characteristics</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Model/Use-Case - Key Characteristics</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Dive - How can you concretely work with this and build on this?</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Organizations Involved</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Authors</t>
-        </is>
-      </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Maturity / Readiness for replication or scaling [INTERNAL]</t>
@@ -546,53 +546,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ui_1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Combatting Air Pollution and GHG Emissions in India through hyperlocal AI-powered mapping</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Combatting Air Pollution and GHG Emissions in India through hyperlocal AI-powered mapping</t>
+          <t>Under this initiative, a novel approach is employed by leveraging citizen scientists and IoT-based low-cost sensors to collect hyperlocal air quality data. This data is used to identify pollution sources and risk zones, facilitating targeted actions by regulatory authorities.To showcase data outreach, the project features the VAYU Android-based application and the VAYU citizen portal digital stack, which support targeted interventions and customized solutions backed by AI/ML algorithms. These tools potentially develop new approaches in air pollution management while reducing public investment costs.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Under this initiative, a novel approach is employed by leveraging citizen scientists and IoT-based low-cost sensors to collect hyperlocal air quality data. This data is used to identify pollution sources and risk zones, facilitating targeted actions by regulatory authorities.To showcase data outreach, the project features the VAYU Android-based application and the VAYU citizen portal digital stack, which support targeted interventions and customized solutions backed by AI/ML algorithms. These tools potentially develop new approaches in air pollution management while reducing public investment costs.</t>
+          <t>https://vayu.undp.org.in/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://vayu.undp.org.in/</t>
+          <t>https://github.com/undpindia/VAYU_OpenAir; https://github.com/EconAIorg/vayu-gnn/tree/main; https://github.com/Alphawarrior21/VayuAssist; https://github.com/akbp24/ClearSky; https://github.com/sherwaldeepesh/vayu_airnode</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://github.com/undpindia/VAYU_OpenAir; https://github.com/EconAIorg/vayu-gnn/tree/main; https://github.com/Alphawarrior21/VayuAssist; https://github.com/akbp24/ClearSky; https://github.com/sherwaldeepesh/vayu_airnode</t>
+          <t>SDG 13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SDG 13</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>UNDP India (https://www.undp.org/india)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>UNDP India (https://www.undp.org/india)</t>
+          <t>India</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">The data for this project is collected by static and dynamic sensor. Static sensors are placed at known hotspots for air pollution while dynamic sensors are moved by citizen scientist continously. 
 •        2 Cities
@@ -603,27 +598,32 @@
 </t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Sensors data is continously shared with specific pollutoin boards, and us ecase dvelopeed under project combined AI and ML to detect pollution sources and provide early alerts, enabling rapid response and policy action.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t>Powered by:  UNDP India
 Catalyzed by: FAIR Forward - AI for All (https://www.bmz-digital.global/en/overview-of-initiatives/fair-forward/)
 Financed by: BMZ (https://www.bmz-digital.global/en/digital-transformation-and-development-cooperation/)</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Jonas Nothnagel, Arun Kumar Yadav</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jonas Nothnagel, Arun Kumar Yadav</t>
+          <t>ui_1</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -649,47 +649,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ui_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>Facilitating access to financial applications in informal settings in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings.  Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.  </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total. The dataset was developed to support the development of financial applications in native Ghanaian languages to allow illiterate and semi-literate people to fully benefit from digital financial services. Secondly, it aims to answer research questions related to domain-specific vs. general-purpose dataset development, dialects, as well as NLP system development in low resource settings.  Overall, a total of 83,829 audios were recorded from which the datasets were published and made publicly accessible.  </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SDG 10, SDG 8</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SDG 10, SDG 8</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Dennis Asamoah Owusu (DOWUSU@ASHESI.EDU.GH)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Dennis Asamoah Owusu (DOWUSU@ASHESI.EDU.GH)</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>The data is freely available for use based on the provided open source license and courtesy the funding from Lacuna Fund. We performed a stratified random sampling (5%) of the data for each language and reviewed it to get the following quality assessments.
 0.1% of the Ga audios were of low quality
@@ -699,27 +694,32 @@
 Low quality means that what the user recorded did not match the given prompt either because there was a truncation or the recording was totally different from the prompt.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>The dataset might be used to devise more inclusive banking platforms that better understand users in  in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The dataset might be used to devise more inclusive banking platforms that better understand users in  in four Ghanaian dialects: Akuapem Twi, Ashante Twi, Fante and Ga. It can thereby help to achive more financial inclusion.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
         <is>
           <t>Powered by:  Ashesi University, Nokwary Technologies
 Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elikplim Sabblah, Balthas Seibold </t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elikplim Sabblah, Balthas Seibold </t>
+          <t>ui_2</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -745,75 +745,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ui_3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>Enabling machine translation from Kiswahili into the indigenous Kenyan languages Kidaw'ida, Kalenjin, and Dholuo, preserving these languages &amp; supporting crowd-sourced voice recognition via Mozilla Common Voice for these languages</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">The dataset was created to enable translation from Kiswahili, which is the national language in Kenya, into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. All three languages are low resource, especially Kidaw'ida, which has only around 400,000 speakers and is at immediate risk of loss. By collecting the text and speech data, the project has taken a step towards preservation of these languages . The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On average, each corpus has thirty thousand sentence pairs. 
 In addition, the dataset has helped to preserve, revitalise and elevate the languages Kidaw'ida, Kalenjin, and Dholuo by making them work on Mozillas Common Voice Platform. The text and speech datasets are thereby supporting crowd-sourced voice recognition, promoting linguistic diversity and empoweromg local communities by enabling Natural Language Processing applications tailored to their needs. Namely, the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input). As of August 2025, 120 hours of speech data have been recorded on Common Voice in Dholuo (with 14692 sentences available), 92 hours have been recorded for Kalendjin (With 29900 sentences available) and 56 hours have been recorded for Kidaw'ida (with 11773 sentences available). To download the crowd-sourced speech datasets in Kidaw'ida, Kalenjin, and Dholuo, visit https://datacollective.mozillafoundation.org/datasets?q=common+voice </t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://zenodo.org/records/13355021</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SDG 10, SDG 5, SDG 2</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SDG 10, SDG 5, SDG 2</t>
+          <t>Voice, Text</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Voice, Text</t>
+          <t>Audrey Mbogho (ambogho@usiu.ac.ke)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Audrey Mbogho (ambogho@usiu.ac.ke)</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili; Kalenjin-Kiswahili; Dholuo-Kiswahili. On averate, each corpus has thirty thousand sentence pairs. This dataset is available on Zenodo and on GitHub where it will continue to be grown and its quality improved. The project had a total of 105 speakers who came from different parts of each region where the three languages are spoken. Thus, different regional accents were included in the speech data, making the dataset more representative. Furthermore, both male and female speakers were contributing to the voice data.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">&gt; The datasets can help to build translation services from Kiswahili into three indigenous languages, namely, Kidaw'ida, Kalenjin, and Dholuo. 
 &gt; The datasets can help to preserve these three low resource languages, promote linguistic diversity and empower local communities by enabling Natural Language Processing applications tailored to their needs.
 &gt; the resulting voice recognition datasets can be used to build AI voice applications such as advisory systems in local languages for farmers, citizens etc that "understand" speech input (instead of written input).  </t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Apache License 2.0</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
-        <is>
-          <t>Apache License 2.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t>Powered by:   USIU - Africa in cooperation with Kabarak University and Maseno University, Kenya
 Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -848,55 +848,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ui_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>Helping to measure solar energy adoption across Madagascar via AI - Labelled Open solar panel data for Madagascar</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>This dataset will help data scientists, government and users to measure solar energy adoption across Madagascar. It laid the groundwork needed to develop a solar panel detection algorithm working in Madagaskar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.
 The team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>SDG 13</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fabienne Rafidiharinirina (f.rafidiharinirina@association-maidi.mg), Association Maidi (assomaidi@gmail.com)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Fabienne Rafidiharinirina (f.rafidiharinirina@association-maidi.mg), Association Maidi (assomaidi@gmail.com)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
           <t>Madagascar</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Powered by:  
 Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ui_4</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -916,18 +916,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ui_5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>Detecting sentiments and combatting hate speech in Hausa, Igbo, Nigerian-Pidgin and Yorùbá - NaijaSenti: a Nigerian Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The NaijaSenti dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria. It consists of around 30,000 annotated tweets per language (except for Nigerian-Pidgin), including a significant fraction of code-mixed tweets. These datasets are useful not only for sentiment analysis but also for hate speech detection. The open-source package consists of datasets, trained models, sentiment lexicons, and code. With more than 200 million people and 522 native languages, Nigeria is the most populous and linguistically diverse country in Africa, as well as the third most multilingual country in the world. The majority of the population speaks either Hausa, Igbo, Yorùbá, or Nigerian-Pidgin.</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The NaijaSenti dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria. It consists of around 30,000 annotated tweets per language (except for Nigerian-Pidgin), including a significant fraction of code-mixed tweets. These datasets are useful not only for sentiment analysis but also for hate speech detection. The open-source package consists of datasets, trained models, sentiment lexicons, and code. With more than 200 million people and 522 native languages, Nigeria is the most populous and linguistically diverse country in Africa, as well as the third most multilingual country in the world. The majority of the population speaks either Hausa, Igbo, Yorùbá, or Nigerian-Pidgin.</t>
+          <t>https://github.com/hausanlp/NaijaSenti</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -937,55 +937,55 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/hausanlp/NaijaSenti</t>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>NaijaSenti (https://github.com/hausanlp/NaijaSenti?tab=readme-ov-file#contact-us)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NaijaSenti (https://github.com/hausanlp/NaijaSenti?tab=readme-ov-file#contact-us)</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>The project developed and made the following resources available:   1. Manually Annotated Twitter Sentiment Dataset 2. Manually Annotated Sentiment Lexicon 3. Semi-automatically Translated emotion lexicon 4. Semi-automatically Translated sentiment lexicon 5. Large Scale Unlabeled Twitter Sentiment Corpus 6. Stop-words for Hausa, Igbo, Pidgin and Yoruba     7. text  collection,  filtering, processing  and  labeling  methods  to  create  datasets  for  these  low-resource  languages.   8. evaluation og a  range of  pre-trained  models  and  transfer  strategies  on  the  dataset. 9. release  of datasets,  trained  models,  sentiment  lexicons,  and  code  to  incentivize research on sentiment analysis in under-represented languages. Authors: Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284 </t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NaijaSenti can be used to advance sentiment analysis and other downstream NLP tasks in the languages involved and to work on hate speech detection. For such follow-up work on hate speech, see also: https://arxiv.org/abs/2501.08284 </t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>Powered by:  Bayero University, Kano, Nigeria, Ahmadu Bello University, Zaria, Nigeria, Masakhane NLP, HausaNLP, Kaduna state University 
 Catalyzed by: Lacuna-Fund / Meridian &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1023,65 +1023,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ui_6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>Enable Cashew, Cocoa and Coffee farmers to make good business decisions - Drone-based Agricultural Dataset for Crop Yield Estimation in Ghana and Uganda</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa.
  It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. Conventional methods of yield estimation are expensive, require a lot of labor and time, and are prone to error due to incomplete ground observations. This results in poor crop yield estimations and hinders farmers’ ability to appropriately plan and manage their fields and production pipelines. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions. Having key details about agricultural production readily accessible enables a timely harvest, helping farmers ensure healthy, fresh produce and, in addition, better sales.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Darlington Akogo (darlington@gudra-studio.com), KaraAgro (https://www.karaagro.com/index.html)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Darlington Akogo (darlington@gudra-studio.com), KaraAgro (https://www.karaagro.com/index.html)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>Ghana,Uganda</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t>Powered by:  Karaagro AI - Ghana, Makerere AI Lab, Uganda Marconi Lab, National Coffee Research Institute, National Crops Resources Research Institute
 Catalyzed by: Lacuna-Fund / Meridian &amp; FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elikplim Sabblah </t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elikplim Sabblah </t>
+          <t>ui_6</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1107,47 +1107,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ui_7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>Preserving privacy and avoiding gender bias of AI systems in Luganda, Lumasaba, Hausa, and Kanuri - The Lacuna personally identifiable information Text Dataset</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The Lacuna PII Multilingual Text Dataset  contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages,  improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Lacuna PII Multilingual Text Dataset  contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The dataset can help to anonymize and pseudonymize personally identifiable information in AI tasks. This can help organizations comply with legal requirements while still being able to analyze and use and share their data effectively. It can also be used to improve machine translation systems for low-resource languages,  improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. It comprises 4000 Luganda sentences, 5000 Lumasaba sentences, 3000 Kanuri sentences, and 3000 Hausa sentences. The team aimed to curate a dataset that is gender inclusive. It was created by Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/CGHWZE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 10 (Reduced inequality through access to info in local languages/NLP), Achieve Gender Equality (SDG 5)</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Andrew Katumba - Makerere University (katumba@mak.ac.ug)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Andrew Katumba - Makerere University (katumba@mak.ac.ug)</t>
+          <t>Uganda,Kenya,Nigeria</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>Uganda,Kenya,Nigeria</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>Text data:
 • Luganda: 4000 PII sentences with representation in entities of
@@ -1160,23 +1155,28 @@
 For more, see data card here: https://dataverse.harvard.edu/file.xhtml?fileId=10577233&amp;version=2.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset of personally identifiable information (PII) can help any organization or initiative, that would like to comply with legal requirements while still being able to analyze and use and share data effectively in one of the languages in Luganda, Lumasaba, Hausa, and Kanuri. It can also be used to improve machine translation systems for these low-resource languages, improve the performance of NLP applications in these languages, and support the extraction of specific information from text, such as automated form filling and information retrieval systems. </t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Powered by:  Makerere Artificial Intelligence Lab in collaboration with Marconi Lab and Clear Global
 Catalyzed by: Lacuna-Fund / Meridian &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_7</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1210,48 +1210,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ui_8</t>
+          <t>Ecuadorian Dataset on Access, Demand, &amp; Availability of Electricity Supply</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ecuadorian Dataset on Access, Demand, &amp; Availability of Electricity Supply</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>Ecuador Electricity Access &amp; Supply Data</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ESPOL University</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ESPOL University</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>Ecuador</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Powered by:  ESPOL University
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>ui_8</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1277,65 +1277,65 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ui_9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>Powering Rural Futures in West Africa: AI-Driven Demand Data for Smarter Electrification</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The project provides two openly accessible datasets that were developed through a complete, reproducible data pipeline combining machine learning with stochastic energy-system simulation. The first dataset contains predicted appliance ownership and household counts for all 1,209 administrative level 2 regions (adm2) across Nigeria, Ghana, Togo, Benin, and Niger, derived from satellite-based features and socio-economic indicators using models trained on more than 3,500 household surveys. The second dataset consists of high-resolution synthetic electricity demand profiles generated with the RAMP tool, offering minute-by-minute load curves for an entire year for each adm2 region. Together, these datasets provide a unique, representative, and scalable foundation for understanding residential electricity demand in regions where measured data is scarce or entirely unavailable.</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The project provides two openly accessible datasets that were developed through a complete, reproducible data pipeline combining machine learning with stochastic energy-system simulation. The first dataset contains predicted appliance ownership and household counts for all 1,209 administrative level 2 regions (adm2) across Nigeria, Ghana, Togo, Benin, and Niger, derived from satellite-based features and socio-economic indicators using models trained on more than 3,500 household surveys. The second dataset consists of high-resolution synthetic electricity demand profiles generated with the RAMP tool, offering minute-by-minute load curves for an entire year for each adm2 region. Together, these datasets provide a unique, representative, and scalable foundation for understanding residential electricity demand in regions where measured data is scarce or entirely unavailable.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/3S7KPQ; https://dataverse.harvard.edu/dataset.xhtml?persistentId=doi:10.7910/DVN/9WT7FJ</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">SDG7 (Universal Energy Access) </t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Reiner Lemoine Institut gGmbH (RLI)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Reiner Lemoine Institut gGmbH (RLI)</t>
+          <t>Benin,Ghana,Niger,Togo, Nigeria</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>Benin,Ghana,Niger,Togo, Nigeria</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">
 The two datasets provide complementary, high-resolution information on household electricity demand across 1,209 administrative level 2 regions in West Africa. The ML dataset contains per-region estimates of household numbers, appliance ownership across 17 categories, and cluster identifiers reflecting typical appliance-use behaviour. The demand dataset includes both full-year, minute-resolution load profiles (527,040 time steps per region) and aggregated daily curves, along with summary statistics such as minimum, maximum, mean, and total annual demand. Files are structured as standardized CSVs, organized by country, and kept in manageable sizes. Users can easily import the data into analytical workflows for energy planning, electrification modelling, scenario design, or spatial analysis. Because the pipeline is fully open source, users may also retrain models, adjust appliance usage parameters, or generate new simulations tailored to local contexts. Together, the datasets offer granular, scalable, and customizable inputs for researchers, utilities, developers, and policymakers working on electricity access and energy-system planning.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>The datasets can be used directly for energy planning, electrification modelling, mini-grid prefeasibility assessments, academic research, or scenario analysis. Users may download the ML dataset to analyse expected appliance adoption patterns or to integrate the predicted household numbers into broader socio-economic models. The synthetic demand profiles can be imported into any energy modelling environment (e.g., Python, R, Excel, PowerFactory, PyPSA, OSeMOSYS) to simulate grid expansion, evaluate supply adequacy, or study temporal consumption behaviour. Because the full codebase is open source, users can also adapt individual steps of the pipeline—such as updating input features, retraining the ML model with local survey data, or running customized RAMP simulations—to generate new or localized demand profiles. Access to both datasets is free under a CC-BY 4.0 license, and additional resources such as documentation, example scripts, and workshop materials are available via GitHub and Harvard Dataverse. This ensures that researchers, planners, and practitioners can build on the existing workflow at no cost and with minimal technical barriers.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Powered by:  Reiner Lemoine Institut gGmbH (RLI)
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Clara Neyrand</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Clara Neyrand</t>
+          <t>ui_9</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1353,48 +1353,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ui_10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>Promoting energy conservation and market analysis in Pakistan through Residential Energy and Weather Data (REWD)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>This dataset helps to understand energy consumption patterns in relation to weather conditions in Pakistan. This can guide policymaking on energy and energy conservation, sustainabe energy initiatives and private sector use (market assessment and strategic planning as new entrants in the restructured energy market). 
 The project produced an energy dataset of residential consumption data from buildings across six climatic zones. The energy dataset is recorded on a 1-minute granularity for entire household usage as well as for individual appliances. With over a year of detailed energy consumption data and 18 months of weather data collected from a diverse array of households across six distinct climatic zones, it is one of the most comprehensive datasets of its kind. This meteorological dataset has been accumulated over a period of 18 months for the six urban centers. This weather data comprises of up to 10 essential variables such as temperature, atmospheric pressure, humidity and Precipitation, thus providing an all-around perspective of the environmental elements impacting energy consumption.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://lei.lums.edu.pk/datasets/residential-energy-and-weather-data-pakistan.html</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), SDG 7</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), SDG 7</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Lahore University of Management Sciences (LUMS)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Lahore University of Management Sciences (LUMS)</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
         <is>
           <t>This Dataset is available in the webpage of the Lahore University. The dataset consist oth three parallel corpora: 
 1. Electricity consumption datacollected over year through advanced smart meters. The dataset consists of 60 households belonging to six major urban centers in varying climatic zones across the country. It is recorded on a 1-minute granularity for entire household usage as well as for individual appliances.  
@@ -1402,23 +1397,28 @@
 3. Meteorological dataset created with infromation of 18 months for six urban centers. It comprises of up to 10 essential variables: temperature, atmospheric pressure, humidity, dew, precipitation, wind direction, wind speed, solar radiation, solar energy and UV index</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>The resources can support policymaking and inform energy sustainability initiatives. They can namely be  utilized by key stakeholders such as the Ministry of Climate Change, Ministry of Energy (Power Division),  Punjab Energy Efficiency &amp; Conservation Authority, and National Energy Efficiency &amp;  Conservation Authority (NEECA)  Moreover,  private sector companies can use the data for market assessment purposes and strategic planning as new entrants in the restructured energy market.  The resources can also support further academic research and innovation.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Powered by: Lahore University (LUMS)
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>ui_10</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1448,82 +1448,82 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ui_11</t>
+          <t>Datasets for transportation impact evaluation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Datasets for transportation impact evaluation</t>
+          <t>Urban roadspace classification data and model</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Urban roadspace classification data and model</t>
+          <t>The team developed a labeled training dataset, derived from 50cm or better satellite imagery, based on a novel, pre-defined road space classification taxonomy appropriate for training and deployment of large-scale deep-learning models</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The team developed a labeled training dataset, derived from 50cm or better satellite imagery, based on a novel, pre-defined road space classification taxonomy appropriate for training and deployment of large-scale deep-learning models</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>https://github.com/yangshao2/UrbanInfraDL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP), SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>Fundación Despacio,World Resources Institute,Fundación Despacio</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fundación Despacio,World Resources Institute,Fundación Despacio</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Dataset and model available in Github. Dataset of  roadspace from 15 areas of Bogota each 1Km. 
 Bogotá’s orthophoto and GIS layers. 
 Data Dictionary </t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Model that was tested for the entire city of Bogotá to clasify urban roadspace..And it worked with 98% reliability. Unfortunately not more info available</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Model that was tested for the entire city of Bogotá to clasify urban roadspace..And it worked with 98% reliability. Unfortunately not more info available</t>
+          <t>The resources allow local governments, urban and infraestructure planning offices to evaluate how much area of the city is destined toe ach mode of transportation. It will be possible to include percentaje of area distribuited per mode as public and transportation allocation policies, to evaluate equity and accessibility.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The resources allow local governments, urban and infraestructure planning offices to evaluate how much area of the city is destined toe ach mode of transportation. It will be possible to include percentaje of area distribuited per mode as public and transportation allocation policies, to evaluate equity and accessibility.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
         <is>
           <t>Powered by: Fundación Despacio
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>ui_11</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1557,74 +1557,74 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ui_12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>Monitoring the impact of palm oil monoculture, shrimp aquaculture &amp; mining in continental Ecuador and the Galapagos using AI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The dataset can help to build systems, that can monitor the impact of palm oil monoculture, shrimp aquaculture, mining and other land transformations in continental Ecuador and Galapagos. The project created a 20.000 points land use/cover classification training dataset from existing data, with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML)  models covering continental Ecuador and the Galapagos islands.</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The dataset can help to build systems, that can monitor the impact of palm oil monoculture, shrimp aquaculture, mining and other land transformations in continental Ecuador and Galapagos. The project created a 20.000 points land use/cover classification training dataset from existing data, with labels that can be used to train multi-spectral Earth observation (EO) data machine learning (ML)  models covering continental Ecuador and the Galapagos islands.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>https://www.kaggle.com/datasets/mapbiomasecuador/lulc-training-data-for-ecuador-ml/data</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>Fundacion Ecociencia</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Fundacion Ecociencia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>Two datasets available: 
 - BaseDatosValidacionFinal30052: This is the raw dataset containing 20,000 georeferenced points along with their respective land cover classifications.
 - LULC Training Data for Ecuador ML: This dataset builds upon the first by incorporating additional information on the conservation status of each point. This includes whether the location falls within protected areas, indigenous territories, areas under government forest incentive programs, and other conservation-related designations.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation. </t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">This dataset will allow for a better understanding of land transformation dynamics taking place, such as forest conversion to palm oil monoculture, mangrove transformation to shrimp aquaculture, water bodies and estuarine vegetation impacted by mining, natural grasslands encroached upon by expanding forest plantation, and more. It also has the potential to identify recovery cases. For example, the Galapagos data might provide the ability to estimate if invasive species control programs have had a positive impact in vegetation regeneration or if governmental forest incentives are promoting deforestation reduction in the Ecuadorian Amazon. The land’s conservation status has the potential to predict risk of future transformation. </t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
         <is>
           <t>Powered by:  Ecociencia
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>ui_12</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1659,42 +1659,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ui_13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
           <t xml:space="preserve">Forest carbon sequestration in the Congo Basin: combining In Situ Data and Artificial Intelligence to unlock climate finance </t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>World Resources Institute</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>World Resources Institute</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>Cameroon,DRC</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Powered by:  World Resource Institution 
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ui_13</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1715,51 +1715,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ui_14</t>
+          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuadorian Amazon with Biodiversity AI-Datasets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Indigenous Knowledge Meets AI: Monitoring Elephants and Rodents in Kenya and Ecuadorian Amazon with Biodiversity AI-Datasets</t>
+          <t>Ltome-Katip: Pioneering Indigenous-Led Biodiversity Datasets for Ethical AI in Kenya and the Ecuadorian Amazon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ltome-Katip: Pioneering Indigenous-Led Biodiversity Datasets for Ethical AI in Kenya and the Ecuadorian Amazon</t>
+          <t>The Ltome-Katip datasets are the first Indigenous-labelled bioacoustic datasets designed specifically to support the development of ethical AI for biodiversity monitoring. Co-created by Indigenous data stewards from the Samburu tribe in northern Kenya and the Shuar Nation in the Ecuadorian Amazon, the recordings focus on two sentinel species: Ltome (elephant) and Katip (rodent), both of which signal ecological shifts under climate stress. All data were collected, annotated, and governed by the Indigenous communities, following locally defined protocols rooted in Indigenous data sovereignty. These datasets are not only scientifically valuable — they establish a precedent for how Indigenous communities can lead in setting standards for responsible, consent-based AI development.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The Ltome-Katip datasets are the first Indigenous-labelled bioacoustic datasets designed specifically to support the development of ethical AI for biodiversity monitoring. Co-created by Indigenous data stewards from the Samburu tribe in northern Kenya and the Shuar Nation in the Ecuadorian Amazon, the recordings focus on two sentinel species: Ltome (elephant) and Katip (rodent), both of which signal ecological shifts under climate stress. All data were collected, annotated, and governed by the Indigenous communities, following locally defined protocols rooted in Indigenous data sovereignty. These datasets are not only scientifically valuable — they establish a precedent for how Indigenous communities can lead in setting standards for responsible, consent-based AI development.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>https://arbimon.org/p/namunyak-conservancy-reteti-elephant-sanctuary; https://arbimon.org/p/shakiam-ecuadorian-amazon/insights</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SGD 1, 2, 3, 4, 5, 8,10, 13, 15 </t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SGD 1, 2, 3, 4, 5, 8,10, 13, 15 </t>
+          <t>Drone Imagery, Text, Voice, Geospatial/Remote Sensing, Images, Meterological, Tabular, Other</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Drone Imagery, Text, Voice, Geospatial/Remote Sensing, Images, Meterological, Tabular, Other</t>
+          <t>Space4Innovation, Diana Mastracci diana@space4innovation.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Space4Innovation, Diana Mastracci diana@space4innovation.com</t>
+          <t>Ecuador,Kenya</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>Ecuador,Kenya</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ltome-Katip Indigenous Bioacoustic Dataset
 Regions: Samburu (Kenya) · Shuar (Ecuadorian Amazon)
@@ -1771,32 +1766,37 @@
 </t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>The Ltome-Katip system uses Indigenous-labelled bioacoustic data to train AI models that detect and classify species like elephants in Samburu (Kenya) and rodents in the Ecuadorian Amazon. These models are already being used to monitor biodiversity, understand ecological stress, and support early warning systems rooted in Indigenous governance. What sets Ltome-Katip apart is that both the dataset and its governance model were co-designed by Indigenous communities. All development follows the CARE Principles for Indigenous Data Sovereignty, and any replication must go through an Ethical AI Assessment to ensure consent, transparency, and benefit-sharing. This project sets a new global benchmark for community-led, responsible AI in biodiversity and conservation.
 The data is processed using the Arbimon platform, where recordings are visualized as spectrograms and labelled through bounding boxes by trained Indigenous data stewards. The outputs — including geospatial and temporal metadata — can be downloaded as CSV files and used for further machine learning or integration with other ecological datasets. These tools are already generating insights into ecosystem change and human–wildlife conflict. The core team is now actively designing Ltome-Katip 2, a next-phase expansion that will deepen Indigenous-led data infrastructure, extend sensor coverage, and explore AI integration with the Namunyak app. While plans are in development, we are currently seeking aligned funding to support this work, which will remain entirely Indigenous-led and ethically governed at every stage.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>The Ltome-Katip datasets can already be used to detect and classify species such as elephants and rodents, enabling real-time biodiversity monitoring and alerts for human–wildlife conflict. They also support ecosystem health assessments by capturing patterns in species richness, activity cycles, and climate-driven changes. Indigenous-led early warning systems are already being built using these datasets and dashboards, allowing communities to visualize and act on local ecological shifts. Researchers can extend this work by adding new species, integrating satellite data, applying transfer learning, or developing explainable AI tools to improve accuracy and cross-ecosystem usability. All reuse must respect Indigenous data sovereignty, undergo an ethical AI review, and credit the original communities. The Ltome-Katip core team is actively seeking funding for the next phase — Ltome-Katip 2 — which will expand the sensor network, strengthen community data infrastructure, and integrate AI capabilities into the Namunyak Indigenous app.</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The Ltome-Katip datasets can already be used to detect and classify species such as elephants and rodents, enabling real-time biodiversity monitoring and alerts for human–wildlife conflict. They also support ecosystem health assessments by capturing patterns in species richness, activity cycles, and climate-driven changes. Indigenous-led early warning systems are already being built using these datasets and dashboards, allowing communities to visualize and act on local ecological shifts. Researchers can extend this work by adding new species, integrating satellite data, applying transfer learning, or developing explainable AI tools to improve accuracy and cross-ecosystem usability. All reuse must respect Indigenous data sovereignty, undergo an ethical AI review, and credit the original communities. The Ltome-Katip core team is actively seeking funding for the next phase — Ltome-Katip 2 — which will expand the sensor network, strengthen community data infrastructure, and integrate AI capabilities into the Namunyak Indigenous app.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
         <is>
           <t>Powered by:  Space4Innovation, Namunyak Conservancy, GEO Indigenous Alliance, MUSAP &amp; Rochester Institute for Technology
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Diana Mastracci, Space4Innovation, GEO Indigenous Alliance</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Diana Mastracci, Space4Innovation, GEO Indigenous Alliance</t>
+          <t>ui_14</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1831,54 +1831,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ui_15</t>
+          <t>AI for Mangrove Carbon Credits: Turning Forest Data into Climate Action in Côte d’Ivoire</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI for Mangrove Carbon Credits: Turning Forest Data into Climate Action in Côte d’Ivoire</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>WatchMyTree</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://figshare.com/articles/dataset/The_First_Open_Dataset_of_Mangrove_Above-_and_Belowground_Biomass_and_Soil_Carbon_Stocks_in_C_te_d_Ivoire_Insights_from_Fresco_and_Sassandra_/30258772</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>data354</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data354</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>Cote d'Ivoire</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Powered by:  Data354
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ui_15</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -1903,47 +1903,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ui_16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
           <t>Mapping Cocoa Landscapes in Ghana: Reference Data for Tracking Land Use Change</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>This dataset was produced by the Centre for Remote Sensing and Geographic Information Services (CERSGIS) as part of the project Reference Data Collection for Improving Land Use Change Mapping in Ghana. The primary objective was to develop high-quality reference data to enhance the accuracy of remote sensing-based land use and land cover (LULC) change mapping using machine learning methods in Ghana’s cocoa production landscapes.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/15778396</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>Center for Remote Sensing and Geographic Information Services</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Center for Remote Sensing and Geographic Information Services</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>Content:
 • 21,031 geocoded cocoa farm polygons (including agroforestry and shadeless cocoa)
@@ -1961,8 +1956,8 @@
 • Not suitable for certification or compliance purposes.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>What can be done immediately:
 • Train and validate machine learning models for cocoa farm detection, deforestation monitoring, and land use classification.
@@ -1986,21 +1981,26 @@
 • Add new field reference data from other cocoa-producing regions (e.g., Côte d’Ivoire, Nigeria) to increase transferability.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
         <is>
           <t>Powered by:  WRI, CERSGIS, NASA SERVIR, Earth System Science Center
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Jonas Nothnagel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jonas Nothnagel</t>
+          <t>ui_16</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2031,51 +2031,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ui_17</t>
+          <t>Miti360: A Comprehensive Dataset for AI-Powered Forest Monitoring</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Miti360: A Comprehensive Dataset for AI-Powered Forest Monitoring</t>
+          <t>Miti360: A Machine Learning Ready Dataset for Automated and Scalable Forest Monitoring</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miti360: A Machine Learning Ready Dataset for Automated and Scalable Forest Monitoring</t>
+          <t>Miti360 is an integrated, machine-learning ready dataset for individual-tree and stand-level reforestation monitoring that fuses high-resolution drone orthophotos, terrestrial stereo and single images, precise ground measurements (tree height, crown diameter, basal diameter and GPS locations), species labels, and multi-year weather time series for nearby stations. The collection is designed to support detection, segmentation, species classification, and biophysical parameter estimation (e.g., crown diameter, height, biomass proxies), and to enable linking short-term growth dynamics to weather. Data are provided in standard GIS and ML formats (GeoTIFF, JPEG, JSON, SHP, time-series API) for immediate integration into research and operational pipelines.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Miti360 is an integrated, machine-learning ready dataset for individual-tree and stand-level reforestation monitoring that fuses high-resolution drone orthophotos, terrestrial stereo and single images, precise ground measurements (tree height, crown diameter, basal diameter and GPS locations), species labels, and multi-year weather time series for nearby stations. The collection is designed to support detection, segmentation, species classification, and biophysical parameter estimation (e.g., crown diameter, height, biomass proxies), and to enable linking short-term growth dynamics to weather. Data are provided in standard GIS and ML formats (GeoTIFF, JPEG, JSON, SHP, time-series API) for immediate integration into research and operational pipelines.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>https://github.com/DeKUT-DSAIL/miti360</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>Geospatial/Remote Sensing, Images</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing, Images</t>
+          <t>Prof. Ciira Maina, Centre for Data Science and Artificial Intelligence, Dedan Kimathi University of Technology</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Prof. Ciira Maina, Centre for Data Science and Artificial Intelligence, Dedan Kimathi University of Technology</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Miti360 contains the following core components and formats (quantities as provided):
 - Orthophotos (GeoTIFF): high-resolution stitched orthomosaics (2 GeoTIFFs) and 844 orthophoto tiles exported for annotation. 
@@ -2088,38 +2083,43 @@
 </t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">The Miti360 dataset is intended for training and assessing machine learning models in various forestry applications.
 - Use the orthophoto tiles and bounding box annotations to train models for individual tree detection, counting, and classification from aerial imagery.
 - Use the terrestrial stereoscopic images to develop and benchmark 3D computer vision models for automating forest inventory, such as estimating biophysical parameters.
 - Combine the ground-truth measurements (TH, CD, BD) and weather data to train models that determine quantitative relationships between tree growth and local weather conditions.
-- Leverage the multi-year data (2024-2025) to analyse changes in biophysical parameters and determine which tree species are growing well in the reforested area.
+- Leverage the multi-year data (2024-2025) to analyse changes in biophysical parameters and determine which tree species are growing well in the reforested area.
 The dataset is designed to be integrated. By augmenting this dataset with others, one can
 - Combine Miti360 with other global forestry datasets mentioned in the report (like NEON Crowns or Auto Arborist) to train models with greater geographic diversity, addressing a key gap this dataset was built to fill.
-- Augment the dataset with socio-economic data on local farming to explore and validate the contribution of farmers to reforestation, an application suggested in the report.
+- Augment the dataset with socio-economic data on local farming to explore and validate the contribution of farmers to reforestation, an application suggested in the report.
 Cost &amp; resources one can use:
 - Cost: Only associated compute costs
 - Resources: The source code used for data analysis as well as preliminary models trained on the dataset will be made available.
 </t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
         <is>
           <t>Powered by:  Dedan Kimathi University of Technology, Kenya
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_17</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2149,80 +2149,80 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ui_19</t>
+          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>African Trees for Climate Resilience: A Comprehensive Database</t>
+          <t>SAT-CARe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAT-CARe</t>
+          <t>Extensive bioinformatics resource that leverages tree species’ distribution, medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Extensive bioinformatics resource that leverages tree species’ distribution, medicinal, food provision, and other trait data, together with southern African trees’ climate relationships and growth characteristics for climate adaptation and mitigation planning.  The data can serve to promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
           <t>https://www.gbif.org/</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Life on Land (SDG 15): sustainably manage forests</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Life on Land (SDG 15): sustainably manage forests</t>
+          <t>Images, Tabular, Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Images, Tabular, Geospatial/Remote Sensing</t>
+          <t>Professor Guy F Midgley gfmidgley@sun.ac.za University of Stellenbosch</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Professor Guy F Midgley gfmidgley@sun.ac.za University of Stellenbosch</t>
+          <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Angola, DRC, Kenya, Mozambique, Nigeria, South Africa,Tanzania, Zambia</t>
+          <t>An extensive relational floristic and plant functional database which, together with matching biogeoclimatic data sets and implementation of the distribution model, may describe the biogeoclimatic relationships and projects the growth and ecological success of all sufficiently recorded Southern African trees under current and future climatic conditions</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An extensive relational floristic and plant functional database which, together with matching biogeoclimatic data sets and implementation of the distribution model, may describe the biogeoclimatic relationships and projects the growth and ecological success of all sufficiently recorded Southern African trees under current and future climatic conditions</t>
+          <t>Automation of a species distribution model that leverages a novel mechanistically based algorithm for 1) quantification of currently suitable planting-range conditions and 2) projection of climate risk for future planting-range suitability. This primary screening effort can be cross-referenced for adaptation and mitigation use-value sources to aid in tree species selection.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Automation of a species distribution model that leverages a novel mechanistically based algorithm for 1) quantification of currently suitable planting-range conditions and 2) projection of climate risk for future planting-range suitability. This primary screening effort can be cross-referenced for adaptation and mitigation use-value sources to aid in tree species selection.</t>
+          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The primary application of this work will include identifying indigenous species that can enhance ecological resilience by mapping adaptation and mitigation opportunities and assessing climate risks to African trees. Existing cutting-edge functional niche modeling will allow for the identification of areas for optimal use of African trees based on the results of tree growth performance. This will promote the use of indigenous trees for reforestation, regenerative agriculture, ecological restoration, human health and livelihood support, and urban afforestation programs to adapt to and mitigate the impacts of climate change.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
         <is>
           <t>Powered by:  Stellenbosch University
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Luisa Olaya</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Luisa Olaya</t>
+          <t>ui_19</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2261,61 +2261,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ui_20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
           <t>Mangroves Protection in West Africa through AI-powered monitoring of mangrove health - Benin Mangroves Open Data (BeMOD)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangroves are valuable coastal ecosystems, providing diverse services to humans and playing a critical role in the global strategy to mitigate impacts of climate change. Regular monitoring of their conditions is essential to provide evidence that supports timely decisions for their management. The “Benin Mangroves Open Data (BeMOD)” project generated annotated images, observations on water quality, observations on soil characteristics, climate observations, forest inventories data (tree diversity, canopy height and cover, tree diameter, total height, biomass, etc.) from plots, and data on socio-cultural contexts (e.g., uses, activities) of mangroves in multiple sites in Benin. </t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), clean water (SDG 6), Life below water (SDG 14), Life on land / biodiversity (SDG 15)</t>
+          <t>Images, Tabular</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Images, Tabular</t>
+          <t>Romain Lucas        Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Romain Lucas        Glèlè Kakaï, Laboratory of Biomathematics and Forest Estimations, University of Abomey-Calavi (glele.romain@gmail.com or romain.glelekakai@fsa.uac.bj)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
           <t>Benin</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">This datasets can be used to build systems for faster, more regular monitoring of mangrove conditions. This is essential to provide evidence that supports timely decisions for mangrove management and mitigate the outcomes of climate change.
 </t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Powered by: University of Abomey-Calavi, Republic of Benin 
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_20</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2345,16 +2345,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ui_21</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
           <t>Mitigating the impacts of oil palm cultivation on forests and climate change in Indonesia through AI and social forestry</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>This dataset contributes to improved understanding and mitigation of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management. 
 The project created open and accessible training and evaluation datasets for machine learning applications focused on forest cover and change in Indonesia. It contains collections of polygons of uniform land cover, with labels indicating land cover type and, possibly, information on land cover change over time. To label land cover patches, the team has reviewed high-resolution satellite imagery facilitated by Collect Earth Online (CEO) and augmented it with field visits to difficult-to-classify areas. It has prioritized areas with significant landcover diversity with a preference for areas with significant smallholder production of  oil palm, coconut, and other commodities - given the well-known difficulties of distinguishing oil palm 
@@ -2362,47 +2357,52 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), 
 SDG 15 (Life on Land)</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Drone Imagery, Geospatial/Remote Sensing</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Drone Imagery, Geospatial/Remote Sensing</t>
+          <t>RECOFTC, Peter Cutter (peter.cutter@recoftc.org)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RECOFTC, Peter Cutter (peter.cutter@recoftc.org)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
           <t>Indonesia</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Powered by:  RECOFTC
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Balthas Seibold</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Balthas Seibold</t>
+          <t>ui_21</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2438,59 +2438,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ui_22</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
           <t>Inclusive MRV for India's Eastern Himalayas</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>An AI-Driven Dataset for Nature-Positive Livelihoods and Forest Restoration in Eastern Himalayas.This open-access dataset and digital MRV (Monitoring, Reporting, and Verification) toolkit was  developed to help communities, NGOs and policymakers in the Eastern Himalayas measure and manage the links between forests, livelihoods and climate resilience. The project was created in response to a persistent data gap in the Himalayan region where limited open data and difficult terrain have hindered effective monitoring of forest degradation and the impact of restoration programs. Using locally calibrated AI models trained on Indian biomass data, the system combines satellite observations with ground level socio-economic surveys to measure forest dependency, identify degradation hotspots and track restoration outcomes. All datasets ranging from community level livelihood surveys in Sikkim and Mizoram to forest biomass and land use layers in Assam are openly available. Together they form a replicable, open-source “digital public good” that can be used to train local AI models for forest monitoring, biodiversity accounting or impact assessment. By providing a scalable, context-aware dataset, this initiative enables indigenous start-ups, environmental NGOs and impact investors to quantify nature positive outcomes, align with IRIS+ indicators, and guide conservation investments.
 The goal is to make environmental monitoring inclusive and data driven, empowering local actors to track changes in forest carbon, identify erosion risks and measure the socio-economic benefits of restoration. Ultimately, this approach helps governments, researchers and entrepreneurs build locally adapted AI systems that support both ecosystem regeneration and sustainable livelihoods in fragile mountain regions.</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://github.com/vertify-earth/biomass-prediction-NorthEastIndia; https://zenodo.org/records/16536024</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://github.com/vertify-earth/biomass-prediction-NorthEastIndia; https://zenodo.org/records/16536024</t>
+          <t>https://docs.google.com/spreadsheets/d/1WaunaB-HU-j9UDs-X5Fn1vJ15H4ENMe-lcEgWM9l3Eg/edit?usp=sharing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1WaunaB-HU-j9UDs-X5Fn1vJ15H4ENMe-lcEgWM9l3Eg/edit?usp=sharing</t>
+          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action), Life on Land (SDG 15): sustainably manage forests, halt and reverse land degradation and halt biodiversity loss.</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
-        <is>
-          <t>Geospatial/Remote Sensing</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>Vertify.earth, Michael Anthony michael@vertify.earth ,
 Alsisar Impact, Saurabh Singhavi saurabh@alsisarimpact.com</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>This dataset integrates geospatial and socio-economic information to monitor forest restoration and livelihoods in the Eastern Himalayas. It combines satellite data from Sentinel-1, Sentinel-2, Landsat-8, and PALSAR with 500+ ground truth points and nearly 300 household surveys collected in Assam, Sikkim, and Mizoram. The data support AI applications for biomass estimation, deforestation detection and nature positive impact assessment.
 A locally trained biomass model improves accuracy for South Asian forest types, addressing calibration bias in global datasets. All personal identifiers have been removed, and sensitive coordinates anonymized to protect community privacy. The dataset is published under a CC-BY 4.0 license and maintained by Vertify.earth GmbH and Earth Analytics India Pvt Ltd, ensuring its ongoing usability as an open and replicable foundation for environmental AI and digital MRV systems.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">The AI model estimates forest biomass and vegetation health in the Eastern Himalayas using multi-source satellite data combined with local ground measurements. It outputs Above-Ground Biomass (AGB) maps, enabling accurate tracking of forest carbon, degradation, and restoration progress.
 The model accepts pre-processed satellite imagery as input and produces spatial biomass layers compatible with MRV dashboards. It runs on standard Python environments and can be adapted for other tropical regions with local calibration.
@@ -2498,28 +2493,33 @@
 </t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>This dataset and AI model can be used immediately for forest monitoring, restoration planning and impact measurement in mountain and forested regions. Users can map biomass, detect forest loss or assess community-level livelihood impacts by combining the open dataset with freely available satellite imagery. NGOs, research institutions, investors can directly apply the dataset to design or evaluate nature positive projects, while developers can integrate the AI model into their own MRV dashboards. Researchers and AI developers can extend this work by retraining the biomass model with local field data from other regions or adding new layers such as soil moisture or biodiversity indicators. Ethical replication should include community consent and data validation steps to ensure fair and context aware use.
+Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
+Model use: Free, standard cloud or local compute</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>This dataset and AI model can be used immediately for forest monitoring, restoration planning and impact measurement in mountain and forested regions. Users can map biomass, detect forest loss or assess community-level livelihood impacts by combining the open dataset with freely available satellite imagery. NGOs, research institutions, investors can directly apply the dataset to design or evaluate nature positive projects, while developers can integrate the AI model into their own MRV dashboards. Researchers and AI developers can extend this work by retraining the biomass model with local field data from other regions or adding new layers such as soil moisture or biodiversity indicators. Ethical replication should include community consent and data validation steps to ensure fair and context aware use.
-Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
-Model use: Free, standard cloud or local compute</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
         <is>
           <t>Powered by:  Vertify.earth GmbH, Earth Analytics India Pvt Ltd, Balipara Foundation, Alsisar Impact
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Arundhati Deshmukh</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arundhati Deshmukh</t>
+          <t>ui_22</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2555,70 +2555,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ui_23</t>
+          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data-enabled climate shock absorbance through agroforestry (Agrof4resilience)</t>
+          <t>Climate resilience through agroforestry</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Climate resilience through agroforestry</t>
+          <t>The Agrof4Resilience geospatial datasets are open-access utilized by artificial intelligence (AI) and machine learning (ML) algorithms that are aimed at creating more robust, productive, resilient and diverse agro-ecological systems to achieve productive agro-ecosystems that have potential to improve resilience over time. This is crucial especially in dryland which are plagued with land degredation and other effects of climate change. The data demonstrates that agroforestry in Kenya is fairly low while models developed from the data indicate high agroforestry potential in Kenya. This is affected by socioeconomic factors such as education levels, occupation, age, landsize, income, gender, marital status, cultural beliefs, and family size. These datasets could be utilized to demostrate regions and practices that are environementally and socio-economically sound. This could provide insights on practices that could enhance livelihoods and promote environmental resilience in target communities across Kenya. The data was collected from 35 out of 47 counties in Kenya, spread across four predetermined transects that cover four main agro-ecological zones, and stored in a freely accessible database within icipe’s servers.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The Agrof4Resilience geospatial datasets are open-access utilized by artificial intelligence (AI) and machine learning (ML) algorithms that are aimed at creating more robust, productive, resilient and diverse agro-ecological systems to achieve productive agro-ecosystems that have potential to improve resilience over time. This is crucial especially in dryland which are plagued with land degredation and other effects of climate change. The data demonstrates that agroforestry in Kenya is fairly low while models developed from the data indicate high agroforestry potential in Kenya. This is affected by socioeconomic factors such as education levels, occupation, age, landsize, income, gender, marital status, cultural beliefs, and family size. These datasets could be utilized to demostrate regions and practices that are environementally and socio-economically sound. This could provide insights on practices that could enhance livelihoods and promote environmental resilience in target communities across Kenya. The data was collected from 35 out of 47 counties in Kenya, spread across four predetermined transects that cover four main agro-ecological zones, and stored in a freely accessible database within icipe’s servers.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>https://dmmg.icipe.org/dataportal/dataset/data-enabled-climate-shock-absorbance-and-ecosystem-resilience</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>International Center of Insect Physiology and Ecology (ICIPE)</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
           <t xml:space="preserve">This geospatial datasets comprises both land use/landcover (LULC) data, plot sampling and socio-economic data from 35 out of 47 counties in Kenya spread across four main agroclimatic zones in Kenya. It contains machine learning-ready data of 2,391 LULC points and polygones of the collected LULC classes, that show the different land uses across Kenya. It also contains a total of a total of 8,194 plant location (gps) points of individual tagged plants collected from a total of 224 1-ha plots from 35 counties in Kenya. Information on the species identification, diameter at breast height (DBH), height, and canopy size is provided. In addition, socio-economic data from 46 focused group discussions with over 44% women and 18% youth conducted within the 35 counties is provided and clearly labeled, detailing agroforestry systems (AFSs) preferences, gender roles, and youth participation in agroforestry systems (AFSs). </t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">The database provides information on tree/plant-level, plot-level and landscape scale across Kenya. Measurements such as DBH, tree height, canopy size and tree identification have been provided. In addition, socio-economic data such as agroforestry systems (AFSs) preferences, gender roles, and youth participation in AFSs are also provided. The datasets are readily and freely available to users who can integrate it to AI and ML algorithms and models as ground-truth data to train and/or validate the models associated and/or related to agroforestry and carbon sequestration across Kenya. The models developed using the Agrof4Resilience data could utilize and take advantage of satellite data from various sources that are both freely available or with commercial licences. </t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Powered by:  ICIPE
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ui_23</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Dataset  &gt; Model &gt; Pilot &gt; Use-Case</t>
@@ -2643,52 +2643,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ui_24</t>
+          <t>Quantifying Colombian mangroves aboveground biomass and carbon content</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quantifying Colombian mangroves aboveground biomass and carbon content</t>
+          <t>Mapping Blue Carbon: Quantifying Mangrove Carbon Stocks for Climate Action and Conservation in the Colombian Caribbean</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Mapping Blue Carbon: Quantifying Mangrove Carbon Stocks for Climate Action and Conservation in the Colombian Caribbean</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">This open-access dataset supports machine learning (ML) applications for mangrove forest monitoring, addressing the need for more openly available and well-annotated datasets to calibrate and validate ML models. It focuses on improving the estimation of above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian Caribbean mangroves. The pilot area, Via Parque Isla de Salamanca National Natural Park (VIPIS) in the Magdalena department, is a Ramsar and UNESCO Biosphere Reserve. Existing global AGB and AGC models often lack the precision and cost-effectiveness needed for regional monitoring.
 The dataset includes both plot-level and tree-level field measurements from 20 newly surveyed plots, providing detailed attributes such as DBH, height, species, AGB (from allometric equations), and AGC. Using these field data, high-resolution satellite imagery, and machine learning models, satellite-based AGB and AGC maps covering ~6,000 ha of mangroves at 10 m spatial resolution have also been generated. </t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://acceso-datos-ambientales-invemar.hub.arcgis.com/maps/a0cab53befd44804923800a194c703d6/about</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SDG 15 (Life of Land)</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SDG 15 (Life of Land)</t>
+          <t>Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing</t>
+          <t>María Cuevas (mcuevas@cttc.es / Centre Tecnològic de Telecomunicacions de Catalunya, CTTC, Spain),  Cristian Montes (cristian.montes@invemar.org.co / Instituto de Investigaciones Marinas y Costeras José Benito Vives de Andreis, INVEMAR, Colombia)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>María Cuevas (mcuevas@cttc.es / Centre Tecnològic de Telecomunicacions de Catalunya, CTTC, Spain),  Cristian Montes (cristian.montes@invemar.org.co / Instituto de Investigaciones Marinas y Costeras José Benito Vives de Andreis, INVEMAR, Colombia)</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">This geodatabase contains geospatial information collected and processed under the LACUNA project, aimed at quantifying above-ground biomass (AGB) and above-ground carbon (AGC) in Colombian mangroves, specifically in the VIPIS area (Vía Parque Isla de Salamanca). The data are organized into two main datasets: Ground_truth and Satellite AGB/AGC.
 Ground_truth Dataset – Field and reference data:
@@ -2701,29 +2696,34 @@
 </t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">The geodatabase provides detailed plot-level and tree-level field data from Colombian Caribbean mangroves, including measurements such as DBH, height, species, above-ground biomass (AGB), and above-ground carbon (AGC). Users can directly integrate the Ground_truth dataset with other similar field datasets to train and validate machine learning models for accurate estimation of mangrove biomass and carbon stocks.
 The satellite dataset supports spatially explicit analysis of forest structure, carbon dynamics, and environmental factors influencing mangrove ecosystems. Combined with additional datasets, it can help improve model robustness, enable cross-site comparisons, and enhance predictive accuracy.
 Beyond modeling, the dataset facilitates carbon stock quantification, conservation planning, forest management, and climate policy development. </t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
         <is>
           <t>Powered by:  CTTC &amp; INVEMAR
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>María Cuevas</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>María Cuevas</t>
+          <t>ui_24</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2754,51 +2754,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ui_25</t>
+          <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Phenological Dataset for Ecological Forecasting (PheDEF Project)</t>
+          <t>Forecasting availaibiltiy of tropical forest resources (leaves, flowers, fruits and seeds) for local communities, forest resource managers, conservationists and restoration managers.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Forecasting availaibiltiy of tropical forest resources (leaves, flowers, fruits and seeds) for local communities, forest resource managers, conservationists and restoration managers.</t>
+          <t>The health of tropical forest ecosystems faces pressures from climate change, threatening the sustainable supply of leaves, flowers and fruits which provide important resources for wildlife, domestic animals and human settlements. Monitoring the timing of plant life cycle events (phenology) is one effective way to track the availability of plant resources and the impact of climate change and weather variability on their sustainable supply. This dataset is on 48 weeks of liana and tree phenology from ground observations, traditonal ecological knowedge and camera traps in the canopy in two tropical forest ecosystems (a moist semi-deciduous and a dry semi-deciduous forest). The dataset also includes land surface phenology from satellite images and in situ weather data. Phenology data from multiple sources and climate data could be combined via a machine learning model that can be used to predict phenology at community and landscape scales. This data will enhance the representation of tropical African forests in phenology research and contribute meaningful data from tropical African forests for machine learning applications in climate, forests and biodiversity conservation. The images and phenology labels could also be used to train an automation of identifying phenology events in forest canopy images.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The health of tropical forest ecosystems faces pressures from climate change, threatening the sustainable supply of leaves, flowers and fruits which provide important resources for wildlife, domestic animals and human settlements. Monitoring the timing of plant life cycle events (phenology) is one effective way to track the availability of plant resources and the impact of climate change and weather variability on their sustainable supply. This dataset is on 48 weeks of liana and tree phenology from ground observations, traditonal ecological knowedge and camera traps in the canopy in two tropical forest ecosystems (a moist semi-deciduous and a dry semi-deciduous forest). The dataset also includes land surface phenology from satellite images and in situ weather data. Phenology data from multiple sources and climate data could be combined via a machine learning model that can be used to predict phenology at community and landscape scales. This data will enhance the representation of tropical African forests in phenology research and contribute meaningful data from tropical African forests for machine learning applications in climate, forests and biodiversity conservation. The images and phenology labels could also be used to train an automation of identifying phenology events in forest canopy images.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
           <t xml:space="preserve">https://doi.org/10.5281/zenodo.15704554; https://doi.org/10.4121/d97e338b-dc94-4e3d-a473-6dd3d4b48898.v1; https://doi.org/10.4121/9e6b4bca-f3d3-40f3-a8f5-4f71f7790c2f.v1; https://doi.org/10.4121/7e6d7ca3-060d-4ca5-bd83-d779b598c11d.v1 </t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SDG 15 (Life of Land)</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SDG 15 (Life of Land)</t>
+          <t>Tabular, Geospatial/Remote Sensing</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tabular, Geospatial/Remote Sensing</t>
+          <t>Bismark Ofosu-Bamfo (bismark.ofosu-bamfo@uenr.edu.gh; bofosubamfo@gmail.com) and Daniel Yawson (daniel.yawson@uenr.edu.gh) Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana/Raul Zurita-Milla (r.zurita-milla@utwente.nl) and Rosa Aguilar (r.aguilar@utwente.nl) Department of Geo-Information Processing, Faculty ITC, University of Twente, The Netherlands. Primary contact/Maintainance of datasets: Bismark Ofosu-Bamfo</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Bismark Ofosu-Bamfo (bismark.ofosu-bamfo@uenr.edu.gh; bofosubamfo@gmail.com) and Daniel Yawson (daniel.yawson@uenr.edu.gh) Department of Biological Science, School of Science, University of Energy and Natural Resources, Sunyani, Ghana/Raul Zurita-Milla (r.zurita-milla@utwente.nl) and Rosa Aguilar (r.aguilar@utwente.nl) Department of Geo-Information Processing, Faculty ITC, University of Twente, The Netherlands. Primary contact/Maintainance of datasets: Bismark Ofosu-Bamfo</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
         <is>
           <t>Description of clean folder (raw folder also available)
 The folder contains files of clean datasets employed for various datasets. 
@@ -2813,23 +2808,28 @@
 Creative Commons Attribution 4.0 International</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
         <is>
           <t>Powered by:  University of Energy and Natural Resources and University of Twente
 Catalyzed by: Lacuna-Fund / Meridian (Climate-call) &amp;  FAIR Forward - AI for All
 Financed by: BMZ</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Bismark Ofosu-Bamfo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bismark Ofosu-Bamfo</t>
+          <t>ui_25</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2850,8 +2850,8 @@
       <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
-— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
-Ghana News Agency: https://gna.org.gh/2025/07/realistic-phenology-data-key-to-predicting-crop-cycles-dr-ofosu-bamfo-2/
+— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
+Ghana News Agency: https://gna.org.gh/2025/07/realistic-phenology-data-key-to-predicting-crop-cycles-dr-ofosu-bamfo-2/
 Joy News (video): https://g.co/kgs/5byh6f7 </t>
         </is>
       </c>
@@ -2870,65 +2870,65 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ui_26</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
           <t>Corpus sobre cultura Qom</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
         <is>
           <t>This project creates two open-access speech corpora for the Qom language, an indigenous language of the Gran Chaco region, to combat its digital marginalization. It was created to provide the foundational data needed to build language technologies like machine translators and voice assistants, which are crucial for its preservation and modern use. The dataset includes a high-quality, professionally recorded corpus and a larger, community-collected corpus capturing diverse dialects, genders, and ages. Linguistically annotated and openly available, this resource directly empowers the Qom community by involving them in its creation and enables developers and researchers to build educational and cultural applications. This initiative supports the linguistic sovereignty of indigenous peoples and aligns with the goals of the International Decade of Indigenous Languages.</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text, Voice</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Instituto de Lingüística, Facultad de Filosofia y Letras, Universidad de Buenos Aires</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Instituto de Lingüística, Facultad de Filosofia y Letras, Universidad de Buenos Aires</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A known limitation is the potential demographic imbalance between the two corpora. The High-Quality Corpus is small (5 hours) and aims for gender parity, but the larger Community Corpus (10+ hours) has a primary focus on geographic and age distribution, with gender balance being a secondary concern. This could introduce a bias where the "high-quality" benchmark is not fully representative of the entire community's speech. Steps for ethical use include a participatory methodology where the community defines culturally relevant topics for recordings, obtaining informed consent that details data usage, and anonymizing speaker identities in the published data. The plan to measure inter-annotator agreement ensures the linguistic annotations are reliable and valid.
 Maintenance &amp; Point of Contact: Maintenance responsibility lies with the leading researchers from the University of Buenos Aires (UBA) and CONICET. The project is designed to build capacity within the Qom community, suggesting a long-term goal of empowering local members to contribute to and maintain the resource.
 Data License &amp; Rights: The data is intended for open access, though a specific license is not named in the text. The explicit goal of promoting use and diffusion via open access suggests a permissive license like Creative Commons (e.g., CC BY or CC BY-SA). Users would likely have the right to reuse and build upon the data for research, education, and application development, with the restriction that attribution must be given to the creators and the Qom community, aligning with the project's ethos of empowering and recognizing the community.M</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>With this corpus, researchers and developers can immediately build foundational language technologies for Qom. Specific use cases include training automated speech recognition (ASR) systems to transcribe Qom speech, developing text-to-speech synthesizers for educational content, and creating basic machine translation tools between Qom and Spanish. The community-collected corpus is particularly valuable for building applications that understand diverse dialects and real-world speech patterns. Developers can extend this work by using the data to train more sophisticated natural language processing (NLP) models for sentiment analysis, grammar checking, or conversational AI assistants tailored to the community's needs. A critical limitation to consider is the demographic imbalance between the two corpora; the high-quality corpus is small and aims for gender balance, while the larger community corpus prioritizes age and geography, which could introduce bias. Replicators must engage in an ethical AI assessment, ensuring any application involves the Qom community in a participatory manner to avoid exploitation and ensure cultural appropriateness. Building a basic application would have low compute costs (est. $100-500 for training on cloud GPUs) if using the existing data for fine-tuning, but significant investment is required for ethical community engagement and continuous improvement.
 Sustainability and Future Plans: Long-term maintenance relies on the lead researchers at UBA/CONICET and the empowerment of trained Qom community members. The plan for sustainability includes using the corpus to build useful community tools that encourage ongoing use and contribution. Readers can partner with the research institutions for linguistic expertise and with the Qom communities directly for data expansion and validation, ensuring the resource evolves with the language.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_26</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2950,65 +2950,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ui_27</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
           <t>Crafting a Bilingual Dataset for Biomedical Natural Language Processing</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>This project addresses a critical gap in healthcare technology by creating a high-quality, bilingual English-Luganda dataset for medical applications. It was developed because the lack of such data prevents the creation of effective digital health tools for millions of Luganda speakers in Uganda, hindering access to accurate medical information. The dataset is built through interviews with healthcare workers, collection of naturalistic clinic speech, translation of medical guidelines, and aggregation of existing resources. Openly available, this dataset can be used by NGOs, health agencies, and local developers to build life-saving applications like diagnostic assistants, automated translation of health materials, and voice-based medical record systems, directly contributing to improved health outcomes and equitable access to care.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SDG 3 (Good Health and Well-being); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SDG 3 (Good Health and Well-being); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text, Voice</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>The Infectious Diseases Institute Limited</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The Infectious Diseases Institute Limited</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A key limitation is the reliance on professional translators and healthcare workers for data creation, which may not fully capture the language used by patients from diverse educational backgrounds, potentially introducing a bias towards more formal or clinical Luganda. The use of existing materials like clinical guidelines also risks propagating any biases present in those original documents. Ethical steps are robust: all data from health sessions is collected with consent, translations are reviewed by both professional linguists and healthcare professionals for medical accuracy, and the focus on community involvement through interviews aims to ground the dataset in authentic, culturally appropriate communication.
 Maintenance &amp; Point of Contact: The maintenance responsibility likely falls to the project team and their host institutions. The mention of approaching the Infectious Diseases Institute (IDI) IRB indicates an ongoing relationship with a major local health institution, which could be a key partner for long-term updates and curation.
 Data License &amp; Rights: The text does not specify a license, but the nature of the project (aiming to improve public health) strongly implies an intention for open access. A license like CC BY or CC BY-NC would be appropriate, allowing researchers and developers to use and build upon the data for non-commercial health applications, requiring attribution to the creators. Restrictions would include the ethical imperative to use the data responsibly in medical contexts and to give back to the Luganda-speaking communities by improving health outcomes.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>This dataset enables the immediate development of critical healthcare NLP applications for Luganda speakers. Developers can build automated translation tools for patient information leaflets, symptom checkers, and public health advisories, or create voice-based interfaces for mobile health apps that allow users to interact in Luganda. Researchers can use it to train and benchmark models for cross-lingual information retrieval, allowing healthcare workers to access English-language medical databases using Luganda queries. This work can be extended by expanding the dataset to include more specialized medical domains (e.g., mental health, nutrition) or by developing speech-based datasets for voice-enabled clinic tools. A key limitation is the potential bias towards formal, clinical language from professionals, which may not reflect patient vocabulary. Any replication must undergo a rigorous ethical assessment focused on medical accuracy and patient safety; outputs must be reviewed by healthcare professionals. The cost to build a application is moderate (est. $1k-5k for compute) due to the complexity of medical language, but the primary cost is in ongoing expert validation to ensure safety.
 Sustainability and Future Plans: Sustainability is tied to partnerships with health institutions like the Infectious Diseases Institute (IDI). The dataset can be kept up-to-date by continuously incorporating new translated guidelines and anonymized, consented health communication data. Readers from the global health and AI communities can collaborate by contributing new parallel health texts or helping to fine-tune models for specific medical tasks.</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_27</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3034,65 +3034,65 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ui_28</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>Project Empowering Indigenous Communities:  AI-Driven Data Corpus for the Revitalization of Indigenous Languages Spoken in Chile"</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>This initiative builds multimodal text and speech corpora for the Rapa Nui and Mapudungun languages (including its Pehuenche, Guluche, Lafkenche, and Huilliche variants) to reverse their exclusion from the digital world. Created in direct response to community needs, it expands on a previous machine translation prototype to include diverse dialects and crucial speech data for the many speakers who are not literate in their native tongue. The open-source corpora will allow local and international developers to create more robust and inclusive language technologies, such as accurate speech-to-text systems. This empowers indigenous communities in Chile to use their languages in daily digital life, safeguarding ancestral knowledge and fostering cultural preservation through technology.</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text, Voice</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Pontifical Catholic University of Chile</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pontifical Catholic University of Chile</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
-        <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A significant acknowledged limitation is the inability to guarantee equal gender and age distribution in the Open Dialogue Speech corpus due to access challenges, which could create imbalances. The Annotated Speech corpus, being read from pre-selected texts, lacks the spontaneity of natural conversation. Ethically, this project is exemplary. It directly responds to community-identified needs, includes an intercultural validation process with published reports, and conducts specific research into community perspectives on Generative AI to guide future ethical development. This ensures the project is community-driven and culturally respectful.
 Maintenance &amp; Point of Contact: The project team, which has pioneered previous work with these communities, is responsible. The deep partnership with Indigenous institutions and the focus on capacity-building suggest a shared, long-term responsibility for maintaining and updating the datasets.
 Data License &amp; Rights: Data will be published alongside detailed documentation and reports. The use of standard formats (MP3, JSONL) ensures interoperability. A permissive license is expected to foster reuse. The commitment to open dialogue and community guidance implies that while the data is for replication and innovation, any future commercial or sensitive use would require further community consultation and benefit-sharing, potentially formalized through a license like CC BY-SA or a community-specific protocol.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>This multi-modal corpus allows for the immediate creation of robust machine translation systems between Spanish and Rapa Nui/Mapudungun variants, directly addressing a community-identified need. Developers can build web browser plugins or mobile apps for real-time translation of text. The speech data enables the development of speech-to-text tools for transcribing elder storytelling and creating subtitled media, as well as text-to-speech systems for hearing written content. Researchers can extend this work by using the collected prompt-response pairs and community feedback reports as a foundation for developing culturally-aligned generative AI models in the future. The critical limitation is the acknowledged imbalance in the open dialogue speech corpus regarding gender and age distribution. Future work must strictly follow the project's ethical framework, using their published reports on community perspectives to guide development and always partnering with indigenous institutions for intercultural validation. Building a translation app would have moderate compute costs (est. $2k-10k), but the non-negotiable cost is the time and resource investment required for deep, respectful community collaboration.
 Sustainability and Future Plans: The long-term plan is for the partnered Indigenous institutions to become stewards of the data and resulting technologies. The project's methodology of community engagement is a replicable model for sustainability. Readers can engage by adopting this participatory methodology in their own work, by contributing to the expansion of the text corpus with new themes, or by helping to transcribe the open dialogue speech data.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_28</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3118,65 +3118,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ui_29</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>Development of a modern Paraguayan Guarani dataset for core NLP</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>This project develops a large, modern corpus of Paraguayan Guarani to overcome its status as a low-resource language despite having millions of speakers. It addresses the lack of data for building essential Natural Language Processing (NLP) tools. The key innovation is its focus on two distinct varieties: half the corpus is in "pure" Guarani and the other half in "Jopara," the common code-switched mix of Guarani and Spanish. This openly licensed dataset, annotated to international standards, is a foundational resource for researchers and developers to create part-of-speech taggers, parsers, and educational tools. It will directly enhance platforms like Maitei for learning Guarani, empowering educators and students and ensuring the language thrives in the digital age.</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text, Tabular</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Text, Tabular</t>
+          <t>Universidad Nacional de Itapua</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Itapua</t>
+          <t>Paraguay, Spain, Uruguay</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
-        <is>
-          <t>Paraguay, Spain, Uruguay</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A known challenge is categorizing texts on a spectrum from "pure" Guarani to "Jopara," a process that requires nuanced linguistic judgment and could introduce subjectivity. The translation hackathon, while innovative, might produce translations that vary in quality and naturalness. The project plans to mitigate these issues through rigorous annotation guidelines, expert linguist oversight, and measures to identify biases related to gender or ethnicity. The very structure of including both varieties is an ethical step to avoid privileging one form of the language over another.
 Maintenance &amp; Point of Contact: The project team is responsible for the initial release. The plan to release the dataset on the Universal Dependencies repository and Hugging Face places it within ecosystems that have built-in mechanisms for community maintenance, versioning, and updates by the global NLP community.
 Data License &amp; Rights: The data will be published under an explicit Creative Commons Attribution 4.0 (CC BY 4.0) license. This is a clear, permissive license that allows anyone to reuse, share, and adapt the data for any purpose, even commercially, as long as they give appropriate credit to the creators. This maximizes the potential for innovation while ensuring recognition.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>This meticulously annotated corpus is a ready-to-use resource for training core NLP tools. Developers can immediately train part-of-speech taggers, dependency parsers, and named entity recognizers for both "academic" Guarani and "Jopara." These tools can be integrated into platforms like Maitei and CINACINA to create intelligent grammar exercises, reading comprehension helpers, and writing assistants. Researchers can extend this work by using the UD-formatted data to include Guarani in massive multilingual NLP models, ensuring the language is represented in future technologies. A key challenge for replication is the subjective spectrum between pure Guarani and Jopara, which requires nuanced linguistic expertise to handle correctly. Future projects must account for this dialect continuum and avoid biasing systems towards one variety. The cost to build upon this work is relatively low (est. $500-2k for compute) as the expensive data creation and annotation is complete; costs are primarily for model training and application development.
 Sustainability and Future Plans: The release of the dataset into the Universal Dependencies repository embeds it within a global ecosystem with built-in version control and community maintenance. The long-term plan is for the NLP community to maintain and extend the resource. Readers can contribute by submitting improvements to the UD annotations, using the data to build new applications that demonstrate value, or organizing new hackathons to expand the corpus.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_29</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3202,65 +3202,65 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ui_30</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>AfriFact &amp; AfriGuard: Dataset for Fact-Checking, Robust Refusal</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>This project creates datasets for fact-checking and harmful prompt refusal in 10 major African languages (Afrikaans, Amharic, Ewe, Hausa, Igbo, Oromo, Shona, Swahili, Yoruba, Zulu). It was created to ensure the safety and reliability of large language models (LLMs) for African users, preventing the spread of misinformation and malicious use. The datasets are manually curated by experts, translating and adapting existing English benchmarks to include locally relevant knowledge from African sources. Openly available, these resources empower local fact-checking organizations, AI developers, and social media platforms to build and audit AI systems that refuse harmful requests and provide accurate, verified information in local languages, fostering a safer digital ecosystem.</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Masakhane Institute</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Masakhane Institute</t>
+          <t>Benin, Chad, Democratic Republic of the Congo, Ethiopia, Gambia, Kenya, Lesotho, Mauritania, Mozambique, Niger, Nigeria, Senegal, South Africa, eSwatini, Togo, Zimbabwe</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
-        <is>
-          <t>Benin, Chad, Democratic Republic of the Congo, Ethiopia, Gambia, Kenya, Lesotho, Mauritania, Mozambique, Niger, Nigeria, Senegal, South Africa, eSwatini, Togo, Zimbabwe</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A major limitation is the project's foundation on translating existing English prompts from datasets like MALICIOUSINSTRUCT. This carries the risk of importing cultural contexts and harmful concepts that are not relevant or are differently perceived in African societies, creating a cultural bias. Steps to ensure ethical use include careful curation and filtering of English prompts to select those most relevant to the African context, extensive training for translators, and a multi-layered quality assurance process (AfriCOMET, back-translation, coordinator review) to ensure accuracy and cultural appropriateness.
 Maintenance &amp; Point of Contact: Maintenance is a community effort coordinated through Masakhane members for each language. This distributed model leverages local expertise but requires strong coordination to ensure consistent updates and quality control across all ten languages.
 Data License &amp; Rights: The datasets are derived from existing resources, so their licenses will need to be compatible. The project will likely adopt a permissive license similar to its sources (e.g., MIT, Apache 2.0, or CC BY) to encourage reuse in AI safety research. Users can replicate the methods and use the data to build safer AI systems, with the restriction that they must acknowledge the source and the contribution of the African NLP community.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>This dataset allows for the immediate development of crucial AI safety features for the 10 African languages. Developers can build content moderation filters for social media platforms, "refusal" mechanisms for chatbots to reject harmful requests in local languages, and fact-checking browser extensions that flag misinformation. Researchers can use the dataset to benchmark the safety and truthfulness of existing LLMs for these languages, holding model developers accountable. This work can be extended by adding more languages, generating more nuanced and culturally-specific harmful prompts, and developing automated evaluation metrics tailored to African linguistic structures. The critical limitation is the risk of cultural bias, as the project translates English prompts, potentially importing concepts irrelevant to African contexts. Replication must include the project's rigorous multi-step validation process (AfriCOMET, back-translation, native speaker review) to ensure cultural relevance and accuracy. The cost to implement a safety layer is low to moderate (est. $1k-5k) as it often involves fine-tuning or designing prompts for an existing model rather than training from scratch.
 Sustainability and Future Plans: Sustainability is managed through the Masakhane network's distributed model, where language leads maintain their respective components. The project aligns with global AI safety initiatives. Readers can contribute by becoming language coordinators within Masakhane, helping to translate more prompts, or developing better automated evaluation tools for their language.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_30</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3286,65 +3286,65 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ui_31</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
           <t>Empowering Ethnic Voices in Tanzania</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
         <is>
           <t>This project creates a comprehensive speech and text dataset for six endangered Ethnic Community Languages (ECLs) in Tanzania to prevent their extinction and promote digital inclusion. It addresses the dominance of Swahili and English which excludes these communities from technological advancements. The dataset comprises over 450 hours of transcribed and translated audio from interviews and storytelling, capturing rich cultural narratives. This open resource enables the development of automatic speech recognition (ASR) systems, bilingual educational tools, and accessible healthcare communication apps. NGOs, government agencies, and local tech developers can use this to build services that empower marginalized communities, preserve cultural heritage, and ensure everyone can access information in their first language.</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SDG 4 (Quality Education); SDG 10 (Reduced inequality through access to info in local languages/NLP)</t>
+          <t>Text, Voice</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Sokoine University of Agriculture</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sokoine University of Agriculture</t>
+          <t>United Republic of Tanzania</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
-        <is>
-          <t>United Republic of Tanzania</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A potential limitation is the sourcing of written text from religious and academic centers (e.g., Bible translations, theses), which may over-represent certain genres, dialects, or ideological viewpoints, creating a lexical and thematic bias. Ethical steps are comprehensive: data collection is based on informed consent, speaker demographics are recorded to ensure diversity, rigorous quality assurance involves native speakers, and the data will be uploaded to Mozilla Common Voice for community-driven validation and expansion, ensuring ongoing community oversight.
 Maintenance &amp; Point of Contact: The project team is initially responsible. The strategy of uploading to Mozilla Common Voice is a masterstroke for maintenance, as it explicitly transfers long-term curation, validation, and expansion to the global and local community, ensuring the dataset remains a living resource.
 Data License &amp; Rights: The data will be hosted on Zenodo with a DOI under a CC BY 4.0 license. This is a gold standard for open scientific data, allowing full reuse and replication for any purpose with attribution. The explicit goal is to enhance reusability for NLP research and applications, empowering a wide range of users from developers to government agencies.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>This large-scale speech and text corpus enables the immediate development of automatic speech recognition (ASR) systems for the six ECLs. This can power voice-activated applications for education (e.g., literacy tools), information access (e.g., voice search), and cultural preservation (e.g., transcribing oral histories). The bilingual text supports the development of translated educational materials. Researchers can extend this work by using the data to build speech synthesis systems that give a voice to digital assistants in these languages. A major limitation is the sourcing of written text from religious/academic centers, which may bias the data towards a specific register. Future users must supplement this data with more contemporary, colloquial text sources. The cost to build a functional ASR model is high (est. $10k-50k+ for compute) due to the volume of audio data required for training, but leveraging pre-trained models can reduce this cost.
 Sustainability and Future Plans: The most robust sustainability plan is the intention to upload data to Mozilla Common Voice, a platform designed for community-driven, continuous data collection and validation. This ensures long-term maintenance by the speakers themselves. Readers can contribute instantly by validating existing clips on Common Voice or recording new sentences in the target languages, directly helping to improve the dataset.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_31</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3370,65 +3370,65 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ui_32</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
           <t>MOZNLP-UP: Scaling Up Mozambican Language Coverage towards NLP inclusion</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>This project expands NLP resources for four key Mozambican languages—Emakhuwa, Xichangana, Nyanja, and Sena—spoken by nearly 25 million people. It was created to provide essential language technology tools for critical domains like news broadcasting and bilingual education, where local language variants are crucial. The project produces a multi-way translation dataset and open translation models, focusing specifically on capturing unique Mozambican dialects and loanword adaptations. The resulting open-language technology platform, featuring dictionary lookup and computer-assisted translation (CAT) tools, can be used by journalists, teachers, and government agencies to create content and services. This fosters digital inclusion and empowers communities by breaking down language barriers in access to information.</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 9 (Industry, Innovation and Infrastructure); SDG 4 (Quality Education) </t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 9 (Industry, Innovation and Infrastructure); SDG 4 (Quality Education) </t>
+          <t>Text</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>SCHOOL OF COMMUNICATION AND ARTS (ECA) - University Eduardo Mondlane</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SCHOOL OF COMMUNICATION AND ARTS (ECA) - University Eduardo Mondlane</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A key focus is on capturing unique Mozambican variants, but a limitation is the risk of these nuances being flattened by using general-purpose pre-trained models (like mT5 or NLLB) for fine-tuning. The project addresses this by developing loanword annotations and creating in-domain evaluation sets to better measure model performance on local usage. Ethical steps include collaboration with linguistic professionals and using workshops to develop localized translation guidelines, ensuring the data reflects authentic language use.
 Maintenance &amp; Point of Contact: The project team will maintain the models and benchmarks on Hugging Face. The rollout of the MUZALING platform (with CAT tools and a dictionary) suggests the team or a partnered Mozambican institution will be responsible for maintaining this applied tool for end-users.
 Data License &amp; Rights: The models and benchmarks will be made available on Hugging Face, which typically uses open licenses like MIT or Apache 2.0 for models and CC BY for data. This allows full public use for replication and innovation. The tools are intended for public use to facilitate language access, meaning developers, businesses, and government agencies can integrate them into their services to promote digital inclusion.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>This project provides the resources to immediately deploy practical machine translation (MT) tools. Developers can integrate the trained models into the MUZALING platform to offer computer-assisted translation (CAT) tools for journalists, dictionary lookup for students, and real-time translation features for news websites or government portals. Researchers can extend the work by using the loanword annotations to study language evolution or by adapting the models for other domains like legal or educational text. A limitation is the risk that the models might not perfectly capture local variants, especially for informal text. Replication should use the provided in-domain evaluation sets, not just general ones like FLORES+, to accurately gauge performance on local usage. The cost to run an existing model is low (est. cents per user), but the cost to train new models from scratch or for new languages is high (est. $10k+).
 Sustainability and Future Plans: The project aims for sustainability through the public release of models on Hugging Face and the operationalization of the MUZALING platform. Long-term maintenance will likely fall to a Mozambican institution. Readers can collaborate by using and improving the open-source models, contributing new parallel text data, or helping to localize other software and content using these tools.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_32</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3454,59 +3454,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ui_33</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
           <t>Constructing a Multilingual Parallel Corpus Dataset of Nahuatl and Totonaco</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>This project builds a parallel corpus for Nahuatl and Totonaco variants from Puebla, Mexico, with translations into Spanish and English. It addresses the gap between legal mandates for indigenous language rights and the practical lack of human and technological resources to implement them. The corpus is constructed through fieldwork and community engagement to ensure authenticity and quality. This open dataset is a foundational tool for developers and government agencies to build accurate machine translation systems, automated public service information platforms, and educational materials. It empowers indigenous communities by ensuring their right to access information and services in their native language, fostering greater inclusion and cultural preservation.</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SDG 10 (Reduced inequality through access to info in local languages/NLP); SDG 16 (Peace, Justice and Strong Institutions)</t>
+          <t>Text, Voice</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Text, Voice</t>
+          <t>Benemérita Universidad Autónoma de Puebla</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Benemérita Universidad Autónoma de Puebla</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
           <t>Brazil, Ireland, Mexico, United Kingdom</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
         <is>
           <t>This parallel corpus enables the immediate development of Spanish-Nahuatl and Spanish-Totonaco machine translation systems. These can be used to translate public service information, legal documents, and educational materials, directly supporting the implementation of linguistic rights laws in Mexico. Developers can build simple web and mobile apps for phrase translation to aid communication in healthcare or municipal settings. The work can be extended by focusing on speech data collection to create speech-to-speech translation tools, which are often more needed for oral languages. A significant challenge is the complexity of the languages and the variations between communities, which requires careful dialectal management. Any replication must be done in close partnership with anthropologists and linguists who understand the socio-linguistic context. The cost is primarily in development and community engagement (est. $5k-15k+), as the data structure itself is not overly complex for modern MT systems.
 Sustainability and Future Plans: The interdisciplinary team, including anthropologists and community specialists, is key to sustainability. Their deep ties to the communities in Puebla ensure that the project is grounded in real needs. Readers can engage by collaborating with this team to expand the corpus to other variants or by developing specific applications for the state government to use in serving its citizens.</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_33</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3519,7 +3519,11 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>· https://www.linkedin.com/posts/laboratoire-de-biomath%C3%A9matiques-et-d-estimations-foresti%C3%A8res-labef-fsa-uac_lacuna-datafordevelopment-benin-ugcPost-7337524551137853440-1ZDi?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAB7J3S4B0vCirsEbxKR0eAzpTimXPCbQv0Q</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
@@ -3532,65 +3536,65 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ui_34</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
           <t>African Tone Project</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
         <is>
           <t>This project creates a time-aligned, annotated audio-visual dataset specifically focused on the tonal features of African languages. It addresses a critical gap in NLP, as tone—a fundamental linguistic feature—is often omitted from datasets, severely hampering the development of accurate speech and language technologies for these languages. The dataset includes both elicited words and natural conversations across different language varieties. Openly available, this resource is invaluable for linguists, speech technology researchers, and language revitalization teams. It enables the development of tone-aware speech recognition and synthesis systems, which are essential for creating truly effective and natural digital tools for the hundreds of millions of speakers of tonal languages in Africa.</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDG 10 (Reduced inequality through access to info in local languages/NLP); : SDG 9 (Industry, Innovation and Infrastructure; SDG 4 (Quality Education) </t>
+          <t>Voice, Images</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Voice, Images</t>
+          <t>African Languages Technologies Initiative</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>African Languages Technologies Initiative</t>
+          <t>Canada, Ghana, Nigeria</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
-        <is>
-          <t>Canada, Ghana, Nigeria</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
         <is>
           <t>Critical Limitations &amp; Ethical Use: A significant challenge is the technical complexity of consistently annotating tone across multiple languages and speakers, which requires highly skilled annotators and can lead to inconsistency. The focus on lab-quality recording with headset microphones, while excellent for clarity, may not fully capture the acoustic properties of speech in naturalistic environments. Ethically, the project is strong: it involves native-speaker linguists in transcription assessment, strives for demographic diversity in speakers, and collaborates with communities to create tone-marking conventions where they don't exist, empowering them linguistically.
 Maintenance &amp; Point of Contact: The Principal Investigators (PIs) and language leads, who are native-speaker linguists, are responsible for the core data assessment and correction. The project is positioned as a resource for the broader research and community communities, suggesting long-term maintenance by the host academic institutions.
 Data License &amp; Rights: The use of archival-standard formats (.wav, .mov) and detailed annotations makes it a high-value resource. While a license is not specified, its creation for the broader research community suggests an open license (likely CC BY) would be used. This would allow linguists and NLP researchers to use it for replication and groundbreaking work on tonal languages. The rights would include use for analysis and model training, with the restriction that users must acknowledge the source and the contributing communities.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>This dataset is a foundational resource for groundbreaking research and development on tonal languages. Immediately, linguists can use it for phonetic and phonological analysis of tone. NLP researchers can use it to train and benchmark tone-aware speech recognition and synthesis models, which are essential for building effective voice AI for these languages. Developers can extend this work by exploring how tone information improves the performance of everything from keyword spotting to speaker identification systems. The primary limitation is the extreme technical complexity of consistently annotating tone across speakers and contexts. Replicating this work requires specialized linguistic expertise in phonetics and the specific languages. The cost to collect and annotate a similar dataset for a new language is very high (est. $50k-100k+) due to the need for expert linguists, high-quality equipment, and extensive manual labor.
 Sustainability and Future Plans: The project is sustained by its academic value to the fields of linguistics and NLP. The PIs and language leads are responsible for maintenance. The high-quality, archival-standard data ensures its long-term usability. Readers can contribute by using the data for their research, publishing findings that highlight its value, and advocating for more resources to be dedicated to the study of tonal phenomena in AI.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Alondra Arellano</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_34</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3616,31 +3620,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ui_35</t>
+          <t>Dataset for Prediction of Landuse and Landcover changes in Uganda</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dataset for Prediction of Landuse and Landcover changes in Uganda</t>
+          <t>Acquisition and Analysis of groundtruth data and Remote Sensing Imagery to develop and Artificial Intelligence solution for Prediction Landuse and Landcover changes in Uganda</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Acquisition and Analysis of groundtruth data and Remote Sensing Imagery to develop and Artificial Intelligence solution for Prediction Landuse and Landcover changes in Uganda</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
           <t>This project provides Uganda’s first openly accessible AI-ready satellite imagery dataset designed to predict land-use and land-cover change. It was created to address persistent deforestation and the lack of reliable, context-specific data needed to detect, forecast, and manage ecosystem degradation. Through an open-source replication kit including annotated Sentinel-2 and Hansen datasets, protocols, and inventory data, this products enables local innovators, forest agencies, and policymakers to build AI tools for monitoring forests, planning restoration, and supporting NDC and SDG15 actions. Its goal is to improve early detection of land-cover change, strengthen climate-smart decision-making, and empower local institutions with high-quality geospatial data.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1. Landus Landcover Datasets (2015 -2023), 2. ArcGIS Pro Project, ArcGIS DEEPLearning Model for Tree Species. https://1drv.ms/f/c/BFFEF9896BFF8791/Es68F3WluONJjORAR_WvTloBdtisO9TGsGyWR8Se5xNYDA?e=q0Afso</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>1. Landus Landcover Datasets (2015 -2023), 2. ArcGIS Pro Project, ArcGIS DEEPLearning Model for Tree Species. https://1drv.ms/f/c/BFFEF9896BFF8791/Es68F3WluONJjORAR_WvTloBdtisO9TGsGyWR8Se5xNYDA?e=q0Afso</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>SDG 13: Climate Action
 By detecting deforestation, modelling future LULC trends, and supporting climate-smart planning, the project strengthens adaptation and mitigation strategies in Uganda.
@@ -3648,49 +3647,54 @@
 Central to the project, as it supports forest conservation, ecosystem restoration, biodiversity protection, and reduction of land degradation.</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Geospatial/Remote Sensing, Images</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Geospatial/Remote Sensing, Images</t>
+          <t xml:space="preserve">1. Makerere University, Makerere AI Lab: https://mak.ac.ug, https://air.ug/    2. National Forestry Authority (NFA): https://nfa.go.ug/  </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Makerere University, Makerere AI Lab: https://mak.ac.ug, https://air.ug/    2. National Forestry Authority (NFA): https://nfa.go.ug/  </t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>The dataset provides georeferenced, annotated Sentinel-2 and Hansen imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. Users can train AI models for landuse and landcover classification, detect deforestation, validate predictions, and support restoration planning. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>The dataset provides georeferenced, annotated Sentinel-2 and Hansen imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. Users can train AI models for landuse and landcover classification, detect deforestation, validate predictions, and support restoration planning. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring.</t>
+          <t>The AI application analyzes historical satellite imagery gereated landuse and landcover maps (2015-2024) and predicts future landuse and land-cover change, offering simple inputs including Sentinel-2 and Hansen datasets of tree cover and outputs such as classified maps and simulations for 2025 and 2030. It identifies deforestation, farmland expansion, and urban growth patterns, supporting evidence-based land management. While highly accurate (ANN: 85.2% OA), limitations include data inconsistencies, sampling bias, and reliance on remote-sensing quality. Ethical use requires adherence to responsible-AI assessment, transparency, and proper citation. The model runs on standard GIS/AI software (QGIS, google colab, Jupyter-notebook) with no special hardware. All derived datasets and protocols are open for reuse under an open license; users must credit the original project to strengthen community knowledge and track downstream impact.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>The AI application analyzes historical satellite imagery gereated landuse and landcover maps (2015-2024) and predicts future landuse and land-cover change, offering simple inputs including Sentinel-2 and Hansen datasets of tree cover and outputs such as classified maps and simulations for 2025 and 2030. It identifies deforestation, farmland expansion, and urban growth patterns, supporting evidence-based land management. While highly accurate (ANN: 85.2% OA), limitations include data inconsistencies, sampling bias, and reliance on remote-sensing quality. Ethical use requires adherence to responsible-AI assessment, transparency, and proper citation. The model runs on standard GIS/AI software (QGIS, google colab, Jupyter-notebook) with no special hardware. All derived datasets and protocols are open for reuse under an open license; users must credit the original project to strengthen community knowledge and track downstream impact.</t>
+          <t>One can immediately use this AI system to classify landuse and landcover types, detect deforestation, and generate LULC predictions for 2025–2030. Users can replicate the full workflow from preprocessing imagery, training ANN models, and simulating future change scenarios to support forest monitoring, restoration planning, district land-use decision-making, or environmental reporting. Researchers can extend the work by integrating socio-economic variables, testing hybrid models, adding additional years of imagery, or adapting the model to new districts. Replication requires awareness of limitations such as sampling imbalance, image quality differences, and potential classification bias; an ethical-AI review is recommended for all downstream use. Costs remain low because the tools (QGIS, GEE, SEPAL) and datasets are free; only compute for model training (standard PCs) and technical time are required. All datasets, protocols, and documentation form an open public-good resource, with opportunities for collaboration through Makerere AI Lab and NFA.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>One can immediately use this AI system to classify landuse and landcover types, detect deforestation, and generate LULC predictions for 2025–2030. Users can replicate the full workflow from preprocessing imagery, training ANN models, and simulating future change scenarios to support forest monitoring, restoration planning, district land-use decision-making, or environmental reporting. Researchers can extend the work by integrating socio-economic variables, testing hybrid models, adding additional years of imagery, or adapting the model to new districts. Replication requires awareness of limitations such as sampling imbalance, image quality differences, and potential classification bias; an ethical-AI review is recommended for all downstream use. Costs remain low because the tools (QGIS, GEE, SEPAL) and datasets are free; only compute for model training (standard PCs) and technical time are required. All datasets, protocols, and documentation form an open public-good resource, with opportunities for collaboration through Makerere AI Lab and NFA.</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
+          <t>Makerere University, College of Agriculture, College of computing and Information science and the National Forestry Authority</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Makerere University, College of Agriculture, College of computing and Information science and the National Forestry Authority</t>
+          <t>Alondra Arellano</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Alondra Arellano</t>
+          <t>ui_35</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3724,86 +3728,86 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ui_36</t>
+          <t>Residential Electricity Consumption Dataset for Sri Lanka</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Residential Electricity Consumption Dataset for Sri Lanka</t>
+          <t>Towards Reliable Detection of Inefficient Residential Electricity Usage for Policy Intervention</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Towards Reliable Detection of Inefficient Residential Electricity Usage for Policy Intervention</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
         <is>
           <t>This project aims to develop a longitudinal household-level electricity dataset by integrating repeated survey data with high-frequency smart meter &amp; non-smart meter data. The survey component captures detailed information about household demographics, dwelling characteristics, appliance ownership, and energy-related behaviors, enabling these attributes to be linked to observed electricity consumption patterns.
 The resulting dataset is meant to facilitate analysis around experimentation with behavioral nudges, tariff reforms, and other demand-side management solutions relevant to energy affordability, efficiency, and policy in Sri Lanka.</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://ieee-dataport.org/open-access/residential-electricity-consumption-dataset-sri-lanka-recon-sl</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://ieee-dataport.org/open-access/residential-electricity-consumption-dataset-sri-lanka-recon-sl</t>
+          <t>https://github.com/LIRNEasia/SL_electricity_consumption</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://github.com/LIRNEasia/SL_electricity_consumption</t>
+          <t>SGD 7: Affordable and Clean Energy</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SGD 7: Affordable and Clean Energy</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
-        <is>
-          <t>Tabular</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">Merl Chandana - Team Lead, Data Algorithms &amp; Policy (merl@lirneasia.net)
 Nilusha Kapugama - COO, LIRNEasia (nilusha@lirneasia.net) </t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
         <is>
           <t>Limitations include limited representativeness due to smart meter coverage spanning only about 10% of LECO customers, residual missingness and contiguous gaps in smart meter time-series data that reduce suitability for fine-grained analysis, and potential recall or estimation bias in selected self-reported survey variables.
 To support responsible and ethical use, the dataset is released with explicit documentation of these limitations, clearly defined suitable and unsuitable use cases, and strong guidance against national-level inference, income estimation, appliance-level disaggregation, or real-time operational forecasting. All data are de-identified, aggregated at the household meter level, and intended strictly for research, re-use, and replication</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>The AI application analyzes historical smart meter electricity consumption data and household survey information to identify anomalous energy-use patterns associated with potentially inefficient appliance usage. It operates on six-hour interval load profiles collected over approximately one year from 1,438 households and produces outputs such as household-level anomaly scores, ranked lists of high-risk households, and comparative anomaly detection results across multiple modeling strategies. The system detects unusual consumption behavior using LSTM-based autoencoders, including a global model, cluster-based models derived from appliance usage patterns, and group-specific models based on socio-economic class. In the absence of labeled ground truth, model performance is evaluated using proxy indicators such as appliance age, household built year, power factor, and nighttime load ratio, both individually and in combination.  Limitations include the lack of true anomaly labels and potential bias introduced by proxy-based validation. The model is implemented using standard AI and data analysis tools (Python, TensorFlow/PyTorch) and can be run on consumer-grade hardware without specialized infrastructure. The framework is scalable, reproducible, and suitable for integration into utility analytics workflows to support evidence-based energy efficiency interventions.</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
-        <is>
-          <t>The AI application analyzes historical smart meter electricity consumption data and household survey information to identify anomalous energy-use patterns associated with potentially inefficient appliance usage. It operates on six-hour interval load profiles collected over approximately one year from 1,438 households and produces outputs such as household-level anomaly scores, ranked lists of high-risk households, and comparative anomaly detection results across multiple modeling strategies. The system detects unusual consumption behavior using LSTM-based autoencoders, including a global model, cluster-based models derived from appliance usage patterns, and group-specific models based on socio-economic class. In the absence of labeled ground truth, model performance is evaluated using proxy indicators such as appliance age, household built year, power factor, and nighttime load ratio, both individually and in combination.  Limitations include the lack of true anomaly labels and potential bias introduced by proxy-based validation. The model is implemented using standard AI and data analysis tools (Python, TensorFlow/PyTorch) and can be run on consumer-grade hardware without specialized infrastructure. The framework is scalable, reproducible, and suitable for integration into utility analytics workflows to support evidence-based energy efficiency interventions.</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">This dataset and AI system can be used immediately by energy utilities, researchers, and policymakers to analyze smart meter data and identify households with potentially inefficient electricity usage, enabling targeted energy audits, awareness programs, or appliance replacement initiatives without requiring appliance-level sub-metering. However, given the contextual nature of the dataset (data from one provider within Sri Lanka), real-life applications are best developed in parternships with Lanka Electricity Company (LECO). Lanka Electricity Company has also shared interest in using this in demand forecasting and planning.
 </t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>The dataset is publicly available under the Creative Commons Attribution 4.0 International (CC BY 4.0) license</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>The dataset is publicly available under the Creative Commons Attribution 4.0 International (CC BY 4.0) license</t>
+          <t xml:space="preserve">Lanka Electricity Company https://www.leco.lk/index_e.php </t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lanka Electricity Company https://www.leco.lk/index_e.php </t>
+          <t>Merl Chandana</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Merl Chandana</t>
+          <t>ui_36</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3845,7 +3849,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ui_37</t>
+          <t>Eyes on the Ground Image Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3855,46 +3859,46 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eyes on the Ground Image Data</t>
+          <t>This machine learning dataset of smallholder farmer's fields includes georeferenced crop images along with labels on input use, crop management, phenology, crop damage, and yields, collected across 8 counties in Kenya. This dataset enables the development of AI systems to monitor crop conditions, predict yields, and support agricultural decision-making for smallholder farmers.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>This machine learning dataset of smallholder farmer's fields includes georeferenced crop images along with labels on input use, crop management, phenology, crop damage, and yields, collected across 8 counties in Kenya. This dataset enables the development of AI systems to monitor crop conditions, predict yields, and support agricultural decision-making for smallholder farmers.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
           <t>https://radiantearth.github.io/stac-browser/#/external/raw.githubusercontent.com/khufkens/EotG_data/main/release_v1/EotG_images/catalog.json</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Lilian Waithaka, Koen Hufkens, Berber Kramer and Benson Njuguna</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ui_37</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3922,7 +3926,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ui_38</t>
+          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3932,46 +3936,46 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High-Accuracy Maize Plot Location and Yield Dataset in East Africa</t>
+          <t>This dataset includes corrected geolocations of fields, improving the usability of the most expansive Eastern Africa crop cut yield estimation. Collected by the non-profit One Acre Fund from 2015 – 2019, this dataset covers major crop producing regions in Kenya, Rwanda, and Tanzania. It enables accurate yield mapping and agricultural monitoring across East Africa.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>This dataset includes corrected geolocations of fields, improving the usability of the most expansive Eastern Africa crop cut yield estimation. Collected by the non-profit One Acre Fund from 2015 – 2019, this dataset covers major crop producing regions in Kenya, Rwanda, and Tanzania. It enables accurate yield mapping and agricultural monitoring across East Africa.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
           <t>https://drive.google.com/drive/folders/140eLeY3Z_JALFa0B77ZTP9gFt-mSPWXl</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>One Acre Fund</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>One Acre Fund</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
           <t>Kenya, Rwanda, Tanzania</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ui_38</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -3999,7 +4003,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ui_39</t>
+          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4009,46 +4013,46 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sensor Based Aquaponics Fish Pond Datasets: IoT Fish Pond Monitoring Datasets</t>
+          <t>This project built a remotely monitored and controlled Internet of Things (IoT) fish pond water quality management system for the generation of labeled datasets both for conventional ponds and the aquaponic pond systems. It enables monitoring and optimization of water quality parameters for sustainable aquaculture.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>This project built a remotely monitored and controlled Internet of Things (IoT) fish pond water quality management system for the generation of labeled datasets both for conventional ponds and the aquaponic pond systems. It enables monitoring and optimization of water quality parameters for sustainable aquaculture.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
           <t>https://www.kaggle.com/ogbuokiriblessing/sensor-based-aquaponics-fish-pond-datasets</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 6 (Clean water and sanitation)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Udanor Collins, Blessing Ogbuokiri, and Nweke Onyiny</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>ui_39</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4076,7 +4080,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ui_40</t>
+          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4086,46 +4090,46 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Machine Learning Datasets for Crop Pest and Disease Diagnosis: Crop Imagery and Spectrometry Data</t>
+          <t>This dataset contains a repository of image and spectrometry datasets for five main food security crops in Sub-Saharan Africa: cassava, maize, beans, bananas, and cocoa. Collected and curated in collaboration with the in-country agricultural experts, the datasets deliver a wide range of machine learning applications, including classification, object detection, early crop disease detection, and spatial analysis. The team collected and annotated 127,046 images and 39,300 spectral data points.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>This dataset contains a repository of image and spectrometry datasets for five main food security crops in Sub-Saharan Africa: cassava, maize, beans, bananas, and cocoa. Collected and curated in collaboration with the in-country agricultural experts, the datasets deliver a wide range of machine learning applications, including classification, object detection, early crop disease detection, and spatial analysis. The team collected and annotated 127,046 images and 39,300 spectral data points.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
           <t>https://dataverse.harvard.edu/dataverse/airlabug/</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Joyce Nakatumba-Nabende, Andrew Katumba, Claire Babirye, Jeremy Francis Tusubira, Godliver Owomugisha, Neema Mduma, Darlington Akogo, Blessing Sibanda</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
           <t>Uganda, Tanzania, Ghana</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>ui_40</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4153,7 +4157,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ui_41</t>
+          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4163,46 +4167,46 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A Decision-Supporting Tool for Developing Community-led Land Use Plans</t>
+          <t>This dataset focuses on locations with predominantly pastoral communities in northern Tanzania to identify fine and broad-scale movements of livestock and land use patterns and to understand how these relate to communal conflicts. It is a high-quality, accurate and labeled dataset containing detailed information on ~ 2000 communal resources (e.g., rangelands, water points, and dips) and their use patterns for over 220 villages across four large districts in northern Tanzania, representative of pastoral systems of livestock production in East Africa.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>This dataset focuses on locations with predominantly pastoral communities in northern Tanzania to identify fine and broad-scale movements of livestock and land use patterns and to understand how these relate to communal conflicts. It is a high-quality, accurate and labeled dataset containing detailed information on ~ 2000 communal resources (e.g., rangelands, water points, and dips) and their use patterns for over 220 villages across four large districts in northern Tanzania, representative of pastoral systems of livestock production in East Africa.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
           <t>http://dtlp.nottech.co.tz/index.html</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 16 (Peace, Justice and Strong Institutions)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Gladness Mwanga (gladnessg@nm-aist.ac.tz), Divine Ekwem (divine.ekwem@glasgow.ac.uk)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Gladness Mwanga (gladnessg@nm-aist.ac.tz), Divine Ekwem (divine.ekwem@glasgow.ac.uk)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
           <t>Tanzania</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>ui_41</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4230,7 +4234,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ui_42</t>
+          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4240,46 +4244,46 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Enhanced Agriculture Datasets for Remote Crop Monitoring to Provide Access to Essential Social and Financial Services to Smallholder Farmers in Zimbabwe</t>
+          <t>The project created labeled yield estimates from 3000 farmers, and was used to train prediction models for yield prediction across the country, consequently using the dataset to generate high resolution crop mask layers for the different value chains. The yield prediction models were enhanced by other biophysical datasets ranging from soil properties and climate related indicators. The datasets proved a concept of scalable machine learning models training, which may be able to respond more appropriately and cost-effectively to agricultural stressors.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>The project created labeled yield estimates from 3000 farmers, and was used to train prediction models for yield prediction across the country, consequently using the dataset to generate high resolution crop mask layers for the different value chains. The yield prediction models were enhanced by other biophysical datasets ranging from soil properties and climate related indicators. The datasets proved a concept of scalable machine learning models training, which may be able to respond more appropriately and cost-effectively to agricultural stressors.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/10060610</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Seth Odhiambo (sodhiambo@pula.io)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Seth Odhiambo (sodhiambo@pula.io)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
           <t>Zimbabwe</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>ui_42</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4307,7 +4311,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ui_43</t>
+          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4317,46 +4321,46 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A region-wide, multi-year set of crop field boundary labels for Africa</t>
+          <t>This dataset provides continent-wide crop field labels for Africa, improving the availability and use of crop field boundary (parcel) maps. It contains 42,403 annotated geospatial polygons indicating the boundaries of individual crop fields spanning the years 2017-2023. This enables the development of automated field boundary detection systems for agricultural monitoring across Africa.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>This dataset provides continent-wide crop field labels for Africa, improving the availability and use of crop field boundary (parcel) maps. It contains 42,403 annotated geospatial polygons indicating the boundaries of individual crop fields spanning the years 2017-2023. This enables the development of automated field boundary detection systems for agricultural monitoring across Africa.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/11060871</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Mary Dziedzorm Afenyo (mary@farmerline.co), Lyndon Estes (lestes@clarku.edu), Primož Kovačič (primoz@spatialcollective.com)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mary Dziedzorm Afenyo (mary@farmerline.co), Lyndon Estes (lestes@clarku.edu), Primož Kovačič (primoz@spatialcollective.com)</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
           <t>Multi-country Africa</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ui_43</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4384,7 +4388,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ui_44</t>
+          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4394,46 +4398,46 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CropHarvest: Informing decision-making around agricultural development, early warning systems, and trade in Sub-Saharan Africa</t>
+          <t>CropHarvest increases the understanding of the main types of food production in Sub-Saharan Africa and can help inform decision-making around agricultural development, early warning systems, and regional trade. It is a global, open-source remote sensing dataset for crop-type classification in Sub-Saharan Africa – specifically in Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, and Nigeria. The team expanded on an existing dataset to include new labeled data points, ground data for crop type mapping, street-level images, crowdsourced labeled images, and price data.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CropHarvest increases the understanding of the main types of food production in Sub-Saharan Africa and can help inform decision-making around agricultural development, early warning systems, and regional trade. It is a global, open-source remote sensing dataset for crop-type classification in Sub-Saharan Africa – specifically in Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, and Nigeria. The team expanded on an existing dataset to include new labeled data points, ground data for crop type mapping, street-level images, crowdsourced labeled images, and price data.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
           <t>https://github.com/nasaharvest/cropharvest</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Catherine Nakalembe (cnakalem@umd.edu)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Catherine Nakalembe (cnakalem@umd.edu)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
           <t>Kenya, Mali, Togo, Rwanda, Uganda, Ethiopia, Malawi, Zambia, Tanzania, Namibia, Sudan, Nigeria</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ui_44</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4461,7 +4465,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ui_45</t>
+          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4471,46 +4475,46 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Improving livelihoods in Ghana and Uganda: Drone-based Agricultural Dataset for Crop Yield Estimation of cashew, cocoa, and coffee</t>
+          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa. It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>This dataset supports yield estimation, crop type detection and classification, fruit detection and counting, and fruit maturity stage detection (unripe, ripe, and spoiled) for three products that are important sources of livelihood for millions of households in Sub-Saharan Africa. It contains 14,870 drone images with bounding box annotations of cashew, cocoa, and coffee trees collected across multiple farms in Ghana and Uganda. This dataset will help transform African agriculture into agribusiness by allowing for the development of yield estimation solutions that enable farmers to make good business decisions.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
           <t>https://huggingface.co/datasets/KaraAgroAI/Drone-based-Agricultural-Dataset-for-Crop-Yield-Estimation</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SDG 2 (End hunger, achieve food security, sustainable agriculture), SDG 1 (No Poverty)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Darlington Akogo (darlington@gudra-studio.com)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Darlington Akogo (darlington@gudra-studio.com)</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
           <t>Ghana, Uganda</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ui_45</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4538,7 +4542,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ui_46</t>
+          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4548,46 +4552,46 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Machine Learning Dataset for Rabies Diagnosis and Outbreak Prediction</t>
+          <t>This dataset will help in the real-time and remote diagnosis of rabies disease for humans and animals in low-resource settings. A time series approach can be applied to the outbreak dataset to predict the number of rabies cases likely to occur within an area after a given time interval. This approach can help with resource mobilization, too, such as identifying the number of vaccines required in a specific area at a given time. The number of observations from the two datasets is 12,684. There are three datasets for rabies diagnosis for animals and humans, with 7,081 and 4,585 observations, respectively. In the outbreak prediction dataset, 1,018 observations were accounted for.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>This dataset will help in the real-time and remote diagnosis of rabies disease for humans and animals in low-resource settings. A time series approach can be applied to the outbreak dataset to predict the number of rabies cases likely to occur within an area after a given time interval. This approach can help with resource mobilization, too, such as identifying the number of vaccines required in a specific area at a given time. The number of observations from the two datasets is 12,684. There are three datasets for rabies diagnosis for animals and humans, with 7,081 and 4,585 observations, respectively. In the outbreak prediction dataset, 1,018 observations were accounted for.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/10068758</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Asa Emmanuel: asakalonga@gmail.com, Kennedy Lushasi: klushasi@ihi.or.tz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Asa Emmanuel: asakalonga@gmail.com, Kennedy Lushasi: klushasi@ihi.or.tz</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
           <t>Global</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>ui_46</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4615,7 +4619,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ui_47</t>
+          <t>Childhood Malnutrition in Chile</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4625,46 +4629,46 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Childhood Malnutrition in Chile</t>
+          <t>This data repository will evaluate factors that contribute to child malnutrition in Chile and children's nutritional status, as well as the associated costs. The focus at this stage is on estimating health costs associated with child malnutrition and identifying biopsychosocial determinants that lead to it.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>This data repository will evaluate factors that contribute to child malnutrition in Chile and children's nutritional status, as well as the associated costs. The focus at this stage is on estimating health costs associated with child malnutrition and identifying biopsychosocial determinants that lead to it.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
           <t>https://goblab.uai.cl/proyecto-reduccion-de-la-malnutricion-infantil-en-chile/</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Maria Paz Hermosilla: paz.hermosilla@uai.cl</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Maria Paz Hermosilla: paz.hermosilla@uai.cl</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
           <t>Chile</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>ui_47</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4692,7 +4696,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ui_48</t>
+          <t>Lacuna Malaria Datasets</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4702,46 +4706,46 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lacuna Malaria Datasets</t>
+          <t>This dataset will aid in the diagnosis of malaria. The dataset contains annotated images of blood samples collected in Uganda and Ghana with objects of interest, including parasites and white blood cells. It significantly increases the number of available microscopy images â€“ including metadata â€“ by 6,000 thick blood slides and 2,000 thin blood slides for use in object detection research and other areas of inquiry.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>This dataset will aid in the diagnosis of malaria. The dataset contains annotated images of blood samples collected in Uganda and Ghana with objects of interest, including parasites and white blood cells. It significantly increases the number of available microscopy images â€“ including metadata â€“ by 6,000 thick blood slides and 2,000 thin blood slides for use in object detection research and other areas of inquiry.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/VEADSE</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Rose Nakasi: g.nakasi.rose@gmail.com or rose.nakasi@mak.ac.ug</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Rose Nakasi: g.nakasi.rose@gmail.com or rose.nakasi@mak.ac.ug</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
           <t>Uganda, Ghana</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ui_48</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4769,7 +4773,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ui_49</t>
+          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4779,46 +4783,46 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Intraoperative Anesthesia and Outcomes Dataset: Improving patient outcomes by predicting risk of mortality and post-operative recovery</t>
+          <t>This dataset can be used to identify patterns of intraoperative anesthesia practice and predict postoperative length of stay and risk of mortality based on intraoperative variables. It includes 2,066 intraoperative anesthesia records from two academic centers in sub-Saharan Africa. The team photographed completed intraoperative anesthesia records using a smartphone, de-identified the images, and securely uploaded them to a HIPAA-compliant server. Using a combination of computer vision AI and manual extraction techniques, the team collected comprehensive intraoperative data: demographic data, medication data, hemodynamic data, physiological data, anesthesia type, surgery type, postoperative length of stay, and 30-day postoperative mortality.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>This dataset can be used to identify patterns of intraoperative anesthesia practice and predict postoperative length of stay and risk of mortality based on intraoperative variables. It includes 2,066 intraoperative anesthesia records from two academic centers in sub-Saharan Africa. The team photographed completed intraoperative anesthesia records using a smartphone, de-identified the images, and securely uploaded them to a HIPAA-compliant server. Using a combination of computer vision AI and manual extraction techniques, the team collected comprehensive intraoperative data: demographic data, medication data, hemodynamic data, physiological data, anesthesia type, surgery type, postoperative length of stay, and 30-day postoperative mortality.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
           <t>https://portal.ithriv.org/#/public_commons/project/d9fc062c-64c9-4481-80e7-3db4aba17e00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Bhiken Naik: bin4n@uvahealth.org</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Bhiken Naik: bin4n@uvahealth.org</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
           <t>Sub-Saharan Africa</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ui_49</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4846,7 +4850,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ui_50</t>
+          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4856,46 +4860,46 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brain Tumor Segmentation Africa (BraTS-Africa) Dataset</t>
+          <t>The BraTS-Africa dataset is an aggregation of magnetic resonance imaging (MRI) scans from six centers in Nigeria aimed at providing a public dataset for the development of machine-learning solutions for the management of brain tumors in African patients. This dataset serves as a starting framework for future expansion in other regions of Africa. The team processed and annotated a total of 584 images from 146 patient scans. Ninety-five of these scans are presumed to have diffuse glioma, and 51 of them have other types of central nervous system (CNS) neoplasms. Expert radiologists annotated three distinct tumor sub-regions to delineate the enhancing tumor (ET), the necrotic tumor core (NCR), and the peritumoral oedematous/infiltrated tissue (ED) sub-regions.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The BraTS-Africa dataset is an aggregation of magnetic resonance imaging (MRI) scans from six centers in Nigeria aimed at providing a public dataset for the development of machine-learning solutions for the management of brain tumors in African patients. This dataset serves as a starting framework for future expansion in other regions of Africa. The team processed and annotated a total of 584 images from 146 patient scans. Ninety-five of these scans are presumed to have diffuse glioma, and 51 of them have other types of central nervous system (CNS) neoplasms. Expert radiologists annotated three distinct tumor sub-regions to delineate the enhancing tumor (ET), the necrotic tumor core (NCR), and the peritumoral oedematous/infiltrated tissue (ED) sub-regions.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
           <t>https://www.cancerimagingarchive.net</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Udunna Anazodo: udunna.anazodo@mcgill.ca</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Udunna Anazodo: udunna.anazodo@mcgill.ca</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ui_50</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -4923,7 +4927,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ui_51</t>
+          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4933,46 +4937,46 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AI-Assisted Smartphone Microscopy for detection of Diarrhea Parasites</t>
+          <t>This dataset helps to detect diarrhea-causing parasites in resource-limited rural areas, particularly across the Global South, where access to expensive diagnostic tools is limited. It contains approximately 400,000 microscopic slide images from water, vegetable, and stool samples from four different provinces across Nepal, making it one of the largest datasets of its kind. The team collected water samples from different sources (i.e., tap water, bottled water, lake, river, pond, stream, spring water, wetland, well, and borewell) and used seven different types of vegetables. Using the dataset and annotations available, this team trained different deep-learning models to automatically detect parasites, specifically Giardia and Cryptosporidium cysts.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>This dataset helps to detect diarrhea-causing parasites in resource-limited rural areas, particularly across the Global South, where access to expensive diagnostic tools is limited. It contains approximately 400,000 microscopic slide images from water, vegetable, and stool samples from four different provinces across Nepal, making it one of the largest datasets of its kind. The team collected water samples from different sources (i.e., tap water, bottled water, lake, river, pond, stream, spring water, wetland, well, and borewell) and used seven different types of vegetables. Using the dataset and annotations available, this team trained different deep-learning models to automatically detect parasites, specifically Giardia and Cryptosporidium cysts.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/13913469</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Bishesh Khanal: bishesh.khanal@naamii.org.np</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Bishesh Khanal: bishesh.khanal@naamii.org.np</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
           <t>Nepal</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ui_51</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5000,7 +5004,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ui_52</t>
+          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5010,46 +5014,46 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Project Climate Change, Health, and Artificial Intelligence (CCHAIN): Public Health Data Insights for the Philippines</t>
+          <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The Project CCHAIN dataset is an open, linked, analysis-ready dataset of validated health, climate, environmental, and socioeconomic variables collected at the village ("barangay") level in 12 Philippine cities spanning 20 years (2003-2022). This dataset includes observations of about 17 diseases collected through field visits to the Philippines Department of Health (DOH) and the Philippine Statistical Authority (PSA). Focusing on the village or "barangay," the smallest administrative unit in the Philippines, also helps disaggregate health risks for vulnerable communities, particularly those in informal settlements, and provides actionable insights for local governments.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
           <t>https://thinkingmachines.github.io/project-cchain/</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Thinking Machines Data Science | data-for-development@thinkingmachin.es</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Thinking Machines Data Science | data-for-development@thinkingmachin.es</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
           <t>Philippines</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>ui_52</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5077,7 +5081,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ui_53</t>
+          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5087,46 +5091,46 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Air quality dataset of abattoir centers in Southern Nigeria</t>
+          <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>This air quality dataset is the first of its kind in the country from abattoir centers. The localized dataset is crucial in air quality monitoring and prediction, as well as accurate modeling of the air quality index for early warning signals and modeling of health risk. The data was obtained from abattoir centers in Southern Nigeria. The team collected data from representative samples of various states (i.e., Anambra, Enugu, Abia, Imo, Ebonyi, and Delta) within the research area. The team visited 27 stations and conducted on-site investigations, collecting over 200,000 numerical values of particulate matter (PM) concentrations using 10 air quality sensors for PM1, PM2.5, and PM10. Additionally, aerial view images were captured using a drone at varying heights (10m, 20m, 30m) during operational hours; the images will be trained with satellite imagery for the prediction of PM values. Exposure to particulate matter and black carbon released in abattoirs has detrimental health outcomes with elevated morbidity and mortality, as shown by previous studies. This project was undertaken by the Alliance for Progressive and Sustainable Environment (APSE), a local NGO focused on environmental sustainability (see more details here: www.apse-ngo.org).</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
           <t>https://www.kaggle.com/datasets/collinsudanor/abattoir-air-quality-dataset/data</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Emmanuel Chukwuma | emmanuel.chukwuma@apse-ngo.org</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Emmanuel Chukwuma | emmanuel.chukwuma@apse-ngo.org</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>ui_53</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5154,7 +5158,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ui_54</t>
+          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5164,46 +5168,46 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Global Horizontal Irradiance Dataset for Mauritius, Rodrigues, and Agalega Islands</t>
+          <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>This dataset includes 146,025 real-time solar irradiance data lines from different locations around Mauritius, Rodrigues, and Agaléga. The solar irradiance data (GHI in W/m2) spans 2017 to 2021, at an interval of one hour, and covers the hours of 07:00-18:00 each day. This dataset allows for the real-time visualization of the solar irradiance profile at the specified locations, helping with better assessment and planning of solar-generated power. The team is now collecting data (from 2023 on) at an interval of 15 minutes and plans to update this data repository to reflect that in the future. The targeted beneficiaries for this project are the Government of Mauritius, which has a goal of 60% electricity generation from renewable energy sources by the year 2030. Similarly, the Mauritius Renewable Energy Agency, which is tasked with ensuring the country's energy demand is increasingly met by renewable energy and keeping up with international commitments, can use this data on solar irradiance and forecasting mechanisms to better manage the utility's power plants, minimize carbon emissions, ensure no loss of loads (blackouts), and allow higher penetration of photovoltaic (PV) projects in the country. With free online solar maps and accuracy-enhanced solar energy data, local PV plant operators will also have accurate information for PV performance appraisal. Additionally, the public at large can benefit from a free online solar energy platform, improving acceptance of solar PV technology and increasing penetration of clean technologies in the country to further reduce greenhouse emissions. Finally, machine learning models can be trained for intra-day, daily, and even weekly predictions of the solar irradiance profiles.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
           <t>https://www.scidb.cn/en/detail?dataSetId=2b499b91a4464fffa9f60fc8b51da03e&amp;version=V2</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
           <t>Mauritius, Rodrigues, and Agalega Islands</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>ui_54</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5231,7 +5235,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ui_55</t>
+          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5241,46 +5245,46 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Labelled Open Solar Panel Data to measure solar energy adoption in Madagascar</t>
+          <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>This team annotated 2,125 Google Earth satellite images and 9,202 drone images, forming a combination of low and high-definition solar panel views in Madagascar. The Madagascar Initiatives for Digital Innovation (MAIDI) team performed field checks for up to 25% of satellite images and, in total, annotated 22,488 polygons. This dataset will help data scientists and users develop a solar panel detection algorithm to measure solar energy adoption across Madagascar. Notably, this project represented all regions of the country; instead of focusing only on big cities, it also covered average and small villages as well as coasts and mountains.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
           <t>https://openstat-madagascar.com/bdd/energie-et-environnement/131-donnees-sur-l-energie-solaire-et-labellisation-d-images-de-panneaux-photovoltaiques-a-madagascar</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Fabienne Rafidiharinirina | f.rafidiharinirina@association-maidi.mg or assomaidi@gmail.com</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Fabienne Rafidiharinirina | f.rafidiharinirina@association-maidi.mg or assomaidi@gmail.com</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
           <t>Madagascar</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>ui_55</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5308,7 +5312,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ui_56</t>
+          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5318,46 +5322,46 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Climate Energy Dataset for Off-Grid Electricity Infrastructure</t>
+          <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>This dataset comprises real-time electrical measurements of a specific climate zone in Pakistan, the Kalam Region, showcasing the energy generation and demand within an off-grid electricity infrastructure. It can be used for research in energy systems analysis, climate change studies, electrical engineering, and artificial intelligence applications. It includes voltages, currents, and power factors for three-phase and single-phase systems across generation, distribution, and consumption stages. Additionally, the dataset incorporates seven different climate parameters from the ERA5 dataset (provided by the Copernicus Climate Change Service), generating a total of 85,596 data points in areas such as temperature, dew point, wind components, precipitation, snowfall, and snow cover. Collected every five minutes from June 3, 2023, to October 24, 2024, it includes over 45 million instances covering data from four micro-hydropower generators, 26 transformers (in addition to four data acquisition systems installed at Micro Hydro Power Plants (MHPs), and 585 end users. With local support, the team will continue monitoring the data until June 2025.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
           <t>https://zenodo.org/records/14195731</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SDG 13 (Climate Action)</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SDG 13 (Climate Action)</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Dr. Zeeshan Shafiq | zeeshanshafiq@uetpeshawar.edu.pk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Dr. Zeeshan Shafiq | zeeshanshafiq@uetpeshawar.edu.pk</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
           <t>Pakistan</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ui_56</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5385,7 +5389,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ui_57</t>
+          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5395,46 +5399,46 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A Nigerian Twitter Sentiment Corpus for Multilingual Sentiment Analysis</t>
+          <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>This dataset is the first large-scale human-annotated Twitter sentiment dataset for Hausa, Igbo, Nigerian-Pidgin, and Yorùbá, the four most widely spoken languages in Nigeria.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
           <t>https://github.com/hausanlp/NaijaSenti</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shamsuddeen Hassan Muhammad, David Ifeoluwa Adelani, Sebastian Ruder, Ibrahim Said Ahmad, Idris Abdulmumin, Bello Shehu Bello, Monojit Choudhury, Chris Chinenye Emezue, Saheed Salahudeen Abdullahi, Anuoluwapo Aremu, Alipio Jeorge, and Pavel Brazdil</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>ui_57</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5462,7 +5466,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ui_58</t>
+          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5472,46 +5476,46 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Machine Translation Benchmark Dataset for Languages in the Horn of Africa</t>
+          <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>This evaluation dataset automatically quantifies the quality of machine translation systems for Afar, Amharic, Oromo, Somali and Tigrinya.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
           <t>https://github.com/asmelashteka/HornMT</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Asmelash Teka Hadgu, Gebrekirstos G. Gebremeskel, Abel Aregawi</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
           <t>Horn of Africa (Ethiopia, Eritrea)</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>ui_58</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5539,7 +5543,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ui_59</t>
+          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5549,46 +5553,46 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kencorpus: Kenyan Languages Corpus for Machine Learning and Natural Language Processing</t>
+          <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>This project collected text and speech corpora for three languages in Kenya: Kiswahili, Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of 4,442 texts were collected and 1,152 files containing spontaneous speech data totaling 176 hours.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/6N5V1K</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Owen McOnyango (Maseno University), Florence Indede (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Owen McOnyango (Maseno University), Florence Indede (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>ui_59</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5616,7 +5620,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ui_60</t>
+          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5626,46 +5630,46 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KenPos: Kenyan Languages Part of Speech Tagged dataset</t>
+          <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>This project developed a Part of Speech (POS) Tagged dataset of 2 languages in Kenya: Dholuo and 3 Luhya dialects (Lumarachi, Lulogooli, and Lubukusi). The project tagged approximately 143,000 words.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/KLCKL5</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lilian D.A. Wanzare (Maseno University), Barack Wanjawa (University of Nairobi), Edward Ombui (Africa Nazarene University), Lawrence Muchemi (University of Nairobi)</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>ui_60</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5693,7 +5697,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ui_61</t>
+          <t>KenSpeech: Swahili Speech Transcriptions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5703,46 +5707,46 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KenSpeech: Swahili Speech Transcriptions</t>
+          <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>This project produced a speech dataset that includes both read and spontaneous speech recordings, recorded in Kenya with native Swahili speakers, and corresponding transcripts. In total, the dataset includes 27 hours, 31 minutes, 50 seconds of speech data from 26 speakers.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/YHXJSU</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Dorcas Awino (University of Nairobi), Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (Maseno University), Owen McOnyango (Maseno University), Florence Indede (Maseno University)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Dorcas Awino (University of Nairobi), Lawrence Muchemi (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (Maseno University), Owen McOnyango (Maseno University), Florence Indede (Maseno University)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>ui_61</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5770,7 +5774,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ui_62</t>
+          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5780,46 +5784,46 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KenTrans: A Parallel Corpora for Swahili and local Kenyan Languages</t>
+          <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>This project produced a parallel corpus between Swahili and two other Kenya Languages: Dholuo and 3 Luhya dialects (Lumarachi, Logooli and Lubukusu). A total of about 12,400 sentences were translated to Kiswahili.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/NOAT0W</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Lilian D.A Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (University of Nairobi), Lawrence Muchemi (University of Nairobi)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Lilian D.A Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Edward Ombui (Africa Nazarene University), Barack Wanjawa (University of Nairobi), Lawrence Muchemi (University of Nairobi)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>ui_62</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5847,7 +5851,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ui_63</t>
+          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5857,46 +5861,46 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KenSwQuAD – A Question Answering Dataset for Swahili Low Resource Language</t>
+          <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>This project produced a large Machine Reading Comprehension dataset for the Kiswahili Language. A total of 7,526 Question-Answer (QA) pairs were developed based on 1,445 Swahili story texts.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/OTL0LM</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Barack Wanjawa (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Barack Wanjawa (University of Nairobi), Lilian D.A. Wanzare (Maseno University), Florence Indede (Maseno University), Owen McOnyango (Maseno University), Lawrence Muchemi (University of Nairobi), Edward Ombui (Africa Nazarene University)</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
           <t>Kenya</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>ui_63</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5924,7 +5928,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ui_64</t>
+          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5934,46 +5938,46 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MasakhaNER 2.0: Named Entity Recognition datasets for 20 African languages</t>
+          <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MasakhaNER 2.0 is the largest human-annotated named entity recognition dataset for 20 African languages. Each language has between 4,800 – 11,000 parallel sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
           <t>https://github.com/masakhane-io/masakhane-ner/tree/main/MasakhaNER2.0/data</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
           <t>Africa (Multi-country)</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>ui_64</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -5997,7 +6001,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ui_65</t>
+          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6007,46 +6011,46 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MAFAND-MT: Masakhane Anglo &amp; Franco African News Corpus for Machine Translation</t>
+          <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>The MAFAND-MT dataset is a few thousand high-quality and human translated parallel sentences for 16 African languages in the news domain. Each language has between 1,466 – 7838 parallel sentences for training and/or evaluation.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
           <t>https://github.com/masakhane-io/lafand-mt</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
           <t>Africa (Multi-country)</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>ui_65</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6070,7 +6074,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ui_66</t>
+          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6080,46 +6084,46 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MasakhaPOS: Part-of-Speech Tagging Dataset for 20 African Languages</t>
+          <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MasakhaPOS is the largest human-annotated part of speech tagging dataset for 20 African languages. Each language has between 1200 – 1500 sentences for training and/or evaluation. The languages covered span across West, Central, East and Southern Africa.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
           <t>https://github.com/masakhane-io/masakhane-pos</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>David Ifeoluwa Adelani, D.ADELANI@UCL.AC.UK</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
           <t>Africa (Multi-country)</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>ui_66</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6143,7 +6147,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ui_67</t>
+          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6153,46 +6157,46 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Financial Inclusion Speech Dataset for some Ghanaian Languages</t>
+          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>This speech dataset for the Ghanian languages Akan (Akuapem Twi, Asante Twi, Fante) and Ga includes 104,000 utterances (speech) across the four dialects/languages with approximately 200 speakers per dialect/language. This amounts to about 148 hours of speech in total.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
           <t>https://github.com/Ashesi-Org/Financial-Inclusion-Speech-Dataset</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Dennis Asamoah Owusu, DOWUSU@ASHESI.EDU.GH</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Dennis Asamoah Owusu, DOWUSU@ASHESI.EDU.GH</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
           <t>Ghana</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>ui_67</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6216,7 +6220,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ui_68</t>
+          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6226,46 +6230,46 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IgboSynCorp: Dataset for Igbo Natural Language Processing Tasks</t>
+          <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>This dataset is the first spoken corpus of labelled and unlabeled datasets for Igbo Natural Language Processing (NLP) tasks. It consists of approximately 40 hours of naturally occurring Igbo speech that is representative of all the dialects of Igbo.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
           <t>https://dataverse.harvard.edu/dataverse/0000-0002-0068-6933</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Gerald Nweya (GERALDNWEYA@GMAIL.COM) and Emeka Onwuegbuzia (EONWUEGBUZIA@GMAIL.COM)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Gerald Nweya (GERALDNWEYA@GMAIL.COM) and Emeka Onwuegbuzia (EONWUEGBUZIA@GMAIL.COM)</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>ui_68</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6289,7 +6293,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ui_69</t>
+          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6299,46 +6303,46 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bayelemabaga Aligned Bambara-French Corpus for Machine Translation</t>
+          <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The Bayelemabaga dataset consists of 46,976 parallel machine translation-ready Bambara-French sentence pairs, originating from the Bambara Reference Corpus from INALCO's LLACAN Lab. The text is extracted from 264 text files.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
           <t>https://robotsmali-ai.github.io/datasets/</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Christopher Homan, christopher.m.homan.phd@gmail.com</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Christopher Homan, christopher.m.homan.phd@gmail.com</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
           <t>Mali/France</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>ui_69</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6362,7 +6366,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ui_70</t>
+          <t>Makerere University NLP Datasets</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6372,46 +6376,46 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Makerere University NLP Datasets</t>
+          <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Makerere University has created text and speech datasets for low-resourced East African Languages in Uganda, Tanzania, and Kenya. This dataset contains 10,000 parallel sentiment-tagged sentences, 100,000 Kiswahili sentences, 100,000 Luganda sentences, 40,037 Acoli sentences, and 39,999 Lumasaaba sentences.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
           <t>https://dataverse.harvard.edu/dataverse/makerereuniversitylacuna</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Andrew Katumba | andrew.katumba@mak.ac.ug</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Andrew Katumba | andrew.katumba@mak.ac.ug</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
           <t>Uganda, Tanzania, Kenya</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>ui_70</t>
+        </is>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6435,7 +6439,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ui_71</t>
+          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6445,46 +6449,46 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BIG-C: A Multimodal Multi-Purpose Dataset for Bemba</t>
+          <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The BIG-C (Bemba Image Grounded Conversations) dataset is comprised of multi-turn dialogues between Bemba speakers grounded on images, transcribed and translated to English. There are over 92,000 sentences, amounting to over 180 hours of speech data with corresponding Bemba transcriptions and English translations.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
           <t>https://github.com/csikasote/bigc</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Claytone Sikasote | claytonsikasote@gmail.com</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Claytone Sikasote | claytonsikasote@gmail.com</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
           <t>Zambia</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>ui_71</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6508,7 +6512,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ui_72</t>
+          <t>KALLAAMA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6518,46 +6522,46 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KALLAAMA</t>
+          <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>This dataset will strengthen natural language processing resources for Wolof, Pulaar, and Serer, the three most widely spoken languages in Senegal. This dataset's repository of transcribed speech includes over 55 hours in Wolof, 38 hours in Serer, and 31 hours in Pulaar.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
           <t>https://github.com/gauthelo/kallaama-speech-dataset</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Aminata Ndiaye | amina.ndiaye@jokalante.com and Elodie Gauthier | elodie.gauthier@orange.com</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Aminata Ndiaye | amina.ndiaye@jokalante.com and Elodie Gauthier | elodie.gauthier@orange.com</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
           <t>Senegal</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>ui_72</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6581,7 +6585,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ui_73</t>
+          <t>NaijaVoices: Our Language is Our Strength</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6591,46 +6595,46 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NaijaVoices: Our Language is Our Strength</t>
+          <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The NaijaVoices project has curated 1,867 hours of speech and text data featuring over 5,000 speakers in the three major Nigerian languages — Hausa, Igbo, and Yoruba. As of its release, it is the largest ever multi-speaker African speech dataset. The dataset consists of circa 1,917,686 instances.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
           <t>https://naijavoices.com/membership#membership_tiers</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>info@naijavoices.com</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>info@naijavoices.com</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
           <t>Nigeria</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>ui_73</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6654,7 +6658,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ui_74</t>
+          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6664,46 +6668,46 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AFRIDOC-MT: Document-level MT Corpus for African Languages</t>
+          <t>AFRIDOC-MT is a document-level and multi-way translation dataset from English into five African languages — Amharic, Hausa, Swahili, Yorùbá, and Zulu. The dataset comprises 334 health and 271 information technology news documents, all of which were human-translated from English to these languages. Each domain has at least 10,000 parallel sentences per language pair and supports multiway translation, allowing translation not only between English and the African languages but also among the African languages themselves. This dataset can be used to evaluate the ability of existing neural machine translation (NMT) models and large language models (LLMs) to translate at the document level.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AFRIDOC-MT is a document-level and multi-way translation dataset from English into five African languages — Amharic, Hausa, Swahili, Yorùbá, and Zulu. The dataset comprises 334 health and 271 information technology news documents, all of which were human-translated from English to these languages. Each domain has at least 10,000 parallel sentences per language pair and supports multiway translation, allowing translation not only between English and the African languages but also among the African languages themselves. This dataset can be used to evaluate the ability of existing neural machine translation (NMT) models and large language models (LLMs) to translate at the document level.</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
           <t>https://github.com/masakhane-io/afridoc-mt</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Jesujoba O. Alabi | jalabi@lsv.uni-saarland.de</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Jesujoba O. Alabi | jalabi@lsv.uni-saarland.de</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>ui_74</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6727,7 +6731,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ui_75</t>
+          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6737,46 +6741,46 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Masakhane-NLU: Conversational AI &amp; Benchmark datasets for African languages</t>
+          <t>This team has developed five conversational AI and benchmark datasets for 16 languages across the African continent: AfriXNLI (natural language inference), AfriMMLU (knowledge-based multi-choice questions), AfriMGSM (grade school mathematics), AfriIntent (intent classification), and AfriSlot (slot classification). These datasets cover languages including Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu. These text-only datasets are useful for conversational chatbots in real-life applications such as banking, restaurants, travel agencies, and more.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>This team has developed five conversational AI and benchmark datasets for 16 languages across the African continent: AfriXNLI (natural language inference), AfriMMLU (knowledge-based multi-choice questions), AfriMGSM (grade school mathematics), AfriIntent (intent classification), and AfriSlot (slot classification). These datasets cover languages including Amharic, Ewe, Hausa, Igbo, Lingala, Luganda, Oromo, Kinyarwanda, Shona, Sesotho, Swahili, Twi, Wolof, Xhosa, Yoruba and Zulu. These text-only datasets are useful for conversational chatbots in real-life applications such as banking, restaurants, travel agencies, and more.</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
           <t>https://github.com/masakhane-io/masakhane-nlu</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>David Adelani | david.adelani@mila.quebec</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>David Adelani | david.adelani@mila.quebec</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>ui_75</t>
+        </is>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6800,7 +6804,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ui_76</t>
+          <t>Lacuna PII Multilingual Dataset</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6810,46 +6814,46 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lacuna PII Multilingual Dataset</t>
+          <t>This dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The team collected 3,000 sentences for both Kanuri and Hausa, 5,000 for Lumasaba, and 4,000 for Luganda. Potential use cases include named entity recognition (NER), text classification, privacy-preserving data analysis and research, language modeling, machine translation, and linguistic research. The team aimed to curate a dataset that is gender inclusive, and their work highlighted the need for standardized guidelines for annotating low-resourced languages.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>This dataset contains annotated sentences with personally identifiable information (PII) in Luganda, Lumasaba, Hausa, and Kanuri. These four languages span Central and Eastern Uganda, Nigeria, Ghana, and Northern Cameroon. The team collected 3,000 sentences for both Kanuri and Hausa, 5,000 for Lumasaba, and 4,000 for Luganda. Potential use cases include named entity recognition (NER), text classification, privacy-preserving data analysis and research, language modeling, machine translation, and linguistic research. The team aimed to curate a dataset that is gender inclusive, and their work highlighted the need for standardized guidelines for annotating low-resourced languages.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
           <t>https://doi.org/10.7910/DVN/CGHWZE</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Andrew Katumba | katumba@mak.ac.ug, Milena Haykowska | milena.haykowska@clearglobal.org, Peter Nabende | nabende@gmail.com</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Andrew Katumba | katumba@mak.ac.ug, Milena Haykowska | milena.haykowska@clearglobal.org, Peter Nabende | nabende@gmail.com</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>ui_76</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6873,7 +6877,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ui_77</t>
+          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6883,42 +6887,46 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hate and Offensive Speech Detection Dataset for African Languages</t>
+          <t>AfriHate is a hate and offensive speech corpus for 15 African languages: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya. The dataset annotates tweets using "offensive," "hateful," and "normal" classes, with target classes such as politics, ethnicity, gender, religion, and disability. The team also created AfriEmotion for emotion detection. Overall, they collected and annotated 10,000 instances each for hate speech and emotion detection per language, making 150,000 annotated observations. This is the first publicly available dataset for hate and offensive speech detection in these target languages.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AfriHate is a hate and offensive speech corpus for 15 African languages: Hausa, Yoruba, Igbo, Nigerian Pidgin, Algerian Arabic, Moroccan Arabic, Swahili, IsiXhosa, IsiZulu, Kinyarwanda, Twi, Amharic, Oromo, Somali, Tigrinya. The dataset annotates tweets using "offensive," "hateful," and "normal" classes, with target classes such as politics, ethnicity, gender, religion, and disability. The team also created AfriEmotion for emotion detection. Overall, they collected and annotated 10,000 instances each for hate speech and emotion detection per language, making 150,000 annotated observations. This is the first publicly available dataset for hate and offensive speech detection in these target languages.</t>
+          <t>https://github.com/AfriHate/AfriHate</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Abinew Ali Ayele | abinewaliayele@gmail.com, Seid Muhie Yiman | muhie.yimam@uni-hamburg.de, Shamsuddeen Hassan Muhammad | muhammad@imperial.ac.uk</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Abinew Ali Ayele | abinewaliayele@gmail.com, Seid Muhie Yiman | muhie.yimam@uni-hamburg.de, Shamsuddeen Hassan Muhammad | muhammad@imperial.ac.uk</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>ui_77</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -6942,7 +6950,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ui_78</t>
+          <t>Ethio Speech Corpora</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6952,42 +6960,46 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ethio Speech Corpora</t>
+          <t>Ethio Speech Corpora comprises over 391 hours of recorded audio in six Ethiopian languages: Amharic (68 hours), Tigrigna (62 hours), Oromo (70 hours), Somali (56 hours), Afar (68 hours), and Sidama (68 hours). This project is a valuable resource for developing well-performing automatic speech recognition (ASR) systems for these languages in monolingual, multilingual, and cross-lingual setups. Use cases include dictation systems, transcription systems, assistive technologies, spoken dialogue systems, speech translation, and other speech technologies. The dataset maintains gender and age balance of readers across six working languages used across regional states of Ethiopia.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ethio Speech Corpora comprises over 391 hours of recorded audio in six Ethiopian languages: Amharic (68 hours), Tigrigna (62 hours), Oromo (70 hours), Somali (56 hours), Afar (68 hours), and Sidama (68 hours). This project is a valuable resource for developing well-performing automatic speech recognition (ASR) systems for these languages in monolingual, multilingual, and cross-lingual setups. Use cases include dictation systems, transcription systems, assistive technologies, spoken dialogue systems, speech translation, and other speech technologies. The dataset maintains gender and age balance of readers across six working languages used across regional states of Ethiopia.</t>
+          <t>https://ethiospeech.com/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Drone Imagery, Tabular, Other</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Solomon Teferra Abate | solomon.teferra@aau.edu.et</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Solomon Teferra Abate | solomon.teferra@aau.edu.et</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>ui_78</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -7011,7 +7023,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ui_79</t>
+          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7021,46 +7033,46 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Building Parallel Corpora for Kenya's Indigenous Languages and Kiswahili</t>
+          <t>This dataset was created to enable translation from Kiswahili, Kenya's national language, into three indigenous languages: Kidaw'ida, Kalenjin, and Dholuo. All three are low-resource languages, with Kidaw'ida having only around 400,000 speakers and being at immediate risk of loss. The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili, Kalenjin-Kiswahili, and Dholuo-Kiswahili, with each corpus averaging thirty thousand sentence pairs. The project has also contributed to Mozilla Common Voice Platform with 120 hours in Dholuo, 92 hours in Kalenjin, and 56 hours in Kidaw'ida for crowd-sourced voice recognition.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>This dataset was created to enable translation from Kiswahili, Kenya's national language, into three indigenous languages: Kidaw'ida, Kalenjin, and Dholuo. All three are low-resource languages, with Kidaw'ida having only around 400,000 speakers and being at immediate risk of loss. The dataset consists of three parallel corpora: Kidaw'ida-Kiswahili, Kalenjin-Kiswahili, and Dholuo-Kiswahili, with each corpus averaging thirty thousand sentence pairs. The project has also contributed to Mozilla Common Voice Platform with 120 hours in Dholuo, 92 hours in Kalenjin, and 56 hours in Kidaw'ida for crowd-sourced voice recognition.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
           <t>https://commonvoice.mozilla.org/en/datasets</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Audrey Mbogho | ambogho@usiu.ac.ke</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Audrey Mbogho | ambogho@usiu.ac.ke</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>ui_79</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -7084,7 +7096,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ui_80</t>
+          <t>Expanding a parallel corpus of Portuguese and the Bantu language Emakhuwa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7094,46 +7106,46 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Expanding a parallel corpus of Portuguese and the Bantu language Emakhuwa</t>
+          <t>This dataset includes the translation of 1,897 news articles comprising 660,242 words from Portuguese to Emakhuwa, an indigenous language of Mozambique. Each article includes news headline, content, and topic classification labels. Articles are divided into training (1,337), development (185), and testing (375) sets, categorized by topics: politics, economy, culture, sports, health, society, and world news. Use cases include topic classification, translation, and loanword recognition. The dataset has shown promising outcomes when fine-tuning multilingual models like ByT5, M2M100, and NLLB200, with improvements in translation quality using loanword information.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>This dataset includes the translation of 1,897 news articles comprising 660,242 words from Portuguese to Emakhuwa, an indigenous language of Mozambique. Each article includes news headline, content, and topic classification labels. Articles are divided into training (1,337), development (185), and testing (375) sets, categorized by topics: politics, economy, culture, sports, health, society, and world news. Use cases include topic classification, translation, and loanword recognition. The dataset has shown promising outcomes when fine-tuning multilingual models like ByT5, M2M100, and NLLB200, with improvements in translation quality using loanword information.</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/collections/LIACC/makhuwa-nlp-66a93ea22df7f4b31e96a5ab</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>https://huggingface.co/LIACC/datasets</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SDG 4</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Felermino D. M. A. Ali | felermino.ali@unilurio.ac.mz or felerminoali@gmail.com</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Felermino D. M. A. Ali | felermino.ali@unilurio.ac.mz or felerminoali@gmail.com</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
           <t>Multiple African Countries</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>ui_80</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -7155,29 +7167,105 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BenMangroves2425: Multidimensional open datasets for developing AI-based models on mangroves health and carbon stock</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BenMangroves2425: Multidimensional open datasets for developing AI-based models on mangroves health and carbon stock</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BenMangroves2425 integrates multi-source environmental, ecological, and socio-economic data for assessing mangrove health, degradation drivers, and restoration potential. The dataset includes:
+•        High-resolution drone imagery (multispectral and hyperspectral) for mangrove vegetation structure, canopy cover, and biomass estimation for 600 monitoring plots.
+•        In situ mangrove forest inventory measurements from 600 monitoring plots spanning the entire mangroves in Benin (which encompasses two RAMSAR sites). This covers tree diameter, height, species composition, regenerations, and health status.
+•        Soil quality analyses, including soil organic carbon, Total Nitrogen, granulometry, CEC, phosphorus, and potassium.
+•        Water quality analyses, including soil nutrients (Nitrates, Nitrites, Sulfate, Ammonium, Orthophosphate) and pollution (Iron, Cadmium, Lead, and Zinc).
+•        Socio-economic survey data on community livelihoods, mangrove forests’ resources use, and climate change adaptation strategies.
+This dataset is unique in providing a multi-season, and multi-dimensional view of mangrove ecosystems in West Africa, enabling advanced AI/ML-based modelling for degradation prediction, restoration prioritization, carbon stock modelling, and climate resilience assessment.
+</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under review in Figshare (https://plus.figshare.com/account/mycontent/items) </t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SDG13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Drone Imagery, Tabular, Other</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Glèlè Kakai Romain (glele.romain@gmail.com) &amp; Salako Valere (salakovalere@gmail.com)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Benin/West Africa</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dataset provides georeferenced, annotated drone imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. The datatset also provide field Carbon inventoried data paired with the drone imagery. As such, users can train AI models for carboj estimation is harsh mangroves ecosystems. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring and carbon estimation. Furthermore, the dataset include (1) Soil quality analyses, including soil organic carbon, Total Nitrogen, granulometry, CEC, phosphorus, and potassium;  (2) Water quality analyses, including soil nutrients (Nitrates, Nitrites, Sulfate, Ammonium, Orthophosphate) and pollution (Iron, Cadmium, Lead, and Zinc), and (3) Socio-economic survey data on community livelihoods, mangrove forests’ resources use, and climate change adaptation strategies; allowing to develop models aiming at understanding how local soil, water, and socio-économic profile affect carbon stock. 
+</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Laboratoire de Biomathématiques et d'Estimations Forestières</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Salako Kolawolé Valère</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>ui_81</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.linkedin.com/posts/laboratoire-de-biomath%C3%A9matiques-et-d-estimations-foresti%C3%A8res-labef-fsa-uac_lacuna-datafordevelopment-benin-ugcPost-7337524551137853440-1ZDi?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAB7J3S4B0vCirsEbxKR0eAzpTimXPCbQv0Q </t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V81" t="inlineStr"/>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Dataset Speaking Titles</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Use Case Speaking Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description - What can be done with this? What is this about?</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Dataset Link</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Model/Use-Case Links</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Domain/SDG</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Point of Contact/Communities</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Country Team</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Data - Key Characteristics</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Model/Use-Case - Key Characteristics</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Deep Dive - How can you concretely work with this and build on this?</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Organizations Involved</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Project ID</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Maturity / Readiness for replication or scaling [INTERNAL]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Technical Domain</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Expressive visualization / picture related to dataset / possible use / story-tellling</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Additional Resources (Paper, Publications, etc)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>GIZ Funded (Yes/No)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t xml:space="preserve">Info on fair sharing as as Digital Public Good </t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -2090,10 +2078,10 @@
 - Use the orthophoto tiles and bounding box annotations to train models for individual tree detection, counting, and classification from aerial imagery.
 - Use the terrestrial stereoscopic images to develop and benchmark 3D computer vision models for automating forest inventory, such as estimating biophysical parameters.
 - Combine the ground-truth measurements (TH, CD, BD) and weather data to train models that determine quantitative relationships between tree growth and local weather conditions.
-- Leverage the multi-year data (2024-2025) to analyse changes in biophysical parameters and determine which tree species are growing well in the reforested area.
+- Leverage the multi-year data (2024-2025) to analyse changes in biophysical parameters and determine which tree species are growing well in the reforested area.
 The dataset is designed to be integrated. By augmenting this dataset with others, one can
 - Combine Miti360 with other global forestry datasets mentioned in the report (like NEON Crowns or Auto Arborist) to train models with greater geographic diversity, addressing a key gap this dataset was built to fill.
-- Augment the dataset with socio-economic data on local farming to explore and validate the contribution of farmers to reforestation, an application suggested in the report.
+- Augment the dataset with socio-economic data on local farming to explore and validate the contribution of farmers to reforestation, an application suggested in the report.
 Cost &amp; resources one can use:
 - Cost: Only associated compute costs
 - Resources: The source code used for data analysis as well as preliminary models trained on the dataset will be made available.
@@ -2496,7 +2484,7 @@
       <c r="L22" t="inlineStr">
         <is>
           <t>This dataset and AI model can be used immediately for forest monitoring, restoration planning and impact measurement in mountain and forested regions. Users can map biomass, detect forest loss or assess community-level livelihood impacts by combining the open dataset with freely available satellite imagery. NGOs, research institutions, investors can directly apply the dataset to design or evaluate nature positive projects, while developers can integrate the AI model into their own MRV dashboards. Researchers and AI developers can extend this work by retraining the biomass model with local field data from other regions or adding new layers such as soil moisture or biodiversity indicators. Ethical replication should include community consent and data validation steps to ensure fair and context aware use.
-Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
+Data access: Free (CC-BY 4.0) via Vertify.earth GitHub
 Model use: Free, standard cloud or local compute</t>
         </is>
       </c>
@@ -2850,8 +2838,8 @@
       <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">Quote: “The threat of climate change on forest health affects leaf, flower, and fruit resource availability, but we cannot be prepared unless we have adequate data with predictive power. We have an incredible opportunity to create a harmonized machine-learning-ready dataset for ecological forecasting with the support of Lacuna Fund. Such a forecast could provide the basis for an early warning system that will help communities and resource managers better plan and prepare for climate change impact on forest resources.”
-— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
-Ghana News Agency: https://gna.org.gh/2025/07/realistic-phenology-data-key-to-predicting-crop-cycles-dr-ofosu-bamfo-2/
+— Bismark Ofosu-Bamfo, Department of Biological Sciences, University of Energy and Natural Resources; Also see news items News coverage
+Ghana News Agency: https://gna.org.gh/2025/07/realistic-phenology-data-key-to-predicting-crop-cycles-dr-ofosu-bamfo-2/
 Joy News (video): https://g.co/kgs/5byh6f7 </t>
         </is>
       </c>
@@ -7217,7 +7205,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">The dataset provides georeferenced, annotated drone imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. The datatset also provide field Carbon inventoried data paired with the drone imagery. As such, users can train AI models for carboj estimation is harsh mangroves ecosystems. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring and carbon estimation. Furthermore, the dataset include (1) Soil quality analyses, including soil organic carbon, Total Nitrogen, granulometry, CEC, phosphorus, and potassium;  (2) Water quality analyses, including soil nutrients (Nitrates, Nitrites, Sulfate, Ammonium, Orthophosphate) and pollution (Iron, Cadmium, Lead, and Zinc), and (3) Socio-economic survey data on community livelihoods, mangrove forests’ resources use, and climate change adaptation strategies; allowing to develop models aiming at understanding how local soil, water, and socio-économic profile affect carbon stock. 
+          <t xml:space="preserve">The dataset provides georeferenced, annotated drone imagery with clear landuse and landcover classes, groundtruth data, and standardized protocols. The datatset also provide field Carbon inventoried data paired with the drone imagery. As such, users can train AI models for carboj estimation is harsh mangroves ecosystems. Its high resolution, temporal coverage, and open accessibility enable accurate, scalable environmental monitoring and carbon estimation. Furthermore, the dataset include (1) Soil quality analyses, including soil organic carbon, Total Nitrogen, granulometry, CEC, phosphorus, and potassium;  (2) Water quality analyses, including soil nutrients (Nitrates, Nitrites, Sulfate, Ammonium, Orthophosphate) and pollution (Iron, Cadmium, Lead, and Zinc), and (3) Socio-economic survey data on community livelihoods, mangrove forests’ resources use, and climate change adaptation strategies; allowing to develop models aiming at understanding how local soil, water, and socio-économic profile affect carbon stock. 
 </t>
         </is>
       </c>

--- a/docs/data_catalog.xlsx
+++ b/docs/data_catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,7 +2333,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitigating the impacts of oil palm cultivation on forests and climate change in Indonesia through AI and social forestry</t>
+          <t>Open Land Use Reference Dataset for Palm Oil Landscapes in Indonesia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -2345,8 +2345,16 @@
 Possible users of these outputs are local communities engaged in community forestry in Indonesia, as well as researchers, policymakers, and civil society organizations. The dataset also contributes to social forestry, which recognizes that people who depend on local forests are best placed to look after them, and that allowing communities to manage and use forest resources can have positive social, environmental and economic impacts. Social forestry is a broad term and has different names in different places. Some examples are community forestry, village forestry, participatory forestry, community-based forest management and people-centred forestry.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/15618532</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>We leveraged 'Collect Earth Online' heavily for this project and several project collaborators have contributed to that software: https://www.collect.earth/</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>SDG 13 (Climate Action), 
@@ -2355,12 +2363,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Drone Imagery, Geospatial/Remote Sensing</t>
+          <t>Geospatial/Remote Sensing, Tabular</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RECOFTC, Peter Cutter (peter.cutter@recoftc.org)</t>
+          <t>Muhammad Warizmi Wafiq (mwafiq@sig-gis.com)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2368,14 +2376,37 @@
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>For access and use, see Zenodo link to the left.
+The dataset was developed through an integrative data collection and validation approach:
+Wall-to-Wall Labeling:
+Training data was created through opportunistic sampling across 6x6 km grids overlapping known oil palm regions. Labels were digitized in QGIS and refined through multi-spectral analysis of Planet NICFI imagery from corresponding months. The land cover classification followed a two-tiered typology covering estate crops (e.g., oil palm, rubber, coconut), annual crops, forests, shrubland, wetlands, and other land uses.
+Satellite Imagery Pairing:
+Each labeled grid is paired with PlanetScope monthly composite images clipped to grid extent. These cloud-minimized mosaics are consistent with the date of interpretation to support supervised machine learning training.
+Validation Dataset (CEO):
+A stratified random sampling method was applied to generate verification points across diverse land cover classes. Interpreters labeled points in CEO using a standardized survey form and high-resolution imagery. Twenty percent of samples were cross-verified by multiple interpreters to calculate agreement scores as part of QA/QC procedures. Select ambiguous classes were also validated through targeted field checks.
+Metadata and Format:
+All spatial layers are delivered in GeoJSON format, accompanied by metadata following ISO 19115 standards. Image tiles are delivered as GeoTIFFs, pre-aligned to vector boundaries.
+Data Type:
+Vector spatial dataset (Polygons, WKT), tabular metadata (.csv/.geojson), JSON-compatible attributes, raster images (GeoTIFF)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>This is a carefully validated dataset for training AI and ML models and for any other applications that users would like to use it for.</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>This dataset can help you to get an improved understanding of the impacts of oil palm cultivation on forests and climate change. It can also serve to support sustainable forest management practices and empower local communities in forest resource management.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>Primary use: for training and validating AI and ML models</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Creative Commons Attribution 4.0 International</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Powered by:  RECOFTC
@@ -2410,7 +2441,8 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.recoftc.org/projects/advancing-oil-palm-mapping-social-forestry-and-machine-learning 
+          <t xml:space="preserve">https://www.researchgate.net/publication/395402380_An_Open_Benchmark_Dataset_for_GeoAI_Foundation_Models_for_Oil_Palm_Mapping_in_Indonesia
+https://www.recoftc.org/projects/advancing-oil-palm-mapping-social-forestry-and-machine-learning 
 Quote: “Communities in the areas targeted by this project are challenged when it comes to mapping the rapidly changing forest landscapes on which they depend. The datasets this project generates will provide valuable insight into these dynamic patterns of change.”  
 — Gamma Galudra, Director, Indonesia Country Office, RECOFTC </t>
         </is>
@@ -7263,6 +7295,35 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>ui_82</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
